--- a/data/default/SheepHerd.xlsx
+++ b/data/default/SheepHerd.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22410" windowHeight="8235" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22410" windowHeight="7635" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="7" r:id="rId1"/>
@@ -610,7 +610,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="298">
   <si>
     <t>Slakt av större lantbruksdjur vid slakteri efter Djurslag, Tabelluppgift och Månad</t>
   </si>
@@ -1494,6 +1494,18 @@
   </si>
   <si>
     <t>feed_per_lifetime</t>
+  </si>
+  <si>
+    <t>max_share_sub_system</t>
+  </si>
+  <si>
+    <t>From shares according to slaughter statistics plus some slack</t>
+  </si>
+  <si>
+    <t>Maximum shares per sub-system on national level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: </t>
   </si>
 </sst>
 </file>
@@ -1504,7 +1516,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0\ _k_r"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1741,6 +1753,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="45">
@@ -2238,7 +2256,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
@@ -2369,6 +2387,7 @@
     <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="29" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2843,7 +2862,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J353"/>
+  <dimension ref="A1:J360"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -3387,7 +3406,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="44" t="s">
-        <v>207</v>
+        <v>296</v>
       </c>
       <c r="B39" s="44"/>
       <c r="C39" s="44"/>
@@ -3400,872 +3419,853 @@
       <c r="J39" s="46"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>297</v>
+      </c>
       <c r="G40" s="89"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>196</v>
       </c>
-      <c r="D41" t="s">
-        <v>205</v>
-      </c>
       <c r="F41" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="G41" s="89">
-        <f>(160+181+163)/3</f>
-        <v>168</v>
+        <f>30*1.1</f>
+        <v>33</v>
       </c>
       <c r="H41" t="s">
-        <v>210</v>
-      </c>
-      <c r="J41" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="I41" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>197</v>
       </c>
-      <c r="D42" t="s">
-        <v>205</v>
-      </c>
       <c r="F42" t="s">
-        <v>209</v>
-      </c>
-      <c r="G42" s="89">
-        <v>113</v>
+        <v>294</v>
+      </c>
+      <c r="G42" s="95">
+        <f>18</f>
+        <v>18</v>
       </c>
       <c r="H42" t="s">
-        <v>210</v>
-      </c>
-      <c r="J42" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>198</v>
       </c>
-      <c r="D43" t="s">
-        <v>205</v>
-      </c>
       <c r="F43" t="s">
-        <v>209</v>
-      </c>
-      <c r="G43" s="89">
-        <v>308</v>
+        <v>294</v>
+      </c>
+      <c r="G43" s="95">
+        <f>13*1.1</f>
+        <v>14.3</v>
       </c>
       <c r="H43" t="s">
-        <v>210</v>
-      </c>
-      <c r="J43" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>204</v>
       </c>
-      <c r="D44" t="s">
-        <v>205</v>
-      </c>
       <c r="F44" t="s">
-        <v>209</v>
-      </c>
-      <c r="G44" s="89">
-        <v>168</v>
+        <v>294</v>
+      </c>
+      <c r="G44" s="95">
+        <f>39*1.1</f>
+        <v>42.900000000000006</v>
       </c>
       <c r="H44" t="s">
-        <v>210</v>
-      </c>
-      <c r="I44" t="s">
-        <v>290</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G45" s="89"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C46" t="s">
+      <c r="A46" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="94"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="46"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G47" s="89"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
         <v>196</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D48" t="s">
+        <v>205</v>
+      </c>
+      <c r="F48" t="s">
+        <v>209</v>
+      </c>
+      <c r="G48" s="89">
+        <f>(160+181+163)/3</f>
+        <v>168</v>
+      </c>
+      <c r="H48" t="s">
+        <v>210</v>
+      </c>
+      <c r="J48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" t="s">
+        <v>205</v>
+      </c>
+      <c r="F49" t="s">
+        <v>209</v>
+      </c>
+      <c r="G49" s="89">
+        <v>113</v>
+      </c>
+      <c r="H49" t="s">
+        <v>210</v>
+      </c>
+      <c r="J49" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" t="s">
+        <v>205</v>
+      </c>
+      <c r="F50" t="s">
+        <v>209</v>
+      </c>
+      <c r="G50" s="89">
+        <v>308</v>
+      </c>
+      <c r="H50" t="s">
+        <v>210</v>
+      </c>
+      <c r="J50" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>204</v>
+      </c>
+      <c r="D51" t="s">
+        <v>205</v>
+      </c>
+      <c r="F51" t="s">
+        <v>209</v>
+      </c>
+      <c r="G51" s="89">
+        <v>168</v>
+      </c>
+      <c r="H51" t="s">
+        <v>210</v>
+      </c>
+      <c r="I51" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G52" s="89"/>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>196</v>
+      </c>
+      <c r="D53" t="s">
         <v>201</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F53" t="s">
         <v>206</v>
       </c>
-      <c r="G46" s="89">
+      <c r="G53" s="89">
         <f>(30+27+30)/3</f>
         <v>29</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H53" t="s">
         <v>208</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J53" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C47" t="s">
+    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
         <v>197</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D54" t="s">
         <v>201</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F54" t="s">
         <v>206</v>
       </c>
-      <c r="G47" s="89">
+      <c r="G54" s="89">
         <v>33</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H54" t="s">
         <v>208</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J54" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C48" t="s">
+    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
         <v>198</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D55" t="s">
         <v>201</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F55" t="s">
         <v>206</v>
       </c>
-      <c r="G48" s="89">
+      <c r="G55" s="89">
         <f>(30+27+30)/3</f>
         <v>29</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H55" t="s">
         <v>208</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J55" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C49" t="s">
+    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
         <v>204</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D56" t="s">
         <v>201</v>
-      </c>
-      <c r="F49" t="s">
-        <v>206</v>
-      </c>
-      <c r="G49" s="89">
-        <v>29</v>
-      </c>
-      <c r="H49" t="s">
-        <v>208</v>
-      </c>
-      <c r="I49" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G50" s="89"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C51" t="s">
-        <v>196</v>
-      </c>
-      <c r="D51" t="s">
-        <v>219</v>
-      </c>
-      <c r="F51" t="s">
-        <v>206</v>
-      </c>
-      <c r="G51" s="89">
-        <v>45</v>
-      </c>
-      <c r="H51" t="s">
-        <v>208</v>
-      </c>
-      <c r="J51" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C52" t="s">
-        <v>197</v>
-      </c>
-      <c r="D52" t="s">
-        <v>219</v>
-      </c>
-      <c r="F52" t="s">
-        <v>206</v>
-      </c>
-      <c r="G52" s="89">
-        <v>48</v>
-      </c>
-      <c r="H52" t="s">
-        <v>208</v>
-      </c>
-      <c r="J52" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C53" t="s">
-        <v>198</v>
-      </c>
-      <c r="D53" t="s">
-        <v>219</v>
-      </c>
-      <c r="F53" t="s">
-        <v>206</v>
-      </c>
-      <c r="G53" s="89">
-        <v>45</v>
-      </c>
-      <c r="H53" t="s">
-        <v>208</v>
-      </c>
-      <c r="J53" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C54" t="s">
-        <v>204</v>
-      </c>
-      <c r="D54" t="s">
-        <v>219</v>
-      </c>
-      <c r="F54" t="s">
-        <v>206</v>
-      </c>
-      <c r="G54" s="89">
-        <v>45</v>
-      </c>
-      <c r="H54" t="s">
-        <v>208</v>
-      </c>
-      <c r="I54" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G55" s="89"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C56" t="s">
-        <v>196</v>
-      </c>
-      <c r="D56" t="s">
-        <v>205</v>
       </c>
       <c r="F56" t="s">
         <v>206</v>
       </c>
-      <c r="G56" s="93">
+      <c r="G56" s="89">
+        <v>29</v>
+      </c>
+      <c r="H56" t="s">
+        <v>208</v>
+      </c>
+      <c r="I56" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G57" s="89"/>
+    </row>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
+        <v>196</v>
+      </c>
+      <c r="D58" t="s">
+        <v>219</v>
+      </c>
+      <c r="F58" t="s">
+        <v>206</v>
+      </c>
+      <c r="G58" s="89">
+        <v>45</v>
+      </c>
+      <c r="H58" t="s">
+        <v>208</v>
+      </c>
+      <c r="J58" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>197</v>
+      </c>
+      <c r="D59" t="s">
+        <v>219</v>
+      </c>
+      <c r="F59" t="s">
+        <v>206</v>
+      </c>
+      <c r="G59" s="89">
+        <v>48</v>
+      </c>
+      <c r="H59" t="s">
+        <v>208</v>
+      </c>
+      <c r="J59" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D60" t="s">
+        <v>219</v>
+      </c>
+      <c r="F60" t="s">
+        <v>206</v>
+      </c>
+      <c r="G60" s="89">
+        <v>45</v>
+      </c>
+      <c r="H60" t="s">
+        <v>208</v>
+      </c>
+      <c r="J60" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>204</v>
+      </c>
+      <c r="D61" t="s">
+        <v>219</v>
+      </c>
+      <c r="F61" t="s">
+        <v>206</v>
+      </c>
+      <c r="G61" s="89">
+        <v>45</v>
+      </c>
+      <c r="H61" t="s">
+        <v>208</v>
+      </c>
+      <c r="I61" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G62" s="89"/>
+    </row>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>196</v>
+      </c>
+      <c r="D63" t="s">
+        <v>205</v>
+      </c>
+      <c r="F63" t="s">
+        <v>206</v>
+      </c>
+      <c r="G63" s="93">
         <f>(20.2+19.2+20.2)/3</f>
         <v>19.866666666666664</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H63" t="s">
         <v>208</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J63" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C57" t="s">
-        <v>197</v>
-      </c>
-      <c r="D57" t="s">
-        <v>205</v>
-      </c>
-      <c r="F57" t="s">
-        <v>206</v>
-      </c>
-      <c r="G57" s="89">
-        <v>20.5</v>
-      </c>
-      <c r="H57" t="s">
-        <v>208</v>
-      </c>
-      <c r="J57" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C58" t="s">
-        <v>198</v>
-      </c>
-      <c r="D58" t="s">
-        <v>205</v>
-      </c>
-      <c r="F58" t="s">
-        <v>206</v>
-      </c>
-      <c r="G58" s="93">
-        <f>(20.2+19.2+20.2)/3</f>
-        <v>19.866666666666664</v>
-      </c>
-      <c r="H58" t="s">
-        <v>208</v>
-      </c>
-      <c r="J58" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C59" t="s">
-        <v>204</v>
-      </c>
-      <c r="D59" t="s">
-        <v>205</v>
-      </c>
-      <c r="F59" t="s">
-        <v>206</v>
-      </c>
-      <c r="G59" s="89">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="H59" t="s">
-        <v>208</v>
-      </c>
-      <c r="I59" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="44" t="s">
-        <v>227</v>
-      </c>
-      <c r="B61" s="44"/>
-      <c r="C61" s="44"/>
-      <c r="D61" s="45"/>
-      <c r="E61" s="45"/>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45"/>
-      <c r="H61" s="45"/>
-      <c r="I61" s="45" t="s">
-        <v>287</v>
-      </c>
-      <c r="J61" s="46"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C63" t="s">
-        <v>196</v>
-      </c>
-      <c r="F63" t="s">
-        <v>292</v>
-      </c>
-      <c r="G63" s="19">
-        <f>'feed rations'!G5</f>
-        <v>748.40000000000009</v>
-      </c>
-      <c r="H63" t="s">
-        <v>279</v>
-      </c>
-      <c r="J63" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>197</v>
       </c>
+      <c r="D64" t="s">
+        <v>205</v>
+      </c>
       <c r="F64" t="s">
-        <v>292</v>
-      </c>
-      <c r="G64" s="19">
-        <f>'feed rations'!G6</f>
-        <v>554.1</v>
+        <v>206</v>
+      </c>
+      <c r="G64" s="89">
+        <v>20.5</v>
       </c>
       <c r="H64" t="s">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="J64" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
         <v>198</v>
       </c>
+      <c r="D65" t="s">
+        <v>205</v>
+      </c>
       <c r="F65" t="s">
-        <v>292</v>
-      </c>
-      <c r="G65" s="19">
-        <f>'feed rations'!G7</f>
-        <v>726.26666666666654</v>
+        <v>206</v>
+      </c>
+      <c r="G65" s="93">
+        <f>(20.2+19.2+20.2)/3</f>
+        <v>19.866666666666664</v>
       </c>
       <c r="H65" t="s">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="J65" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
         <v>204</v>
       </c>
+      <c r="D66" t="s">
+        <v>205</v>
+      </c>
       <c r="F66" t="s">
+        <v>206</v>
+      </c>
+      <c r="G66" s="89">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H66" t="s">
+        <v>208</v>
+      </c>
+      <c r="I66" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="45"/>
+      <c r="E68" s="45"/>
+      <c r="F68" s="45"/>
+      <c r="G68" s="45"/>
+      <c r="H68" s="45"/>
+      <c r="I68" s="45" t="s">
+        <v>287</v>
+      </c>
+      <c r="J68" s="46"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
+        <v>196</v>
+      </c>
+      <c r="F70" t="s">
         <v>292</v>
       </c>
-      <c r="G66" s="19">
+      <c r="G70" s="19">
+        <f>'feed rations'!G5</f>
+        <v>748.40000000000009</v>
+      </c>
+      <c r="H70" t="s">
+        <v>279</v>
+      </c>
+      <c r="J70" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>197</v>
+      </c>
+      <c r="F71" t="s">
+        <v>292</v>
+      </c>
+      <c r="G71" s="19">
+        <f>'feed rations'!G6</f>
+        <v>554.1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>279</v>
+      </c>
+      <c r="J71" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
+        <v>198</v>
+      </c>
+      <c r="F72" t="s">
+        <v>292</v>
+      </c>
+      <c r="G72" s="19">
+        <f>'feed rations'!G7</f>
+        <v>726.26666666666654</v>
+      </c>
+      <c r="H72" t="s">
+        <v>279</v>
+      </c>
+      <c r="J72" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>204</v>
+      </c>
+      <c r="F73" t="s">
+        <v>292</v>
+      </c>
+      <c r="G73" s="19">
         <f>'feed rations'!G8</f>
         <v>748.40000000000009</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H73" t="s">
         <v>279</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I73" t="s">
         <v>280</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C68" t="s">
-        <v>196</v>
-      </c>
-      <c r="D68" t="s">
-        <v>205</v>
-      </c>
-      <c r="F68" t="s">
-        <v>293</v>
-      </c>
-      <c r="G68" s="19">
-        <f>'feed rations'!N5</f>
-        <v>157.56666666666666</v>
-      </c>
-      <c r="H68" t="s">
-        <v>279</v>
-      </c>
-      <c r="J68" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C69" t="s">
-        <v>197</v>
-      </c>
-      <c r="D69" t="s">
-        <v>205</v>
-      </c>
-      <c r="F69" t="s">
-        <v>293</v>
-      </c>
-      <c r="G69" s="19">
-        <f>'feed rations'!N6</f>
-        <v>114</v>
-      </c>
-      <c r="H69" t="s">
-        <v>279</v>
-      </c>
-      <c r="J69" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C70" t="s">
-        <v>198</v>
-      </c>
-      <c r="D70" t="s">
-        <v>205</v>
-      </c>
-      <c r="F70" t="s">
-        <v>293</v>
-      </c>
-      <c r="G70" s="19">
-        <f>'feed rations'!N7</f>
-        <v>254.56666666666669</v>
-      </c>
-      <c r="H70" t="s">
-        <v>279</v>
-      </c>
-      <c r="J70" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C71" t="s">
-        <v>204</v>
-      </c>
-      <c r="D71" t="s">
-        <v>205</v>
-      </c>
-      <c r="F71" t="s">
-        <v>293</v>
-      </c>
-      <c r="G71" s="19">
-        <f>'feed rations'!N8</f>
-        <v>157.56666666666666</v>
-      </c>
-      <c r="H71" t="s">
-        <v>279</v>
-      </c>
-      <c r="I71" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="44" t="s">
-        <v>281</v>
-      </c>
-      <c r="B73" s="44"/>
-      <c r="C73" s="44"/>
-      <c r="D73" s="45"/>
-      <c r="E73" s="45"/>
-      <c r="F73" s="45"/>
-      <c r="G73" s="45"/>
-      <c r="H73" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="I73" s="45" t="s">
-        <v>287</v>
-      </c>
-      <c r="J73" s="46"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F74" s="91" t="s">
-        <v>285</v>
-      </c>
-      <c r="G74" s="91">
-        <v>0</v>
-      </c>
-      <c r="H74" s="91"/>
-      <c r="I74" s="91" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
         <v>196</v>
       </c>
-      <c r="E75" s="21" t="s">
-        <v>276</v>
+      <c r="D75" t="s">
+        <v>205</v>
       </c>
       <c r="F75" t="s">
-        <v>285</v>
-      </c>
-      <c r="G75" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E75,'feed rations'!$Y$13:$Y$46,0),MATCH(C75&amp;D75,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>14.502048815250316</v>
+        <v>293</v>
+      </c>
+      <c r="G75" s="19">
+        <f>'feed rations'!N5</f>
+        <v>157.56666666666666</v>
+      </c>
+      <c r="H75" t="s">
+        <v>279</v>
+      </c>
+      <c r="J75" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
-        <v>196</v>
-      </c>
-      <c r="E76" s="21" t="s">
-        <v>274</v>
+        <v>197</v>
+      </c>
+      <c r="D76" t="s">
+        <v>205</v>
       </c>
       <c r="F76" t="s">
-        <v>285</v>
-      </c>
-      <c r="G76" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E76,'feed rations'!$Y$13:$Y$46,0),MATCH(C76&amp;D76,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>29.004097630500631</v>
+        <v>293</v>
+      </c>
+      <c r="G76" s="19">
+        <f>'feed rations'!N6</f>
+        <v>114</v>
+      </c>
+      <c r="H76" t="s">
+        <v>279</v>
+      </c>
+      <c r="J76" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
-        <v>196</v>
-      </c>
-      <c r="E77" t="s">
-        <v>277</v>
+        <v>198</v>
+      </c>
+      <c r="D77" t="s">
+        <v>205</v>
       </c>
       <c r="F77" t="s">
-        <v>285</v>
-      </c>
-      <c r="G77" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E77,'feed rations'!$Y$13:$Y$46,0),MATCH(C77&amp;D77,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>52.618920363442022</v>
+        <v>293</v>
+      </c>
+      <c r="G77" s="19">
+        <f>'feed rations'!N7</f>
+        <v>254.56666666666669</v>
+      </c>
+      <c r="H77" t="s">
+        <v>279</v>
+      </c>
+      <c r="J77" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
-        <v>196</v>
-      </c>
-      <c r="E78" t="s">
-        <v>229</v>
+        <v>204</v>
+      </c>
+      <c r="D78" t="s">
+        <v>205</v>
       </c>
       <c r="F78" t="s">
-        <v>285</v>
-      </c>
-      <c r="G78" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E78,'feed rations'!$Y$13:$Y$46,0),MATCH(C78&amp;D78,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.84682253603719471</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C79" t="s">
-        <v>196</v>
-      </c>
-      <c r="E79" t="s">
-        <v>230</v>
-      </c>
-      <c r="F79" t="s">
-        <v>285</v>
-      </c>
-      <c r="G79" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E79,'feed rations'!$Y$13:$Y$46,0),MATCH(C79&amp;D79,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.43737940455400331</v>
+        <v>293</v>
+      </c>
+      <c r="G78" s="19">
+        <f>'feed rations'!N8</f>
+        <v>157.56666666666666</v>
+      </c>
+      <c r="H78" t="s">
+        <v>279</v>
+      </c>
+      <c r="I78" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C80" t="s">
-        <v>196</v>
-      </c>
-      <c r="E80" t="s">
-        <v>231</v>
-      </c>
-      <c r="F80" t="s">
-        <v>285</v>
-      </c>
-      <c r="G80" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E80,'feed rations'!$Y$13:$Y$46,0),MATCH(C80&amp;D80,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.66303507614130686</v>
-      </c>
-    </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C81" t="s">
-        <v>196</v>
-      </c>
-      <c r="E81" t="s">
-        <v>232</v>
-      </c>
-      <c r="F81" t="s">
-        <v>285</v>
-      </c>
-      <c r="G81" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E81,'feed rations'!$Y$13:$Y$46,0),MATCH(C81&amp;D81,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.0988815290634705E-3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="B80" s="44"/>
+      <c r="C80" s="44"/>
+      <c r="D80" s="45"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="I80" s="45" t="s">
+        <v>287</v>
+      </c>
+      <c r="J80" s="46"/>
+    </row>
+    <row r="81" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="F81" s="91" t="s">
+        <v>285</v>
+      </c>
+      <c r="G81" s="91">
+        <v>0</v>
+      </c>
+      <c r="H81" s="91"/>
+      <c r="I81" s="91" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="82" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C82" t="s">
         <v>196</v>
       </c>
-      <c r="E82" t="s">
-        <v>233</v>
+      <c r="E82" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F82" t="s">
         <v>285</v>
       </c>
       <c r="G82" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E82,'feed rations'!$Y$13:$Y$46,0),MATCH(C82&amp;D82,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+        <v>14.502048815250316</v>
+      </c>
+    </row>
+    <row r="83" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C83" t="s">
         <v>196</v>
       </c>
-      <c r="E83" t="s">
-        <v>234</v>
+      <c r="E83" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F83" t="s">
         <v>285</v>
       </c>
       <c r="G83" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E83,'feed rations'!$Y$13:$Y$46,0),MATCH(C83&amp;D83,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.17270238081001552</v>
-      </c>
-    </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+        <v>29.004097630500631</v>
+      </c>
+    </row>
+    <row r="84" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C84" t="s">
         <v>196</v>
       </c>
       <c r="E84" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F84" t="s">
         <v>285</v>
       </c>
       <c r="G84" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E84,'feed rations'!$Y$13:$Y$46,0),MATCH(C84&amp;D84,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7776312249885764E-3</v>
-      </c>
-    </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+        <v>52.618920363442022</v>
+      </c>
+    </row>
+    <row r="85" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C85" t="s">
         <v>196</v>
       </c>
       <c r="E85" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F85" t="s">
         <v>285</v>
       </c>
       <c r="G85" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E85,'feed rations'!$Y$13:$Y$46,0),MATCH(C85&amp;D85,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3699111545736139E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.84682253603719471</v>
+      </c>
+    </row>
+    <row r="86" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
         <v>196</v>
       </c>
       <c r="E86" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F86" t="s">
         <v>285</v>
       </c>
       <c r="G86" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E86,'feed rations'!$Y$13:$Y$46,0),MATCH(C86&amp;D86,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.45638940058232602</v>
-      </c>
-    </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.43737940455400331</v>
+      </c>
+    </row>
+    <row r="87" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
         <v>196</v>
       </c>
       <c r="E87" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F87" t="s">
         <v>285</v>
       </c>
       <c r="G87" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E87,'feed rations'!$Y$13:$Y$46,0),MATCH(C87&amp;D87,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.1509220070385851E-4</v>
-      </c>
-    </row>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.66303507614130686</v>
+      </c>
+    </row>
+    <row r="88" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>196</v>
       </c>
       <c r="E88" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F88" t="s">
         <v>285</v>
       </c>
       <c r="G88" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E88,'feed rations'!$Y$13:$Y$46,0),MATCH(C88&amp;D88,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.19248525926546745</v>
-      </c>
-    </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+        <v>4.0988815290634705E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
         <v>196</v>
       </c>
       <c r="E89" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F89" t="s">
         <v>285</v>
       </c>
       <c r="G89" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E89,'feed rations'!$Y$13:$Y$46,0),MATCH(C89&amp;D89,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1540482816582413E-5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C90" t="s">
         <v>196</v>
       </c>
       <c r="E90" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F90" t="s">
         <v>285</v>
       </c>
       <c r="G90" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E90,'feed rations'!$Y$13:$Y$46,0),MATCH(C90&amp;D90,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.49074140742335415</v>
-      </c>
-    </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.17270238081001552</v>
+      </c>
+    </row>
+    <row r="91" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C91" t="s">
         <v>196</v>
       </c>
       <c r="E91" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F91" t="s">
         <v>285</v>
       </c>
       <c r="G91" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E91,'feed rations'!$Y$13:$Y$46,0),MATCH(C91&amp;D91,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.938643453492417E-5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.7776312249885764E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C92" t="s">
         <v>196</v>
       </c>
       <c r="E92" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F92" t="s">
         <v>285</v>
       </c>
       <c r="G92" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E92,'feed rations'!$Y$13:$Y$46,0),MATCH(C92&amp;D92,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.21035091095436523</v>
-      </c>
-    </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.3699111545736139E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C93" t="s">
         <v>196</v>
       </c>
       <c r="E93" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F93" t="s">
         <v>285</v>
       </c>
       <c r="G93" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E93,'feed rations'!$Y$13:$Y$46,0),MATCH(C93&amp;D93,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2346905713762435E-3</v>
-      </c>
-    </row>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.45638940058232602</v>
+      </c>
+    </row>
+    <row r="94" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C94" t="s">
         <v>196</v>
       </c>
       <c r="E94" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F94" t="s">
         <v>285</v>
       </c>
       <c r="G94" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E94,'feed rations'!$Y$13:$Y$46,0),MATCH(C94&amp;D94,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5441026802460426E-3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.1509220070385851E-4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
         <v>196</v>
       </c>
       <c r="E95" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F95" t="s">
         <v>285</v>
       </c>
       <c r="G95" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E95,'feed rations'!$Y$13:$Y$46,0),MATCH(C95&amp;D95,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.7314817761965576E-2</v>
-      </c>
-    </row>
-    <row r="96" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.19248525926546745</v>
+      </c>
+    </row>
+    <row r="96" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C96" t="s">
         <v>196</v>
       </c>
       <c r="E96" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F96" t="s">
         <v>285</v>
       </c>
       <c r="G96" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E96,'feed rations'!$Y$13:$Y$46,0),MATCH(C96&amp;D96,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.16311530612857034</v>
+        <v>2.1540482816582413E-5</v>
       </c>
     </row>
     <row r="97" spans="3:7" x14ac:dyDescent="0.25">
@@ -4273,14 +4273,14 @@
         <v>196</v>
       </c>
       <c r="E97" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F97" t="s">
         <v>285</v>
       </c>
       <c r="G97" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E97,'feed rations'!$Y$13:$Y$46,0),MATCH(C97&amp;D97,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.3607807918891001E-2</v>
+        <v>0.49074140742335415</v>
       </c>
     </row>
     <row r="98" spans="3:7" x14ac:dyDescent="0.25">
@@ -4288,14 +4288,14 @@
         <v>196</v>
       </c>
       <c r="E98" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F98" t="s">
         <v>285</v>
       </c>
       <c r="G98" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E98,'feed rations'!$Y$13:$Y$46,0),MATCH(C98&amp;D98,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.598428273092974E-2</v>
+        <v>1.938643453492417E-5</v>
       </c>
     </row>
     <row r="99" spans="3:7" x14ac:dyDescent="0.25">
@@ -4303,14 +4303,14 @@
         <v>196</v>
       </c>
       <c r="E99" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F99" t="s">
         <v>285</v>
       </c>
       <c r="G99" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E99,'feed rations'!$Y$13:$Y$46,0),MATCH(C99&amp;D99,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.9986464582958335E-3</v>
+        <v>0.21035091095436523</v>
       </c>
     </row>
     <row r="100" spans="3:7" x14ac:dyDescent="0.25">
@@ -4318,14 +4318,14 @@
         <v>196</v>
       </c>
       <c r="E100" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F100" t="s">
         <v>285</v>
       </c>
       <c r="G100" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E100,'feed rations'!$Y$13:$Y$46,0),MATCH(C100&amp;D100,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>1.2346905713762435E-3</v>
       </c>
     </row>
     <row r="101" spans="3:7" x14ac:dyDescent="0.25">
@@ -4333,14 +4333,14 @@
         <v>196</v>
       </c>
       <c r="E101" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F101" t="s">
         <v>285</v>
       </c>
       <c r="G101" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E101,'feed rations'!$Y$13:$Y$46,0),MATCH(C101&amp;D101,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5731980208800535E-2</v>
+        <v>3.5441026802460426E-3</v>
       </c>
     </row>
     <row r="102" spans="3:7" x14ac:dyDescent="0.25">
@@ -4348,14 +4348,14 @@
         <v>196</v>
       </c>
       <c r="E102" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F102" t="s">
         <v>285</v>
       </c>
       <c r="G102" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E102,'feed rations'!$Y$13:$Y$46,0),MATCH(C102&amp;D102,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>2.7314817761965576E-2</v>
       </c>
     </row>
     <row r="103" spans="3:7" x14ac:dyDescent="0.25">
@@ -4363,14 +4363,14 @@
         <v>196</v>
       </c>
       <c r="E103" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F103" t="s">
         <v>285</v>
       </c>
       <c r="G103" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E103,'feed rations'!$Y$13:$Y$46,0),MATCH(C103&amp;D103,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5338309315945754E-4</v>
+        <v>0.16311530612857034</v>
       </c>
     </row>
     <row r="104" spans="3:7" x14ac:dyDescent="0.25">
@@ -4378,14 +4378,14 @@
         <v>196</v>
       </c>
       <c r="E104" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F104" t="s">
         <v>285</v>
       </c>
       <c r="G104" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E104,'feed rations'!$Y$13:$Y$46,0),MATCH(C104&amp;D104,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0152180129671942E-2</v>
+        <v>3.3607807918891001E-2</v>
       </c>
     </row>
     <row r="105" spans="3:7" x14ac:dyDescent="0.25">
@@ -4393,14 +4393,14 @@
         <v>196</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F105" t="s">
         <v>285</v>
       </c>
       <c r="G105" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E105,'feed rations'!$Y$13:$Y$46,0),MATCH(C105&amp;D105,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.188362213479006E-2</v>
+        <v>3.598428273092974E-2</v>
       </c>
     </row>
     <row r="106" spans="3:7" x14ac:dyDescent="0.25">
@@ -4408,14 +4408,14 @@
         <v>196</v>
       </c>
       <c r="E106" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F106" t="s">
         <v>285</v>
       </c>
       <c r="G106" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E106,'feed rations'!$Y$13:$Y$46,0),MATCH(C106&amp;D106,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>9.9986464582958335E-3</v>
       </c>
     </row>
     <row r="107" spans="3:7" x14ac:dyDescent="0.25">
@@ -4423,14 +4423,14 @@
         <v>196</v>
       </c>
       <c r="E107" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F107" t="s">
         <v>285</v>
       </c>
       <c r="G107" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E107,'feed rations'!$Y$13:$Y$46,0),MATCH(C107&amp;D107,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.4351804480686189E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="3:7" x14ac:dyDescent="0.25">
@@ -4438,149 +4438,149 @@
         <v>196</v>
       </c>
       <c r="E108" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F108" t="s">
         <v>285</v>
       </c>
       <c r="G108" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E108,'feed rations'!$Y$13:$Y$46,0),MATCH(C108&amp;D108,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>1.5731980208800535E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C109" t="s">
+        <v>196</v>
+      </c>
+      <c r="E109" t="s">
+        <v>253</v>
+      </c>
+      <c r="F109" t="s">
+        <v>285</v>
+      </c>
+      <c r="G109" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E109,'feed rations'!$Y$13:$Y$46,0),MATCH(C109&amp;D109,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C110" t="s">
-        <v>197</v>
-      </c>
-      <c r="E110" s="21" t="s">
-        <v>276</v>
+        <v>196</v>
+      </c>
+      <c r="E110" t="s">
+        <v>254</v>
       </c>
       <c r="F110" t="s">
         <v>285</v>
       </c>
       <c r="G110" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E110,'feed rations'!$Y$13:$Y$46,0),MATCH(C110&amp;D110,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>15.175760492490328</v>
+        <v>1.5338309315945754E-4</v>
       </c>
     </row>
     <row r="111" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E111" s="21" t="s">
-        <v>274</v>
+        <v>196</v>
+      </c>
+      <c r="E111" t="s">
+        <v>255</v>
       </c>
       <c r="F111" t="s">
         <v>285</v>
       </c>
       <c r="G111" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E111,'feed rations'!$Y$13:$Y$46,0),MATCH(C111&amp;D111,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>30.351520984980656</v>
+        <v>2.0152180129671942E-2</v>
       </c>
     </row>
     <row r="112" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C112" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E112" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="F112" t="s">
         <v>285</v>
       </c>
       <c r="G112" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E112,'feed rations'!$Y$13:$Y$46,0),MATCH(C112&amp;D112,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>43.343560127534147</v>
+        <v>6.188362213479006E-2</v>
       </c>
     </row>
     <row r="113" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C113" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E113" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="F113" t="s">
         <v>285</v>
       </c>
       <c r="G113" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E113,'feed rations'!$Y$13:$Y$46,0),MATCH(C113&amp;D113,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4321508712376856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C114" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E114" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="F114" t="s">
         <v>285</v>
       </c>
       <c r="G114" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E114,'feed rations'!$Y$13:$Y$46,0),MATCH(C114&amp;D114,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2561931863852942</v>
+        <v>7.4351804480686189E-5</v>
       </c>
     </row>
     <row r="115" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C115" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E115" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="F115" t="s">
         <v>285</v>
       </c>
       <c r="G115" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E115,'feed rations'!$Y$13:$Y$46,0),MATCH(C115&amp;D115,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.9042966731194728</v>
-      </c>
-    </row>
-    <row r="116" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C116" t="s">
-        <v>197</v>
-      </c>
-      <c r="E116" t="s">
-        <v>232</v>
-      </c>
-      <c r="F116" t="s">
-        <v>285</v>
-      </c>
-      <c r="G116" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E116,'feed rations'!$Y$13:$Y$46,0),MATCH(C116&amp;D116,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.1772358266069939E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C117" t="s">
         <v>197</v>
       </c>
-      <c r="E117" t="s">
-        <v>233</v>
+      <c r="E117" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F117" t="s">
         <v>285</v>
       </c>
       <c r="G117" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E117,'feed rations'!$Y$13:$Y$46,0),MATCH(C117&amp;D117,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>15.175760492490328</v>
       </c>
     </row>
     <row r="118" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C118" t="s">
         <v>197</v>
       </c>
-      <c r="E118" t="s">
-        <v>234</v>
+      <c r="E118" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F118" t="s">
         <v>285</v>
       </c>
       <c r="G118" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E118,'feed rations'!$Y$13:$Y$46,0),MATCH(C118&amp;D118,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.4960168489581302</v>
+        <v>30.351520984980656</v>
       </c>
     </row>
     <row r="119" spans="3:7" x14ac:dyDescent="0.25">
@@ -4588,14 +4588,14 @@
         <v>197</v>
       </c>
       <c r="E119" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F119" t="s">
         <v>285</v>
       </c>
       <c r="G119" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E119,'feed rations'!$Y$13:$Y$46,0),MATCH(C119&amp;D119,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.084969835364313E-2</v>
+        <v>43.343560127534147</v>
       </c>
     </row>
     <row r="120" spans="3:7" x14ac:dyDescent="0.25">
@@ -4603,14 +4603,14 @@
         <v>197</v>
       </c>
       <c r="E120" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F120" t="s">
         <v>285</v>
       </c>
       <c r="G120" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E120,'feed rations'!$Y$13:$Y$46,0),MATCH(C120&amp;D120,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.8065990618593489E-2</v>
+        <v>2.4321508712376856</v>
       </c>
     </row>
     <row r="121" spans="3:7" x14ac:dyDescent="0.25">
@@ -4618,14 +4618,14 @@
         <v>197</v>
       </c>
       <c r="E121" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F121" t="s">
         <v>285</v>
       </c>
       <c r="G121" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E121,'feed rations'!$Y$13:$Y$46,0),MATCH(C121&amp;D121,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.310791613369622</v>
+        <v>1.2561931863852942</v>
       </c>
     </row>
     <row r="122" spans="3:7" x14ac:dyDescent="0.25">
@@ -4633,14 +4633,14 @@
         <v>197</v>
       </c>
       <c r="E122" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F122" t="s">
         <v>285</v>
       </c>
       <c r="G122" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E122,'feed rations'!$Y$13:$Y$46,0),MATCH(C122&amp;D122,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7666004011112982E-3</v>
+        <v>1.9042966731194728</v>
       </c>
     </row>
     <row r="123" spans="3:7" x14ac:dyDescent="0.25">
@@ -4648,14 +4648,14 @@
         <v>197</v>
       </c>
       <c r="E123" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F123" t="s">
         <v>285</v>
       </c>
       <c r="G123" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E123,'feed rations'!$Y$13:$Y$46,0),MATCH(C123&amp;D123,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.55283506413716399</v>
+        <v>1.1772358266069939E-2</v>
       </c>
     </row>
     <row r="124" spans="3:7" x14ac:dyDescent="0.25">
@@ -4663,14 +4663,14 @@
         <v>197</v>
       </c>
       <c r="E124" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F124" t="s">
         <v>285</v>
       </c>
       <c r="G124" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E124,'feed rations'!$Y$13:$Y$46,0),MATCH(C124&amp;D124,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.1866213781219229E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="3:7" x14ac:dyDescent="0.25">
@@ -4678,14 +4678,14 @@
         <v>197</v>
       </c>
       <c r="E125" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F125" t="s">
         <v>285</v>
       </c>
       <c r="G125" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E125,'feed rations'!$Y$13:$Y$46,0),MATCH(C125&amp;D125,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.4094536822348984</v>
+        <v>0.4960168489581302</v>
       </c>
     </row>
     <row r="126" spans="3:7" x14ac:dyDescent="0.25">
@@ -4693,14 +4693,14 @@
         <v>197</v>
       </c>
       <c r="E126" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F126" t="s">
         <v>285</v>
       </c>
       <c r="G126" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E126,'feed rations'!$Y$13:$Y$46,0),MATCH(C126&amp;D126,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.5679592403097307E-5</v>
+        <v>1.084969835364313E-2</v>
       </c>
     </row>
     <row r="127" spans="3:7" x14ac:dyDescent="0.25">
@@ -4708,14 +4708,14 @@
         <v>197</v>
       </c>
       <c r="E127" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F127" t="s">
         <v>285</v>
       </c>
       <c r="G127" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E127,'feed rations'!$Y$13:$Y$46,0),MATCH(C127&amp;D127,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.60414683073671682</v>
+        <v>6.8065990618593489E-2</v>
       </c>
     </row>
     <row r="128" spans="3:7" x14ac:dyDescent="0.25">
@@ -4723,14 +4723,14 @@
         <v>197</v>
       </c>
       <c r="E128" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F128" t="s">
         <v>285</v>
       </c>
       <c r="G128" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E128,'feed rations'!$Y$13:$Y$46,0),MATCH(C128&amp;D128,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5461429297032662E-3</v>
+        <v>1.310791613369622</v>
       </c>
     </row>
     <row r="129" spans="3:7" x14ac:dyDescent="0.25">
@@ -4738,14 +4738,14 @@
         <v>197</v>
       </c>
       <c r="E129" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F129" t="s">
         <v>285</v>
       </c>
       <c r="G129" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E129,'feed rations'!$Y$13:$Y$46,0),MATCH(C129&amp;D129,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.0178983263546054E-2</v>
+        <v>1.7666004011112982E-3</v>
       </c>
     </row>
     <row r="130" spans="3:7" x14ac:dyDescent="0.25">
@@ -4753,14 +4753,14 @@
         <v>197</v>
       </c>
       <c r="E130" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F130" t="s">
         <v>285</v>
       </c>
       <c r="G130" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E130,'feed rations'!$Y$13:$Y$46,0),MATCH(C130&amp;D130,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.8450625710019192E-2</v>
+        <v>0.55283506413716399</v>
       </c>
     </row>
     <row r="131" spans="3:7" x14ac:dyDescent="0.25">
@@ -4768,14 +4768,14 @@
         <v>197</v>
       </c>
       <c r="E131" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F131" t="s">
         <v>285</v>
       </c>
       <c r="G131" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E131,'feed rations'!$Y$13:$Y$46,0),MATCH(C131&amp;D131,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.4684819038582827</v>
+        <v>6.1866213781219229E-5</v>
       </c>
     </row>
     <row r="132" spans="3:7" x14ac:dyDescent="0.25">
@@ -4783,14 +4783,14 @@
         <v>197</v>
       </c>
       <c r="E132" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F132" t="s">
         <v>285</v>
       </c>
       <c r="G132" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E132,'feed rations'!$Y$13:$Y$46,0),MATCH(C132&amp;D132,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.6524662289726004E-2</v>
+        <v>1.4094536822348984</v>
       </c>
     </row>
     <row r="133" spans="3:7" x14ac:dyDescent="0.25">
@@ -4798,14 +4798,14 @@
         <v>197</v>
       </c>
       <c r="E133" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F133" t="s">
         <v>285</v>
       </c>
       <c r="G133" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E133,'feed rations'!$Y$13:$Y$46,0),MATCH(C133&amp;D133,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10335011276914095</v>
+        <v>5.5679592403097307E-5</v>
       </c>
     </row>
     <row r="134" spans="3:7" x14ac:dyDescent="0.25">
@@ -4813,14 +4813,14 @@
         <v>197</v>
       </c>
       <c r="E134" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F134" t="s">
         <v>285</v>
       </c>
       <c r="G134" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E134,'feed rations'!$Y$13:$Y$46,0),MATCH(C134&amp;D134,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8717016446612009E-2</v>
+        <v>0.60414683073671682</v>
       </c>
     </row>
     <row r="135" spans="3:7" x14ac:dyDescent="0.25">
@@ -4828,14 +4828,14 @@
         <v>197</v>
       </c>
       <c r="E135" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F135" t="s">
         <v>285</v>
       </c>
       <c r="G135" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E135,'feed rations'!$Y$13:$Y$46,0),MATCH(C135&amp;D135,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>3.5461429297032662E-3</v>
       </c>
     </row>
     <row r="136" spans="3:7" x14ac:dyDescent="0.25">
@@ -4843,14 +4843,14 @@
         <v>197</v>
       </c>
       <c r="E136" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F136" t="s">
         <v>285</v>
       </c>
       <c r="G136" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E136,'feed rations'!$Y$13:$Y$46,0),MATCH(C136&amp;D136,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.5183669237455988E-2</v>
+        <v>1.0178983263546054E-2</v>
       </c>
     </row>
     <row r="137" spans="3:7" x14ac:dyDescent="0.25">
@@ -4858,14 +4858,14 @@
         <v>197</v>
       </c>
       <c r="E137" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F137" t="s">
         <v>285</v>
       </c>
       <c r="G137" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E137,'feed rations'!$Y$13:$Y$46,0),MATCH(C137&amp;D137,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>7.8450625710019192E-2</v>
       </c>
     </row>
     <row r="138" spans="3:7" x14ac:dyDescent="0.25">
@@ -4873,14 +4873,14 @@
         <v>197</v>
       </c>
       <c r="E138" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F138" t="s">
         <v>285</v>
       </c>
       <c r="G138" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E138,'feed rations'!$Y$13:$Y$46,0),MATCH(C138&amp;D138,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.4053010847661285E-4</v>
+        <v>0.4684819038582827</v>
       </c>
     </row>
     <row r="139" spans="3:7" x14ac:dyDescent="0.25">
@@ -4888,14 +4888,14 @@
         <v>197</v>
       </c>
       <c r="E139" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F139" t="s">
         <v>285</v>
       </c>
       <c r="G139" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E139,'feed rations'!$Y$13:$Y$46,0),MATCH(C139&amp;D139,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.7878882970076748E-2</v>
+        <v>9.6524662289726004E-2</v>
       </c>
     </row>
     <row r="140" spans="3:7" x14ac:dyDescent="0.25">
@@ -4903,14 +4903,14 @@
         <v>197</v>
       </c>
       <c r="E140" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F140" t="s">
         <v>285</v>
       </c>
       <c r="G140" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E140,'feed rations'!$Y$13:$Y$46,0),MATCH(C140&amp;D140,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.17773535668382656</v>
+        <v>0.10335011276914095</v>
       </c>
     </row>
     <row r="141" spans="3:7" x14ac:dyDescent="0.25">
@@ -4918,14 +4918,14 @@
         <v>197</v>
       </c>
       <c r="E141" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F141" t="s">
         <v>285</v>
       </c>
       <c r="G141" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E141,'feed rations'!$Y$13:$Y$46,0),MATCH(C141&amp;D141,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>2.8717016446612009E-2</v>
       </c>
     </row>
     <row r="142" spans="3:7" x14ac:dyDescent="0.25">
@@ -4933,14 +4933,14 @@
         <v>197</v>
       </c>
       <c r="E142" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F142" t="s">
         <v>285</v>
       </c>
       <c r="G142" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E142,'feed rations'!$Y$13:$Y$46,0),MATCH(C142&amp;D142,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1354510343103608E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="3:7" x14ac:dyDescent="0.25">
@@ -4948,149 +4948,149 @@
         <v>197</v>
       </c>
       <c r="E143" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F143" t="s">
         <v>285</v>
       </c>
       <c r="G143" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E143,'feed rations'!$Y$13:$Y$46,0),MATCH(C143&amp;D143,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>4.5183669237455988E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C144" t="s">
+        <v>197</v>
+      </c>
+      <c r="E144" t="s">
+        <v>253</v>
+      </c>
+      <c r="F144" t="s">
+        <v>285</v>
+      </c>
+      <c r="G144" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E144,'feed rations'!$Y$13:$Y$46,0),MATCH(C144&amp;D144,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C145" t="s">
-        <v>198</v>
-      </c>
-      <c r="E145" s="21" t="s">
-        <v>276</v>
+        <v>197</v>
+      </c>
+      <c r="E145" t="s">
+        <v>254</v>
       </c>
       <c r="F145" t="s">
         <v>285</v>
       </c>
       <c r="G145" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E145,'feed rations'!$Y$13:$Y$46,0),MATCH(C145&amp;D145,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>14.556942659567957</v>
+        <v>4.4053010847661285E-4</v>
       </c>
     </row>
     <row r="146" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C146" t="s">
-        <v>198</v>
-      </c>
-      <c r="E146" s="21" t="s">
-        <v>274</v>
+        <v>197</v>
+      </c>
+      <c r="E146" t="s">
+        <v>255</v>
       </c>
       <c r="F146" t="s">
         <v>285</v>
       </c>
       <c r="G146" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E146,'feed rations'!$Y$13:$Y$46,0),MATCH(C146&amp;D146,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>29.113885319135914</v>
+        <v>5.7878882970076748E-2</v>
       </c>
     </row>
     <row r="147" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C147" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E147" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="F147" t="s">
         <v>285</v>
       </c>
       <c r="G147" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E147,'feed rations'!$Y$13:$Y$46,0),MATCH(C147&amp;D147,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>55.686616486139165</v>
+        <v>0.17773535668382656</v>
       </c>
     </row>
     <row r="148" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C148" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E148" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="F148" t="s">
         <v>285</v>
       </c>
       <c r="G148" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E148,'feed rations'!$Y$13:$Y$46,0),MATCH(C148&amp;D148,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.14042319726111982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C149" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E149" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="F149" t="s">
         <v>285</v>
       </c>
       <c r="G149" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E149,'feed rations'!$Y$13:$Y$46,0),MATCH(C149&amp;D149,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.252784590624109E-2</v>
+        <v>2.1354510343103608E-4</v>
       </c>
     </row>
     <row r="150" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E150" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="F150" t="s">
         <v>285</v>
       </c>
       <c r="G150" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E150,'feed rations'!$Y$13:$Y$46,0),MATCH(C150&amp;D150,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10994689126216511</v>
-      </c>
-    </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C151" t="s">
-        <v>198</v>
-      </c>
-      <c r="E151" t="s">
-        <v>232</v>
-      </c>
-      <c r="F151" t="s">
-        <v>285</v>
-      </c>
-      <c r="G151" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E151,'feed rations'!$Y$13:$Y$46,0),MATCH(C151&amp;D151,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.7969146428143638E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C152" t="s">
         <v>198</v>
       </c>
-      <c r="E152" t="s">
-        <v>233</v>
+      <c r="E152" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F152" t="s">
         <v>285</v>
       </c>
       <c r="G152" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E152,'feed rations'!$Y$13:$Y$46,0),MATCH(C152&amp;D152,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>14.556942659567957</v>
       </c>
     </row>
     <row r="153" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C153" t="s">
         <v>198</v>
       </c>
-      <c r="E153" t="s">
-        <v>234</v>
+      <c r="E153" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F153" t="s">
         <v>285</v>
       </c>
       <c r="G153" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E153,'feed rations'!$Y$13:$Y$46,0),MATCH(C153&amp;D153,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8638137810357785E-2</v>
+        <v>29.113885319135914</v>
       </c>
     </row>
     <row r="154" spans="3:7" x14ac:dyDescent="0.25">
@@ -5098,14 +5098,14 @@
         <v>198</v>
       </c>
       <c r="E154" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F154" t="s">
         <v>285</v>
       </c>
       <c r="G154" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E154,'feed rations'!$Y$13:$Y$46,0),MATCH(C154&amp;D154,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.2642056878731579E-4</v>
+        <v>55.686616486139165</v>
       </c>
     </row>
     <row r="155" spans="3:7" x14ac:dyDescent="0.25">
@@ -5113,14 +5113,14 @@
         <v>198</v>
       </c>
       <c r="E155" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F155" t="s">
         <v>285</v>
       </c>
       <c r="G155" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E155,'feed rations'!$Y$13:$Y$46,0),MATCH(C155&amp;D155,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.9298729944924589E-3</v>
+        <v>0.14042319726111982</v>
       </c>
     </row>
     <row r="156" spans="3:7" x14ac:dyDescent="0.25">
@@ -5128,14 +5128,14 @@
         <v>198</v>
       </c>
       <c r="E156" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F156" t="s">
         <v>285</v>
       </c>
       <c r="G156" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E156,'feed rations'!$Y$13:$Y$46,0),MATCH(C156&amp;D156,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.5680152686726926E-2</v>
+        <v>7.252784590624109E-2</v>
       </c>
     </row>
     <row r="157" spans="3:7" x14ac:dyDescent="0.25">
@@ -5143,14 +5143,14 @@
         <v>198</v>
       </c>
       <c r="E157" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F157" t="s">
         <v>285</v>
       </c>
       <c r="G157" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E157,'feed rations'!$Y$13:$Y$46,0),MATCH(C157&amp;D157,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.01996829037413E-4</v>
+        <v>0.10994689126216511</v>
       </c>
     </row>
     <row r="158" spans="3:7" x14ac:dyDescent="0.25">
@@ -5158,14 +5158,14 @@
         <v>198</v>
       </c>
       <c r="E158" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F158" t="s">
         <v>285</v>
       </c>
       <c r="G158" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E158,'feed rations'!$Y$13:$Y$46,0),MATCH(C158&amp;D158,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.1918606769937602E-2</v>
+        <v>6.7969146428143638E-4</v>
       </c>
     </row>
     <row r="159" spans="3:7" x14ac:dyDescent="0.25">
@@ -5173,14 +5173,14 @@
         <v>198</v>
       </c>
       <c r="E159" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F159" t="s">
         <v>285</v>
       </c>
       <c r="G159" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E159,'feed rations'!$Y$13:$Y$46,0),MATCH(C159&amp;D159,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5719213163687675E-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="3:7" x14ac:dyDescent="0.25">
@@ -5188,14 +5188,14 @@
         <v>198</v>
       </c>
       <c r="E160" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F160" t="s">
         <v>285</v>
       </c>
       <c r="G160" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E160,'feed rations'!$Y$13:$Y$46,0),MATCH(C160&amp;D160,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.1376527579542932E-2</v>
+        <v>2.8638137810357785E-2</v>
       </c>
     </row>
     <row r="161" spans="3:7" x14ac:dyDescent="0.25">
@@ -5203,14 +5203,14 @@
         <v>198</v>
       </c>
       <c r="E161" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F161" t="s">
         <v>285</v>
       </c>
       <c r="G161" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E161,'feed rations'!$Y$13:$Y$46,0),MATCH(C161&amp;D161,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.2147291847318914E-6</v>
+        <v>6.2642056878731579E-4</v>
       </c>
     </row>
     <row r="162" spans="3:7" x14ac:dyDescent="0.25">
@@ -5218,14 +5218,14 @@
         <v>198</v>
       </c>
       <c r="E162" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F162" t="s">
         <v>285</v>
       </c>
       <c r="G162" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E162,'feed rations'!$Y$13:$Y$46,0),MATCH(C162&amp;D162,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.4881154204077169E-2</v>
+        <v>3.9298729944924589E-3</v>
       </c>
     </row>
     <row r="163" spans="3:7" x14ac:dyDescent="0.25">
@@ -5233,14 +5233,14 @@
         <v>198</v>
       </c>
       <c r="E163" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F163" t="s">
         <v>285</v>
       </c>
       <c r="G163" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E163,'feed rations'!$Y$13:$Y$46,0),MATCH(C163&amp;D163,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0474088759158359E-4</v>
+        <v>7.5680152686726926E-2</v>
       </c>
     </row>
     <row r="164" spans="3:7" x14ac:dyDescent="0.25">
@@ -5248,14 +5248,14 @@
         <v>198</v>
       </c>
       <c r="E164" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F164" t="s">
         <v>285</v>
       </c>
       <c r="G164" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E164,'feed rations'!$Y$13:$Y$46,0),MATCH(C164&amp;D164,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.8769601492985593E-4</v>
+        <v>1.01996829037413E-4</v>
       </c>
     </row>
     <row r="165" spans="3:7" x14ac:dyDescent="0.25">
@@ -5263,14 +5263,14 @@
         <v>198</v>
       </c>
       <c r="E165" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F165" t="s">
         <v>285</v>
       </c>
       <c r="G165" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E165,'feed rations'!$Y$13:$Y$46,0),MATCH(C165&amp;D165,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.5294425685567267E-3</v>
+        <v>3.1918606769937602E-2</v>
       </c>
     </row>
     <row r="166" spans="3:7" x14ac:dyDescent="0.25">
@@ -5278,14 +5278,14 @@
         <v>198</v>
       </c>
       <c r="E166" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F166" t="s">
         <v>285</v>
       </c>
       <c r="G166" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E166,'feed rations'!$Y$13:$Y$46,0),MATCH(C166&amp;D166,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.7048374168202494E-2</v>
+        <v>3.5719213163687675E-6</v>
       </c>
     </row>
     <row r="167" spans="3:7" x14ac:dyDescent="0.25">
@@ -5293,14 +5293,14 @@
         <v>198</v>
       </c>
       <c r="E167" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F167" t="s">
         <v>285</v>
       </c>
       <c r="G167" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E167,'feed rations'!$Y$13:$Y$46,0),MATCH(C167&amp;D167,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.5729691169921491E-3</v>
+        <v>8.1376527579542932E-2</v>
       </c>
     </row>
     <row r="168" spans="3:7" x14ac:dyDescent="0.25">
@@ -5308,14 +5308,14 @@
         <v>198</v>
       </c>
       <c r="E168" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F168" t="s">
         <v>285</v>
       </c>
       <c r="G168" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E168,'feed rations'!$Y$13:$Y$46,0),MATCH(C168&amp;D168,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.9670448260287137E-3</v>
+        <v>3.2147291847318914E-6</v>
       </c>
     </row>
     <row r="169" spans="3:7" x14ac:dyDescent="0.25">
@@ -5323,14 +5323,14 @@
         <v>198</v>
       </c>
       <c r="E169" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F169" t="s">
         <v>285</v>
       </c>
       <c r="G169" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E169,'feed rations'!$Y$13:$Y$46,0),MATCH(C169&amp;D169,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6580119732380434E-3</v>
+        <v>3.4881154204077169E-2</v>
       </c>
     </row>
     <row r="170" spans="3:7" x14ac:dyDescent="0.25">
@@ -5338,14 +5338,14 @@
         <v>198</v>
       </c>
       <c r="E170" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F170" t="s">
         <v>285</v>
       </c>
       <c r="G170" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E170,'feed rations'!$Y$13:$Y$46,0),MATCH(C170&amp;D170,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>2.0474088759158359E-4</v>
       </c>
     </row>
     <row r="171" spans="3:7" x14ac:dyDescent="0.25">
@@ -5353,14 +5353,14 @@
         <v>198</v>
       </c>
       <c r="E171" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F171" t="s">
         <v>285</v>
       </c>
       <c r="G171" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E171,'feed rations'!$Y$13:$Y$46,0),MATCH(C171&amp;D171,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.6087342579548447E-3</v>
+        <v>5.8769601492985593E-4</v>
       </c>
     </row>
     <row r="172" spans="3:7" x14ac:dyDescent="0.25">
@@ -5368,14 +5368,14 @@
         <v>198</v>
       </c>
       <c r="E172" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F172" t="s">
         <v>285</v>
       </c>
       <c r="G172" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E172,'feed rations'!$Y$13:$Y$46,0),MATCH(C172&amp;D172,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>4.5294425685567267E-3</v>
       </c>
     </row>
     <row r="173" spans="3:7" x14ac:dyDescent="0.25">
@@ -5383,14 +5383,14 @@
         <v>198</v>
       </c>
       <c r="E173" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F173" t="s">
         <v>285</v>
       </c>
       <c r="G173" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E173,'feed rations'!$Y$13:$Y$46,0),MATCH(C173&amp;D173,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.5434543166556919E-5</v>
+        <v>2.7048374168202494E-2</v>
       </c>
     </row>
     <row r="174" spans="3:7" x14ac:dyDescent="0.25">
@@ -5398,14 +5398,14 @@
         <v>198</v>
       </c>
       <c r="E174" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F174" t="s">
         <v>285</v>
       </c>
       <c r="G174" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E174,'feed rations'!$Y$13:$Y$46,0),MATCH(C174&amp;D174,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.3417079082862866E-3</v>
+        <v>5.5729691169921491E-3</v>
       </c>
     </row>
     <row r="175" spans="3:7" x14ac:dyDescent="0.25">
@@ -5413,14 +5413,14 @@
         <v>198</v>
       </c>
       <c r="E175" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F175" t="s">
         <v>285</v>
       </c>
       <c r="G175" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E175,'feed rations'!$Y$13:$Y$46,0),MATCH(C175&amp;D175,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.0261767617724977E-2</v>
+        <v>5.9670448260287137E-3</v>
       </c>
     </row>
     <row r="176" spans="3:7" x14ac:dyDescent="0.25">
@@ -5428,14 +5428,14 @@
         <v>198</v>
       </c>
       <c r="E176" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F176" t="s">
         <v>285</v>
       </c>
       <c r="G176" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E176,'feed rations'!$Y$13:$Y$46,0),MATCH(C176&amp;D176,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>1.6580119732380434E-3</v>
       </c>
     </row>
     <row r="177" spans="3:7" x14ac:dyDescent="0.25">
@@ -5443,14 +5443,14 @@
         <v>198</v>
       </c>
       <c r="E177" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F177" t="s">
         <v>285</v>
       </c>
       <c r="G177" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E177,'feed rations'!$Y$13:$Y$46,0),MATCH(C177&amp;D177,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2329287026500471E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="3:7" x14ac:dyDescent="0.25">
@@ -5458,149 +5458,149 @@
         <v>198</v>
       </c>
       <c r="E178" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F178" t="s">
         <v>285</v>
       </c>
       <c r="G178" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E178,'feed rations'!$Y$13:$Y$46,0),MATCH(C178&amp;D178,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>2.6087342579548447E-3</v>
+      </c>
+    </row>
+    <row r="179" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C179" t="s">
+        <v>198</v>
+      </c>
+      <c r="E179" t="s">
+        <v>253</v>
+      </c>
+      <c r="F179" t="s">
+        <v>285</v>
+      </c>
+      <c r="G179" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E179,'feed rations'!$Y$13:$Y$46,0),MATCH(C179&amp;D179,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C180" t="s">
-        <v>204</v>
-      </c>
-      <c r="E180" s="21" t="s">
-        <v>276</v>
+        <v>198</v>
+      </c>
+      <c r="E180" t="s">
+        <v>254</v>
       </c>
       <c r="F180" t="s">
         <v>285</v>
       </c>
       <c r="G180" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E180,'feed rations'!$Y$13:$Y$46,0),MATCH(C180&amp;D180,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>14.502048815250316</v>
+        <v>2.5434543166556919E-5</v>
       </c>
     </row>
     <row r="181" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C181" t="s">
-        <v>204</v>
-      </c>
-      <c r="E181" s="21" t="s">
-        <v>274</v>
+        <v>198</v>
+      </c>
+      <c r="E181" t="s">
+        <v>255</v>
       </c>
       <c r="F181" t="s">
         <v>285</v>
       </c>
       <c r="G181" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E181,'feed rations'!$Y$13:$Y$46,0),MATCH(C181&amp;D181,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>29.004097630500631</v>
+        <v>3.3417079082862866E-3</v>
       </c>
     </row>
     <row r="182" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C182" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E182" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="F182" t="s">
         <v>285</v>
       </c>
       <c r="G182" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E182,'feed rations'!$Y$13:$Y$46,0),MATCH(C182&amp;D182,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>52.618920363442022</v>
+        <v>1.0261767617724977E-2</v>
       </c>
     </row>
     <row r="183" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C183" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E183" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="F183" t="s">
         <v>285</v>
       </c>
       <c r="G183" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E183,'feed rations'!$Y$13:$Y$46,0),MATCH(C183&amp;D183,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.84682253603719471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C184" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E184" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="F184" t="s">
         <v>285</v>
       </c>
       <c r="G184" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E184,'feed rations'!$Y$13:$Y$46,0),MATCH(C184&amp;D184,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.43737940455400331</v>
+        <v>1.2329287026500471E-5</v>
       </c>
     </row>
     <row r="185" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C185" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E185" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="F185" t="s">
         <v>285</v>
       </c>
       <c r="G185" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E185,'feed rations'!$Y$13:$Y$46,0),MATCH(C185&amp;D185,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.66303507614130686</v>
-      </c>
-    </row>
-    <row r="186" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C186" t="s">
-        <v>204</v>
-      </c>
-      <c r="E186" t="s">
-        <v>232</v>
-      </c>
-      <c r="F186" t="s">
-        <v>285</v>
-      </c>
-      <c r="G186" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E186,'feed rations'!$Y$13:$Y$46,0),MATCH(C186&amp;D186,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.0988815290634705E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C187" t="s">
         <v>204</v>
       </c>
-      <c r="E187" t="s">
-        <v>233</v>
+      <c r="E187" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F187" t="s">
         <v>285</v>
       </c>
       <c r="G187" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E187,'feed rations'!$Y$13:$Y$46,0),MATCH(C187&amp;D187,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>14.502048815250316</v>
       </c>
     </row>
     <row r="188" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C188" t="s">
         <v>204</v>
       </c>
-      <c r="E188" t="s">
-        <v>234</v>
+      <c r="E188" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F188" t="s">
         <v>285</v>
       </c>
       <c r="G188" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E188,'feed rations'!$Y$13:$Y$46,0),MATCH(C188&amp;D188,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.17270238081001552</v>
+        <v>29.004097630500631</v>
       </c>
     </row>
     <row r="189" spans="3:7" x14ac:dyDescent="0.25">
@@ -5608,14 +5608,14 @@
         <v>204</v>
       </c>
       <c r="E189" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F189" t="s">
         <v>285</v>
       </c>
       <c r="G189" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E189,'feed rations'!$Y$13:$Y$46,0),MATCH(C189&amp;D189,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7776312249885764E-3</v>
+        <v>52.618920363442022</v>
       </c>
     </row>
     <row r="190" spans="3:7" x14ac:dyDescent="0.25">
@@ -5623,14 +5623,14 @@
         <v>204</v>
       </c>
       <c r="E190" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F190" t="s">
         <v>285</v>
       </c>
       <c r="G190" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E190,'feed rations'!$Y$13:$Y$46,0),MATCH(C190&amp;D190,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3699111545736139E-2</v>
+        <v>0.84682253603719471</v>
       </c>
     </row>
     <row r="191" spans="3:7" x14ac:dyDescent="0.25">
@@ -5638,14 +5638,14 @@
         <v>204</v>
       </c>
       <c r="E191" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F191" t="s">
         <v>285</v>
       </c>
       <c r="G191" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E191,'feed rations'!$Y$13:$Y$46,0),MATCH(C191&amp;D191,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.45638940058232602</v>
+        <v>0.43737940455400331</v>
       </c>
     </row>
     <row r="192" spans="3:7" x14ac:dyDescent="0.25">
@@ -5653,14 +5653,14 @@
         <v>204</v>
       </c>
       <c r="E192" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F192" t="s">
         <v>285</v>
       </c>
       <c r="G192" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E192,'feed rations'!$Y$13:$Y$46,0),MATCH(C192&amp;D192,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.1509220070385851E-4</v>
+        <v>0.66303507614130686</v>
       </c>
     </row>
     <row r="193" spans="3:7" x14ac:dyDescent="0.25">
@@ -5668,14 +5668,14 @@
         <v>204</v>
       </c>
       <c r="E193" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F193" t="s">
         <v>285</v>
       </c>
       <c r="G193" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E193,'feed rations'!$Y$13:$Y$46,0),MATCH(C193&amp;D193,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.19248525926546745</v>
+        <v>4.0988815290634705E-3</v>
       </c>
     </row>
     <row r="194" spans="3:7" x14ac:dyDescent="0.25">
@@ -5683,14 +5683,14 @@
         <v>204</v>
       </c>
       <c r="E194" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F194" t="s">
         <v>285</v>
       </c>
       <c r="G194" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E194,'feed rations'!$Y$13:$Y$46,0),MATCH(C194&amp;D194,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1540482816582413E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="3:7" x14ac:dyDescent="0.25">
@@ -5698,14 +5698,14 @@
         <v>204</v>
       </c>
       <c r="E195" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F195" t="s">
         <v>285</v>
       </c>
       <c r="G195" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E195,'feed rations'!$Y$13:$Y$46,0),MATCH(C195&amp;D195,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.49074140742335415</v>
+        <v>0.17270238081001552</v>
       </c>
     </row>
     <row r="196" spans="3:7" x14ac:dyDescent="0.25">
@@ -5713,14 +5713,14 @@
         <v>204</v>
       </c>
       <c r="E196" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F196" t="s">
         <v>285</v>
       </c>
       <c r="G196" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E196,'feed rations'!$Y$13:$Y$46,0),MATCH(C196&amp;D196,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.938643453492417E-5</v>
+        <v>3.7776312249885764E-3</v>
       </c>
     </row>
     <row r="197" spans="3:7" x14ac:dyDescent="0.25">
@@ -5728,14 +5728,14 @@
         <v>204</v>
       </c>
       <c r="E197" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F197" t="s">
         <v>285</v>
       </c>
       <c r="G197" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E197,'feed rations'!$Y$13:$Y$46,0),MATCH(C197&amp;D197,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.21035091095436523</v>
+        <v>2.3699111545736139E-2</v>
       </c>
     </row>
     <row r="198" spans="3:7" x14ac:dyDescent="0.25">
@@ -5743,14 +5743,14 @@
         <v>204</v>
       </c>
       <c r="E198" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F198" t="s">
         <v>285</v>
       </c>
       <c r="G198" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E198,'feed rations'!$Y$13:$Y$46,0),MATCH(C198&amp;D198,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2346905713762435E-3</v>
+        <v>0.45638940058232602</v>
       </c>
     </row>
     <row r="199" spans="3:7" x14ac:dyDescent="0.25">
@@ -5758,14 +5758,14 @@
         <v>204</v>
       </c>
       <c r="E199" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F199" t="s">
         <v>285</v>
       </c>
       <c r="G199" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E199,'feed rations'!$Y$13:$Y$46,0),MATCH(C199&amp;D199,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5441026802460426E-3</v>
+        <v>6.1509220070385851E-4</v>
       </c>
     </row>
     <row r="200" spans="3:7" x14ac:dyDescent="0.25">
@@ -5773,14 +5773,14 @@
         <v>204</v>
       </c>
       <c r="E200" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F200" t="s">
         <v>285</v>
       </c>
       <c r="G200" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E200,'feed rations'!$Y$13:$Y$46,0),MATCH(C200&amp;D200,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.7314817761965576E-2</v>
+        <v>0.19248525926546745</v>
       </c>
     </row>
     <row r="201" spans="3:7" x14ac:dyDescent="0.25">
@@ -5788,14 +5788,14 @@
         <v>204</v>
       </c>
       <c r="E201" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F201" t="s">
         <v>285</v>
       </c>
       <c r="G201" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E201,'feed rations'!$Y$13:$Y$46,0),MATCH(C201&amp;D201,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.16311530612857034</v>
+        <v>2.1540482816582413E-5</v>
       </c>
     </row>
     <row r="202" spans="3:7" x14ac:dyDescent="0.25">
@@ -5803,14 +5803,14 @@
         <v>204</v>
       </c>
       <c r="E202" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F202" t="s">
         <v>285</v>
       </c>
       <c r="G202" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E202,'feed rations'!$Y$13:$Y$46,0),MATCH(C202&amp;D202,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.3607807918891001E-2</v>
+        <v>0.49074140742335415</v>
       </c>
     </row>
     <row r="203" spans="3:7" x14ac:dyDescent="0.25">
@@ -5818,14 +5818,14 @@
         <v>204</v>
       </c>
       <c r="E203" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F203" t="s">
         <v>285</v>
       </c>
       <c r="G203" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E203,'feed rations'!$Y$13:$Y$46,0),MATCH(C203&amp;D203,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.598428273092974E-2</v>
+        <v>1.938643453492417E-5</v>
       </c>
     </row>
     <row r="204" spans="3:7" x14ac:dyDescent="0.25">
@@ -5833,14 +5833,14 @@
         <v>204</v>
       </c>
       <c r="E204" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F204" t="s">
         <v>285</v>
       </c>
       <c r="G204" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E204,'feed rations'!$Y$13:$Y$46,0),MATCH(C204&amp;D204,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.9986464582958335E-3</v>
+        <v>0.21035091095436523</v>
       </c>
     </row>
     <row r="205" spans="3:7" x14ac:dyDescent="0.25">
@@ -5848,14 +5848,14 @@
         <v>204</v>
       </c>
       <c r="E205" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F205" t="s">
         <v>285</v>
       </c>
       <c r="G205" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E205,'feed rations'!$Y$13:$Y$46,0),MATCH(C205&amp;D205,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>1.2346905713762435E-3</v>
       </c>
     </row>
     <row r="206" spans="3:7" x14ac:dyDescent="0.25">
@@ -5863,14 +5863,14 @@
         <v>204</v>
       </c>
       <c r="E206" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F206" t="s">
         <v>285</v>
       </c>
       <c r="G206" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E206,'feed rations'!$Y$13:$Y$46,0),MATCH(C206&amp;D206,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5731980208800535E-2</v>
+        <v>3.5441026802460426E-3</v>
       </c>
     </row>
     <row r="207" spans="3:7" x14ac:dyDescent="0.25">
@@ -5878,14 +5878,14 @@
         <v>204</v>
       </c>
       <c r="E207" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F207" t="s">
         <v>285</v>
       </c>
       <c r="G207" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E207,'feed rations'!$Y$13:$Y$46,0),MATCH(C207&amp;D207,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>2.7314817761965576E-2</v>
       </c>
     </row>
     <row r="208" spans="3:7" x14ac:dyDescent="0.25">
@@ -5893,14 +5893,14 @@
         <v>204</v>
       </c>
       <c r="E208" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F208" t="s">
         <v>285</v>
       </c>
       <c r="G208" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E208,'feed rations'!$Y$13:$Y$46,0),MATCH(C208&amp;D208,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5338309315945754E-4</v>
+        <v>0.16311530612857034</v>
       </c>
     </row>
     <row r="209" spans="3:7" x14ac:dyDescent="0.25">
@@ -5908,14 +5908,14 @@
         <v>204</v>
       </c>
       <c r="E209" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F209" t="s">
         <v>285</v>
       </c>
       <c r="G209" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E209,'feed rations'!$Y$13:$Y$46,0),MATCH(C209&amp;D209,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0152180129671942E-2</v>
+        <v>3.3607807918891001E-2</v>
       </c>
     </row>
     <row r="210" spans="3:7" x14ac:dyDescent="0.25">
@@ -5923,14 +5923,14 @@
         <v>204</v>
       </c>
       <c r="E210" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F210" t="s">
         <v>285</v>
       </c>
       <c r="G210" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E210,'feed rations'!$Y$13:$Y$46,0),MATCH(C210&amp;D210,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.188362213479006E-2</v>
+        <v>3.598428273092974E-2</v>
       </c>
     </row>
     <row r="211" spans="3:7" x14ac:dyDescent="0.25">
@@ -5938,14 +5938,14 @@
         <v>204</v>
       </c>
       <c r="E211" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F211" t="s">
         <v>285</v>
       </c>
       <c r="G211" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E211,'feed rations'!$Y$13:$Y$46,0),MATCH(C211&amp;D211,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>9.9986464582958335E-3</v>
       </c>
     </row>
     <row r="212" spans="3:7" x14ac:dyDescent="0.25">
@@ -5953,14 +5953,14 @@
         <v>204</v>
       </c>
       <c r="E212" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F212" t="s">
         <v>285</v>
       </c>
       <c r="G212" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E212,'feed rations'!$Y$13:$Y$46,0),MATCH(C212&amp;D212,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.4351804480686189E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="3:7" x14ac:dyDescent="0.25">
@@ -5968,140 +5968,119 @@
         <v>204</v>
       </c>
       <c r="E213" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F213" t="s">
         <v>285</v>
       </c>
       <c r="G213" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E213,'feed rations'!$Y$13:$Y$46,0),MATCH(C213&amp;D213,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>1.5731980208800535E-2</v>
+      </c>
+    </row>
+    <row r="214" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C214" t="s">
+        <v>204</v>
+      </c>
+      <c r="E214" t="s">
+        <v>253</v>
+      </c>
+      <c r="F214" t="s">
+        <v>285</v>
+      </c>
+      <c r="G214" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E214,'feed rations'!$Y$13:$Y$46,0),MATCH(C214&amp;D214,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="215" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C215" t="s">
-        <v>196</v>
-      </c>
-      <c r="D215" t="s">
-        <v>205</v>
-      </c>
-      <c r="E215" s="21" t="s">
-        <v>276</v>
+        <v>204</v>
+      </c>
+      <c r="E215" t="s">
+        <v>254</v>
       </c>
       <c r="F215" t="s">
         <v>285</v>
       </c>
       <c r="G215" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E215,'feed rations'!$Y$13:$Y$46,0),MATCH(C215&amp;D215,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.69811719906917724</v>
+        <v>1.5338309315945754E-4</v>
       </c>
     </row>
     <row r="216" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C216" t="s">
-        <v>196</v>
-      </c>
-      <c r="D216" t="s">
-        <v>205</v>
-      </c>
-      <c r="E216" s="21" t="s">
-        <v>274</v>
+        <v>204</v>
+      </c>
+      <c r="E216" t="s">
+        <v>255</v>
       </c>
       <c r="F216" t="s">
         <v>285</v>
       </c>
       <c r="G216" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E216,'feed rations'!$Y$13:$Y$46,0),MATCH(C216&amp;D216,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3962343981383545</v>
+        <v>2.0152180129671942E-2</v>
       </c>
     </row>
     <row r="217" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C217" t="s">
-        <v>196</v>
-      </c>
-      <c r="D217" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E217" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="F217" t="s">
         <v>285</v>
       </c>
       <c r="G217" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E217,'feed rations'!$Y$13:$Y$46,0),MATCH(C217&amp;D217,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>83.30865242225515</v>
+        <v>6.188362213479006E-2</v>
       </c>
     </row>
     <row r="218" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C218" t="s">
-        <v>196</v>
-      </c>
-      <c r="D218" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E218" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="F218" t="s">
         <v>285</v>
       </c>
       <c r="G218" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E218,'feed rations'!$Y$13:$Y$46,0),MATCH(C218&amp;D218,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.1900072971810016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C219" t="s">
-        <v>196</v>
-      </c>
-      <c r="D219" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E219" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="F219" t="s">
         <v>285</v>
       </c>
       <c r="G219" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E219,'feed rations'!$Y$13:$Y$46,0),MATCH(C219&amp;D219,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6476220610438137</v>
+        <v>7.4351804480686189E-5</v>
       </c>
     </row>
     <row r="220" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C220" t="s">
-        <v>196</v>
-      </c>
-      <c r="D220" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E220" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="F220" t="s">
         <v>285</v>
       </c>
       <c r="G220" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E220,'feed rations'!$Y$13:$Y$46,0),MATCH(C220&amp;D220,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4976741184469726</v>
-      </c>
-    </row>
-    <row r="221" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C221" t="s">
-        <v>196</v>
-      </c>
-      <c r="D221" t="s">
-        <v>205</v>
-      </c>
-      <c r="E221" t="s">
-        <v>232</v>
-      </c>
-      <c r="F221" t="s">
-        <v>285</v>
-      </c>
-      <c r="G221" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E221,'feed rations'!$Y$13:$Y$46,0),MATCH(C221&amp;D221,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.544061645924192E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="3:7" x14ac:dyDescent="0.25">
@@ -6111,15 +6090,15 @@
       <c r="D222" t="s">
         <v>205</v>
       </c>
-      <c r="E222" t="s">
-        <v>233</v>
+      <c r="E222" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F222" t="s">
         <v>285</v>
       </c>
       <c r="G222" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E222,'feed rations'!$Y$13:$Y$46,0),MATCH(C222&amp;D222,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.69811719906917724</v>
       </c>
     </row>
     <row r="223" spans="3:7" x14ac:dyDescent="0.25">
@@ -6129,15 +6108,15 @@
       <c r="D223" t="s">
         <v>205</v>
       </c>
-      <c r="E223" t="s">
-        <v>234</v>
+      <c r="E223" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F223" t="s">
         <v>285</v>
       </c>
       <c r="G223" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E223,'feed rations'!$Y$13:$Y$46,0),MATCH(C223&amp;D223,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.65057533494867192</v>
+        <v>1.3962343981383545</v>
       </c>
     </row>
     <row r="224" spans="3:7" x14ac:dyDescent="0.25">
@@ -6148,14 +6127,14 @@
         <v>205</v>
       </c>
       <c r="E224" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F224" t="s">
         <v>285</v>
       </c>
       <c r="G224" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E224,'feed rations'!$Y$13:$Y$46,0),MATCH(C224&amp;D224,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.4230456395462613E-2</v>
+        <v>83.30865242225515</v>
       </c>
     </row>
     <row r="225" spans="3:7" x14ac:dyDescent="0.25">
@@ -6166,14 +6145,14 @@
         <v>205</v>
       </c>
       <c r="E225" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F225" t="s">
         <v>285</v>
       </c>
       <c r="G225" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E225,'feed rations'!$Y$13:$Y$46,0),MATCH(C225&amp;D225,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.9275303325517821E-2</v>
+        <v>3.1900072971810016</v>
       </c>
     </row>
     <row r="226" spans="3:7" x14ac:dyDescent="0.25">
@@ -6184,14 +6163,14 @@
         <v>205</v>
       </c>
       <c r="E226" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F226" t="s">
         <v>285</v>
       </c>
       <c r="G226" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E226,'feed rations'!$Y$13:$Y$46,0),MATCH(C226&amp;D226,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7192333177936787</v>
+        <v>1.6476220610438137</v>
       </c>
     </row>
     <row r="227" spans="3:7" x14ac:dyDescent="0.25">
@@ -6202,14 +6181,14 @@
         <v>205</v>
       </c>
       <c r="E227" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F227" t="s">
         <v>285</v>
       </c>
       <c r="G227" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E227,'feed rations'!$Y$13:$Y$46,0),MATCH(C227&amp;D227,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.317071789169115E-3</v>
+        <v>2.4976741184469726</v>
       </c>
     </row>
     <row r="228" spans="3:7" x14ac:dyDescent="0.25">
@@ -6220,14 +6199,14 @@
         <v>205</v>
       </c>
       <c r="E228" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F228" t="s">
         <v>285</v>
       </c>
       <c r="G228" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E228,'feed rations'!$Y$13:$Y$46,0),MATCH(C228&amp;D228,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.72509806426508272</v>
+        <v>1.544061645924192E-2</v>
       </c>
     </row>
     <row r="229" spans="3:7" x14ac:dyDescent="0.25">
@@ -6238,14 +6217,14 @@
         <v>205</v>
       </c>
       <c r="E229" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F229" t="s">
         <v>285</v>
       </c>
       <c r="G229" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E229,'feed rations'!$Y$13:$Y$46,0),MATCH(C229&amp;D229,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.1143680577109445E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="3:7" x14ac:dyDescent="0.25">
@@ -6256,14 +6235,14 @@
         <v>205</v>
       </c>
       <c r="E230" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F230" t="s">
         <v>285</v>
       </c>
       <c r="G230" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E230,'feed rations'!$Y$13:$Y$46,0),MATCH(C230&amp;D230,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.8486384148858024</v>
+        <v>0.65057533494867192</v>
       </c>
     </row>
     <row r="231" spans="3:7" x14ac:dyDescent="0.25">
@@ -6274,14 +6253,14 @@
         <v>205</v>
       </c>
       <c r="E231" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F231" t="s">
         <v>285</v>
       </c>
       <c r="G231" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E231,'feed rations'!$Y$13:$Y$46,0),MATCH(C231&amp;D231,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.3029312519398498E-5</v>
+        <v>1.4230456395462613E-2</v>
       </c>
     </row>
     <row r="232" spans="3:7" x14ac:dyDescent="0.25">
@@ -6292,14 +6271,14 @@
         <v>205</v>
       </c>
       <c r="E232" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F232" t="s">
         <v>285</v>
       </c>
       <c r="G232" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E232,'feed rations'!$Y$13:$Y$46,0),MATCH(C232&amp;D232,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.79239853966713902</v>
+        <v>8.9275303325517821E-2</v>
       </c>
     </row>
     <row r="233" spans="3:7" x14ac:dyDescent="0.25">
@@ -6310,14 +6289,14 @@
         <v>205</v>
       </c>
       <c r="E233" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F233" t="s">
         <v>285</v>
       </c>
       <c r="G233" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E233,'feed rations'!$Y$13:$Y$46,0),MATCH(C233&amp;D233,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.6511184632405684E-3</v>
+        <v>1.7192333177936787</v>
       </c>
     </row>
     <row r="234" spans="3:7" x14ac:dyDescent="0.25">
@@ -6328,14 +6307,14 @@
         <v>205</v>
       </c>
       <c r="E234" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F234" t="s">
         <v>285</v>
       </c>
       <c r="G234" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E234,'feed rations'!$Y$13:$Y$46,0),MATCH(C234&amp;D234,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3350746975688711E-2</v>
+        <v>2.317071789169115E-3</v>
       </c>
     </row>
     <row r="235" spans="3:7" x14ac:dyDescent="0.25">
@@ -6346,14 +6325,14 @@
         <v>205</v>
       </c>
       <c r="E235" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F235" t="s">
         <v>285</v>
       </c>
       <c r="G235" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E235,'feed rations'!$Y$13:$Y$46,0),MATCH(C235&amp;D235,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10289578308767665</v>
+        <v>0.72509806426508272</v>
       </c>
     </row>
     <row r="236" spans="3:7" x14ac:dyDescent="0.25">
@@ -6364,14 +6343,14 @@
         <v>205</v>
       </c>
       <c r="E236" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F236" t="s">
         <v>285</v>
       </c>
       <c r="G236" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E236,'feed rations'!$Y$13:$Y$46,0),MATCH(C236&amp;D236,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.61446052117016126</v>
+        <v>8.1143680577109445E-5</v>
       </c>
     </row>
     <row r="237" spans="3:7" x14ac:dyDescent="0.25">
@@ -6382,14 +6361,14 @@
         <v>205</v>
       </c>
       <c r="E237" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F237" t="s">
         <v>285</v>
       </c>
       <c r="G237" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E237,'feed rations'!$Y$13:$Y$46,0),MATCH(C237&amp;D237,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.12660167619678325</v>
+        <v>1.8486384148858024</v>
       </c>
     </row>
     <row r="238" spans="3:7" x14ac:dyDescent="0.25">
@@ -6400,14 +6379,14 @@
         <v>205</v>
       </c>
       <c r="E238" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F238" t="s">
         <v>285</v>
       </c>
       <c r="G238" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E238,'feed rations'!$Y$13:$Y$46,0),MATCH(C238&amp;D238,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13555393203476143</v>
+        <v>7.3029312519398498E-5</v>
       </c>
     </row>
     <row r="239" spans="3:7" x14ac:dyDescent="0.25">
@@ -6418,14 +6397,14 @@
         <v>205</v>
       </c>
       <c r="E239" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F239" t="s">
         <v>285</v>
       </c>
       <c r="G239" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E239,'feed rations'!$Y$13:$Y$46,0),MATCH(C239&amp;D239,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7665217689123641E-2</v>
+        <v>0.79239853966713902</v>
       </c>
     </row>
     <row r="240" spans="3:7" x14ac:dyDescent="0.25">
@@ -6436,14 +6415,14 @@
         <v>205</v>
       </c>
       <c r="E240" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F240" t="s">
         <v>285</v>
       </c>
       <c r="G240" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E240,'feed rations'!$Y$13:$Y$46,0),MATCH(C240&amp;D240,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>4.6511184632405684E-3</v>
       </c>
     </row>
     <row r="241" spans="3:7" x14ac:dyDescent="0.25">
@@ -6454,14 +6433,14 @@
         <v>205</v>
       </c>
       <c r="E241" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F241" t="s">
         <v>285</v>
       </c>
       <c r="G241" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E241,'feed rations'!$Y$13:$Y$46,0),MATCH(C241&amp;D241,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.9262867400799252E-2</v>
+        <v>1.3350746975688711E-2</v>
       </c>
     </row>
     <row r="242" spans="3:7" x14ac:dyDescent="0.25">
@@ -6472,14 +6451,14 @@
         <v>205</v>
       </c>
       <c r="E242" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F242" t="s">
         <v>285</v>
       </c>
       <c r="G242" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E242,'feed rations'!$Y$13:$Y$46,0),MATCH(C242&amp;D242,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.10289578308767665</v>
       </c>
     </row>
     <row r="243" spans="3:7" x14ac:dyDescent="0.25">
@@ -6490,14 +6469,14 @@
         <v>205</v>
       </c>
       <c r="E243" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F243" t="s">
         <v>285</v>
       </c>
       <c r="G243" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E243,'feed rations'!$Y$13:$Y$46,0),MATCH(C243&amp;D243,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.7779896686803802E-4</v>
+        <v>0.61446052117016126</v>
       </c>
     </row>
     <row r="244" spans="3:7" x14ac:dyDescent="0.25">
@@ -6508,14 +6487,14 @@
         <v>205</v>
       </c>
       <c r="E244" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F244" t="s">
         <v>285</v>
       </c>
       <c r="G244" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E244,'feed rations'!$Y$13:$Y$46,0),MATCH(C244&amp;D244,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.5913900412465971E-2</v>
+        <v>0.12660167619678325</v>
       </c>
     </row>
     <row r="245" spans="3:7" x14ac:dyDescent="0.25">
@@ -6526,14 +6505,14 @@
         <v>205</v>
       </c>
       <c r="E245" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F245" t="s">
         <v>285</v>
       </c>
       <c r="G245" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E245,'feed rations'!$Y$13:$Y$46,0),MATCH(C245&amp;D245,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.23311756334422978</v>
+        <v>0.13555393203476143</v>
       </c>
     </row>
     <row r="246" spans="3:7" x14ac:dyDescent="0.25">
@@ -6544,14 +6523,14 @@
         <v>205</v>
       </c>
       <c r="E246" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F246" t="s">
         <v>285</v>
       </c>
       <c r="G246" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E246,'feed rations'!$Y$13:$Y$46,0),MATCH(C246&amp;D246,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>3.7665217689123641E-2</v>
       </c>
     </row>
     <row r="247" spans="3:7" x14ac:dyDescent="0.25">
@@ -6562,14 +6541,14 @@
         <v>205</v>
       </c>
       <c r="E247" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F247" t="s">
         <v>285</v>
       </c>
       <c r="G247" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E247,'feed rations'!$Y$13:$Y$46,0),MATCH(C247&amp;D247,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8008560088857437E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="3:7" x14ac:dyDescent="0.25">
@@ -6580,140 +6559,140 @@
         <v>205</v>
       </c>
       <c r="E248" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F248" t="s">
         <v>285</v>
       </c>
       <c r="G248" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E248,'feed rations'!$Y$13:$Y$46,0),MATCH(C248&amp;D248,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>5.9262867400799252E-2</v>
+      </c>
+    </row>
+    <row r="249" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C249" t="s">
+        <v>196</v>
+      </c>
+      <c r="D249" t="s">
+        <v>205</v>
+      </c>
+      <c r="E249" t="s">
+        <v>253</v>
+      </c>
+      <c r="F249" t="s">
+        <v>285</v>
+      </c>
+      <c r="G249" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E249,'feed rations'!$Y$13:$Y$46,0),MATCH(C249&amp;D249,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C250" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D250" t="s">
         <v>205</v>
       </c>
-      <c r="E250" s="21" t="s">
-        <v>276</v>
+      <c r="E250" t="s">
+        <v>254</v>
       </c>
       <c r="F250" t="s">
         <v>285</v>
       </c>
       <c r="G250" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E250,'feed rations'!$Y$13:$Y$46,0),MATCH(C250&amp;D250,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>16.081871345029242</v>
+        <v>5.7779896686803802E-4</v>
       </c>
     </row>
     <row r="251" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C251" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D251" t="s">
         <v>205</v>
       </c>
-      <c r="E251" s="21" t="s">
-        <v>274</v>
+      <c r="E251" t="s">
+        <v>255</v>
       </c>
       <c r="F251" t="s">
         <v>285</v>
       </c>
       <c r="G251" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E251,'feed rations'!$Y$13:$Y$46,0),MATCH(C251&amp;D251,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>32.163742690058484</v>
+        <v>7.5913900412465971E-2</v>
       </c>
     </row>
     <row r="252" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C252" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D252" t="s">
         <v>205</v>
       </c>
       <c r="E252" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="F252" t="s">
         <v>285</v>
       </c>
       <c r="G252" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E252,'feed rations'!$Y$13:$Y$46,0),MATCH(C252&amp;D252,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.23311756334422978</v>
       </c>
     </row>
     <row r="253" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C253" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D253" t="s">
         <v>205</v>
       </c>
       <c r="E253" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="F253" t="s">
         <v>285</v>
       </c>
       <c r="G253" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E253,'feed rations'!$Y$13:$Y$46,0),MATCH(C253&amp;D253,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>11.310331873032048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C254" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D254" t="s">
         <v>205</v>
       </c>
       <c r="E254" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="F254" t="s">
         <v>285</v>
       </c>
       <c r="G254" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E254,'feed rations'!$Y$13:$Y$46,0),MATCH(C254&amp;D254,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.8417271735404546</v>
+        <v>2.8008560088857437E-4</v>
       </c>
     </row>
     <row r="255" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C255" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D255" t="s">
         <v>205</v>
       </c>
       <c r="E255" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="F255" t="s">
         <v>285</v>
       </c>
       <c r="G255" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E255,'feed rations'!$Y$13:$Y$46,0),MATCH(C255&amp;D255,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.8556296455127299</v>
-      </c>
-    </row>
-    <row r="256" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C256" t="s">
-        <v>197</v>
-      </c>
-      <c r="D256" t="s">
-        <v>205</v>
-      </c>
-      <c r="E256" t="s">
-        <v>232</v>
-      </c>
-      <c r="F256" t="s">
-        <v>285</v>
-      </c>
-      <c r="G256" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E256,'feed rations'!$Y$13:$Y$46,0),MATCH(C256&amp;D256,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.4745484950004523E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="3:7" x14ac:dyDescent="0.25">
@@ -6723,15 +6702,15 @@
       <c r="D257" t="s">
         <v>205</v>
       </c>
-      <c r="E257" t="s">
-        <v>233</v>
+      <c r="E257" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F257" t="s">
         <v>285</v>
       </c>
       <c r="G257" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E257,'feed rations'!$Y$13:$Y$46,0),MATCH(C257&amp;D257,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>16.081871345029242</v>
       </c>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.25">
@@ -6741,15 +6720,15 @@
       <c r="D258" t="s">
         <v>205</v>
       </c>
-      <c r="E258" t="s">
-        <v>234</v>
+      <c r="E258" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F258" t="s">
         <v>285</v>
       </c>
       <c r="G258" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E258,'feed rations'!$Y$13:$Y$46,0),MATCH(C258&amp;D258,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3066476848441386</v>
+        <v>32.163742690058484</v>
       </c>
     </row>
     <row r="259" spans="3:7" x14ac:dyDescent="0.25">
@@ -6760,14 +6739,14 @@
         <v>205</v>
       </c>
       <c r="E259" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F259" t="s">
         <v>285</v>
       </c>
       <c r="G259" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E259,'feed rations'!$Y$13:$Y$46,0),MATCH(C259&amp;D259,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.0454801366638102E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="3:7" x14ac:dyDescent="0.25">
@@ -6778,14 +6757,14 @@
         <v>205</v>
       </c>
       <c r="E260" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F260" t="s">
         <v>285</v>
       </c>
       <c r="G260" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E260,'feed rations'!$Y$13:$Y$46,0),MATCH(C260&amp;D260,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.31653009369900376</v>
+        <v>11.310331873032048</v>
       </c>
     </row>
     <row r="261" spans="3:7" x14ac:dyDescent="0.25">
@@ -6796,14 +6775,14 @@
         <v>205</v>
       </c>
       <c r="E261" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F261" t="s">
         <v>285</v>
       </c>
       <c r="G261" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E261,'feed rations'!$Y$13:$Y$46,0),MATCH(C261&amp;D261,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.0956284985943601</v>
+        <v>5.8417271735404546</v>
       </c>
     </row>
     <row r="262" spans="3:7" x14ac:dyDescent="0.25">
@@ -6814,14 +6793,14 @@
         <v>205</v>
       </c>
       <c r="E262" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F262" t="s">
         <v>285</v>
       </c>
       <c r="G262" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E262,'feed rations'!$Y$13:$Y$46,0),MATCH(C262&amp;D262,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.2152949719901079E-3</v>
+        <v>8.8556296455127299</v>
       </c>
     </row>
     <row r="263" spans="3:7" x14ac:dyDescent="0.25">
@@ -6832,14 +6811,14 @@
         <v>205</v>
       </c>
       <c r="E263" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F263" t="s">
         <v>285</v>
       </c>
       <c r="G263" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E263,'feed rations'!$Y$13:$Y$46,0),MATCH(C263&amp;D263,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.5708717828258543</v>
+        <v>5.4745484950004523E-2</v>
       </c>
     </row>
     <row r="264" spans="3:7" x14ac:dyDescent="0.25">
@@ -6850,14 +6829,14 @@
         <v>205</v>
       </c>
       <c r="E264" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F264" t="s">
         <v>285</v>
       </c>
       <c r="G264" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E264,'feed rations'!$Y$13:$Y$46,0),MATCH(C264&amp;D264,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8769901483844112E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="3:7" x14ac:dyDescent="0.25">
@@ -6868,14 +6847,14 @@
         <v>205</v>
       </c>
       <c r="E265" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F265" t="s">
         <v>285</v>
       </c>
       <c r="G265" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E265,'feed rations'!$Y$13:$Y$46,0),MATCH(C265&amp;D265,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.5544408014587594</v>
+        <v>2.3066476848441386</v>
       </c>
     </row>
     <row r="266" spans="3:7" x14ac:dyDescent="0.25">
@@ -6886,14 +6865,14 @@
         <v>205</v>
       </c>
       <c r="E266" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F266" t="s">
         <v>285</v>
       </c>
       <c r="G266" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E266,'feed rations'!$Y$13:$Y$46,0),MATCH(C266&amp;D266,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.58929113354597E-4</v>
+        <v>5.0454801366638102E-2</v>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.25">
@@ -6904,14 +6883,14 @@
         <v>205</v>
       </c>
       <c r="E267" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F267" t="s">
         <v>285</v>
       </c>
       <c r="G267" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E267,'feed rations'!$Y$13:$Y$46,0),MATCH(C267&amp;D267,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8094890150443339</v>
+        <v>0.31653009369900376</v>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.25">
@@ -6922,14 +6901,14 @@
         <v>205</v>
       </c>
       <c r="E268" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F268" t="s">
         <v>285</v>
       </c>
       <c r="G268" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E268,'feed rations'!$Y$13:$Y$46,0),MATCH(C268&amp;D268,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6490775255130326E-2</v>
+        <v>6.0956284985943601</v>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.25">
@@ -6940,14 +6919,14 @@
         <v>205</v>
       </c>
       <c r="E269" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F269" t="s">
         <v>285</v>
       </c>
       <c r="G269" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E269,'feed rations'!$Y$13:$Y$46,0),MATCH(C269&amp;D269,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.7335747219562054E-2</v>
+        <v>8.2152949719901079E-3</v>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.25">
@@ -6958,14 +6937,14 @@
         <v>205</v>
       </c>
       <c r="E270" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F270" t="s">
         <v>285</v>
       </c>
       <c r="G270" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E270,'feed rations'!$Y$13:$Y$46,0),MATCH(C270&amp;D270,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.36482219212651157</v>
+        <v>2.5708717828258543</v>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.25">
@@ -6976,14 +6955,14 @@
         <v>205</v>
       </c>
       <c r="E271" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F271" t="s">
         <v>285</v>
       </c>
       <c r="G271" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E271,'feed rations'!$Y$13:$Y$46,0),MATCH(C271&amp;D271,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1786007898640953</v>
+        <v>2.8769901483844112E-4</v>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.25">
@@ -6994,14 +6973,14 @@
         <v>205</v>
       </c>
       <c r="E272" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F272" t="s">
         <v>285</v>
       </c>
       <c r="G272" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E272,'feed rations'!$Y$13:$Y$46,0),MATCH(C272&amp;D272,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.44887263259025506</v>
+        <v>6.5544408014587594</v>
       </c>
     </row>
     <row r="273" spans="3:7" x14ac:dyDescent="0.25">
@@ -7012,14 +6991,14 @@
         <v>205</v>
       </c>
       <c r="E273" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F273" t="s">
         <v>285</v>
       </c>
       <c r="G273" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E273,'feed rations'!$Y$13:$Y$46,0),MATCH(C273&amp;D273,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.48061330748755038</v>
+        <v>2.58929113354597E-4</v>
       </c>
     </row>
     <row r="274" spans="3:7" x14ac:dyDescent="0.25">
@@ -7030,14 +7009,14 @@
         <v>205</v>
       </c>
       <c r="E274" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F274" t="s">
         <v>285</v>
       </c>
       <c r="G274" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E274,'feed rations'!$Y$13:$Y$46,0),MATCH(C274&amp;D274,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13354393029459391</v>
+        <v>2.8094890150443339</v>
       </c>
     </row>
     <row r="275" spans="3:7" x14ac:dyDescent="0.25">
@@ -7048,14 +7027,14 @@
         <v>205</v>
       </c>
       <c r="E275" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F275" t="s">
         <v>285</v>
       </c>
       <c r="G275" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E275,'feed rations'!$Y$13:$Y$46,0),MATCH(C275&amp;D275,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>1.6490775255130326E-2</v>
       </c>
     </row>
     <row r="276" spans="3:7" x14ac:dyDescent="0.25">
@@ -7066,14 +7045,14 @@
         <v>205</v>
       </c>
       <c r="E276" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F276" t="s">
         <v>285</v>
       </c>
       <c r="G276" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E276,'feed rations'!$Y$13:$Y$46,0),MATCH(C276&amp;D276,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.21011948738890288</v>
+        <v>4.7335747219562054E-2</v>
       </c>
     </row>
     <row r="277" spans="3:7" x14ac:dyDescent="0.25">
@@ -7084,14 +7063,14 @@
         <v>205</v>
       </c>
       <c r="E277" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F277" t="s">
         <v>285</v>
       </c>
       <c r="G277" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E277,'feed rations'!$Y$13:$Y$46,0),MATCH(C277&amp;D277,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.36482219212651157</v>
       </c>
     </row>
     <row r="278" spans="3:7" x14ac:dyDescent="0.25">
@@ -7102,14 +7081,14 @@
         <v>205</v>
       </c>
       <c r="E278" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F278" t="s">
         <v>285</v>
       </c>
       <c r="G278" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E278,'feed rations'!$Y$13:$Y$46,0),MATCH(C278&amp;D278,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0486153987633827E-3</v>
+        <v>2.1786007898640953</v>
       </c>
     </row>
     <row r="279" spans="3:7" x14ac:dyDescent="0.25">
@@ -7120,14 +7099,14 @@
         <v>205</v>
       </c>
       <c r="E279" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F279" t="s">
         <v>285</v>
       </c>
       <c r="G279" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E279,'feed rations'!$Y$13:$Y$46,0),MATCH(C279&amp;D279,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.26915656531571153</v>
+        <v>0.44887263259025506</v>
       </c>
     </row>
     <row r="280" spans="3:7" x14ac:dyDescent="0.25">
@@ -7138,14 +7117,14 @@
         <v>205</v>
       </c>
       <c r="E280" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F280" t="s">
         <v>285</v>
       </c>
       <c r="G280" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E280,'feed rations'!$Y$13:$Y$46,0),MATCH(C280&amp;D280,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.82653008636870395</v>
+        <v>0.48061330748755038</v>
       </c>
     </row>
     <row r="281" spans="3:7" x14ac:dyDescent="0.25">
@@ -7156,14 +7135,14 @@
         <v>205</v>
       </c>
       <c r="E281" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F281" t="s">
         <v>285</v>
       </c>
       <c r="G281" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E281,'feed rations'!$Y$13:$Y$46,0),MATCH(C281&amp;D281,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.13354393029459391</v>
       </c>
     </row>
     <row r="282" spans="3:7" x14ac:dyDescent="0.25">
@@ -7174,14 +7153,14 @@
         <v>205</v>
       </c>
       <c r="E282" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F282" t="s">
         <v>285</v>
       </c>
       <c r="G282" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E282,'feed rations'!$Y$13:$Y$46,0),MATCH(C282&amp;D282,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.9305763397682621E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="3:7" x14ac:dyDescent="0.25">
@@ -7192,140 +7171,140 @@
         <v>205</v>
       </c>
       <c r="E283" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F283" t="s">
         <v>285</v>
       </c>
       <c r="G283" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E283,'feed rations'!$Y$13:$Y$46,0),MATCH(C283&amp;D283,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0.21011948738890288</v>
+      </c>
+    </row>
+    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C284" t="s">
+        <v>197</v>
+      </c>
+      <c r="D284" t="s">
+        <v>205</v>
+      </c>
+      <c r="E284" t="s">
+        <v>253</v>
+      </c>
+      <c r="F284" t="s">
+        <v>285</v>
+      </c>
+      <c r="G284" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E284,'feed rations'!$Y$13:$Y$46,0),MATCH(C284&amp;D284,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="285" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C285" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D285" t="s">
         <v>205</v>
       </c>
-      <c r="E285" s="21" t="s">
-        <v>276</v>
+      <c r="E285" t="s">
+        <v>254</v>
       </c>
       <c r="F285" t="s">
         <v>285</v>
       </c>
       <c r="G285" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E285,'feed rations'!$Y$13:$Y$46,0),MATCH(C285&amp;D285,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>18.580594474270001</v>
+        <v>2.0486153987633827E-3</v>
       </c>
     </row>
     <row r="286" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C286" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D286" t="s">
         <v>205</v>
       </c>
-      <c r="E286" s="21" t="s">
-        <v>274</v>
+      <c r="E286" t="s">
+        <v>255</v>
       </c>
       <c r="F286" t="s">
         <v>285</v>
       </c>
       <c r="G286" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E286,'feed rations'!$Y$13:$Y$46,0),MATCH(C286&amp;D286,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>37.161188948540001</v>
+        <v>0.26915656531571153</v>
       </c>
     </row>
     <row r="287" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C287" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D287" t="s">
         <v>205</v>
       </c>
       <c r="E287" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="F287" t="s">
         <v>285</v>
       </c>
       <c r="G287" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E287,'feed rations'!$Y$13:$Y$46,0),MATCH(C287&amp;D287,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>41.770328663087604</v>
+        <v>0.82653008636870395</v>
       </c>
     </row>
     <row r="288" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C288" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D288" t="s">
         <v>205</v>
       </c>
       <c r="E288" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="F288" t="s">
         <v>285</v>
       </c>
       <c r="G288" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E288,'feed rations'!$Y$13:$Y$46,0),MATCH(C288&amp;D288,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.5436995811423736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C289" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D289" t="s">
         <v>205</v>
       </c>
       <c r="E289" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="F289" t="s">
         <v>285</v>
       </c>
       <c r="G289" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E289,'feed rations'!$Y$13:$Y$46,0),MATCH(C289&amp;D289,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.28081798598457164</v>
+        <v>9.9305763397682621E-4</v>
       </c>
     </row>
     <row r="290" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C290" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D290" t="s">
         <v>205</v>
       </c>
       <c r="E290" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="F290" t="s">
         <v>285</v>
       </c>
       <c r="G290" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E290,'feed rations'!$Y$13:$Y$46,0),MATCH(C290&amp;D290,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.42569945630839534</v>
-      </c>
-    </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C291" t="s">
-        <v>198</v>
-      </c>
-      <c r="D291" t="s">
-        <v>205</v>
-      </c>
-      <c r="E291" t="s">
-        <v>232</v>
-      </c>
-      <c r="F291" t="s">
-        <v>285</v>
-      </c>
-      <c r="G291" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E291,'feed rations'!$Y$13:$Y$46,0),MATCH(C291&amp;D291,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.6316731967630778E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="3:7" x14ac:dyDescent="0.25">
@@ -7335,15 +7314,15 @@
       <c r="D292" t="s">
         <v>205</v>
       </c>
-      <c r="E292" t="s">
-        <v>233</v>
+      <c r="E292" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F292" t="s">
         <v>285</v>
       </c>
       <c r="G292" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E292,'feed rations'!$Y$13:$Y$46,0),MATCH(C292&amp;D292,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>18.580594474270001</v>
       </c>
     </row>
     <row r="293" spans="3:7" x14ac:dyDescent="0.25">
@@ -7353,15 +7332,15 @@
       <c r="D293" t="s">
         <v>205</v>
       </c>
-      <c r="E293" t="s">
-        <v>234</v>
+      <c r="E293" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F293" t="s">
         <v>285</v>
       </c>
       <c r="G293" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E293,'feed rations'!$Y$13:$Y$46,0),MATCH(C293&amp;D293,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.11088298682756348</v>
+        <v>37.161188948540001</v>
       </c>
     </row>
     <row r="294" spans="3:7" x14ac:dyDescent="0.25">
@@ -7372,14 +7351,14 @@
         <v>205</v>
       </c>
       <c r="E294" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F294" t="s">
         <v>285</v>
       </c>
       <c r="G294" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E294,'feed rations'!$Y$13:$Y$46,0),MATCH(C294&amp;D294,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4254155119065326E-3</v>
+        <v>41.770328663087604</v>
       </c>
     </row>
     <row r="295" spans="3:7" x14ac:dyDescent="0.25">
@@ -7390,14 +7369,14 @@
         <v>205</v>
       </c>
       <c r="E295" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F295" t="s">
         <v>285</v>
       </c>
       <c r="G295" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E295,'feed rations'!$Y$13:$Y$46,0),MATCH(C295&amp;D295,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5215935420378532E-2</v>
+        <v>0.5436995811423736</v>
       </c>
     </row>
     <row r="296" spans="3:7" x14ac:dyDescent="0.25">
@@ -7408,14 +7387,14 @@
         <v>205</v>
       </c>
       <c r="E296" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F296" t="s">
         <v>285</v>
       </c>
       <c r="G296" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E296,'feed rations'!$Y$13:$Y$46,0),MATCH(C296&amp;D296,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.29302329044716247</v>
+        <v>0.28081798598457164</v>
       </c>
     </row>
     <row r="297" spans="3:7" x14ac:dyDescent="0.25">
@@ -7426,14 +7405,14 @@
         <v>205</v>
       </c>
       <c r="E297" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F297" t="s">
         <v>285</v>
       </c>
       <c r="G297" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E297,'feed rations'!$Y$13:$Y$46,0),MATCH(C297&amp;D297,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.9491789324787145E-4</v>
+        <v>0.42569945630839534</v>
       </c>
     </row>
     <row r="298" spans="3:7" x14ac:dyDescent="0.25">
@@ -7444,14 +7423,14 @@
         <v>205</v>
       </c>
       <c r="E298" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F298" t="s">
         <v>285</v>
       </c>
       <c r="G298" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E298,'feed rations'!$Y$13:$Y$46,0),MATCH(C298&amp;D298,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.12358451787130892</v>
+        <v>2.6316731967630778E-3</v>
       </c>
     </row>
     <row r="299" spans="3:7" x14ac:dyDescent="0.25">
@@ -7462,14 +7441,14 @@
         <v>205</v>
       </c>
       <c r="E299" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F299" t="s">
         <v>285</v>
       </c>
       <c r="G299" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E299,'feed rations'!$Y$13:$Y$46,0),MATCH(C299&amp;D299,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3829995053964826E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="3:7" x14ac:dyDescent="0.25">
@@ -7480,14 +7459,14 @@
         <v>205</v>
       </c>
       <c r="E300" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F300" t="s">
         <v>285</v>
       </c>
       <c r="G300" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E300,'feed rations'!$Y$13:$Y$46,0),MATCH(C300&amp;D300,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.31507888171457132</v>
+        <v>0.11088298682756348</v>
       </c>
     </row>
     <row r="301" spans="3:7" x14ac:dyDescent="0.25">
@@ -7498,14 +7477,14 @@
         <v>205</v>
       </c>
       <c r="E301" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F301" t="s">
         <v>285</v>
       </c>
       <c r="G301" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E301,'feed rations'!$Y$13:$Y$46,0),MATCH(C301&amp;D301,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2446995548568345E-5</v>
+        <v>2.4254155119065326E-3</v>
       </c>
     </row>
     <row r="302" spans="3:7" x14ac:dyDescent="0.25">
@@ -7516,14 +7495,14 @@
         <v>205</v>
       </c>
       <c r="E302" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F302" t="s">
         <v>285</v>
       </c>
       <c r="G302" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E302,'feed rations'!$Y$13:$Y$46,0),MATCH(C302&amp;D302,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13505509987252132</v>
+        <v>1.5215935420378532E-2</v>
       </c>
     </row>
     <row r="303" spans="3:7" x14ac:dyDescent="0.25">
@@ -7534,14 +7513,14 @@
         <v>205</v>
       </c>
       <c r="E303" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F303" t="s">
         <v>285</v>
       </c>
       <c r="G303" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E303,'feed rations'!$Y$13:$Y$46,0),MATCH(C303&amp;D303,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.9272895787484826E-4</v>
+        <v>0.29302329044716247</v>
       </c>
     </row>
     <row r="304" spans="3:7" x14ac:dyDescent="0.25">
@@ -7552,14 +7531,14 @@
         <v>205</v>
       </c>
       <c r="E304" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F304" t="s">
         <v>285</v>
       </c>
       <c r="G304" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E304,'feed rations'!$Y$13:$Y$46,0),MATCH(C304&amp;D304,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.2754792896663078E-3</v>
+        <v>3.9491789324787145E-4</v>
       </c>
     </row>
     <row r="305" spans="3:7" x14ac:dyDescent="0.25">
@@ -7570,14 +7549,14 @@
         <v>205</v>
       </c>
       <c r="E305" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F305" t="s">
         <v>285</v>
       </c>
       <c r="G305" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E305,'feed rations'!$Y$13:$Y$46,0),MATCH(C305&amp;D305,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7537387521189746E-2</v>
+        <v>0.12358451787130892</v>
       </c>
     </row>
     <row r="306" spans="3:7" x14ac:dyDescent="0.25">
@@ -7588,14 +7567,14 @@
         <v>205</v>
       </c>
       <c r="E306" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F306" t="s">
         <v>285</v>
       </c>
       <c r="G306" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E306,'feed rations'!$Y$13:$Y$46,0),MATCH(C306&amp;D306,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10472763754614865</v>
+        <v>1.3829995053964826E-5</v>
       </c>
     </row>
     <row r="307" spans="3:7" x14ac:dyDescent="0.25">
@@ -7606,14 +7585,14 @@
         <v>205</v>
       </c>
       <c r="E307" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F307" t="s">
         <v>285</v>
       </c>
       <c r="G307" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E307,'feed rations'!$Y$13:$Y$46,0),MATCH(C307&amp;D307,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1577780834840472E-2</v>
+        <v>0.31507888171457132</v>
       </c>
     </row>
     <row r="308" spans="3:7" x14ac:dyDescent="0.25">
@@ -7624,14 +7603,14 @@
         <v>205</v>
       </c>
       <c r="E308" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F308" t="s">
         <v>285</v>
       </c>
       <c r="G308" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E308,'feed rations'!$Y$13:$Y$46,0),MATCH(C308&amp;D308,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3103588551233269E-2</v>
+        <v>1.2446995548568345E-5</v>
       </c>
     </row>
     <row r="309" spans="3:7" x14ac:dyDescent="0.25">
@@ -7642,14 +7621,14 @@
         <v>205</v>
       </c>
       <c r="E309" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F309" t="s">
         <v>285</v>
       </c>
       <c r="G309" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E309,'feed rations'!$Y$13:$Y$46,0),MATCH(C309&amp;D309,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.41959756622177E-3</v>
+        <v>0.13505509987252132</v>
       </c>
     </row>
     <row r="310" spans="3:7" x14ac:dyDescent="0.25">
@@ -7660,14 +7639,14 @@
         <v>205</v>
       </c>
       <c r="E310" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F310" t="s">
         <v>285</v>
       </c>
       <c r="G310" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E310,'feed rations'!$Y$13:$Y$46,0),MATCH(C310&amp;D310,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>7.9272895787484826E-4</v>
       </c>
     </row>
     <row r="311" spans="3:7" x14ac:dyDescent="0.25">
@@ -7678,14 +7657,14 @@
         <v>205</v>
       </c>
       <c r="E311" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F311" t="s">
         <v>285</v>
       </c>
       <c r="G311" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E311,'feed rations'!$Y$13:$Y$46,0),MATCH(C311&amp;D311,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.0100665353206037E-2</v>
+        <v>2.2754792896663078E-3</v>
       </c>
     </row>
     <row r="312" spans="3:7" x14ac:dyDescent="0.25">
@@ -7696,14 +7675,14 @@
         <v>205</v>
       </c>
       <c r="E312" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F312" t="s">
         <v>285</v>
       </c>
       <c r="G312" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E312,'feed rations'!$Y$13:$Y$46,0),MATCH(C312&amp;D312,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>1.7537387521189746E-2</v>
       </c>
     </row>
     <row r="313" spans="3:7" x14ac:dyDescent="0.25">
@@ -7714,14 +7693,14 @@
         <v>205</v>
       </c>
       <c r="E313" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F313" t="s">
         <v>285</v>
       </c>
       <c r="G313" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E313,'feed rations'!$Y$13:$Y$46,0),MATCH(C313&amp;D313,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.8479102711852997E-5</v>
+        <v>0.10472763754614865</v>
       </c>
     </row>
     <row r="314" spans="3:7" x14ac:dyDescent="0.25">
@@ -7732,14 +7711,14 @@
         <v>205</v>
       </c>
       <c r="E314" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F314" t="s">
         <v>285</v>
       </c>
       <c r="G314" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E314,'feed rations'!$Y$13:$Y$46,0),MATCH(C314&amp;D314,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2938639950327263E-2</v>
+        <v>2.1577780834840472E-2</v>
       </c>
     </row>
     <row r="315" spans="3:7" x14ac:dyDescent="0.25">
@@ -7750,14 +7729,14 @@
         <v>205</v>
       </c>
       <c r="E315" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F315" t="s">
         <v>285</v>
       </c>
       <c r="G315" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E315,'feed rations'!$Y$13:$Y$46,0),MATCH(C315&amp;D315,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.9732172919853009E-2</v>
+        <v>2.3103588551233269E-2</v>
       </c>
     </row>
     <row r="316" spans="3:7" x14ac:dyDescent="0.25">
@@ -7768,14 +7747,14 @@
         <v>205</v>
       </c>
       <c r="E316" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F316" t="s">
         <v>285</v>
       </c>
       <c r="G316" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E316,'feed rations'!$Y$13:$Y$46,0),MATCH(C316&amp;D316,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>6.41959756622177E-3</v>
       </c>
     </row>
     <row r="317" spans="3:7" x14ac:dyDescent="0.25">
@@ -7786,14 +7765,14 @@
         <v>205</v>
       </c>
       <c r="E317" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F317" t="s">
         <v>285</v>
       </c>
       <c r="G317" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E317,'feed rations'!$Y$13:$Y$46,0),MATCH(C317&amp;D317,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.773732775523721E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="3:7" x14ac:dyDescent="0.25">
@@ -7804,140 +7783,140 @@
         <v>205</v>
       </c>
       <c r="E318" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F318" t="s">
         <v>285</v>
       </c>
       <c r="G318" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E318,'feed rations'!$Y$13:$Y$46,0),MATCH(C318&amp;D318,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>1.0100665353206037E-2</v>
+      </c>
+    </row>
+    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C319" t="s">
+        <v>198</v>
+      </c>
+      <c r="D319" t="s">
+        <v>205</v>
+      </c>
+      <c r="E319" t="s">
+        <v>253</v>
+      </c>
+      <c r="F319" t="s">
+        <v>285</v>
+      </c>
+      <c r="G319" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E319,'feed rations'!$Y$13:$Y$46,0),MATCH(C319&amp;D319,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="320" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C320" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D320" t="s">
         <v>205</v>
       </c>
-      <c r="E320" s="21" t="s">
-        <v>276</v>
+      <c r="E320" t="s">
+        <v>254</v>
       </c>
       <c r="F320" t="s">
         <v>285</v>
       </c>
       <c r="G320" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E320,'feed rations'!$Y$13:$Y$46,0),MATCH(C320&amp;D320,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.69811719906917724</v>
+        <v>9.8479102711852997E-5</v>
       </c>
     </row>
     <row r="321" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C321" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D321" t="s">
         <v>205</v>
       </c>
-      <c r="E321" s="21" t="s">
-        <v>274</v>
+      <c r="E321" t="s">
+        <v>255</v>
       </c>
       <c r="F321" t="s">
         <v>285</v>
       </c>
       <c r="G321" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E321,'feed rations'!$Y$13:$Y$46,0),MATCH(C321&amp;D321,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3962343981383545</v>
+        <v>1.2938639950327263E-2</v>
       </c>
     </row>
     <row r="322" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C322" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D322" t="s">
         <v>205</v>
       </c>
       <c r="E322" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="F322" t="s">
         <v>285</v>
       </c>
       <c r="G322" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E322,'feed rations'!$Y$13:$Y$46,0),MATCH(C322&amp;D322,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>83.30865242225515</v>
+        <v>3.9732172919853009E-2</v>
       </c>
     </row>
     <row r="323" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C323" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D323" t="s">
         <v>205</v>
       </c>
       <c r="E323" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="F323" t="s">
         <v>285</v>
       </c>
       <c r="G323" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E323,'feed rations'!$Y$13:$Y$46,0),MATCH(C323&amp;D323,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.1900072971810016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C324" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D324" t="s">
         <v>205</v>
       </c>
       <c r="E324" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="F324" t="s">
         <v>285</v>
       </c>
       <c r="G324" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E324,'feed rations'!$Y$13:$Y$46,0),MATCH(C324&amp;D324,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6476220610438137</v>
+        <v>4.773732775523721E-5</v>
       </c>
     </row>
     <row r="325" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C325" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D325" t="s">
         <v>205</v>
       </c>
       <c r="E325" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="F325" t="s">
         <v>285</v>
       </c>
       <c r="G325" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E325,'feed rations'!$Y$13:$Y$46,0),MATCH(C325&amp;D325,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4976741184469726</v>
-      </c>
-    </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C326" t="s">
-        <v>204</v>
-      </c>
-      <c r="D326" t="s">
-        <v>205</v>
-      </c>
-      <c r="E326" t="s">
-        <v>232</v>
-      </c>
-      <c r="F326" t="s">
-        <v>285</v>
-      </c>
-      <c r="G326" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E326,'feed rations'!$Y$13:$Y$46,0),MATCH(C326&amp;D326,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.544061645924192E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="3:7" x14ac:dyDescent="0.25">
@@ -7947,15 +7926,15 @@
       <c r="D327" t="s">
         <v>205</v>
       </c>
-      <c r="E327" t="s">
-        <v>233</v>
+      <c r="E327" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F327" t="s">
         <v>285</v>
       </c>
       <c r="G327" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E327,'feed rations'!$Y$13:$Y$46,0),MATCH(C327&amp;D327,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.69811719906917724</v>
       </c>
     </row>
     <row r="328" spans="3:7" x14ac:dyDescent="0.25">
@@ -7965,15 +7944,15 @@
       <c r="D328" t="s">
         <v>205</v>
       </c>
-      <c r="E328" t="s">
-        <v>234</v>
+      <c r="E328" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F328" t="s">
         <v>285</v>
       </c>
       <c r="G328" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E328,'feed rations'!$Y$13:$Y$46,0),MATCH(C328&amp;D328,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.65057533494867192</v>
+        <v>1.3962343981383545</v>
       </c>
     </row>
     <row r="329" spans="3:7" x14ac:dyDescent="0.25">
@@ -7984,14 +7963,14 @@
         <v>205</v>
       </c>
       <c r="E329" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F329" t="s">
         <v>285</v>
       </c>
       <c r="G329" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E329,'feed rations'!$Y$13:$Y$46,0),MATCH(C329&amp;D329,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.4230456395462613E-2</v>
+        <v>83.30865242225515</v>
       </c>
     </row>
     <row r="330" spans="3:7" x14ac:dyDescent="0.25">
@@ -8002,14 +7981,14 @@
         <v>205</v>
       </c>
       <c r="E330" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F330" t="s">
         <v>285</v>
       </c>
       <c r="G330" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E330,'feed rations'!$Y$13:$Y$46,0),MATCH(C330&amp;D330,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.9275303325517821E-2</v>
+        <v>3.1900072971810016</v>
       </c>
     </row>
     <row r="331" spans="3:7" x14ac:dyDescent="0.25">
@@ -8020,14 +7999,14 @@
         <v>205</v>
       </c>
       <c r="E331" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F331" t="s">
         <v>285</v>
       </c>
       <c r="G331" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E331,'feed rations'!$Y$13:$Y$46,0),MATCH(C331&amp;D331,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7192333177936787</v>
+        <v>1.6476220610438137</v>
       </c>
     </row>
     <row r="332" spans="3:7" x14ac:dyDescent="0.25">
@@ -8038,14 +8017,14 @@
         <v>205</v>
       </c>
       <c r="E332" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F332" t="s">
         <v>285</v>
       </c>
       <c r="G332" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E332,'feed rations'!$Y$13:$Y$46,0),MATCH(C332&amp;D332,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.317071789169115E-3</v>
+        <v>2.4976741184469726</v>
       </c>
     </row>
     <row r="333" spans="3:7" x14ac:dyDescent="0.25">
@@ -8056,14 +8035,14 @@
         <v>205</v>
       </c>
       <c r="E333" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F333" t="s">
         <v>285</v>
       </c>
       <c r="G333" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E333,'feed rations'!$Y$13:$Y$46,0),MATCH(C333&amp;D333,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.72509806426508272</v>
+        <v>1.544061645924192E-2</v>
       </c>
     </row>
     <row r="334" spans="3:7" x14ac:dyDescent="0.25">
@@ -8074,14 +8053,14 @@
         <v>205</v>
       </c>
       <c r="E334" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F334" t="s">
         <v>285</v>
       </c>
       <c r="G334" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E334,'feed rations'!$Y$13:$Y$46,0),MATCH(C334&amp;D334,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.1143680577109445E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="3:7" x14ac:dyDescent="0.25">
@@ -8092,14 +8071,14 @@
         <v>205</v>
       </c>
       <c r="E335" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F335" t="s">
         <v>285</v>
       </c>
       <c r="G335" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E335,'feed rations'!$Y$13:$Y$46,0),MATCH(C335&amp;D335,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.8486384148858024</v>
+        <v>0.65057533494867192</v>
       </c>
     </row>
     <row r="336" spans="3:7" x14ac:dyDescent="0.25">
@@ -8110,14 +8089,14 @@
         <v>205</v>
       </c>
       <c r="E336" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F336" t="s">
         <v>285</v>
       </c>
       <c r="G336" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E336,'feed rations'!$Y$13:$Y$46,0),MATCH(C336&amp;D336,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.3029312519398498E-5</v>
+        <v>1.4230456395462613E-2</v>
       </c>
     </row>
     <row r="337" spans="3:7" x14ac:dyDescent="0.25">
@@ -8128,14 +8107,14 @@
         <v>205</v>
       </c>
       <c r="E337" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F337" t="s">
         <v>285</v>
       </c>
       <c r="G337" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E337,'feed rations'!$Y$13:$Y$46,0),MATCH(C337&amp;D337,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.79239853966713902</v>
+        <v>8.9275303325517821E-2</v>
       </c>
     </row>
     <row r="338" spans="3:7" x14ac:dyDescent="0.25">
@@ -8146,14 +8125,14 @@
         <v>205</v>
       </c>
       <c r="E338" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F338" t="s">
         <v>285</v>
       </c>
       <c r="G338" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E338,'feed rations'!$Y$13:$Y$46,0),MATCH(C338&amp;D338,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.6511184632405684E-3</v>
+        <v>1.7192333177936787</v>
       </c>
     </row>
     <row r="339" spans="3:7" x14ac:dyDescent="0.25">
@@ -8164,14 +8143,14 @@
         <v>205</v>
       </c>
       <c r="E339" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F339" t="s">
         <v>285</v>
       </c>
       <c r="G339" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E339,'feed rations'!$Y$13:$Y$46,0),MATCH(C339&amp;D339,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3350746975688711E-2</v>
+        <v>2.317071789169115E-3</v>
       </c>
     </row>
     <row r="340" spans="3:7" x14ac:dyDescent="0.25">
@@ -8182,14 +8161,14 @@
         <v>205</v>
       </c>
       <c r="E340" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F340" t="s">
         <v>285</v>
       </c>
       <c r="G340" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E340,'feed rations'!$Y$13:$Y$46,0),MATCH(C340&amp;D340,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10289578308767665</v>
+        <v>0.72509806426508272</v>
       </c>
     </row>
     <row r="341" spans="3:7" x14ac:dyDescent="0.25">
@@ -8200,14 +8179,14 @@
         <v>205</v>
       </c>
       <c r="E341" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F341" t="s">
         <v>285</v>
       </c>
       <c r="G341" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E341,'feed rations'!$Y$13:$Y$46,0),MATCH(C341&amp;D341,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.61446052117016126</v>
+        <v>8.1143680577109445E-5</v>
       </c>
     </row>
     <row r="342" spans="3:7" x14ac:dyDescent="0.25">
@@ -8218,14 +8197,14 @@
         <v>205</v>
       </c>
       <c r="E342" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F342" t="s">
         <v>285</v>
       </c>
       <c r="G342" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E342,'feed rations'!$Y$13:$Y$46,0),MATCH(C342&amp;D342,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.12660167619678325</v>
+        <v>1.8486384148858024</v>
       </c>
     </row>
     <row r="343" spans="3:7" x14ac:dyDescent="0.25">
@@ -8236,14 +8215,14 @@
         <v>205</v>
       </c>
       <c r="E343" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F343" t="s">
         <v>285</v>
       </c>
       <c r="G343" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E343,'feed rations'!$Y$13:$Y$46,0),MATCH(C343&amp;D343,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13555393203476143</v>
+        <v>7.3029312519398498E-5</v>
       </c>
     </row>
     <row r="344" spans="3:7" x14ac:dyDescent="0.25">
@@ -8254,14 +8233,14 @@
         <v>205</v>
       </c>
       <c r="E344" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F344" t="s">
         <v>285</v>
       </c>
       <c r="G344" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E344,'feed rations'!$Y$13:$Y$46,0),MATCH(C344&amp;D344,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7665217689123641E-2</v>
+        <v>0.79239853966713902</v>
       </c>
     </row>
     <row r="345" spans="3:7" x14ac:dyDescent="0.25">
@@ -8272,14 +8251,14 @@
         <v>205</v>
       </c>
       <c r="E345" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F345" t="s">
         <v>285</v>
       </c>
       <c r="G345" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E345,'feed rations'!$Y$13:$Y$46,0),MATCH(C345&amp;D345,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>4.6511184632405684E-3</v>
       </c>
     </row>
     <row r="346" spans="3:7" x14ac:dyDescent="0.25">
@@ -8290,14 +8269,14 @@
         <v>205</v>
       </c>
       <c r="E346" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F346" t="s">
         <v>285</v>
       </c>
       <c r="G346" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E346,'feed rations'!$Y$13:$Y$46,0),MATCH(C346&amp;D346,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.9262867400799252E-2</v>
+        <v>1.3350746975688711E-2</v>
       </c>
     </row>
     <row r="347" spans="3:7" x14ac:dyDescent="0.25">
@@ -8308,14 +8287,14 @@
         <v>205</v>
       </c>
       <c r="E347" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F347" t="s">
         <v>285</v>
       </c>
       <c r="G347" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E347,'feed rations'!$Y$13:$Y$46,0),MATCH(C347&amp;D347,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.10289578308767665</v>
       </c>
     </row>
     <row r="348" spans="3:7" x14ac:dyDescent="0.25">
@@ -8326,14 +8305,14 @@
         <v>205</v>
       </c>
       <c r="E348" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F348" t="s">
         <v>285</v>
       </c>
       <c r="G348" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E348,'feed rations'!$Y$13:$Y$46,0),MATCH(C348&amp;D348,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.7779896686803802E-4</v>
+        <v>0.61446052117016126</v>
       </c>
     </row>
     <row r="349" spans="3:7" x14ac:dyDescent="0.25">
@@ -8344,14 +8323,14 @@
         <v>205</v>
       </c>
       <c r="E349" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F349" t="s">
         <v>285</v>
       </c>
       <c r="G349" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E349,'feed rations'!$Y$13:$Y$46,0),MATCH(C349&amp;D349,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.5913900412465971E-2</v>
+        <v>0.12660167619678325</v>
       </c>
     </row>
     <row r="350" spans="3:7" x14ac:dyDescent="0.25">
@@ -8362,14 +8341,14 @@
         <v>205</v>
       </c>
       <c r="E350" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F350" t="s">
         <v>285</v>
       </c>
       <c r="G350" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E350,'feed rations'!$Y$13:$Y$46,0),MATCH(C350&amp;D350,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.23311756334422978</v>
+        <v>0.13555393203476143</v>
       </c>
     </row>
     <row r="351" spans="3:7" x14ac:dyDescent="0.25">
@@ -8380,14 +8359,14 @@
         <v>205</v>
       </c>
       <c r="E351" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F351" t="s">
         <v>285</v>
       </c>
       <c r="G351" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E351,'feed rations'!$Y$13:$Y$46,0),MATCH(C351&amp;D351,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>3.7665217689123641E-2</v>
       </c>
     </row>
     <row r="352" spans="3:7" x14ac:dyDescent="0.25">
@@ -8398,14 +8377,14 @@
         <v>205</v>
       </c>
       <c r="E352" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F352" t="s">
         <v>285</v>
       </c>
       <c r="G352" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E352,'feed rations'!$Y$13:$Y$46,0),MATCH(C352&amp;D352,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8008560088857437E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353" spans="3:7" x14ac:dyDescent="0.25">
@@ -8416,13 +8395,139 @@
         <v>205</v>
       </c>
       <c r="E353" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F353" t="s">
         <v>285</v>
       </c>
       <c r="G353" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E353,'feed rations'!$Y$13:$Y$46,0),MATCH(C353&amp;D353,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>5.9262867400799252E-2</v>
+      </c>
+    </row>
+    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C354" t="s">
+        <v>204</v>
+      </c>
+      <c r="D354" t="s">
+        <v>205</v>
+      </c>
+      <c r="E354" t="s">
+        <v>253</v>
+      </c>
+      <c r="F354" t="s">
+        <v>285</v>
+      </c>
+      <c r="G354" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E354,'feed rations'!$Y$13:$Y$46,0),MATCH(C354&amp;D354,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C355" t="s">
+        <v>204</v>
+      </c>
+      <c r="D355" t="s">
+        <v>205</v>
+      </c>
+      <c r="E355" t="s">
+        <v>254</v>
+      </c>
+      <c r="F355" t="s">
+        <v>285</v>
+      </c>
+      <c r="G355" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E355,'feed rations'!$Y$13:$Y$46,0),MATCH(C355&amp;D355,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>5.7779896686803802E-4</v>
+      </c>
+    </row>
+    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C356" t="s">
+        <v>204</v>
+      </c>
+      <c r="D356" t="s">
+        <v>205</v>
+      </c>
+      <c r="E356" t="s">
+        <v>255</v>
+      </c>
+      <c r="F356" t="s">
+        <v>285</v>
+      </c>
+      <c r="G356" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E356,'feed rations'!$Y$13:$Y$46,0),MATCH(C356&amp;D356,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>7.5913900412465971E-2</v>
+      </c>
+    </row>
+    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C357" t="s">
+        <v>204</v>
+      </c>
+      <c r="D357" t="s">
+        <v>205</v>
+      </c>
+      <c r="E357" t="s">
+        <v>256</v>
+      </c>
+      <c r="F357" t="s">
+        <v>285</v>
+      </c>
+      <c r="G357" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E357,'feed rations'!$Y$13:$Y$46,0),MATCH(C357&amp;D357,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0.23311756334422978</v>
+      </c>
+    </row>
+    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C358" t="s">
+        <v>204</v>
+      </c>
+      <c r="D358" t="s">
+        <v>205</v>
+      </c>
+      <c r="E358" t="s">
+        <v>257</v>
+      </c>
+      <c r="F358" t="s">
+        <v>285</v>
+      </c>
+      <c r="G358" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E358,'feed rations'!$Y$13:$Y$46,0),MATCH(C358&amp;D358,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C359" t="s">
+        <v>204</v>
+      </c>
+      <c r="D359" t="s">
+        <v>205</v>
+      </c>
+      <c r="E359" t="s">
+        <v>258</v>
+      </c>
+      <c r="F359" t="s">
+        <v>285</v>
+      </c>
+      <c r="G359" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E359,'feed rations'!$Y$13:$Y$46,0),MATCH(C359&amp;D359,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>2.8008560088857437E-4</v>
+      </c>
+    </row>
+    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C360" t="s">
+        <v>204</v>
+      </c>
+      <c r="D360" t="s">
+        <v>205</v>
+      </c>
+      <c r="E360" t="s">
+        <v>259</v>
+      </c>
+      <c r="F360" t="s">
+        <v>285</v>
+      </c>
+      <c r="G360" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E360,'feed rations'!$Y$13:$Y$46,0),MATCH(C360&amp;D360,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -8905,7 +9010,7 @@
         <v>34202.371999999996</v>
       </c>
       <c r="K13" s="82">
-        <f>J13/SUM(J$13:J$43)</f>
+        <f t="shared" ref="K13:K43" si="10">J13/SUM(J$13:J$43)</f>
         <v>0.21853861585180565</v>
       </c>
       <c r="M13" s="21" t="s">
@@ -8951,31 +9056,31 @@
         <v>14.502048815250316</v>
       </c>
       <c r="AC13" s="19">
-        <f t="shared" ref="AC13:AI13" si="10">Q13/Q$48*100</f>
+        <f t="shared" ref="AC13:AI13" si="11">Q13/Q$48*100</f>
         <v>0.69811719906917724</v>
       </c>
       <c r="AD13" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15.175760492490328</v>
       </c>
       <c r="AE13" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>16.081871345029242</v>
       </c>
       <c r="AF13" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>14.556942659567957</v>
       </c>
       <c r="AG13" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>18.580594474270001</v>
       </c>
       <c r="AH13" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>14.502048815250316</v>
       </c>
       <c r="AI13" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.69811719906917724</v>
       </c>
     </row>
@@ -8996,15 +9101,15 @@
         <v>0</v>
       </c>
       <c r="I14" s="54">
-        <f t="shared" ref="I14:I44" si="11">SUM(G14:H14)</f>
+        <f t="shared" ref="I14:I44" si="12">SUM(G14:H14)</f>
         <v>20541.099999999999</v>
       </c>
       <c r="J14" s="55">
-        <f t="shared" ref="J14:J44" si="12">F14*I14</f>
+        <f t="shared" ref="J14:J44" si="13">F14*I14</f>
         <v>17665.345999999998</v>
       </c>
       <c r="K14" s="82">
-        <f>J14/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>0.11287405047179862</v>
       </c>
       <c r="M14" s="21" t="s">
@@ -9046,35 +9151,35 @@
         <v>274</v>
       </c>
       <c r="AB14" s="19">
-        <f t="shared" ref="AB14:AB46" si="13">P14/P$48*100</f>
+        <f t="shared" ref="AB14:AB46" si="14">P14/P$48*100</f>
         <v>29.004097630500631</v>
       </c>
       <c r="AC14" s="19">
-        <f t="shared" ref="AC14:AC46" si="14">Q14/Q$48*100</f>
+        <f t="shared" ref="AC14:AC46" si="15">Q14/Q$48*100</f>
         <v>1.3962343981383545</v>
       </c>
       <c r="AD14" s="19">
-        <f t="shared" ref="AD14:AD46" si="15">R14/R$48*100</f>
+        <f t="shared" ref="AD14:AD46" si="16">R14/R$48*100</f>
         <v>30.351520984980656</v>
       </c>
       <c r="AE14" s="19">
-        <f t="shared" ref="AE14:AE46" si="16">S14/S$48*100</f>
+        <f t="shared" ref="AE14:AE46" si="17">S14/S$48*100</f>
         <v>32.163742690058484</v>
       </c>
       <c r="AF14" s="19">
-        <f t="shared" ref="AF14:AF46" si="17">T14/T$48*100</f>
+        <f t="shared" ref="AF14:AF46" si="18">T14/T$48*100</f>
         <v>29.113885319135914</v>
       </c>
       <c r="AG14" s="19">
-        <f t="shared" ref="AG14:AG46" si="18">U14/U$48*100</f>
+        <f t="shared" ref="AG14:AG46" si="19">U14/U$48*100</f>
         <v>37.161188948540001</v>
       </c>
       <c r="AH14" s="19">
-        <f t="shared" ref="AH14:AH46" si="19">V14/V$48*100</f>
+        <f t="shared" ref="AH14:AH46" si="20">V14/V$48*100</f>
         <v>29.004097630500631</v>
       </c>
       <c r="AI14" s="19">
-        <f t="shared" ref="AI14:AI46" si="20">W14/W$48*100</f>
+        <f t="shared" ref="AI14:AI46" si="21">W14/W$48*100</f>
         <v>1.3962343981383545</v>
       </c>
     </row>
@@ -9095,15 +9200,15 @@
         <v>0</v>
       </c>
       <c r="I15" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>31138.799999999999</v>
       </c>
       <c r="J15" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>26779.367999999999</v>
       </c>
       <c r="K15" s="82">
-        <f>J15/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>0.17110877620143239</v>
       </c>
       <c r="M15" t="s">
@@ -9145,35 +9250,35 @@
         <v>277</v>
       </c>
       <c r="AB15" s="19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>52.618920363442022</v>
       </c>
       <c r="AC15" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>83.30865242225515</v>
       </c>
       <c r="AD15" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>43.343560127534147</v>
       </c>
       <c r="AE15" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF15" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>55.686616486139165</v>
       </c>
       <c r="AG15" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>41.770328663087604</v>
       </c>
       <c r="AH15" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>52.618920363442022</v>
       </c>
       <c r="AI15" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>83.30865242225515</v>
       </c>
     </row>
@@ -9194,85 +9299,85 @@
         <v>0</v>
       </c>
       <c r="I16" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>192.5</v>
       </c>
       <c r="J16" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>165.55</v>
       </c>
       <c r="K16" s="82">
-        <f>J16/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>1.0577941159831382E-3</v>
       </c>
       <c r="M16" t="s">
         <v>229</v>
       </c>
       <c r="P16" s="47">
-        <f>F$5*K13</f>
+        <f t="shared" ref="P16:P46" si="22">F$5*K13</f>
         <v>6.3376198597023636</v>
       </c>
       <c r="Q16" s="47">
-        <f>M$5*K13</f>
+        <f t="shared" ref="Q16:Q46" si="23">M$5*K13</f>
         <v>5.0263881645915296</v>
       </c>
       <c r="R16" s="47">
-        <f>F$6*K13</f>
+        <f t="shared" ref="R16:R46" si="24">F$6*K13</f>
         <v>13.476547977528014</v>
       </c>
       <c r="S16" s="47">
-        <f>M$6*K13</f>
+        <f t="shared" ref="S16:S46" si="25">M$6*K13</f>
         <v>12.893778335256533</v>
       </c>
       <c r="T16" s="47">
-        <f>F$7*K13</f>
+        <f t="shared" ref="T16:T46" si="26">F$7*K13</f>
         <v>1.019846873975093</v>
       </c>
       <c r="U16" s="47">
-        <f>M$7*K13</f>
+        <f t="shared" ref="U16:U46" si="27">M$7*K13</f>
         <v>1.384077900394769</v>
       </c>
       <c r="V16" s="47">
-        <f>F$8*K13</f>
+        <f t="shared" ref="V16:V46" si="28">F$8*K13</f>
         <v>6.3376198597023636</v>
       </c>
       <c r="W16" s="47">
-        <f>M$8*K13</f>
+        <f t="shared" ref="W16:W46" si="29">M$8*K13</f>
         <v>5.0263881645915296</v>
       </c>
       <c r="Y16" t="s">
         <v>229</v>
       </c>
       <c r="AB16" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.84682253603719471</v>
       </c>
       <c r="AC16" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.1900072971810016</v>
       </c>
       <c r="AD16" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.4321508712376856</v>
       </c>
       <c r="AE16" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.310331873032048</v>
       </c>
       <c r="AF16" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14042319726111982</v>
       </c>
       <c r="AG16" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.5436995811423736</v>
       </c>
       <c r="AH16" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.84682253603719471</v>
       </c>
       <c r="AI16" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.1900072971810016</v>
       </c>
     </row>
@@ -9293,85 +9398,85 @@
         <v>0</v>
       </c>
       <c r="I17" s="54">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="55">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="J17" s="55">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="82">
-        <f>J17/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M17" t="s">
         <v>230</v>
       </c>
       <c r="P17" s="47">
-        <f>F$5*K14</f>
+        <f t="shared" si="22"/>
         <v>3.27334746368216</v>
       </c>
       <c r="Q17" s="47">
-        <f>M$5*K14</f>
+        <f t="shared" si="23"/>
         <v>2.5961031608513681</v>
       </c>
       <c r="R17" s="47">
-        <f>F$6*K14</f>
+        <f t="shared" si="24"/>
         <v>6.9605664457609144</v>
       </c>
       <c r="S17" s="47">
-        <f>M$6*K14</f>
+        <f t="shared" si="25"/>
         <v>6.659568977836118</v>
       </c>
       <c r="T17" s="47">
-        <f>F$7*K14</f>
+        <f t="shared" si="26"/>
         <v>0.52674556886839363</v>
       </c>
       <c r="U17" s="47">
-        <f>M$7*K14</f>
+        <f t="shared" si="27"/>
         <v>0.71486898632139118</v>
       </c>
       <c r="V17" s="47">
-        <f>F$8*K14</f>
+        <f t="shared" si="28"/>
         <v>3.27334746368216</v>
       </c>
       <c r="W17" s="47">
-        <f>M$8*K14</f>
+        <f t="shared" si="29"/>
         <v>2.5961031608513681</v>
       </c>
       <c r="Y17" t="s">
         <v>230</v>
       </c>
       <c r="AB17" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.43737940455400331</v>
       </c>
       <c r="AC17" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.6476220610438137</v>
       </c>
       <c r="AD17" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.2561931863852942</v>
       </c>
       <c r="AE17" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>5.8417271735404546</v>
       </c>
       <c r="AF17" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7.252784590624109E-2</v>
       </c>
       <c r="AG17" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.28081798598457164</v>
       </c>
       <c r="AH17" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.43737940455400331</v>
       </c>
       <c r="AI17" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.6476220610438137</v>
       </c>
     </row>
@@ -9392,85 +9497,85 @@
         <v>84</v>
       </c>
       <c r="I18" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8110.8</v>
       </c>
       <c r="J18" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6975.2880000000005</v>
       </c>
       <c r="K18" s="82">
-        <f>J18/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>4.4569124758005382E-2</v>
       </c>
       <c r="M18" t="s">
         <v>231</v>
       </c>
       <c r="P18" s="47">
-        <f>F$5*K15</f>
+        <f t="shared" si="22"/>
         <v>4.9621545098415396</v>
       </c>
       <c r="Q18" s="47">
-        <f>M$5*K15</f>
+        <f t="shared" si="23"/>
         <v>3.9355018526329451</v>
       </c>
       <c r="R18" s="47">
-        <f>F$6*K15</f>
+        <f t="shared" si="24"/>
         <v>10.551707865754997</v>
       </c>
       <c r="S18" s="47">
-        <f>M$6*K15</f>
+        <f t="shared" si="25"/>
         <v>10.095417795884511</v>
       </c>
       <c r="T18" s="47">
-        <f>F$7*K15</f>
+        <f t="shared" si="26"/>
         <v>0.79850762227335115</v>
       </c>
       <c r="U18" s="47">
-        <f>M$7*K15</f>
+        <f t="shared" si="27"/>
         <v>1.083688915942405</v>
       </c>
       <c r="V18" s="47">
-        <f>F$8*K15</f>
+        <f t="shared" si="28"/>
         <v>4.9621545098415396</v>
       </c>
       <c r="W18" s="47">
-        <f>M$8*K15</f>
+        <f t="shared" si="29"/>
         <v>3.9355018526329451</v>
       </c>
       <c r="Y18" t="s">
         <v>231</v>
       </c>
       <c r="AB18" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.66303507614130686</v>
       </c>
       <c r="AC18" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.4976741184469726</v>
       </c>
       <c r="AD18" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.9042966731194728</v>
       </c>
       <c r="AE18" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>8.8556296455127299</v>
       </c>
       <c r="AF18" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.10994689126216511</v>
       </c>
       <c r="AG18" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.42569945630839534</v>
       </c>
       <c r="AH18" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.66303507614130686</v>
       </c>
       <c r="AI18" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.4976741184469726</v>
       </c>
     </row>
@@ -9491,15 +9596,15 @@
         <v>24</v>
       </c>
       <c r="I19" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>179.5</v>
       </c>
       <c r="J19" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>152.57499999999999</v>
       </c>
       <c r="K19" s="82">
-        <f>J19/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>9.7488938233843104E-4</v>
       </c>
       <c r="L19" s="58"/>
@@ -9507,70 +9612,70 @@
         <v>232</v>
       </c>
       <c r="P19" s="47">
-        <f>F$5*K16</f>
+        <f t="shared" si="22"/>
         <v>3.0676029363511007E-2</v>
       </c>
       <c r="Q19" s="47">
-        <f>M$5*K16</f>
+        <f t="shared" si="23"/>
         <v>2.4329264667612177E-2</v>
       </c>
       <c r="R19" s="47">
-        <f>F$6*K16</f>
+        <f t="shared" si="24"/>
         <v>6.5230637152293519E-2</v>
       </c>
       <c r="S19" s="47">
-        <f>M$6*K16</f>
+        <f t="shared" si="25"/>
         <v>6.2409852843005154E-2</v>
       </c>
       <c r="T19" s="47">
-        <f>F$7*K16</f>
+        <f t="shared" si="26"/>
         <v>4.9363725412546449E-3</v>
       </c>
       <c r="U19" s="47">
-        <f>M$7*K16</f>
+        <f t="shared" si="27"/>
         <v>6.6993627345598751E-3</v>
       </c>
       <c r="V19" s="47">
-        <f>F$8*K16</f>
+        <f t="shared" si="28"/>
         <v>3.0676029363511007E-2</v>
       </c>
       <c r="W19" s="47">
-        <f>M$8*K16</f>
+        <f t="shared" si="29"/>
         <v>2.4329264667612177E-2</v>
       </c>
       <c r="Y19" t="s">
         <v>232</v>
       </c>
       <c r="AB19" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0988815290634705E-3</v>
       </c>
       <c r="AC19" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.544061645924192E-2</v>
       </c>
       <c r="AD19" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.1772358266069939E-2</v>
       </c>
       <c r="AE19" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>5.4745484950004523E-2</v>
       </c>
       <c r="AF19" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>6.7969146428143638E-4</v>
       </c>
       <c r="AG19" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.6316731967630778E-3</v>
       </c>
       <c r="AH19" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.0988815290634705E-3</v>
       </c>
       <c r="AI19" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.544061645924192E-2</v>
       </c>
     </row>
@@ -9591,15 +9696,15 @@
         <v>0</v>
       </c>
       <c r="I20" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1126.0999999999999</v>
       </c>
       <c r="J20" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>957.18499999999995</v>
       </c>
       <c r="K20" s="82">
-        <f>J20/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>6.1160052002858347E-3</v>
       </c>
       <c r="L20" s="59"/>
@@ -9607,70 +9712,70 @@
         <v>233</v>
       </c>
       <c r="P20" s="47">
-        <f>F$5*K17</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q20" s="47">
-        <f>M$5*K17</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R20" s="47">
-        <f>F$6*K17</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S20" s="47">
-        <f>M$6*K17</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T20" s="47">
-        <f>F$7*K17</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="U20" s="47">
-        <f>M$7*K17</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V20" s="47">
-        <f>F$8*K17</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W20" s="47">
-        <f>M$8*K17</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Y20" t="s">
         <v>233</v>
       </c>
       <c r="AB20" s="47">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC20" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD20" s="47">
+      <c r="AC20" s="47">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE20" s="47">
+      <c r="AD20" s="47">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AF20" s="47">
+      <c r="AE20" s="47">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="47">
+      <c r="AF20" s="47">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="47">
+      <c r="AG20" s="47">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
+      <c r="AH20" s="47">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AI20" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -9691,15 +9796,15 @@
         <v>29</v>
       </c>
       <c r="I21" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>20256.2</v>
       </c>
       <c r="J21" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>18433.142</v>
       </c>
       <c r="K21" s="82">
-        <f>J21/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>0.11777994048131472</v>
       </c>
       <c r="L21" s="60"/>
@@ -9707,70 +9812,70 @@
         <v>234</v>
       </c>
       <c r="P21" s="47">
-        <f>F$5*K18</f>
+        <f t="shared" si="22"/>
         <v>1.292504617982156</v>
       </c>
       <c r="Q21" s="47">
-        <f>M$5*K18</f>
+        <f t="shared" si="23"/>
         <v>1.0250898694341237</v>
       </c>
       <c r="R21" s="47">
-        <f>F$6*K18</f>
+        <f t="shared" si="24"/>
         <v>2.7484293600769987</v>
       </c>
       <c r="S21" s="47">
-        <f>M$6*K18</f>
+        <f t="shared" si="25"/>
         <v>2.6295783607223178</v>
       </c>
       <c r="T21" s="47">
-        <f>F$7*K18</f>
+        <f t="shared" si="26"/>
         <v>0.20798924887069178</v>
       </c>
       <c r="U21" s="47">
-        <f>M$7*K18</f>
+        <f t="shared" si="27"/>
         <v>0.28227112346736744</v>
       </c>
       <c r="V21" s="47">
-        <f>F$8*K18</f>
+        <f t="shared" si="28"/>
         <v>1.292504617982156</v>
       </c>
       <c r="W21" s="47">
-        <f>M$8*K18</f>
+        <f t="shared" si="29"/>
         <v>1.0250898694341237</v>
       </c>
       <c r="Y21" t="s">
         <v>234</v>
       </c>
       <c r="AB21" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.17270238081001552</v>
       </c>
       <c r="AC21" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.65057533494867192</v>
       </c>
       <c r="AD21" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.4960168489581302</v>
       </c>
       <c r="AE21" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.3066476848441386</v>
       </c>
       <c r="AF21" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.8638137810357785E-2</v>
       </c>
       <c r="AG21" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.11088298682756348</v>
       </c>
       <c r="AH21" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.17270238081001552</v>
       </c>
       <c r="AI21" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.65057533494867192</v>
       </c>
     </row>
@@ -9791,15 +9896,15 @@
         <v>21</v>
       </c>
       <c r="I22" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>27.3</v>
       </c>
       <c r="J22" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24.843</v>
       </c>
       <c r="K22" s="82">
-        <f>J22/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>1.5873620793336815E-4</v>
       </c>
       <c r="L22" s="61"/>
@@ -9807,70 +9912,70 @@
         <v>235</v>
       </c>
       <c r="P22" s="47">
-        <f>F$5*K19</f>
+        <f t="shared" si="22"/>
         <v>2.8271792087814499E-2</v>
       </c>
       <c r="Q22" s="47">
-        <f>M$5*K19</f>
+        <f t="shared" si="23"/>
         <v>2.2422455793783914E-2</v>
       </c>
       <c r="R22" s="47">
-        <f>F$6*K19</f>
+        <f t="shared" si="24"/>
         <v>6.0118178577536575E-2</v>
       </c>
       <c r="S22" s="47">
-        <f>M$6*K19</f>
+        <f t="shared" si="25"/>
         <v>5.751847355796743E-2</v>
       </c>
       <c r="T22" s="47">
-        <f>F$7*K19</f>
+        <f t="shared" si="26"/>
         <v>4.5494837842460119E-3</v>
       </c>
       <c r="U22" s="47">
-        <f>M$7*K19</f>
+        <f t="shared" si="27"/>
         <v>6.1742994214767297E-3</v>
       </c>
       <c r="V22" s="47">
-        <f>F$8*K19</f>
+        <f t="shared" si="28"/>
         <v>2.8271792087814499E-2</v>
       </c>
       <c r="W22" s="47">
-        <f>M$8*K19</f>
+        <f t="shared" si="29"/>
         <v>2.2422455793783914E-2</v>
       </c>
       <c r="Y22" t="s">
         <v>235</v>
       </c>
       <c r="AB22" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.7776312249885764E-3</v>
       </c>
       <c r="AC22" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.4230456395462613E-2</v>
       </c>
       <c r="AD22" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.084969835364313E-2</v>
       </c>
       <c r="AE22" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>5.0454801366638102E-2</v>
       </c>
       <c r="AF22" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>6.2642056878731579E-4</v>
       </c>
       <c r="AG22" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.4254155119065326E-3</v>
       </c>
       <c r="AH22" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.7776312249885764E-3</v>
       </c>
       <c r="AI22" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.4230456395462613E-2</v>
       </c>
     </row>
@@ -9891,15 +9996,15 @@
         <v>7774.3</v>
       </c>
       <c r="I23" s="54">
-        <f t="shared" si="11"/>
-        <v>7774.3</v>
-      </c>
-      <c r="J23" s="55">
         <f t="shared" si="12"/>
         <v>7774.3</v>
       </c>
+      <c r="J23" s="55">
+        <f t="shared" si="13"/>
+        <v>7774.3</v>
+      </c>
       <c r="K23" s="82">
-        <f>J23/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>4.9674471735957175E-2</v>
       </c>
       <c r="L23" s="61"/>
@@ -9907,70 +10012,70 @@
         <v>236</v>
       </c>
       <c r="P23" s="47">
-        <f>F$5*K20</f>
+        <f t="shared" si="22"/>
         <v>0.17736415080828921</v>
       </c>
       <c r="Q23" s="47">
-        <f>M$5*K20</f>
+        <f t="shared" si="23"/>
         <v>0.14066811960657419</v>
       </c>
       <c r="R23" s="47">
-        <f>F$6*K20</f>
+        <f t="shared" si="24"/>
         <v>0.37715365401762646</v>
       </c>
       <c r="S23" s="47">
-        <f>M$6*K20</f>
+        <f t="shared" si="25"/>
         <v>0.36084430681686425</v>
       </c>
       <c r="T23" s="47">
-        <f>F$7*K20</f>
+        <f t="shared" si="26"/>
         <v>2.8541357601333896E-2</v>
       </c>
       <c r="U23" s="47">
-        <f>M$7*K20</f>
+        <f t="shared" si="27"/>
         <v>3.8734699601810287E-2</v>
       </c>
       <c r="V23" s="47">
-        <f>F$8*K20</f>
+        <f t="shared" si="28"/>
         <v>0.17736415080828921</v>
       </c>
       <c r="W23" s="47">
-        <f>M$8*K20</f>
+        <f t="shared" si="29"/>
         <v>0.14066811960657419</v>
       </c>
       <c r="Y23" t="s">
         <v>236</v>
       </c>
       <c r="AB23" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.3699111545736139E-2</v>
       </c>
       <c r="AC23" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.9275303325517821E-2</v>
       </c>
       <c r="AD23" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.8065990618593489E-2</v>
       </c>
       <c r="AE23" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.31653009369900376</v>
       </c>
       <c r="AF23" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.9298729944924589E-3</v>
       </c>
       <c r="AG23" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.5215935420378532E-2</v>
       </c>
       <c r="AH23" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.3699111545736139E-2</v>
       </c>
       <c r="AI23" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8.9275303325517821E-2</v>
       </c>
     </row>
@@ -9991,15 +10096,15 @@
         <v>1</v>
       </c>
       <c r="I24" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J24" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.87</v>
       </c>
       <c r="K24" s="82">
-        <f>J24/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>5.5589301172173361E-6</v>
       </c>
       <c r="L24" s="61"/>
@@ -10007,70 +10112,70 @@
         <v>237</v>
       </c>
       <c r="P24" s="47">
-        <f>F$5*K21</f>
+        <f t="shared" si="22"/>
         <v>3.4156182739581271</v>
       </c>
       <c r="Q24" s="47">
-        <f>M$5*K21</f>
+        <f t="shared" si="23"/>
         <v>2.7089386310702386</v>
       </c>
       <c r="R24" s="47">
-        <f>F$6*K21</f>
+        <f t="shared" si="24"/>
         <v>7.2630963296810744</v>
       </c>
       <c r="S24" s="47">
-        <f>M$6*K21</f>
+        <f t="shared" si="25"/>
         <v>6.9490164883975689</v>
       </c>
       <c r="T24" s="47">
-        <f>F$7*K21</f>
+        <f t="shared" si="26"/>
         <v>0.54963972224613544</v>
       </c>
       <c r="U24" s="47">
-        <f>M$7*K21</f>
+        <f t="shared" si="27"/>
         <v>0.74593962304832651</v>
       </c>
       <c r="V24" s="47">
-        <f>F$8*K21</f>
+        <f t="shared" si="28"/>
         <v>3.4156182739581271</v>
       </c>
       <c r="W24" s="47">
-        <f>M$8*K21</f>
+        <f t="shared" si="29"/>
         <v>2.7089386310702386</v>
       </c>
       <c r="Y24" t="s">
         <v>237</v>
       </c>
       <c r="AB24" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.45638940058232602</v>
       </c>
       <c r="AC24" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.7192333177936787</v>
       </c>
       <c r="AD24" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.310791613369622</v>
       </c>
       <c r="AE24" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6.0956284985943601</v>
       </c>
       <c r="AF24" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7.5680152686726926E-2</v>
       </c>
       <c r="AG24" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.29302329044716247</v>
       </c>
       <c r="AH24" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.45638940058232602</v>
       </c>
       <c r="AI24" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.7192333177936787</v>
       </c>
     </row>
@@ -10091,15 +10196,15 @@
         <v>22511.5</v>
       </c>
       <c r="I25" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>22652.1</v>
       </c>
       <c r="J25" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19820.587499999998</v>
       </c>
       <c r="K25" s="82">
-        <f>J25/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>0.12664512735022007</v>
       </c>
       <c r="L25" s="61"/>
@@ -10107,70 +10212,70 @@
         <v>238</v>
       </c>
       <c r="P25" s="47">
-        <f>F$5*K22</f>
+        <f t="shared" si="22"/>
         <v>4.6033500300676766E-3</v>
       </c>
       <c r="Q25" s="47">
-        <f>M$5*K22</f>
+        <f t="shared" si="23"/>
         <v>3.6509327824674675E-3</v>
       </c>
       <c r="R25" s="47">
-        <f>F$6*K22</f>
+        <f t="shared" si="24"/>
         <v>9.7887328225577021E-3</v>
       </c>
       <c r="S25" s="47">
-        <f>M$6*K22</f>
+        <f t="shared" si="25"/>
         <v>9.3654362680687213E-3</v>
       </c>
       <c r="T25" s="47">
-        <f>F$7*K22</f>
+        <f t="shared" si="26"/>
         <v>7.4076897035571803E-4</v>
       </c>
       <c r="U25" s="47">
-        <f>M$7*K22</f>
+        <f t="shared" si="27"/>
         <v>1.0053293169113315E-3</v>
       </c>
       <c r="V25" s="47">
-        <f>F$8*K22</f>
+        <f t="shared" si="28"/>
         <v>4.6033500300676766E-3</v>
       </c>
       <c r="W25" s="47">
-        <f>M$8*K22</f>
+        <f t="shared" si="29"/>
         <v>3.6509327824674675E-3</v>
       </c>
       <c r="Y25" t="s">
         <v>238</v>
       </c>
       <c r="AB25" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.1509220070385851E-4</v>
       </c>
       <c r="AC25" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.317071789169115E-3</v>
       </c>
       <c r="AD25" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.7666004011112982E-3</v>
       </c>
       <c r="AE25" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>8.2152949719901079E-3</v>
       </c>
       <c r="AF25" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.01996829037413E-4</v>
       </c>
       <c r="AG25" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3.9491789324787145E-4</v>
       </c>
       <c r="AH25" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.1509220070385851E-4</v>
       </c>
       <c r="AI25" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.317071789169115E-3</v>
       </c>
     </row>
@@ -10191,15 +10296,15 @@
         <v>0.9</v>
       </c>
       <c r="I26" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.9</v>
       </c>
       <c r="J26" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.78300000000000003</v>
       </c>
       <c r="K26" s="82">
-        <f>J26/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>5.0030371054956028E-6</v>
       </c>
       <c r="L26" s="61"/>
@@ -10207,70 +10312,70 @@
         <v>239</v>
       </c>
       <c r="P26" s="47">
-        <f>F$5*K23</f>
+        <f t="shared" si="22"/>
         <v>1.4405596803427581</v>
       </c>
       <c r="Q26" s="47">
-        <f>M$5*K23</f>
+        <f t="shared" si="23"/>
         <v>1.142512849927015</v>
       </c>
       <c r="R26" s="47">
-        <f>F$6*K23</f>
+        <f t="shared" si="24"/>
         <v>3.0632590903840256</v>
       </c>
       <c r="S26" s="47">
-        <f>M$6*K23</f>
+        <f t="shared" si="25"/>
         <v>2.9307938324214735</v>
       </c>
       <c r="T26" s="47">
-        <f>F$7*K23</f>
+        <f t="shared" si="26"/>
         <v>0.23181420143446682</v>
       </c>
       <c r="U26" s="47">
-        <f>M$7*K23</f>
+        <f t="shared" si="27"/>
         <v>0.3146049876610621</v>
       </c>
       <c r="V26" s="47">
-        <f>F$8*K23</f>
+        <f t="shared" si="28"/>
         <v>1.4405596803427581</v>
       </c>
       <c r="W26" s="47">
-        <f>M$8*K23</f>
+        <f t="shared" si="29"/>
         <v>1.142512849927015</v>
       </c>
       <c r="Y26" t="s">
         <v>239</v>
       </c>
       <c r="AB26" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.19248525926546745</v>
       </c>
       <c r="AC26" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.72509806426508272</v>
       </c>
       <c r="AD26" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.55283506413716399</v>
       </c>
       <c r="AE26" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.5708717828258543</v>
       </c>
       <c r="AF26" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.1918606769937602E-2</v>
       </c>
       <c r="AG26" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.12358451787130892</v>
       </c>
       <c r="AH26" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.19248525926546745</v>
       </c>
       <c r="AI26" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.72509806426508272</v>
       </c>
     </row>
@@ -10291,15 +10396,15 @@
         <v>191</v>
       </c>
       <c r="I27" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9492.6</v>
       </c>
       <c r="J27" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8495.8770000000004</v>
       </c>
       <c r="K27" s="82">
-        <f>J27/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>5.4285041985602384E-2</v>
       </c>
       <c r="L27" s="61"/>
@@ -10307,70 +10412,70 @@
         <v>240</v>
       </c>
       <c r="P27" s="47">
-        <f>F$5*K24</f>
+        <f t="shared" si="22"/>
         <v>1.6120897339930274E-4</v>
       </c>
       <c r="Q27" s="47">
-        <f>M$5*K24</f>
+        <f t="shared" si="23"/>
         <v>1.2785539269599873E-4</v>
       </c>
       <c r="R27" s="47">
-        <f>F$6*K24</f>
+        <f t="shared" si="24"/>
         <v>3.4280069056173571E-4</v>
       </c>
       <c r="S27" s="47">
-        <f>M$6*K24</f>
+        <f t="shared" si="25"/>
         <v>3.2797687691582284E-4</v>
       </c>
       <c r="T27" s="47">
-        <f>F$7*K24</f>
+        <f t="shared" si="26"/>
         <v>2.5941673880347568E-5</v>
       </c>
       <c r="U27" s="47">
-        <f>M$7*K24</f>
+        <f t="shared" si="27"/>
         <v>3.5206557409043125E-5</v>
       </c>
       <c r="V27" s="47">
-        <f>F$8*K24</f>
+        <f t="shared" si="28"/>
         <v>1.6120897339930274E-4</v>
       </c>
       <c r="W27" s="47">
-        <f>M$8*K24</f>
+        <f t="shared" si="29"/>
         <v>1.2785539269599873E-4</v>
       </c>
       <c r="Y27" t="s">
         <v>240</v>
       </c>
       <c r="AB27" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.1540482816582413E-5</v>
       </c>
       <c r="AC27" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.1143680577109445E-5</v>
       </c>
       <c r="AD27" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.1866213781219229E-5</v>
       </c>
       <c r="AE27" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.8769901483844112E-4</v>
       </c>
       <c r="AF27" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.5719213163687675E-6</v>
       </c>
       <c r="AG27" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.3829995053964826E-5</v>
       </c>
       <c r="AH27" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.1540482816582413E-5</v>
       </c>
       <c r="AI27" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8.1143680577109445E-5</v>
       </c>
     </row>
@@ -10391,15 +10496,15 @@
         <v>0</v>
       </c>
       <c r="I28" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>54.8</v>
       </c>
       <c r="J28" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>49.868000000000002</v>
       </c>
       <c r="K28" s="82">
-        <f>J28/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>3.1863531848895879E-4</v>
       </c>
       <c r="L28" s="61"/>
@@ -10407,70 +10512,70 @@
         <v>241</v>
       </c>
       <c r="P28" s="47">
-        <f>F$5*K25</f>
+        <f t="shared" si="22"/>
         <v>3.6727086931563822</v>
       </c>
       <c r="Q28" s="47">
-        <f>M$5*K25</f>
+        <f t="shared" si="23"/>
         <v>2.9128379290550614</v>
       </c>
       <c r="R28" s="47">
-        <f>F$6*K25</f>
+        <f t="shared" si="24"/>
         <v>7.8097828532635711</v>
       </c>
       <c r="S28" s="47">
-        <f>M$6*K25</f>
+        <f t="shared" si="25"/>
         <v>7.4720625136629844</v>
       </c>
       <c r="T28" s="47">
-        <f>F$7*K25</f>
+        <f t="shared" si="26"/>
         <v>0.59101059430102709</v>
       </c>
       <c r="U28" s="47">
-        <f>M$7*K25</f>
+        <f t="shared" si="27"/>
         <v>0.80208580655139372</v>
       </c>
       <c r="V28" s="47">
-        <f>F$8*K25</f>
+        <f t="shared" si="28"/>
         <v>3.6727086931563822</v>
       </c>
       <c r="W28" s="47">
-        <f>M$8*K25</f>
+        <f t="shared" si="29"/>
         <v>2.9128379290550614</v>
       </c>
       <c r="Y28" t="s">
         <v>241</v>
       </c>
       <c r="AB28" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.49074140742335415</v>
       </c>
       <c r="AC28" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.8486384148858024</v>
       </c>
       <c r="AD28" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.4094536822348984</v>
       </c>
       <c r="AE28" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6.5544408014587594</v>
       </c>
       <c r="AF28" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8.1376527579542932E-2</v>
       </c>
       <c r="AG28" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.31507888171457132</v>
       </c>
       <c r="AH28" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.49074140742335415</v>
       </c>
       <c r="AI28" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8486384148858024</v>
       </c>
     </row>
@@ -10491,15 +10596,15 @@
         <v>144</v>
       </c>
       <c r="I29" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>157.30000000000001</v>
       </c>
       <c r="J29" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>143.14300000000003</v>
       </c>
       <c r="K29" s="82">
-        <f>J29/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>9.1462291237797853E-4</v>
       </c>
       <c r="L29" s="61"/>
@@ -10507,70 +10612,70 @@
         <v>242</v>
       </c>
       <c r="P29" s="47">
-        <f>F$5*K26</f>
+        <f t="shared" si="22"/>
         <v>1.4508807605937248E-4</v>
       </c>
       <c r="Q29" s="47">
-        <f>M$5*K26</f>
+        <f t="shared" si="23"/>
         <v>1.1506985342639886E-4</v>
       </c>
       <c r="R29" s="47">
-        <f>F$6*K26</f>
+        <f t="shared" si="24"/>
         <v>3.0852062150556214E-4</v>
       </c>
       <c r="S29" s="47">
-        <f>M$6*K26</f>
+        <f t="shared" si="25"/>
         <v>2.9517918922424057E-4</v>
       </c>
       <c r="T29" s="47">
-        <f>F$7*K26</f>
+        <f t="shared" si="26"/>
         <v>2.3347506492312814E-5</v>
       </c>
       <c r="U29" s="47">
-        <f>M$7*K26</f>
+        <f t="shared" si="27"/>
         <v>3.1685901668138813E-5</v>
       </c>
       <c r="V29" s="47">
-        <f>F$8*K26</f>
+        <f t="shared" si="28"/>
         <v>1.4508807605937248E-4</v>
       </c>
       <c r="W29" s="47">
-        <f>M$8*K26</f>
+        <f t="shared" si="29"/>
         <v>1.1506985342639886E-4</v>
       </c>
       <c r="Y29" t="s">
         <v>242</v>
       </c>
       <c r="AB29" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.938643453492417E-5</v>
       </c>
       <c r="AC29" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.3029312519398498E-5</v>
       </c>
       <c r="AD29" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.5679592403097307E-5</v>
       </c>
       <c r="AE29" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.58929113354597E-4</v>
       </c>
       <c r="AF29" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.2147291847318914E-6</v>
       </c>
       <c r="AG29" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.2446995548568345E-5</v>
       </c>
       <c r="AH29" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.938643453492417E-5</v>
       </c>
       <c r="AI29" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7.3029312519398498E-5</v>
       </c>
     </row>
@@ -10591,15 +10696,15 @@
         <v>44</v>
       </c>
       <c r="I30" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1225.8</v>
       </c>
       <c r="J30" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1103.22</v>
       </c>
       <c r="K30" s="82">
-        <f>J30/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>7.0491067631224258E-3</v>
       </c>
       <c r="L30" s="61"/>
@@ -10607,70 +10712,70 @@
         <v>243</v>
       </c>
       <c r="P30" s="47">
-        <f>F$5*K27</f>
+        <f t="shared" si="22"/>
         <v>1.5742662175824691</v>
       </c>
       <c r="Q30" s="47">
-        <f>M$5*K27</f>
+        <f t="shared" si="23"/>
         <v>1.2485559656688547</v>
       </c>
       <c r="R30" s="47">
-        <f>F$6*K27</f>
+        <f t="shared" si="24"/>
         <v>3.3475775891121469</v>
       </c>
       <c r="S30" s="47">
-        <f>M$6*K27</f>
+        <f t="shared" si="25"/>
         <v>3.2028174771505404</v>
       </c>
       <c r="T30" s="47">
-        <f>F$7*K27</f>
+        <f t="shared" si="26"/>
         <v>0.25333019593281114</v>
       </c>
       <c r="U30" s="47">
-        <f>M$7*K27</f>
+        <f t="shared" si="27"/>
         <v>0.34380526590881511</v>
       </c>
       <c r="V30" s="47">
-        <f>F$8*K27</f>
+        <f t="shared" si="28"/>
         <v>1.5742662175824691</v>
       </c>
       <c r="W30" s="47">
-        <f>M$8*K27</f>
+        <f t="shared" si="29"/>
         <v>1.2485559656688547</v>
       </c>
       <c r="Y30" t="s">
         <v>243</v>
       </c>
       <c r="AB30" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.21035091095436523</v>
       </c>
       <c r="AC30" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.79239853966713902</v>
       </c>
       <c r="AD30" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.60414683073671682</v>
       </c>
       <c r="AE30" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.8094890150443339</v>
       </c>
       <c r="AF30" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.4881154204077169E-2</v>
       </c>
       <c r="AG30" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.13505509987252132</v>
       </c>
       <c r="AH30" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.21035091095436523</v>
       </c>
       <c r="AI30" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.79239853966713902</v>
       </c>
     </row>
@@ -10691,15 +10796,15 @@
         <v>0</v>
       </c>
       <c r="I31" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7572.5</v>
       </c>
       <c r="J31" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6588.0749999999998</v>
       </c>
       <c r="K31" s="82">
-        <f>J31/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>4.2094998312628279E-2</v>
       </c>
       <c r="L31" s="61"/>
@@ -10707,70 +10812,70 @@
         <v>244</v>
       </c>
       <c r="P31" s="47">
-        <f>F$5*K28</f>
+        <f t="shared" si="22"/>
         <v>9.2404242361798054E-3</v>
       </c>
       <c r="Q31" s="47">
-        <f>M$5*K28</f>
+        <f t="shared" si="23"/>
         <v>7.3286123252460523E-3</v>
       </c>
       <c r="R31" s="47">
-        <f>F$6*K28</f>
+        <f t="shared" si="24"/>
         <v>1.9649177973485792E-2</v>
       </c>
       <c r="S31" s="47">
-        <f>M$6*K28</f>
+        <f t="shared" si="25"/>
         <v>1.8799483790848569E-2</v>
       </c>
       <c r="T31" s="47">
-        <f>F$7*K28</f>
+        <f t="shared" si="26"/>
         <v>1.4869648196151411E-3</v>
       </c>
       <c r="U31" s="47">
-        <f>M$7*K28</f>
+        <f t="shared" si="27"/>
         <v>2.0180236837634056E-3</v>
       </c>
       <c r="V31" s="47">
-        <f>F$8*K28</f>
+        <f t="shared" si="28"/>
         <v>9.2404242361798054E-3</v>
       </c>
       <c r="W31" s="47">
-        <f>M$8*K28</f>
+        <f t="shared" si="29"/>
         <v>7.3286123252460523E-3</v>
       </c>
       <c r="Y31" t="s">
         <v>244</v>
       </c>
       <c r="AB31" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.2346905713762435E-3</v>
       </c>
       <c r="AC31" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.6511184632405684E-3</v>
       </c>
       <c r="AD31" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.5461429297032662E-3</v>
       </c>
       <c r="AE31" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.6490775255130326E-2</v>
       </c>
       <c r="AF31" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.0474088759158359E-4</v>
       </c>
       <c r="AG31" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.9272895787484826E-4</v>
       </c>
       <c r="AH31" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.2346905713762435E-3</v>
       </c>
       <c r="AI31" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4.6511184632405684E-3</v>
       </c>
     </row>
@@ -10791,15 +10896,15 @@
         <v>0</v>
       </c>
       <c r="I32" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1546</v>
       </c>
       <c r="J32" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1357.3879999999999</v>
       </c>
       <c r="K32" s="82">
-        <f>J32/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>8.6731322229303513E-3</v>
       </c>
       <c r="L32" s="61"/>
@@ -10807,70 +10912,70 @@
         <v>245</v>
       </c>
       <c r="P32" s="47">
-        <f>F$5*K29</f>
+        <f t="shared" si="22"/>
         <v>2.6524064458961376E-2</v>
       </c>
       <c r="Q32" s="47">
-        <f>M$5*K29</f>
+        <f t="shared" si="23"/>
         <v>2.1036326984693505E-2</v>
       </c>
       <c r="R32" s="47">
-        <f>F$6*K29</f>
+        <f t="shared" si="24"/>
         <v>5.6401746263308676E-2</v>
       </c>
       <c r="S32" s="47">
-        <f>M$6*K29</f>
+        <f t="shared" si="25"/>
         <v>5.3962751830300734E-2</v>
       </c>
       <c r="T32" s="47">
-        <f>F$7*K29</f>
+        <f t="shared" si="26"/>
         <v>4.2682402577639E-3</v>
       </c>
       <c r="U32" s="47">
-        <f>M$7*K29</f>
+        <f t="shared" si="27"/>
         <v>5.7926117783938637E-3</v>
       </c>
       <c r="V32" s="47">
-        <f>F$8*K29</f>
+        <f t="shared" si="28"/>
         <v>2.6524064458961376E-2</v>
       </c>
       <c r="W32" s="47">
-        <f>M$8*K29</f>
+        <f t="shared" si="29"/>
         <v>2.1036326984693505E-2</v>
       </c>
       <c r="Y32" t="s">
         <v>245</v>
       </c>
       <c r="AB32" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.5441026802460426E-3</v>
       </c>
       <c r="AC32" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.3350746975688711E-2</v>
       </c>
       <c r="AD32" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.0178983263546054E-2</v>
       </c>
       <c r="AE32" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4.7335747219562054E-2</v>
       </c>
       <c r="AF32" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.8769601492985593E-4</v>
       </c>
       <c r="AG32" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.2754792896663078E-3</v>
       </c>
       <c r="AH32" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.5441026802460426E-3</v>
       </c>
       <c r="AI32" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.3350746975688711E-2</v>
       </c>
     </row>
@@ -10891,15 +10996,15 @@
         <v>0</v>
       </c>
       <c r="I33" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1659.1</v>
       </c>
       <c r="J33" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1453.3715999999997</v>
       </c>
       <c r="K33" s="82">
-        <f>J33/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>9.2864266192509721E-3</v>
       </c>
       <c r="L33" s="61"/>
@@ -10907,70 +11012,70 @@
         <v>246</v>
       </c>
       <c r="P33" s="47">
-        <f>F$5*K30</f>
+        <f t="shared" si="22"/>
         <v>0.20442409613055035</v>
       </c>
       <c r="Q33" s="47">
-        <f>M$5*K30</f>
+        <f t="shared" si="23"/>
         <v>0.16212945555181579</v>
       </c>
       <c r="R33" s="47">
-        <f>F$6*K30</f>
+        <f t="shared" si="24"/>
         <v>0.43469491705921626</v>
       </c>
       <c r="S33" s="47">
-        <f>M$6*K30</f>
+        <f t="shared" si="25"/>
         <v>0.41589729902422312</v>
       </c>
       <c r="T33" s="47">
-        <f>F$7*K30</f>
+        <f t="shared" si="26"/>
         <v>3.2895831561237987E-2</v>
       </c>
       <c r="U33" s="47">
-        <f>M$7*K30</f>
+        <f t="shared" si="27"/>
         <v>4.4644342833108697E-2</v>
       </c>
       <c r="V33" s="47">
-        <f>F$8*K30</f>
+        <f t="shared" si="28"/>
         <v>0.20442409613055035</v>
       </c>
       <c r="W33" s="47">
-        <f>M$8*K30</f>
+        <f t="shared" si="29"/>
         <v>0.16212945555181579</v>
       </c>
       <c r="Y33" t="s">
         <v>246</v>
       </c>
       <c r="AB33" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.7314817761965576E-2</v>
       </c>
       <c r="AC33" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.10289578308767665</v>
       </c>
       <c r="AD33" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.8450625710019192E-2</v>
       </c>
       <c r="AE33" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.36482219212651157</v>
       </c>
       <c r="AF33" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4.5294425685567267E-3</v>
       </c>
       <c r="AG33" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.7537387521189746E-2</v>
       </c>
       <c r="AH33" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.7314817761965576E-2</v>
       </c>
       <c r="AI33" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.10289578308767665</v>
       </c>
     </row>
@@ -10991,15 +11096,15 @@
         <v>0</v>
       </c>
       <c r="I34" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>461</v>
       </c>
       <c r="J34" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>403.83599999999996</v>
       </c>
       <c r="K34" s="82">
-        <f>J34/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>2.5803403480650347E-3</v>
       </c>
       <c r="L34" s="61"/>
@@ -11007,70 +11112,70 @@
         <v>247</v>
       </c>
       <c r="P34" s="47">
-        <f>F$5*K31</f>
+        <f t="shared" si="22"/>
         <v>1.2207549510662201</v>
       </c>
       <c r="Q34" s="47">
-        <f>M$5*K31</f>
+        <f t="shared" si="23"/>
         <v>0.96818496119045039</v>
       </c>
       <c r="R34" s="47">
-        <f>F$6*K31</f>
+        <f t="shared" si="24"/>
         <v>2.5958582292787438</v>
       </c>
       <c r="S34" s="47">
-        <f>M$6*K31</f>
+        <f t="shared" si="25"/>
         <v>2.4836049004450684</v>
       </c>
       <c r="T34" s="47">
-        <f>F$7*K31</f>
+        <f t="shared" si="26"/>
         <v>0.19644332545893198</v>
       </c>
       <c r="U34" s="47">
-        <f>M$7*K31</f>
+        <f t="shared" si="27"/>
         <v>0.26660165597997909</v>
       </c>
       <c r="V34" s="47">
-        <f>F$8*K31</f>
+        <f t="shared" si="28"/>
         <v>1.2207549510662201</v>
       </c>
       <c r="W34" s="47">
-        <f>M$8*K31</f>
+        <f t="shared" si="29"/>
         <v>0.96818496119045039</v>
       </c>
       <c r="Y34" t="s">
         <v>247</v>
       </c>
       <c r="AB34" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.16311530612857034</v>
       </c>
       <c r="AC34" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.61446052117016126</v>
       </c>
       <c r="AD34" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.4684819038582827</v>
       </c>
       <c r="AE34" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.1786007898640953</v>
       </c>
       <c r="AF34" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.7048374168202494E-2</v>
       </c>
       <c r="AG34" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.10472763754614865</v>
       </c>
       <c r="AH34" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.16311530612857034</v>
       </c>
       <c r="AI34" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.61446052117016126</v>
       </c>
     </row>
@@ -11091,15 +11196,15 @@
         <v>0</v>
       </c>
       <c r="I35" s="54">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J35" s="55">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="J35" s="55">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="K35" s="82">
-        <f>J35/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L35" s="61"/>
@@ -11107,70 +11212,70 @@
         <v>248</v>
       </c>
       <c r="P35" s="47">
-        <f>F$5*K32</f>
+        <f t="shared" si="22"/>
         <v>0.25152083446498019</v>
       </c>
       <c r="Q35" s="47">
-        <f>M$5*K32</f>
+        <f t="shared" si="23"/>
         <v>0.19948204112739809</v>
       </c>
       <c r="R35" s="47">
-        <f>F$6*K32</f>
+        <f t="shared" si="24"/>
         <v>0.53484315374737168</v>
       </c>
       <c r="S35" s="47">
-        <f>M$6*K32</f>
+        <f t="shared" si="25"/>
         <v>0.5117148011528907</v>
       </c>
       <c r="T35" s="47">
-        <f>F$7*K32</f>
+        <f t="shared" si="26"/>
         <v>4.0474617040341644E-2</v>
       </c>
       <c r="U35" s="47">
-        <f>M$7*K32</f>
+        <f t="shared" si="27"/>
         <v>5.4929837411892224E-2</v>
       </c>
       <c r="V35" s="47">
-        <f>F$8*K32</f>
+        <f t="shared" si="28"/>
         <v>0.25152083446498019</v>
       </c>
       <c r="W35" s="47">
-        <f>M$8*K32</f>
+        <f t="shared" si="29"/>
         <v>0.19948204112739809</v>
       </c>
       <c r="Y35" t="s">
         <v>248</v>
       </c>
       <c r="AB35" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.3607807918891001E-2</v>
       </c>
       <c r="AC35" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.12660167619678325</v>
       </c>
       <c r="AD35" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.6524662289726004E-2</v>
       </c>
       <c r="AE35" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.44887263259025506</v>
       </c>
       <c r="AF35" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.5729691169921491E-3</v>
       </c>
       <c r="AG35" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.1577780834840472E-2</v>
       </c>
       <c r="AH35" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.3607807918891001E-2</v>
       </c>
       <c r="AI35" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.12660167619678325</v>
       </c>
     </row>
@@ -11191,15 +11296,15 @@
         <v>0</v>
       </c>
       <c r="I36" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>706</v>
       </c>
       <c r="J36" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>635.4</v>
       </c>
       <c r="K36" s="82">
-        <f>J36/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>4.0599358580228687E-3</v>
       </c>
       <c r="L36" s="61"/>
@@ -11207,70 +11312,70 @@
         <v>249</v>
       </c>
       <c r="P36" s="47">
-        <f>F$5*K33</f>
+        <f t="shared" si="22"/>
         <v>0.26930637195827817</v>
       </c>
       <c r="Q36" s="47">
-        <f>M$5*K33</f>
+        <f t="shared" si="23"/>
         <v>0.21358781224277235</v>
       </c>
       <c r="R36" s="47">
-        <f>F$6*K33</f>
+        <f t="shared" si="24"/>
         <v>0.5726629748538099</v>
       </c>
       <c r="S36" s="47">
-        <f>M$6*K33</f>
+        <f t="shared" si="25"/>
         <v>0.54789917053580739</v>
       </c>
       <c r="T36" s="47">
-        <f>F$7*K33</f>
+        <f t="shared" si="26"/>
         <v>4.3336657556504538E-2</v>
       </c>
       <c r="U36" s="47">
-        <f>M$7*K33</f>
+        <f t="shared" si="27"/>
         <v>5.8814035255256157E-2</v>
       </c>
       <c r="V36" s="47">
-        <f>F$8*K33</f>
+        <f t="shared" si="28"/>
         <v>0.26930637195827817</v>
       </c>
       <c r="W36" s="47">
-        <f>M$8*K33</f>
+        <f t="shared" si="29"/>
         <v>0.21358781224277235</v>
       </c>
       <c r="Y36" t="s">
         <v>249</v>
       </c>
       <c r="AB36" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.598428273092974E-2</v>
       </c>
       <c r="AC36" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.13555393203476143</v>
       </c>
       <c r="AD36" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.10335011276914095</v>
       </c>
       <c r="AE36" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.48061330748755038</v>
       </c>
       <c r="AF36" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.9670448260287137E-3</v>
       </c>
       <c r="AG36" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.3103588551233269E-2</v>
       </c>
       <c r="AH36" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.598428273092974E-2</v>
       </c>
       <c r="AI36" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.13555393203476143</v>
       </c>
     </row>
@@ -11287,15 +11392,15 @@
       <c r="G37" s="54"/>
       <c r="H37" s="54"/>
       <c r="I37" s="54">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="55">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="J37" s="55">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="K37" s="82">
-        <f>J37/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L37" s="61"/>
@@ -11303,70 +11408,70 @@
         <v>250</v>
       </c>
       <c r="P37" s="47">
-        <f>F$5*K34</f>
+        <f t="shared" si="22"/>
         <v>7.4829870093886003E-2</v>
       </c>
       <c r="Q37" s="47">
-        <f>M$5*K34</f>
+        <f t="shared" si="23"/>
         <v>5.9347828005495797E-2</v>
       </c>
       <c r="R37" s="47">
-        <f>F$6*K34</f>
+        <f t="shared" si="24"/>
         <v>0.15912098813067713</v>
       </c>
       <c r="S37" s="47">
-        <f>M$6*K34</f>
+        <f t="shared" si="25"/>
         <v>0.15224008053583704</v>
       </c>
       <c r="T37" s="47">
-        <f>F$7*K34</f>
+        <f t="shared" si="26"/>
         <v>1.2041588290970162E-2</v>
       </c>
       <c r="U37" s="47">
-        <f>M$7*K34</f>
+        <f t="shared" si="27"/>
         <v>1.634215553774522E-2</v>
       </c>
       <c r="V37" s="47">
-        <f>F$8*K34</f>
+        <f t="shared" si="28"/>
         <v>7.4829870093886003E-2</v>
       </c>
       <c r="W37" s="47">
-        <f>M$8*K34</f>
+        <f t="shared" si="29"/>
         <v>5.9347828005495797E-2</v>
       </c>
       <c r="Y37" t="s">
         <v>250</v>
       </c>
       <c r="AB37" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.9986464582958335E-3</v>
       </c>
       <c r="AC37" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.7665217689123641E-2</v>
       </c>
       <c r="AD37" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.8717016446612009E-2</v>
       </c>
       <c r="AE37" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.13354393029459391</v>
       </c>
       <c r="AF37" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.6580119732380434E-3</v>
       </c>
       <c r="AG37" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.41959756622177E-3</v>
       </c>
       <c r="AH37" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.9986464582958335E-3</v>
       </c>
       <c r="AI37" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.7665217689123641E-2</v>
       </c>
     </row>
@@ -11387,15 +11492,15 @@
         <v>0</v>
       </c>
       <c r="I38" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="J38" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.1950000000000003</v>
       </c>
       <c r="K38" s="82">
-        <f>J38/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>3.9583416179495865E-5</v>
       </c>
       <c r="L38" s="61"/>
@@ -11403,70 +11508,70 @@
         <v>251</v>
       </c>
       <c r="P38" s="47">
-        <f>F$5*K35</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q38" s="47">
-        <f>M$5*K35</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R38" s="47">
-        <f>F$6*K35</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S38" s="47">
-        <f>M$6*K35</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T38" s="47">
-        <f>F$7*K35</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="U38" s="47">
-        <f>M$7*K35</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V38" s="47">
-        <f>F$8*K35</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W38" s="47">
-        <f>M$8*K35</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Y38" t="s">
         <v>251</v>
       </c>
       <c r="AB38" s="47">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC38" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD38" s="47">
+      <c r="AC38" s="47">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE38" s="47">
+      <c r="AD38" s="47">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AF38" s="47">
+      <c r="AE38" s="47">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AG38" s="47">
+      <c r="AF38" s="47">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH38" s="47">
+      <c r="AG38" s="47">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
+      <c r="AH38" s="47">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AI38" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -11487,15 +11592,15 @@
         <v>0</v>
       </c>
       <c r="I39" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1078.05</v>
       </c>
       <c r="J39" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>813.92774999999995</v>
       </c>
       <c r="K39" s="82">
-        <f>J39/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>5.2006522789815436E-3</v>
       </c>
       <c r="L39" s="61"/>
@@ -11503,70 +11608,70 @@
         <v>252</v>
       </c>
       <c r="P39" s="47">
-        <f>F$5*K36</f>
+        <f t="shared" si="22"/>
         <v>0.11773813988266318</v>
       </c>
       <c r="Q39" s="47">
-        <f>M$5*K36</f>
+        <f t="shared" si="23"/>
         <v>9.3378524734525986E-2</v>
       </c>
       <c r="R39" s="47">
-        <f>F$6*K36</f>
+        <f t="shared" si="24"/>
         <v>0.25036271124474357</v>
       </c>
       <c r="S39" s="47">
-        <f>M$6*K36</f>
+        <f t="shared" si="25"/>
         <v>0.23953621562334926</v>
       </c>
       <c r="T39" s="47">
-        <f>F$7*K36</f>
+        <f t="shared" si="26"/>
         <v>1.8946367337440054E-2</v>
       </c>
       <c r="U39" s="47">
-        <f>M$7*K36</f>
+        <f t="shared" si="27"/>
         <v>2.5712927100811502E-2</v>
       </c>
       <c r="V39" s="47">
-        <f>F$8*K36</f>
+        <f t="shared" si="28"/>
         <v>0.11773813988266318</v>
       </c>
       <c r="W39" s="47">
-        <f>M$8*K36</f>
+        <f t="shared" si="29"/>
         <v>9.3378524734525986E-2</v>
       </c>
       <c r="Y39" t="s">
         <v>252</v>
       </c>
       <c r="AB39" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.5731980208800535E-2</v>
       </c>
       <c r="AC39" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.9262867400799252E-2</v>
       </c>
       <c r="AD39" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.5183669237455988E-2</v>
       </c>
       <c r="AE39" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.21011948738890288</v>
       </c>
       <c r="AF39" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.6087342579548447E-3</v>
       </c>
       <c r="AG39" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.0100665353206037E-2</v>
       </c>
       <c r="AH39" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.5731980208800535E-2</v>
       </c>
       <c r="AI39" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.9262867400799252E-2</v>
       </c>
     </row>
@@ -11587,15 +11692,15 @@
         <v>2559.4</v>
       </c>
       <c r="I40" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2792.65</v>
       </c>
       <c r="J40" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2499.42175</v>
       </c>
       <c r="K40" s="82">
-        <f>J40/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>1.5970242346785127E-2</v>
       </c>
       <c r="L40" s="61"/>
@@ -11603,70 +11708,70 @@
         <v>253</v>
       </c>
       <c r="P40" s="47">
-        <f>F$5*K37</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q40" s="47">
-        <f>M$5*K37</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R40" s="47">
-        <f>F$6*K37</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S40" s="47">
-        <f>M$6*K37</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T40" s="47">
-        <f>F$7*K37</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="U40" s="47">
-        <f>M$7*K37</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V40" s="47">
-        <f>F$8*K37</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W40" s="47">
-        <f>M$8*K37</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Y40" t="s">
         <v>253</v>
       </c>
       <c r="AB40" s="47">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC40" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD40" s="47">
+      <c r="AC40" s="47">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE40" s="47">
+      <c r="AD40" s="47">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AF40" s="47">
+      <c r="AE40" s="47">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AG40" s="47">
+      <c r="AF40" s="47">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH40" s="47">
+      <c r="AG40" s="47">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
+      <c r="AH40" s="47">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AI40" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -11687,15 +11792,15 @@
         <v>0</v>
       </c>
       <c r="I41" s="54">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="55">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="J41" s="55">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="K41" s="82">
-        <f>J41/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L41" s="61"/>
@@ -11703,70 +11808,70 @@
         <v>254</v>
       </c>
       <c r="P41" s="47">
-        <f>F$5*K38</f>
+        <f t="shared" si="22"/>
         <v>1.14791906920538E-3</v>
       </c>
       <c r="Q41" s="47">
-        <f>M$5*K38</f>
+        <f t="shared" si="23"/>
         <v>9.1041857212840484E-4</v>
       </c>
       <c r="R41" s="47">
-        <f>F$6*K38</f>
+        <f t="shared" si="24"/>
         <v>2.4409773310689114E-3</v>
       </c>
       <c r="S41" s="47">
-        <f>M$6*K38</f>
+        <f t="shared" si="25"/>
         <v>2.3354215545902559E-3</v>
       </c>
       <c r="T41" s="47">
-        <f>F$7*K38</f>
+        <f t="shared" si="26"/>
         <v>1.8472260883764738E-4</v>
       </c>
       <c r="U41" s="47">
-        <f>M$7*K38</f>
+        <f t="shared" si="27"/>
         <v>2.5069496913680714E-4</v>
       </c>
       <c r="V41" s="47">
-        <f>F$8*K38</f>
+        <f t="shared" si="28"/>
         <v>1.14791906920538E-3</v>
       </c>
       <c r="W41" s="47">
-        <f>M$8*K38</f>
+        <f t="shared" si="29"/>
         <v>9.1041857212840484E-4</v>
       </c>
       <c r="Y41" t="s">
         <v>254</v>
       </c>
       <c r="AB41" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.5338309315945754E-4</v>
       </c>
       <c r="AC41" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.7779896686803802E-4</v>
       </c>
       <c r="AD41" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.4053010847661285E-4</v>
       </c>
       <c r="AE41" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.0486153987633827E-3</v>
       </c>
       <c r="AF41" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.5434543166556919E-5</v>
       </c>
       <c r="AG41" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.8479102711852997E-5</v>
       </c>
       <c r="AH41" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.5338309315945754E-4</v>
       </c>
       <c r="AI41" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.7779896686803802E-4</v>
       </c>
     </row>
@@ -11787,15 +11892,15 @@
         <v>0</v>
       </c>
       <c r="I42" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.3</v>
       </c>
       <c r="J42" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.0030000000000001</v>
       </c>
       <c r="K42" s="82">
-        <f>J42/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>1.9187893266670875E-5</v>
       </c>
       <c r="L42" s="61"/>
@@ -11803,70 +11908,70 @@
         <v>255</v>
       </c>
       <c r="P42" s="47">
-        <f>F$5*K39</f>
+        <f t="shared" si="22"/>
         <v>0.15081891609046477</v>
       </c>
       <c r="Q42" s="47">
-        <f>M$5*K39</f>
+        <f t="shared" si="23"/>
         <v>0.11961500241657551</v>
       </c>
       <c r="R42" s="47">
-        <f>F$6*K39</f>
+        <f t="shared" si="24"/>
         <v>0.3207068905371952</v>
       </c>
       <c r="S42" s="47">
-        <f>M$6*K39</f>
+        <f t="shared" si="25"/>
         <v>0.30683848445991108</v>
       </c>
       <c r="T42" s="47">
-        <f>F$7*K39</f>
+        <f t="shared" si="26"/>
         <v>2.4269710635247205E-2</v>
       </c>
       <c r="U42" s="47">
-        <f>M$7*K39</f>
+        <f t="shared" si="27"/>
         <v>3.2937464433549772E-2</v>
       </c>
       <c r="V42" s="47">
-        <f>F$8*K39</f>
+        <f t="shared" si="28"/>
         <v>0.15081891609046477</v>
       </c>
       <c r="W42" s="47">
-        <f>M$8*K39</f>
+        <f t="shared" si="29"/>
         <v>0.11961500241657551</v>
       </c>
       <c r="Y42" t="s">
         <v>255</v>
       </c>
       <c r="AB42" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.0152180129671942E-2</v>
       </c>
       <c r="AC42" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.5913900412465971E-2</v>
       </c>
       <c r="AD42" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.7878882970076748E-2</v>
       </c>
       <c r="AE42" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.26915656531571153</v>
       </c>
       <c r="AF42" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.3417079082862866E-3</v>
       </c>
       <c r="AG42" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.2938639950327263E-2</v>
       </c>
       <c r="AH42" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.0152180129671942E-2</v>
       </c>
       <c r="AI42" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7.5913900412465971E-2</v>
       </c>
     </row>
@@ -11887,15 +11992,15 @@
         <v>0</v>
       </c>
       <c r="I43" s="54">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="55">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="J43" s="55">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="K43" s="82">
-        <f>J43/SUM(J$13:J$43)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L43" s="61"/>
@@ -11903,70 +12008,70 @@
         <v>256</v>
       </c>
       <c r="P43" s="47">
-        <f>F$5*K40</f>
+        <f t="shared" si="22"/>
         <v>0.46313702805676871</v>
       </c>
       <c r="Q43" s="47">
-        <f>M$5*K40</f>
+        <f t="shared" si="23"/>
         <v>0.36731557397605791</v>
       </c>
       <c r="R43" s="47">
-        <f>F$6*K40</f>
+        <f t="shared" si="24"/>
         <v>0.98483161138508279</v>
       </c>
       <c r="S43" s="47">
-        <f>M$6*K40</f>
+        <f t="shared" si="25"/>
         <v>0.94224429846032254</v>
       </c>
       <c r="T43" s="47">
-        <f>F$7*K40</f>
+        <f t="shared" si="26"/>
         <v>7.4527797618330602E-2</v>
       </c>
       <c r="U43" s="47">
-        <f>M$7*K40</f>
+        <f t="shared" si="27"/>
         <v>0.1011448681963058</v>
       </c>
       <c r="V43" s="47">
-        <f>F$8*K40</f>
+        <f t="shared" si="28"/>
         <v>0.46313702805676871</v>
       </c>
       <c r="W43" s="47">
-        <f>M$8*K40</f>
+        <f t="shared" si="29"/>
         <v>0.36731557397605791</v>
       </c>
       <c r="Y43" t="s">
         <v>256</v>
       </c>
       <c r="AB43" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.188362213479006E-2</v>
       </c>
       <c r="AC43" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.23311756334422978</v>
       </c>
       <c r="AD43" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.17773535668382656</v>
       </c>
       <c r="AE43" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.82653008636870395</v>
       </c>
       <c r="AF43" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.0261767617724977E-2</v>
       </c>
       <c r="AG43" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3.9732172919853009E-2</v>
       </c>
       <c r="AH43" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.188362213479006E-2</v>
       </c>
       <c r="AI43" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.23311756334422978</v>
       </c>
     </row>
@@ -11987,11 +12092,11 @@
         <v>3456.4</v>
       </c>
       <c r="I44" s="86">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7119.9</v>
       </c>
       <c r="J44" s="87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7119.9</v>
       </c>
       <c r="K44" s="88"/>
@@ -12000,70 +12105,70 @@
         <v>257</v>
       </c>
       <c r="P44" s="47">
-        <f>F$5*K41</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q44" s="47">
-        <f>M$5*K41</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R44" s="47">
-        <f>F$6*K41</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S44" s="47">
-        <f>M$6*K41</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T44" s="47">
-        <f>F$7*K41</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="U44" s="47">
-        <f>M$7*K41</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V44" s="47">
-        <f>F$8*K41</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W44" s="47">
-        <f>M$8*K41</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Y44" t="s">
         <v>257</v>
       </c>
       <c r="AB44" s="47">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC44" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD44" s="47">
+      <c r="AC44" s="47">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE44" s="47">
+      <c r="AD44" s="47">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AF44" s="47">
+      <c r="AE44" s="47">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AG44" s="47">
+      <c r="AF44" s="47">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH44" s="47">
+      <c r="AG44" s="47">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
+      <c r="AH44" s="47">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AI44" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -12073,70 +12178,70 @@
         <v>258</v>
       </c>
       <c r="P45" s="47">
-        <f>F$5*K42</f>
+        <f t="shared" si="22"/>
         <v>5.5644890473345533E-4</v>
       </c>
       <c r="Q45" s="47">
-        <f>M$5*K42</f>
+        <f t="shared" si="23"/>
         <v>4.4132154513343015E-4</v>
       </c>
       <c r="R45" s="47">
-        <f>F$6*K42</f>
+        <f t="shared" si="24"/>
         <v>1.1832534181113706E-3</v>
       </c>
       <c r="S45" s="47">
-        <f>M$6*K42</f>
+        <f t="shared" si="25"/>
         <v>1.1320857027335817E-3</v>
       </c>
       <c r="T45" s="47">
-        <f>F$7*K42</f>
+        <f t="shared" si="26"/>
         <v>8.954350191113076E-5</v>
       </c>
       <c r="U45" s="47">
-        <f>M$7*K42</f>
+        <f t="shared" si="27"/>
         <v>1.2152332402224887E-4</v>
       </c>
       <c r="V45" s="47">
-        <f>F$8*K42</f>
+        <f t="shared" si="28"/>
         <v>5.5644890473345533E-4</v>
       </c>
       <c r="W45" s="47">
-        <f>M$8*K42</f>
+        <f t="shared" si="29"/>
         <v>4.4132154513343015E-4</v>
       </c>
       <c r="Y45" t="s">
         <v>258</v>
       </c>
       <c r="AB45" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.4351804480686189E-5</v>
       </c>
       <c r="AC45" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.8008560088857437E-4</v>
       </c>
       <c r="AD45" s="47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.1354510343103608E-4</v>
       </c>
       <c r="AE45" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.9305763397682621E-4</v>
       </c>
       <c r="AF45" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.2329287026500471E-5</v>
       </c>
       <c r="AG45" s="47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4.773732775523721E-5</v>
       </c>
       <c r="AH45" s="47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.4351804480686189E-5</v>
       </c>
       <c r="AI45" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.8008560088857437E-4</v>
       </c>
     </row>
@@ -12146,70 +12251,70 @@
         <v>259</v>
       </c>
       <c r="P46" s="47">
-        <f>F$5*K43</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q46" s="47">
-        <f>M$5*K43</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R46" s="47">
-        <f>F$6*K43</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S46" s="47">
-        <f>M$6*K43</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T46" s="47">
-        <f>F$7*K43</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="U46" s="47">
-        <f>M$7*K43</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V46" s="47">
-        <f>F$8*K43</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W46" s="47">
-        <f>M$8*K43</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Y46" t="s">
         <v>259</v>
       </c>
       <c r="AB46" s="47">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC46" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD46" s="47">
+      <c r="AC46" s="47">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE46" s="47">
+      <c r="AD46" s="47">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AF46" s="47">
+      <c r="AE46" s="47">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AG46" s="47">
+      <c r="AF46" s="47">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH46" s="47">
+      <c r="AG46" s="47">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
+      <c r="AH46" s="47">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AI46" s="47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -12231,31 +12336,31 @@
         <v>748.39999999999986</v>
       </c>
       <c r="Q48" s="19">
-        <f t="shared" ref="Q48:W48" si="21">SUM(Q13:Q46)</f>
+        <f t="shared" ref="Q48:W48" si="30">SUM(Q13:Q46)</f>
         <v>157.56666666666661</v>
       </c>
       <c r="R48" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>554.09999999999991</v>
       </c>
       <c r="S48" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>113.99999999999999</v>
       </c>
       <c r="T48" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>726.26666666666665</v>
       </c>
       <c r="U48" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>254.56666666666666</v>
       </c>
       <c r="V48" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>748.39999999999986</v>
       </c>
       <c r="W48" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>157.56666666666661</v>
       </c>
       <c r="Y48" t="s">
@@ -12268,31 +12373,31 @@
         <v>100.00000000000004</v>
       </c>
       <c r="AC48" s="19">
-        <f t="shared" ref="AC48:AI48" si="22">SUM(AC13:AC46)</f>
+        <f t="shared" ref="AC48:AI48" si="31">SUM(AC13:AC46)</f>
         <v>100.00000000000001</v>
       </c>
       <c r="AD48" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>100</v>
       </c>
       <c r="AE48" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>100</v>
       </c>
       <c r="AF48" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>100</v>
       </c>
       <c r="AG48" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>100</v>
       </c>
       <c r="AH48" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>100.00000000000004</v>
       </c>
       <c r="AI48" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>100.00000000000001</v>
       </c>
     </row>
@@ -12755,7 +12860,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM166"/>
+  <dimension ref="A1:AN166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -14994,7 +15099,7 @@
       <c r="AL48" s="26"/>
       <c r="AM48" s="27"/>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>36</v>
       </c>
@@ -15076,7 +15181,7 @@
       <c r="AL49" s="29"/>
       <c r="AM49" s="30"/>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="6">
@@ -15205,7 +15310,7 @@
         <v>Kraftfoder</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>15</v>
       </c>
@@ -15321,7 +15426,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
       <c r="C52" s="6">
         <f>C51/SUM($C$51:$N$51)</f>
@@ -15376,7 +15481,7 @@
       <c r="Q52" s="21"/>
       <c r="R52" s="21"/>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>89</v>
       </c>
@@ -15435,7 +15540,7 @@
       <c r="S53" s="11"/>
       <c r="T53" s="11"/>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>37</v>
       </c>
@@ -15483,7 +15588,7 @@
       <c r="Q54" s="21"/>
       <c r="R54" s="21"/>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="6">
@@ -15554,7 +15659,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>15</v>
       </c>
@@ -15624,7 +15729,7 @@
       <c r="AL56" s="26"/>
       <c r="AM56" s="27"/>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
       <c r="C57" s="6">
         <f>C56/SUM($C$56:$N$56)</f>
         <v>4.7008547008547001E-2</v>
@@ -15703,7 +15808,7 @@
       <c r="AL57" s="29"/>
       <c r="AM57" s="30"/>
     </row>
-    <row r="58" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -15785,7 +15890,7 @@
       <c r="AL58" s="37"/>
       <c r="AM58" s="38"/>
     </row>
-    <row r="59" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>88</v>
       </c>
@@ -15908,7 +16013,7 @@
         <v>Kraftfoder</v>
       </c>
     </row>
-    <row r="60" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B60" s="13" t="s">
         <v>91</v>
       </c>
@@ -16005,8 +16110,12 @@
       <c r="AK60" s="29"/>
       <c r="AL60" s="29"/>
       <c r="AM60" s="30"/>
-    </row>
-    <row r="61" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN60" s="96">
+        <f>AD60/SUM(AD$60:AD$62,AD$78)</f>
+        <v>0.1308869454237663</v>
+      </c>
+    </row>
+    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>92</v>
       </c>
@@ -16091,8 +16200,12 @@
       <c r="AK61" s="29"/>
       <c r="AL61" s="29"/>
       <c r="AM61" s="30"/>
-    </row>
-    <row r="62" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN61" s="96">
+        <f>AD61/SUM(AD$60:AD$62,AD$78)</f>
+        <v>0.17556454806174038</v>
+      </c>
+    </row>
+    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>93</v>
       </c>
@@ -16177,8 +16290,12 @@
         <f>$AD$62*AM51/1000</f>
         <v>2328.5294117647059</v>
       </c>
-    </row>
-    <row r="63" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN62" s="96">
+        <f>AD62/SUM(AD$60:AD$62,AD$78)</f>
+        <v>0.30362339488324513</v>
+      </c>
+    </row>
+    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>94</v>
       </c>
@@ -16246,7 +16363,7 @@
       <c r="AL63" s="33"/>
       <c r="AM63" s="34"/>
     </row>
-    <row r="64" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>95</v>
       </c>
@@ -16286,7 +16403,7 @@
       <c r="R64" s="21"/>
       <c r="AD64" s="19"/>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>96</v>
       </c>
@@ -16319,7 +16436,7 @@
       <c r="Q65" s="21"/>
       <c r="R65" s="21"/>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>97</v>
       </c>
@@ -16358,7 +16475,7 @@
       <c r="W66" s="26"/>
       <c r="X66" s="27"/>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>98</v>
       </c>
@@ -16399,7 +16516,7 @@
       </c>
       <c r="X67" s="30"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>99</v>
       </c>
@@ -16448,7 +16565,7 @@
       </c>
       <c r="X68" s="34"/>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>100</v>
       </c>
@@ -16495,7 +16612,7 @@
         <v>11410</v>
       </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>101</v>
       </c>
@@ -16549,7 +16666,7 @@
         <v>232324.03361344538</v>
       </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>102</v>
       </c>
@@ -16597,7 +16714,7 @@
       </c>
       <c r="T71" s="19"/>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>126</v>
       </c>
@@ -16664,7 +16781,7 @@
       <c r="AL72" s="26"/>
       <c r="AM72" s="27"/>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.25">
       <c r="C73" s="5">
         <f>C72/$O$72</f>
         <v>7.6722745976352938E-2</v>
@@ -16757,7 +16874,7 @@
       <c r="AL73" s="29"/>
       <c r="AM73" s="30"/>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>103</v>
       </c>
@@ -16860,7 +16977,7 @@
       <c r="AL74" s="29"/>
       <c r="AM74" s="30"/>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.25">
       <c r="C75" s="5">
         <f>C74/$O$74</f>
         <v>4.5659030603852124E-2</v>
@@ -16931,7 +17048,7 @@
       <c r="AL75" s="29"/>
       <c r="AM75" s="30"/>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.25">
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
@@ -16974,7 +17091,7 @@
       <c r="AL76" s="29"/>
       <c r="AM76" s="30"/>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.25">
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -17027,7 +17144,7 @@
       <c r="AL77" s="29"/>
       <c r="AM77" s="30"/>
     </row>
-    <row r="78" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:40" x14ac:dyDescent="0.25">
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
@@ -17089,8 +17206,12 @@
       <c r="AK78" s="33"/>
       <c r="AL78" s="33"/>
       <c r="AM78" s="34"/>
-    </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AN78" s="96">
+        <f>AD78/SUM(AD$60:AD$62,AD$78)</f>
+        <v>0.38992511163124816</v>
+      </c>
+    </row>
+    <row r="79" spans="2:40" x14ac:dyDescent="0.25">
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -17104,7 +17225,7 @@
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.25">
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>

--- a/data/default/SheepHerd.xlsx
+++ b/data/default/SheepHerd.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\CIBUSmod\data\default\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -610,7 +610,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="302">
   <si>
     <t>Slakt av större lantbruksdjur vid slakteri efter Djurslag, Tabelluppgift och Månad</t>
   </si>
@@ -1506,6 +1506,18 @@
   </si>
   <si>
     <t xml:space="preserve">Note: </t>
+  </si>
+  <si>
+    <t>rapeseed cake</t>
+  </si>
+  <si>
+    <t>organic</t>
+  </si>
+  <si>
+    <t>conventional</t>
+  </si>
+  <si>
+    <t>rapeseed cake for organic rations</t>
   </si>
 </sst>
 </file>
@@ -1516,7 +1528,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0\ _k_r"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1757,6 +1769,19 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2256,7 +2281,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
@@ -2388,6 +2413,9 @@
     <xf numFmtId="0" fontId="29" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2579,34 +2607,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -2862,7 +2890,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J360"/>
+  <dimension ref="A1:J368"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -4268,7 +4296,7 @@
         <v>2.1540482816582413E-5</v>
       </c>
     </row>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C97" t="s">
         <v>196</v>
       </c>
@@ -4283,7 +4311,7 @@
         <v>0.49074140742335415</v>
       </c>
     </row>
-    <row r="98" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C98" t="s">
         <v>196</v>
       </c>
@@ -4298,7 +4326,10 @@
         <v>1.938643453492417E-5</v>
       </c>
     </row>
-    <row r="99" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>300</v>
+      </c>
       <c r="C99" t="s">
         <v>196</v>
       </c>
@@ -4313,199 +4344,207 @@
         <v>0.21035091095436523</v>
       </c>
     </row>
-    <row r="100" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C100" t="s">
-        <v>196</v>
-      </c>
-      <c r="E100" t="s">
-        <v>244</v>
-      </c>
-      <c r="F100" t="s">
-        <v>285</v>
-      </c>
-      <c r="G100" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E100,'feed rations'!$Y$13:$Y$46,0),MATCH(C100&amp;D100,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2346905713762435E-3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B100" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C100" s="97" t="str">
+        <f>C99</f>
+        <v>autumn lamb</v>
+      </c>
+      <c r="E100" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F100" s="97" t="str">
+        <f>F99</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G100" s="99">
+        <f>G99</f>
+        <v>0.21035091095436523</v>
+      </c>
+      <c r="I100" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C101" t="s">
         <v>196</v>
       </c>
       <c r="E101" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F101" t="s">
         <v>285</v>
       </c>
       <c r="G101" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E101,'feed rations'!$Y$13:$Y$46,0),MATCH(C101&amp;D101,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5441026802460426E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.2346905713762435E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C102" t="s">
         <v>196</v>
       </c>
       <c r="E102" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F102" t="s">
         <v>285</v>
       </c>
       <c r="G102" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E102,'feed rations'!$Y$13:$Y$46,0),MATCH(C102&amp;D102,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.7314817761965576E-2</v>
-      </c>
-    </row>
-    <row r="103" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.5441026802460426E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C103" t="s">
         <v>196</v>
       </c>
       <c r="E103" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F103" t="s">
         <v>285</v>
       </c>
       <c r="G103" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E103,'feed rations'!$Y$13:$Y$46,0),MATCH(C103&amp;D103,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.16311530612857034</v>
-      </c>
-    </row>
-    <row r="104" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.7314817761965576E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C104" t="s">
         <v>196</v>
       </c>
       <c r="E104" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F104" t="s">
         <v>285</v>
       </c>
       <c r="G104" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E104,'feed rations'!$Y$13:$Y$46,0),MATCH(C104&amp;D104,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.3607807918891001E-2</v>
-      </c>
-    </row>
-    <row r="105" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.16311530612857034</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C105" t="s">
         <v>196</v>
       </c>
       <c r="E105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F105" t="s">
         <v>285</v>
       </c>
       <c r="G105" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E105,'feed rations'!$Y$13:$Y$46,0),MATCH(C105&amp;D105,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.598428273092974E-2</v>
-      </c>
-    </row>
-    <row r="106" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.3607807918891001E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C106" t="s">
         <v>196</v>
       </c>
       <c r="E106" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F106" t="s">
         <v>285</v>
       </c>
       <c r="G106" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E106,'feed rations'!$Y$13:$Y$46,0),MATCH(C106&amp;D106,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.9986464582958335E-3</v>
-      </c>
-    </row>
-    <row r="107" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.598428273092974E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C107" t="s">
         <v>196</v>
       </c>
       <c r="E107" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F107" t="s">
         <v>285</v>
       </c>
       <c r="G107" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E107,'feed rations'!$Y$13:$Y$46,0),MATCH(C107&amp;D107,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="3:7" x14ac:dyDescent="0.25">
+        <v>9.9986464582958335E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C108" t="s">
         <v>196</v>
       </c>
       <c r="E108" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F108" t="s">
         <v>285</v>
       </c>
       <c r="G108" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E108,'feed rations'!$Y$13:$Y$46,0),MATCH(C108&amp;D108,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5731980208800535E-2</v>
-      </c>
-    </row>
-    <row r="109" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C109" t="s">
         <v>196</v>
       </c>
       <c r="E109" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F109" t="s">
         <v>285</v>
       </c>
       <c r="G109" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E109,'feed rations'!$Y$13:$Y$46,0),MATCH(C109&amp;D109,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.5731980208800535E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C110" t="s">
         <v>196</v>
       </c>
       <c r="E110" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F110" t="s">
         <v>285</v>
       </c>
       <c r="G110" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E110,'feed rations'!$Y$13:$Y$46,0),MATCH(C110&amp;D110,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5338309315945754E-4</v>
-      </c>
-    </row>
-    <row r="111" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C111" t="s">
         <v>196</v>
       </c>
       <c r="E111" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F111" t="s">
         <v>285</v>
       </c>
       <c r="G111" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E111,'feed rations'!$Y$13:$Y$46,0),MATCH(C111&amp;D111,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0152180129671942E-2</v>
-      </c>
-    </row>
-    <row r="112" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.5338309315945754E-4</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C112" t="s">
         <v>196</v>
       </c>
       <c r="E112" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F112" t="s">
         <v>285</v>
       </c>
       <c r="G112" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E112,'feed rations'!$Y$13:$Y$46,0),MATCH(C112&amp;D112,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.188362213479006E-2</v>
+        <v>2.0152180129671942E-2</v>
       </c>
     </row>
     <row r="113" spans="3:7" x14ac:dyDescent="0.25">
@@ -4513,14 +4552,14 @@
         <v>196</v>
       </c>
       <c r="E113" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F113" t="s">
         <v>285</v>
       </c>
       <c r="G113" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E113,'feed rations'!$Y$13:$Y$46,0),MATCH(C113&amp;D113,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>6.188362213479006E-2</v>
       </c>
     </row>
     <row r="114" spans="3:7" x14ac:dyDescent="0.25">
@@ -4528,14 +4567,14 @@
         <v>196</v>
       </c>
       <c r="E114" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F114" t="s">
         <v>285</v>
       </c>
       <c r="G114" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E114,'feed rations'!$Y$13:$Y$46,0),MATCH(C114&amp;D114,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.4351804480686189E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="3:7" x14ac:dyDescent="0.25">
@@ -4543,29 +4582,29 @@
         <v>196</v>
       </c>
       <c r="E115" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F115" t="s">
         <v>285</v>
       </c>
       <c r="G115" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E115,'feed rations'!$Y$13:$Y$46,0),MATCH(C115&amp;D115,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>7.4351804480686189E-5</v>
+      </c>
+    </row>
+    <row r="116" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C116" t="s">
+        <v>196</v>
+      </c>
+      <c r="E116" t="s">
+        <v>259</v>
+      </c>
+      <c r="F116" t="s">
+        <v>285</v>
+      </c>
+      <c r="G116" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E116,'feed rations'!$Y$13:$Y$46,0),MATCH(C116&amp;D116,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C117" t="s">
-        <v>197</v>
-      </c>
-      <c r="E117" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F117" t="s">
-        <v>285</v>
-      </c>
-      <c r="G117" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E117,'feed rations'!$Y$13:$Y$46,0),MATCH(C117&amp;D117,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>15.175760492490328</v>
       </c>
     </row>
     <row r="118" spans="3:7" x14ac:dyDescent="0.25">
@@ -4573,29 +4612,29 @@
         <v>197</v>
       </c>
       <c r="E118" s="21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F118" t="s">
         <v>285</v>
       </c>
       <c r="G118" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E118,'feed rations'!$Y$13:$Y$46,0),MATCH(C118&amp;D118,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>30.351520984980656</v>
+        <v>15.175760492490328</v>
       </c>
     </row>
     <row r="119" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C119" t="s">
         <v>197</v>
       </c>
-      <c r="E119" t="s">
-        <v>277</v>
+      <c r="E119" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F119" t="s">
         <v>285</v>
       </c>
       <c r="G119" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E119,'feed rations'!$Y$13:$Y$46,0),MATCH(C119&amp;D119,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>43.343560127534147</v>
+        <v>30.351520984980656</v>
       </c>
     </row>
     <row r="120" spans="3:7" x14ac:dyDescent="0.25">
@@ -4603,14 +4642,14 @@
         <v>197</v>
       </c>
       <c r="E120" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="F120" t="s">
         <v>285</v>
       </c>
       <c r="G120" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E120,'feed rations'!$Y$13:$Y$46,0),MATCH(C120&amp;D120,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4321508712376856</v>
+        <v>43.343560127534147</v>
       </c>
     </row>
     <row r="121" spans="3:7" x14ac:dyDescent="0.25">
@@ -4618,14 +4657,14 @@
         <v>197</v>
       </c>
       <c r="E121" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F121" t="s">
         <v>285</v>
       </c>
       <c r="G121" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E121,'feed rations'!$Y$13:$Y$46,0),MATCH(C121&amp;D121,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2561931863852942</v>
+        <v>2.4321508712376856</v>
       </c>
     </row>
     <row r="122" spans="3:7" x14ac:dyDescent="0.25">
@@ -4633,14 +4672,14 @@
         <v>197</v>
       </c>
       <c r="E122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F122" t="s">
         <v>285</v>
       </c>
       <c r="G122" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E122,'feed rations'!$Y$13:$Y$46,0),MATCH(C122&amp;D122,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.9042966731194728</v>
+        <v>1.2561931863852942</v>
       </c>
     </row>
     <row r="123" spans="3:7" x14ac:dyDescent="0.25">
@@ -4648,14 +4687,14 @@
         <v>197</v>
       </c>
       <c r="E123" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F123" t="s">
         <v>285</v>
       </c>
       <c r="G123" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E123,'feed rations'!$Y$13:$Y$46,0),MATCH(C123&amp;D123,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.1772358266069939E-2</v>
+        <v>1.9042966731194728</v>
       </c>
     </row>
     <row r="124" spans="3:7" x14ac:dyDescent="0.25">
@@ -4663,14 +4702,14 @@
         <v>197</v>
       </c>
       <c r="E124" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F124" t="s">
         <v>285</v>
       </c>
       <c r="G124" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E124,'feed rations'!$Y$13:$Y$46,0),MATCH(C124&amp;D124,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>1.1772358266069939E-2</v>
       </c>
     </row>
     <row r="125" spans="3:7" x14ac:dyDescent="0.25">
@@ -4678,14 +4717,14 @@
         <v>197</v>
       </c>
       <c r="E125" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F125" t="s">
         <v>285</v>
       </c>
       <c r="G125" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E125,'feed rations'!$Y$13:$Y$46,0),MATCH(C125&amp;D125,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.4960168489581302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="3:7" x14ac:dyDescent="0.25">
@@ -4693,14 +4732,14 @@
         <v>197</v>
       </c>
       <c r="E126" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F126" t="s">
         <v>285</v>
       </c>
       <c r="G126" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E126,'feed rations'!$Y$13:$Y$46,0),MATCH(C126&amp;D126,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.084969835364313E-2</v>
+        <v>0.4960168489581302</v>
       </c>
     </row>
     <row r="127" spans="3:7" x14ac:dyDescent="0.25">
@@ -4708,14 +4747,14 @@
         <v>197</v>
       </c>
       <c r="E127" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F127" t="s">
         <v>285</v>
       </c>
       <c r="G127" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E127,'feed rations'!$Y$13:$Y$46,0),MATCH(C127&amp;D127,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.8065990618593489E-2</v>
+        <v>1.084969835364313E-2</v>
       </c>
     </row>
     <row r="128" spans="3:7" x14ac:dyDescent="0.25">
@@ -4723,247 +4762,258 @@
         <v>197</v>
       </c>
       <c r="E128" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F128" t="s">
         <v>285</v>
       </c>
       <c r="G128" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E128,'feed rations'!$Y$13:$Y$46,0),MATCH(C128&amp;D128,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.310791613369622</v>
-      </c>
-    </row>
-    <row r="129" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.8065990618593489E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C129" t="s">
         <v>197</v>
       </c>
       <c r="E129" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F129" t="s">
         <v>285</v>
       </c>
       <c r="G129" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E129,'feed rations'!$Y$13:$Y$46,0),MATCH(C129&amp;D129,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7666004011112982E-3</v>
-      </c>
-    </row>
-    <row r="130" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.310791613369622</v>
+      </c>
+    </row>
+    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C130" t="s">
         <v>197</v>
       </c>
       <c r="E130" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F130" t="s">
         <v>285</v>
       </c>
       <c r="G130" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E130,'feed rations'!$Y$13:$Y$46,0),MATCH(C130&amp;D130,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.55283506413716399</v>
-      </c>
-    </row>
-    <row r="131" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.7666004011112982E-3</v>
+      </c>
+    </row>
+    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C131" t="s">
         <v>197</v>
       </c>
       <c r="E131" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F131" t="s">
         <v>285</v>
       </c>
       <c r="G131" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E131,'feed rations'!$Y$13:$Y$46,0),MATCH(C131&amp;D131,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.1866213781219229E-5</v>
-      </c>
-    </row>
-    <row r="132" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.55283506413716399</v>
+      </c>
+    </row>
+    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C132" t="s">
         <v>197</v>
       </c>
       <c r="E132" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F132" t="s">
         <v>285</v>
       </c>
       <c r="G132" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E132,'feed rations'!$Y$13:$Y$46,0),MATCH(C132&amp;D132,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.4094536822348984</v>
-      </c>
-    </row>
-    <row r="133" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.1866213781219229E-5</v>
+      </c>
+    </row>
+    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C133" t="s">
         <v>197</v>
       </c>
       <c r="E133" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F133" t="s">
         <v>285</v>
       </c>
       <c r="G133" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E133,'feed rations'!$Y$13:$Y$46,0),MATCH(C133&amp;D133,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.5679592403097307E-5</v>
-      </c>
-    </row>
-    <row r="134" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.4094536822348984</v>
+      </c>
+    </row>
+    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C134" t="s">
         <v>197</v>
       </c>
       <c r="E134" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F134" t="s">
         <v>285</v>
       </c>
       <c r="G134" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E134,'feed rations'!$Y$13:$Y$46,0),MATCH(C134&amp;D134,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.60414683073671682</v>
-      </c>
-    </row>
-    <row r="135" spans="3:7" x14ac:dyDescent="0.25">
+        <v>5.5679592403097307E-5</v>
+      </c>
+    </row>
+    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>300</v>
+      </c>
       <c r="C135" t="s">
         <v>197</v>
       </c>
       <c r="E135" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F135" t="s">
         <v>285</v>
       </c>
       <c r="G135" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E135,'feed rations'!$Y$13:$Y$46,0),MATCH(C135&amp;D135,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5461429297032662E-3</v>
-      </c>
-    </row>
-    <row r="136" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C136" t="s">
-        <v>197</v>
-      </c>
-      <c r="E136" t="s">
-        <v>245</v>
-      </c>
-      <c r="F136" t="s">
-        <v>285</v>
-      </c>
-      <c r="G136" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E136,'feed rations'!$Y$13:$Y$46,0),MATCH(C136&amp;D136,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.0178983263546054E-2</v>
-      </c>
-    </row>
-    <row r="137" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.60414683073671682</v>
+      </c>
+    </row>
+    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B136" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C136" s="97" t="str">
+        <f>C135</f>
+        <v>spring lamb</v>
+      </c>
+      <c r="E136" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F136" s="97" t="str">
+        <f>F135</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G136" s="99">
+        <f>G135</f>
+        <v>0.60414683073671682</v>
+      </c>
+      <c r="I136" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C137" t="s">
         <v>197</v>
       </c>
       <c r="E137" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F137" t="s">
         <v>285</v>
       </c>
       <c r="G137" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E137,'feed rations'!$Y$13:$Y$46,0),MATCH(C137&amp;D137,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.8450625710019192E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.5461429297032662E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C138" t="s">
         <v>197</v>
       </c>
       <c r="E138" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F138" t="s">
         <v>285</v>
       </c>
       <c r="G138" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E138,'feed rations'!$Y$13:$Y$46,0),MATCH(C138&amp;D138,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.4684819038582827</v>
-      </c>
-    </row>
-    <row r="139" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.0178983263546054E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C139" t="s">
         <v>197</v>
       </c>
       <c r="E139" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F139" t="s">
         <v>285</v>
       </c>
       <c r="G139" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E139,'feed rations'!$Y$13:$Y$46,0),MATCH(C139&amp;D139,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.6524662289726004E-2</v>
-      </c>
-    </row>
-    <row r="140" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.8450625710019192E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
         <v>197</v>
       </c>
       <c r="E140" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F140" t="s">
         <v>285</v>
       </c>
       <c r="G140" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E140,'feed rations'!$Y$13:$Y$46,0),MATCH(C140&amp;D140,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10335011276914095</v>
-      </c>
-    </row>
-    <row r="141" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.4684819038582827</v>
+      </c>
+    </row>
+    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C141" t="s">
         <v>197</v>
       </c>
       <c r="E141" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F141" t="s">
         <v>285</v>
       </c>
       <c r="G141" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E141,'feed rations'!$Y$13:$Y$46,0),MATCH(C141&amp;D141,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8717016446612009E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="3:7" x14ac:dyDescent="0.25">
+        <v>9.6524662289726004E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C142" t="s">
         <v>197</v>
       </c>
       <c r="E142" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F142" t="s">
         <v>285</v>
       </c>
       <c r="G142" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E142,'feed rations'!$Y$13:$Y$46,0),MATCH(C142&amp;D142,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.10335011276914095</v>
+      </c>
+    </row>
+    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C143" t="s">
         <v>197</v>
       </c>
       <c r="E143" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F143" t="s">
         <v>285</v>
       </c>
       <c r="G143" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E143,'feed rations'!$Y$13:$Y$46,0),MATCH(C143&amp;D143,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.5183669237455988E-2</v>
-      </c>
-    </row>
-    <row r="144" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.8717016446612009E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C144" t="s">
         <v>197</v>
       </c>
       <c r="E144" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F144" t="s">
         <v>285</v>
@@ -4978,14 +5028,14 @@
         <v>197</v>
       </c>
       <c r="E145" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F145" t="s">
         <v>285</v>
       </c>
       <c r="G145" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E145,'feed rations'!$Y$13:$Y$46,0),MATCH(C145&amp;D145,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.4053010847661285E-4</v>
+        <v>4.5183669237455988E-2</v>
       </c>
     </row>
     <row r="146" spans="3:7" x14ac:dyDescent="0.25">
@@ -4993,14 +5043,14 @@
         <v>197</v>
       </c>
       <c r="E146" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F146" t="s">
         <v>285</v>
       </c>
       <c r="G146" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E146,'feed rations'!$Y$13:$Y$46,0),MATCH(C146&amp;D146,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.7878882970076748E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="3:7" x14ac:dyDescent="0.25">
@@ -5008,14 +5058,14 @@
         <v>197</v>
       </c>
       <c r="E147" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F147" t="s">
         <v>285</v>
       </c>
       <c r="G147" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E147,'feed rations'!$Y$13:$Y$46,0),MATCH(C147&amp;D147,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.17773535668382656</v>
+        <v>4.4053010847661285E-4</v>
       </c>
     </row>
     <row r="148" spans="3:7" x14ac:dyDescent="0.25">
@@ -5023,14 +5073,14 @@
         <v>197</v>
       </c>
       <c r="E148" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F148" t="s">
         <v>285</v>
       </c>
       <c r="G148" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E148,'feed rations'!$Y$13:$Y$46,0),MATCH(C148&amp;D148,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>5.7878882970076748E-2</v>
       </c>
     </row>
     <row r="149" spans="3:7" x14ac:dyDescent="0.25">
@@ -5038,14 +5088,14 @@
         <v>197</v>
       </c>
       <c r="E149" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F149" t="s">
         <v>285</v>
       </c>
       <c r="G149" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E149,'feed rations'!$Y$13:$Y$46,0),MATCH(C149&amp;D149,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1354510343103608E-4</v>
+        <v>0.17773535668382656</v>
       </c>
     </row>
     <row r="150" spans="3:7" x14ac:dyDescent="0.25">
@@ -5053,7 +5103,7 @@
         <v>197</v>
       </c>
       <c r="E150" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F150" t="s">
         <v>285</v>
@@ -5063,64 +5113,64 @@
         <v>0</v>
       </c>
     </row>
+    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C151" t="s">
+        <v>197</v>
+      </c>
+      <c r="E151" t="s">
+        <v>258</v>
+      </c>
+      <c r="F151" t="s">
+        <v>285</v>
+      </c>
+      <c r="G151" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E151,'feed rations'!$Y$13:$Y$46,0),MATCH(C151&amp;D151,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>2.1354510343103608E-4</v>
+      </c>
+    </row>
     <row r="152" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C152" t="s">
-        <v>198</v>
-      </c>
-      <c r="E152" s="21" t="s">
-        <v>276</v>
+        <v>197</v>
+      </c>
+      <c r="E152" t="s">
+        <v>259</v>
       </c>
       <c r="F152" t="s">
         <v>285</v>
       </c>
       <c r="G152" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E152,'feed rations'!$Y$13:$Y$46,0),MATCH(C152&amp;D152,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>14.556942659567957</v>
-      </c>
-    </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C153" t="s">
-        <v>198</v>
-      </c>
-      <c r="E153" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="F153" t="s">
-        <v>285</v>
-      </c>
-      <c r="G153" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E153,'feed rations'!$Y$13:$Y$46,0),MATCH(C153&amp;D153,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>29.113885319135914</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C154" t="s">
         <v>198</v>
       </c>
-      <c r="E154" t="s">
-        <v>277</v>
+      <c r="E154" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F154" t="s">
         <v>285</v>
       </c>
       <c r="G154" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E154,'feed rations'!$Y$13:$Y$46,0),MATCH(C154&amp;D154,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>55.686616486139165</v>
+        <v>14.556942659567957</v>
       </c>
     </row>
     <row r="155" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C155" t="s">
         <v>198</v>
       </c>
-      <c r="E155" t="s">
-        <v>229</v>
+      <c r="E155" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F155" t="s">
         <v>285</v>
       </c>
       <c r="G155" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E155,'feed rations'!$Y$13:$Y$46,0),MATCH(C155&amp;D155,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.14042319726111982</v>
+        <v>29.113885319135914</v>
       </c>
     </row>
     <row r="156" spans="3:7" x14ac:dyDescent="0.25">
@@ -5128,14 +5178,14 @@
         <v>198</v>
       </c>
       <c r="E156" t="s">
-        <v>230</v>
+        <v>277</v>
       </c>
       <c r="F156" t="s">
         <v>285</v>
       </c>
       <c r="G156" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E156,'feed rations'!$Y$13:$Y$46,0),MATCH(C156&amp;D156,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.252784590624109E-2</v>
+        <v>55.686616486139165</v>
       </c>
     </row>
     <row r="157" spans="3:7" x14ac:dyDescent="0.25">
@@ -5143,14 +5193,14 @@
         <v>198</v>
       </c>
       <c r="E157" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F157" t="s">
         <v>285</v>
       </c>
       <c r="G157" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E157,'feed rations'!$Y$13:$Y$46,0),MATCH(C157&amp;D157,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10994689126216511</v>
+        <v>0.14042319726111982</v>
       </c>
     </row>
     <row r="158" spans="3:7" x14ac:dyDescent="0.25">
@@ -5158,14 +5208,14 @@
         <v>198</v>
       </c>
       <c r="E158" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F158" t="s">
         <v>285</v>
       </c>
       <c r="G158" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E158,'feed rations'!$Y$13:$Y$46,0),MATCH(C158&amp;D158,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.7969146428143638E-4</v>
+        <v>7.252784590624109E-2</v>
       </c>
     </row>
     <row r="159" spans="3:7" x14ac:dyDescent="0.25">
@@ -5173,14 +5223,14 @@
         <v>198</v>
       </c>
       <c r="E159" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F159" t="s">
         <v>285</v>
       </c>
       <c r="G159" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E159,'feed rations'!$Y$13:$Y$46,0),MATCH(C159&amp;D159,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.10994689126216511</v>
       </c>
     </row>
     <row r="160" spans="3:7" x14ac:dyDescent="0.25">
@@ -5188,254 +5238,265 @@
         <v>198</v>
       </c>
       <c r="E160" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F160" t="s">
         <v>285</v>
       </c>
       <c r="G160" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E160,'feed rations'!$Y$13:$Y$46,0),MATCH(C160&amp;D160,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8638137810357785E-2</v>
-      </c>
-    </row>
-    <row r="161" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.7969146428143638E-4</v>
+      </c>
+    </row>
+    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C161" t="s">
         <v>198</v>
       </c>
       <c r="E161" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F161" t="s">
         <v>285</v>
       </c>
       <c r="G161" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E161,'feed rations'!$Y$13:$Y$46,0),MATCH(C161&amp;D161,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.2642056878731579E-4</v>
-      </c>
-    </row>
-    <row r="162" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C162" t="s">
         <v>198</v>
       </c>
       <c r="E162" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F162" t="s">
         <v>285</v>
       </c>
       <c r="G162" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E162,'feed rations'!$Y$13:$Y$46,0),MATCH(C162&amp;D162,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.9298729944924589E-3</v>
-      </c>
-    </row>
-    <row r="163" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.8638137810357785E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C163" t="s">
         <v>198</v>
       </c>
       <c r="E163" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F163" t="s">
         <v>285</v>
       </c>
       <c r="G163" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E163,'feed rations'!$Y$13:$Y$46,0),MATCH(C163&amp;D163,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.5680152686726926E-2</v>
-      </c>
-    </row>
-    <row r="164" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.2642056878731579E-4</v>
+      </c>
+    </row>
+    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C164" t="s">
         <v>198</v>
       </c>
       <c r="E164" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F164" t="s">
         <v>285</v>
       </c>
       <c r="G164" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E164,'feed rations'!$Y$13:$Y$46,0),MATCH(C164&amp;D164,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.01996829037413E-4</v>
-      </c>
-    </row>
-    <row r="165" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.9298729944924589E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C165" t="s">
         <v>198</v>
       </c>
       <c r="E165" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F165" t="s">
         <v>285</v>
       </c>
       <c r="G165" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E165,'feed rations'!$Y$13:$Y$46,0),MATCH(C165&amp;D165,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.1918606769937602E-2</v>
-      </c>
-    </row>
-    <row r="166" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.5680152686726926E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C166" t="s">
         <v>198</v>
       </c>
       <c r="E166" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F166" t="s">
         <v>285</v>
       </c>
       <c r="G166" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E166,'feed rations'!$Y$13:$Y$46,0),MATCH(C166&amp;D166,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5719213163687675E-6</v>
-      </c>
-    </row>
-    <row r="167" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.01996829037413E-4</v>
+      </c>
+    </row>
+    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C167" t="s">
         <v>198</v>
       </c>
       <c r="E167" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F167" t="s">
         <v>285</v>
       </c>
       <c r="G167" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E167,'feed rations'!$Y$13:$Y$46,0),MATCH(C167&amp;D167,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.1376527579542932E-2</v>
-      </c>
-    </row>
-    <row r="168" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.1918606769937602E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C168" t="s">
         <v>198</v>
       </c>
       <c r="E168" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F168" t="s">
         <v>285</v>
       </c>
       <c r="G168" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E168,'feed rations'!$Y$13:$Y$46,0),MATCH(C168&amp;D168,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.2147291847318914E-6</v>
-      </c>
-    </row>
-    <row r="169" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.5719213163687675E-6</v>
+      </c>
+    </row>
+    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C169" t="s">
         <v>198</v>
       </c>
       <c r="E169" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F169" t="s">
         <v>285</v>
       </c>
       <c r="G169" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E169,'feed rations'!$Y$13:$Y$46,0),MATCH(C169&amp;D169,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.4881154204077169E-2</v>
-      </c>
-    </row>
-    <row r="170" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.1376527579542932E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C170" t="s">
         <v>198</v>
       </c>
       <c r="E170" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F170" t="s">
         <v>285</v>
       </c>
       <c r="G170" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E170,'feed rations'!$Y$13:$Y$46,0),MATCH(C170&amp;D170,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0474088759158359E-4</v>
-      </c>
-    </row>
-    <row r="171" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.2147291847318914E-6</v>
+      </c>
+    </row>
+    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
+        <v>300</v>
+      </c>
       <c r="C171" t="s">
         <v>198</v>
       </c>
       <c r="E171" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F171" t="s">
         <v>285</v>
       </c>
       <c r="G171" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E171,'feed rations'!$Y$13:$Y$46,0),MATCH(C171&amp;D171,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.8769601492985593E-4</v>
-      </c>
-    </row>
-    <row r="172" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C172" t="s">
-        <v>198</v>
-      </c>
-      <c r="E172" t="s">
-        <v>246</v>
-      </c>
-      <c r="F172" t="s">
-        <v>285</v>
-      </c>
-      <c r="G172" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E172,'feed rations'!$Y$13:$Y$46,0),MATCH(C172&amp;D172,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.5294425685567267E-3</v>
-      </c>
-    </row>
-    <row r="173" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.4881154204077169E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B172" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C172" s="97" t="str">
+        <f>C171</f>
+        <v>winter lamb</v>
+      </c>
+      <c r="E172" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F172" s="97" t="str">
+        <f>F171</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G172" s="99">
+        <f>G171</f>
+        <v>3.4881154204077169E-2</v>
+      </c>
+      <c r="I172" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C173" t="s">
         <v>198</v>
       </c>
       <c r="E173" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F173" t="s">
         <v>285</v>
       </c>
       <c r="G173" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E173,'feed rations'!$Y$13:$Y$46,0),MATCH(C173&amp;D173,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.7048374168202494E-2</v>
-      </c>
-    </row>
-    <row r="174" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.0474088759158359E-4</v>
+      </c>
+    </row>
+    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C174" t="s">
         <v>198</v>
       </c>
       <c r="E174" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F174" t="s">
         <v>285</v>
       </c>
       <c r="G174" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E174,'feed rations'!$Y$13:$Y$46,0),MATCH(C174&amp;D174,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.5729691169921491E-3</v>
-      </c>
-    </row>
-    <row r="175" spans="3:7" x14ac:dyDescent="0.25">
+        <v>5.8769601492985593E-4</v>
+      </c>
+    </row>
+    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C175" t="s">
         <v>198</v>
       </c>
       <c r="E175" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F175" t="s">
         <v>285</v>
       </c>
       <c r="G175" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E175,'feed rations'!$Y$13:$Y$46,0),MATCH(C175&amp;D175,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.9670448260287137E-3</v>
-      </c>
-    </row>
-    <row r="176" spans="3:7" x14ac:dyDescent="0.25">
+        <v>4.5294425685567267E-3</v>
+      </c>
+    </row>
+    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C176" t="s">
         <v>198</v>
       </c>
       <c r="E176" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F176" t="s">
         <v>285</v>
       </c>
       <c r="G176" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E176,'feed rations'!$Y$13:$Y$46,0),MATCH(C176&amp;D176,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6580119732380434E-3</v>
+        <v>2.7048374168202494E-2</v>
       </c>
     </row>
     <row r="177" spans="3:7" x14ac:dyDescent="0.25">
@@ -5443,14 +5504,14 @@
         <v>198</v>
       </c>
       <c r="E177" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F177" t="s">
         <v>285</v>
       </c>
       <c r="G177" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E177,'feed rations'!$Y$13:$Y$46,0),MATCH(C177&amp;D177,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>5.5729691169921491E-3</v>
       </c>
     </row>
     <row r="178" spans="3:7" x14ac:dyDescent="0.25">
@@ -5458,14 +5519,14 @@
         <v>198</v>
       </c>
       <c r="E178" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F178" t="s">
         <v>285</v>
       </c>
       <c r="G178" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E178,'feed rations'!$Y$13:$Y$46,0),MATCH(C178&amp;D178,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.6087342579548447E-3</v>
+        <v>5.9670448260287137E-3</v>
       </c>
     </row>
     <row r="179" spans="3:7" x14ac:dyDescent="0.25">
@@ -5473,14 +5534,14 @@
         <v>198</v>
       </c>
       <c r="E179" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F179" t="s">
         <v>285</v>
       </c>
       <c r="G179" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E179,'feed rations'!$Y$13:$Y$46,0),MATCH(C179&amp;D179,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>1.6580119732380434E-3</v>
       </c>
     </row>
     <row r="180" spans="3:7" x14ac:dyDescent="0.25">
@@ -5488,14 +5549,14 @@
         <v>198</v>
       </c>
       <c r="E180" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F180" t="s">
         <v>285</v>
       </c>
       <c r="G180" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E180,'feed rations'!$Y$13:$Y$46,0),MATCH(C180&amp;D180,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.5434543166556919E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="3:7" x14ac:dyDescent="0.25">
@@ -5503,14 +5564,14 @@
         <v>198</v>
       </c>
       <c r="E181" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F181" t="s">
         <v>285</v>
       </c>
       <c r="G181" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E181,'feed rations'!$Y$13:$Y$46,0),MATCH(C181&amp;D181,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.3417079082862866E-3</v>
+        <v>2.6087342579548447E-3</v>
       </c>
     </row>
     <row r="182" spans="3:7" x14ac:dyDescent="0.25">
@@ -5518,14 +5579,14 @@
         <v>198</v>
       </c>
       <c r="E182" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F182" t="s">
         <v>285</v>
       </c>
       <c r="G182" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E182,'feed rations'!$Y$13:$Y$46,0),MATCH(C182&amp;D182,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.0261767617724977E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="3:7" x14ac:dyDescent="0.25">
@@ -5533,14 +5594,14 @@
         <v>198</v>
       </c>
       <c r="E183" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F183" t="s">
         <v>285</v>
       </c>
       <c r="G183" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E183,'feed rations'!$Y$13:$Y$46,0),MATCH(C183&amp;D183,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>2.5434543166556919E-5</v>
       </c>
     </row>
     <row r="184" spans="3:7" x14ac:dyDescent="0.25">
@@ -5548,14 +5609,14 @@
         <v>198</v>
       </c>
       <c r="E184" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F184" t="s">
         <v>285</v>
       </c>
       <c r="G184" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E184,'feed rations'!$Y$13:$Y$46,0),MATCH(C184&amp;D184,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2329287026500471E-5</v>
+        <v>3.3417079082862866E-3</v>
       </c>
     </row>
     <row r="185" spans="3:7" x14ac:dyDescent="0.25">
@@ -5563,89 +5624,89 @@
         <v>198</v>
       </c>
       <c r="E185" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F185" t="s">
         <v>285</v>
       </c>
       <c r="G185" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E185,'feed rations'!$Y$13:$Y$46,0),MATCH(C185&amp;D185,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>1.0261767617724977E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C186" t="s">
+        <v>198</v>
+      </c>
+      <c r="E186" t="s">
+        <v>257</v>
+      </c>
+      <c r="F186" t="s">
+        <v>285</v>
+      </c>
+      <c r="G186" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E186,'feed rations'!$Y$13:$Y$46,0),MATCH(C186&amp;D186,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C187" t="s">
-        <v>204</v>
-      </c>
-      <c r="E187" s="21" t="s">
-        <v>276</v>
+        <v>198</v>
+      </c>
+      <c r="E187" t="s">
+        <v>258</v>
       </c>
       <c r="F187" t="s">
         <v>285</v>
       </c>
       <c r="G187" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E187,'feed rations'!$Y$13:$Y$46,0),MATCH(C187&amp;D187,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>14.502048815250316</v>
+        <v>1.2329287026500471E-5</v>
       </c>
     </row>
     <row r="188" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C188" t="s">
-        <v>204</v>
-      </c>
-      <c r="E188" s="21" t="s">
-        <v>274</v>
+        <v>198</v>
+      </c>
+      <c r="E188" t="s">
+        <v>259</v>
       </c>
       <c r="F188" t="s">
         <v>285</v>
       </c>
       <c r="G188" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E188,'feed rations'!$Y$13:$Y$46,0),MATCH(C188&amp;D188,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>29.004097630500631</v>
-      </c>
-    </row>
-    <row r="189" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C189" t="s">
-        <v>204</v>
-      </c>
-      <c r="E189" t="s">
-        <v>277</v>
-      </c>
-      <c r="F189" t="s">
-        <v>285</v>
-      </c>
-      <c r="G189" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E189,'feed rations'!$Y$13:$Y$46,0),MATCH(C189&amp;D189,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>52.618920363442022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C190" t="s">
         <v>204</v>
       </c>
-      <c r="E190" t="s">
-        <v>229</v>
+      <c r="E190" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F190" t="s">
         <v>285</v>
       </c>
       <c r="G190" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E190,'feed rations'!$Y$13:$Y$46,0),MATCH(C190&amp;D190,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.84682253603719471</v>
+        <v>14.502048815250316</v>
       </c>
     </row>
     <row r="191" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C191" t="s">
         <v>204</v>
       </c>
-      <c r="E191" t="s">
-        <v>230</v>
+      <c r="E191" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F191" t="s">
         <v>285</v>
       </c>
       <c r="G191" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E191,'feed rations'!$Y$13:$Y$46,0),MATCH(C191&amp;D191,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.43737940455400331</v>
+        <v>29.004097630500631</v>
       </c>
     </row>
     <row r="192" spans="3:7" x14ac:dyDescent="0.25">
@@ -5653,254 +5714,265 @@
         <v>204</v>
       </c>
       <c r="E192" t="s">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="F192" t="s">
         <v>285</v>
       </c>
       <c r="G192" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E192,'feed rations'!$Y$13:$Y$46,0),MATCH(C192&amp;D192,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.66303507614130686</v>
-      </c>
-    </row>
-    <row r="193" spans="3:7" x14ac:dyDescent="0.25">
+        <v>52.618920363442022</v>
+      </c>
+    </row>
+    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C193" t="s">
         <v>204</v>
       </c>
       <c r="E193" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F193" t="s">
         <v>285</v>
       </c>
       <c r="G193" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E193,'feed rations'!$Y$13:$Y$46,0),MATCH(C193&amp;D193,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.0988815290634705E-3</v>
-      </c>
-    </row>
-    <row r="194" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.84682253603719471</v>
+      </c>
+    </row>
+    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C194" t="s">
         <v>204</v>
       </c>
       <c r="E194" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F194" t="s">
         <v>285</v>
       </c>
       <c r="G194" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E194,'feed rations'!$Y$13:$Y$46,0),MATCH(C194&amp;D194,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.43737940455400331</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C195" t="s">
         <v>204</v>
       </c>
       <c r="E195" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F195" t="s">
         <v>285</v>
       </c>
       <c r="G195" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E195,'feed rations'!$Y$13:$Y$46,0),MATCH(C195&amp;D195,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.17270238081001552</v>
-      </c>
-    </row>
-    <row r="196" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.66303507614130686</v>
+      </c>
+    </row>
+    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C196" t="s">
         <v>204</v>
       </c>
       <c r="E196" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F196" t="s">
         <v>285</v>
       </c>
       <c r="G196" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E196,'feed rations'!$Y$13:$Y$46,0),MATCH(C196&amp;D196,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7776312249885764E-3</v>
-      </c>
-    </row>
-    <row r="197" spans="3:7" x14ac:dyDescent="0.25">
+        <v>4.0988815290634705E-3</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C197" t="s">
         <v>204</v>
       </c>
       <c r="E197" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F197" t="s">
         <v>285</v>
       </c>
       <c r="G197" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E197,'feed rations'!$Y$13:$Y$46,0),MATCH(C197&amp;D197,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3699111545736139E-2</v>
-      </c>
-    </row>
-    <row r="198" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C198" t="s">
         <v>204</v>
       </c>
       <c r="E198" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F198" t="s">
         <v>285</v>
       </c>
       <c r="G198" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E198,'feed rations'!$Y$13:$Y$46,0),MATCH(C198&amp;D198,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.45638940058232602</v>
-      </c>
-    </row>
-    <row r="199" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.17270238081001552</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C199" t="s">
         <v>204</v>
       </c>
       <c r="E199" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F199" t="s">
         <v>285</v>
       </c>
       <c r="G199" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E199,'feed rations'!$Y$13:$Y$46,0),MATCH(C199&amp;D199,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.1509220070385851E-4</v>
-      </c>
-    </row>
-    <row r="200" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.7776312249885764E-3</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C200" t="s">
         <v>204</v>
       </c>
       <c r="E200" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F200" t="s">
         <v>285</v>
       </c>
       <c r="G200" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E200,'feed rations'!$Y$13:$Y$46,0),MATCH(C200&amp;D200,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.19248525926546745</v>
-      </c>
-    </row>
-    <row r="201" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.3699111545736139E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C201" t="s">
         <v>204</v>
       </c>
       <c r="E201" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F201" t="s">
         <v>285</v>
       </c>
       <c r="G201" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E201,'feed rations'!$Y$13:$Y$46,0),MATCH(C201&amp;D201,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1540482816582413E-5</v>
-      </c>
-    </row>
-    <row r="202" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.45638940058232602</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C202" t="s">
         <v>204</v>
       </c>
       <c r="E202" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F202" t="s">
         <v>285</v>
       </c>
       <c r="G202" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E202,'feed rations'!$Y$13:$Y$46,0),MATCH(C202&amp;D202,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.49074140742335415</v>
-      </c>
-    </row>
-    <row r="203" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.1509220070385851E-4</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C203" t="s">
         <v>204</v>
       </c>
       <c r="E203" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F203" t="s">
         <v>285</v>
       </c>
       <c r="G203" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E203,'feed rations'!$Y$13:$Y$46,0),MATCH(C203&amp;D203,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.938643453492417E-5</v>
-      </c>
-    </row>
-    <row r="204" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.19248525926546745</v>
+      </c>
+    </row>
+    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C204" t="s">
         <v>204</v>
       </c>
       <c r="E204" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F204" t="s">
         <v>285</v>
       </c>
       <c r="G204" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E204,'feed rations'!$Y$13:$Y$46,0),MATCH(C204&amp;D204,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.21035091095436523</v>
-      </c>
-    </row>
-    <row r="205" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.1540482816582413E-5</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C205" t="s">
         <v>204</v>
       </c>
       <c r="E205" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F205" t="s">
         <v>285</v>
       </c>
       <c r="G205" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E205,'feed rations'!$Y$13:$Y$46,0),MATCH(C205&amp;D205,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2346905713762435E-3</v>
-      </c>
-    </row>
-    <row r="206" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.49074140742335415</v>
+      </c>
+    </row>
+    <row r="206" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C206" t="s">
         <v>204</v>
       </c>
       <c r="E206" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F206" t="s">
         <v>285</v>
       </c>
       <c r="G206" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E206,'feed rations'!$Y$13:$Y$46,0),MATCH(C206&amp;D206,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5441026802460426E-3</v>
-      </c>
-    </row>
-    <row r="207" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.938643453492417E-5</v>
+      </c>
+    </row>
+    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B207" t="s">
+        <v>300</v>
+      </c>
       <c r="C207" t="s">
         <v>204</v>
       </c>
       <c r="E207" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F207" t="s">
         <v>285</v>
       </c>
       <c r="G207" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E207,'feed rations'!$Y$13:$Y$46,0),MATCH(C207&amp;D207,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.7314817761965576E-2</v>
-      </c>
-    </row>
-    <row r="208" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C208" t="s">
-        <v>204</v>
-      </c>
-      <c r="E208" t="s">
-        <v>247</v>
-      </c>
-      <c r="F208" t="s">
-        <v>285</v>
-      </c>
-      <c r="G208" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E208,'feed rations'!$Y$13:$Y$46,0),MATCH(C208&amp;D208,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.16311530612857034</v>
+        <v>0.21035091095436523</v>
+      </c>
+    </row>
+    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B208" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C208" s="97" t="str">
+        <f>C207</f>
+        <v>other sheep</v>
+      </c>
+      <c r="E208" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F208" s="97" t="str">
+        <f>F207</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G208" s="99">
+        <f>G207</f>
+        <v>0.21035091095436523</v>
+      </c>
+      <c r="I208" s="97" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="209" spans="3:7" x14ac:dyDescent="0.25">
@@ -5908,14 +5980,14 @@
         <v>204</v>
       </c>
       <c r="E209" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F209" t="s">
         <v>285</v>
       </c>
       <c r="G209" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E209,'feed rations'!$Y$13:$Y$46,0),MATCH(C209&amp;D209,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.3607807918891001E-2</v>
+        <v>1.2346905713762435E-3</v>
       </c>
     </row>
     <row r="210" spans="3:7" x14ac:dyDescent="0.25">
@@ -5923,14 +5995,14 @@
         <v>204</v>
       </c>
       <c r="E210" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F210" t="s">
         <v>285</v>
       </c>
       <c r="G210" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E210,'feed rations'!$Y$13:$Y$46,0),MATCH(C210&amp;D210,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.598428273092974E-2</v>
+        <v>3.5441026802460426E-3</v>
       </c>
     </row>
     <row r="211" spans="3:7" x14ac:dyDescent="0.25">
@@ -5938,14 +6010,14 @@
         <v>204</v>
       </c>
       <c r="E211" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F211" t="s">
         <v>285</v>
       </c>
       <c r="G211" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E211,'feed rations'!$Y$13:$Y$46,0),MATCH(C211&amp;D211,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.9986464582958335E-3</v>
+        <v>2.7314817761965576E-2</v>
       </c>
     </row>
     <row r="212" spans="3:7" x14ac:dyDescent="0.25">
@@ -5953,14 +6025,14 @@
         <v>204</v>
       </c>
       <c r="E212" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F212" t="s">
         <v>285</v>
       </c>
       <c r="G212" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E212,'feed rations'!$Y$13:$Y$46,0),MATCH(C212&amp;D212,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.16311530612857034</v>
       </c>
     </row>
     <row r="213" spans="3:7" x14ac:dyDescent="0.25">
@@ -5968,14 +6040,14 @@
         <v>204</v>
       </c>
       <c r="E213" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F213" t="s">
         <v>285</v>
       </c>
       <c r="G213" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E213,'feed rations'!$Y$13:$Y$46,0),MATCH(C213&amp;D213,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5731980208800535E-2</v>
+        <v>3.3607807918891001E-2</v>
       </c>
     </row>
     <row r="214" spans="3:7" x14ac:dyDescent="0.25">
@@ -5983,14 +6055,14 @@
         <v>204</v>
       </c>
       <c r="E214" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F214" t="s">
         <v>285</v>
       </c>
       <c r="G214" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E214,'feed rations'!$Y$13:$Y$46,0),MATCH(C214&amp;D214,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>3.598428273092974E-2</v>
       </c>
     </row>
     <row r="215" spans="3:7" x14ac:dyDescent="0.25">
@@ -5998,14 +6070,14 @@
         <v>204</v>
       </c>
       <c r="E215" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F215" t="s">
         <v>285</v>
       </c>
       <c r="G215" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E215,'feed rations'!$Y$13:$Y$46,0),MATCH(C215&amp;D215,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5338309315945754E-4</v>
+        <v>9.9986464582958335E-3</v>
       </c>
     </row>
     <row r="216" spans="3:7" x14ac:dyDescent="0.25">
@@ -6013,14 +6085,14 @@
         <v>204</v>
       </c>
       <c r="E216" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F216" t="s">
         <v>285</v>
       </c>
       <c r="G216" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E216,'feed rations'!$Y$13:$Y$46,0),MATCH(C216&amp;D216,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0152180129671942E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="3:7" x14ac:dyDescent="0.25">
@@ -6028,14 +6100,14 @@
         <v>204</v>
       </c>
       <c r="E217" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F217" t="s">
         <v>285</v>
       </c>
       <c r="G217" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E217,'feed rations'!$Y$13:$Y$46,0),MATCH(C217&amp;D217,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.188362213479006E-2</v>
+        <v>1.5731980208800535E-2</v>
       </c>
     </row>
     <row r="218" spans="3:7" x14ac:dyDescent="0.25">
@@ -6043,7 +6115,7 @@
         <v>204</v>
       </c>
       <c r="E218" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F218" t="s">
         <v>285</v>
@@ -6058,14 +6130,14 @@
         <v>204</v>
       </c>
       <c r="E219" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F219" t="s">
         <v>285</v>
       </c>
       <c r="G219" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E219,'feed rations'!$Y$13:$Y$46,0),MATCH(C219&amp;D219,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.4351804480686189E-5</v>
+        <v>1.5338309315945754E-4</v>
       </c>
     </row>
     <row r="220" spans="3:7" x14ac:dyDescent="0.25">
@@ -6073,86 +6145,74 @@
         <v>204</v>
       </c>
       <c r="E220" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F220" t="s">
         <v>285</v>
       </c>
       <c r="G220" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E220,'feed rations'!$Y$13:$Y$46,0),MATCH(C220&amp;D220,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>2.0152180129671942E-2</v>
+      </c>
+    </row>
+    <row r="221" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C221" t="s">
+        <v>204</v>
+      </c>
+      <c r="E221" t="s">
+        <v>256</v>
+      </c>
+      <c r="F221" t="s">
+        <v>285</v>
+      </c>
+      <c r="G221" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E221,'feed rations'!$Y$13:$Y$46,0),MATCH(C221&amp;D221,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>6.188362213479006E-2</v>
       </c>
     </row>
     <row r="222" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C222" t="s">
-        <v>196</v>
-      </c>
-      <c r="D222" t="s">
-        <v>205</v>
-      </c>
-      <c r="E222" s="21" t="s">
-        <v>276</v>
+        <v>204</v>
+      </c>
+      <c r="E222" t="s">
+        <v>257</v>
       </c>
       <c r="F222" t="s">
         <v>285</v>
       </c>
       <c r="G222" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E222,'feed rations'!$Y$13:$Y$46,0),MATCH(C222&amp;D222,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.69811719906917724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C223" t="s">
-        <v>196</v>
-      </c>
-      <c r="D223" t="s">
-        <v>205</v>
-      </c>
-      <c r="E223" s="21" t="s">
-        <v>274</v>
+        <v>204</v>
+      </c>
+      <c r="E223" t="s">
+        <v>258</v>
       </c>
       <c r="F223" t="s">
         <v>285</v>
       </c>
       <c r="G223" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E223,'feed rations'!$Y$13:$Y$46,0),MATCH(C223&amp;D223,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3962343981383545</v>
+        <v>7.4351804480686189E-5</v>
       </c>
     </row>
     <row r="224" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C224" t="s">
-        <v>196</v>
-      </c>
-      <c r="D224" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E224" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="F224" t="s">
         <v>285</v>
       </c>
       <c r="G224" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E224,'feed rations'!$Y$13:$Y$46,0),MATCH(C224&amp;D224,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>83.30865242225515</v>
-      </c>
-    </row>
-    <row r="225" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C225" t="s">
-        <v>196</v>
-      </c>
-      <c r="D225" t="s">
-        <v>205</v>
-      </c>
-      <c r="E225" t="s">
-        <v>229</v>
-      </c>
-      <c r="F225" t="s">
-        <v>285</v>
-      </c>
-      <c r="G225" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E225,'feed rations'!$Y$13:$Y$46,0),MATCH(C225&amp;D225,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.1900072971810016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="3:7" x14ac:dyDescent="0.25">
@@ -6162,15 +6222,15 @@
       <c r="D226" t="s">
         <v>205</v>
       </c>
-      <c r="E226" t="s">
-        <v>230</v>
+      <c r="E226" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F226" t="s">
         <v>285</v>
       </c>
       <c r="G226" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E226,'feed rations'!$Y$13:$Y$46,0),MATCH(C226&amp;D226,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6476220610438137</v>
+        <v>0.69811719906917724</v>
       </c>
     </row>
     <row r="227" spans="3:7" x14ac:dyDescent="0.25">
@@ -6180,15 +6240,15 @@
       <c r="D227" t="s">
         <v>205</v>
       </c>
-      <c r="E227" t="s">
-        <v>231</v>
+      <c r="E227" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F227" t="s">
         <v>285</v>
       </c>
       <c r="G227" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E227,'feed rations'!$Y$13:$Y$46,0),MATCH(C227&amp;D227,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4976741184469726</v>
+        <v>1.3962343981383545</v>
       </c>
     </row>
     <row r="228" spans="3:7" x14ac:dyDescent="0.25">
@@ -6199,14 +6259,14 @@
         <v>205</v>
       </c>
       <c r="E228" t="s">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="F228" t="s">
         <v>285</v>
       </c>
       <c r="G228" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E228,'feed rations'!$Y$13:$Y$46,0),MATCH(C228&amp;D228,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.544061645924192E-2</v>
+        <v>83.30865242225515</v>
       </c>
     </row>
     <row r="229" spans="3:7" x14ac:dyDescent="0.25">
@@ -6217,14 +6277,14 @@
         <v>205</v>
       </c>
       <c r="E229" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F229" t="s">
         <v>285</v>
       </c>
       <c r="G229" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E229,'feed rations'!$Y$13:$Y$46,0),MATCH(C229&amp;D229,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>3.1900072971810016</v>
       </c>
     </row>
     <row r="230" spans="3:7" x14ac:dyDescent="0.25">
@@ -6235,14 +6295,14 @@
         <v>205</v>
       </c>
       <c r="E230" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F230" t="s">
         <v>285</v>
       </c>
       <c r="G230" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E230,'feed rations'!$Y$13:$Y$46,0),MATCH(C230&amp;D230,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.65057533494867192</v>
+        <v>1.6476220610438137</v>
       </c>
     </row>
     <row r="231" spans="3:7" x14ac:dyDescent="0.25">
@@ -6253,14 +6313,14 @@
         <v>205</v>
       </c>
       <c r="E231" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F231" t="s">
         <v>285</v>
       </c>
       <c r="G231" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E231,'feed rations'!$Y$13:$Y$46,0),MATCH(C231&amp;D231,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.4230456395462613E-2</v>
+        <v>2.4976741184469726</v>
       </c>
     </row>
     <row r="232" spans="3:7" x14ac:dyDescent="0.25">
@@ -6271,14 +6331,14 @@
         <v>205</v>
       </c>
       <c r="E232" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F232" t="s">
         <v>285</v>
       </c>
       <c r="G232" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E232,'feed rations'!$Y$13:$Y$46,0),MATCH(C232&amp;D232,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.9275303325517821E-2</v>
+        <v>1.544061645924192E-2</v>
       </c>
     </row>
     <row r="233" spans="3:7" x14ac:dyDescent="0.25">
@@ -6289,14 +6349,14 @@
         <v>205</v>
       </c>
       <c r="E233" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F233" t="s">
         <v>285</v>
       </c>
       <c r="G233" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E233,'feed rations'!$Y$13:$Y$46,0),MATCH(C233&amp;D233,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7192333177936787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="3:7" x14ac:dyDescent="0.25">
@@ -6307,14 +6367,14 @@
         <v>205</v>
       </c>
       <c r="E234" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F234" t="s">
         <v>285</v>
       </c>
       <c r="G234" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E234,'feed rations'!$Y$13:$Y$46,0),MATCH(C234&amp;D234,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.317071789169115E-3</v>
+        <v>0.65057533494867192</v>
       </c>
     </row>
     <row r="235" spans="3:7" x14ac:dyDescent="0.25">
@@ -6325,14 +6385,14 @@
         <v>205</v>
       </c>
       <c r="E235" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F235" t="s">
         <v>285</v>
       </c>
       <c r="G235" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E235,'feed rations'!$Y$13:$Y$46,0),MATCH(C235&amp;D235,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.72509806426508272</v>
+        <v>1.4230456395462613E-2</v>
       </c>
     </row>
     <row r="236" spans="3:7" x14ac:dyDescent="0.25">
@@ -6343,14 +6403,14 @@
         <v>205</v>
       </c>
       <c r="E236" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F236" t="s">
         <v>285</v>
       </c>
       <c r="G236" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E236,'feed rations'!$Y$13:$Y$46,0),MATCH(C236&amp;D236,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.1143680577109445E-5</v>
+        <v>8.9275303325517821E-2</v>
       </c>
     </row>
     <row r="237" spans="3:7" x14ac:dyDescent="0.25">
@@ -6361,14 +6421,14 @@
         <v>205</v>
       </c>
       <c r="E237" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F237" t="s">
         <v>285</v>
       </c>
       <c r="G237" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E237,'feed rations'!$Y$13:$Y$46,0),MATCH(C237&amp;D237,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.8486384148858024</v>
+        <v>1.7192333177936787</v>
       </c>
     </row>
     <row r="238" spans="3:7" x14ac:dyDescent="0.25">
@@ -6379,14 +6439,14 @@
         <v>205</v>
       </c>
       <c r="E238" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F238" t="s">
         <v>285</v>
       </c>
       <c r="G238" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E238,'feed rations'!$Y$13:$Y$46,0),MATCH(C238&amp;D238,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.3029312519398498E-5</v>
+        <v>2.317071789169115E-3</v>
       </c>
     </row>
     <row r="239" spans="3:7" x14ac:dyDescent="0.25">
@@ -6397,14 +6457,14 @@
         <v>205</v>
       </c>
       <c r="E239" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F239" t="s">
         <v>285</v>
       </c>
       <c r="G239" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E239,'feed rations'!$Y$13:$Y$46,0),MATCH(C239&amp;D239,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.79239853966713902</v>
+        <v>0.72509806426508272</v>
       </c>
     </row>
     <row r="240" spans="3:7" x14ac:dyDescent="0.25">
@@ -6415,17 +6475,17 @@
         <v>205</v>
       </c>
       <c r="E240" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F240" t="s">
         <v>285</v>
       </c>
       <c r="G240" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E240,'feed rations'!$Y$13:$Y$46,0),MATCH(C240&amp;D240,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.6511184632405684E-3</v>
-      </c>
-    </row>
-    <row r="241" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.1143680577109445E-5</v>
+      </c>
+    </row>
+    <row r="241" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C241" t="s">
         <v>196</v>
       </c>
@@ -6433,17 +6493,17 @@
         <v>205</v>
       </c>
       <c r="E241" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F241" t="s">
         <v>285</v>
       </c>
       <c r="G241" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E241,'feed rations'!$Y$13:$Y$46,0),MATCH(C241&amp;D241,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3350746975688711E-2</v>
-      </c>
-    </row>
-    <row r="242" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.8486384148858024</v>
+      </c>
+    </row>
+    <row r="242" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C242" t="s">
         <v>196</v>
       </c>
@@ -6451,17 +6511,20 @@
         <v>205</v>
       </c>
       <c r="E242" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F242" t="s">
         <v>285</v>
       </c>
       <c r="G242" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E242,'feed rations'!$Y$13:$Y$46,0),MATCH(C242&amp;D242,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10289578308767665</v>
-      </c>
-    </row>
-    <row r="243" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.3029312519398498E-5</v>
+      </c>
+    </row>
+    <row r="243" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B243" t="s">
+        <v>300</v>
+      </c>
       <c r="C243" t="s">
         <v>196</v>
       </c>
@@ -6469,35 +6532,44 @@
         <v>205</v>
       </c>
       <c r="E243" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F243" t="s">
         <v>285</v>
       </c>
       <c r="G243" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E243,'feed rations'!$Y$13:$Y$46,0),MATCH(C243&amp;D243,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.61446052117016126</v>
-      </c>
-    </row>
-    <row r="244" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C244" t="s">
-        <v>196</v>
-      </c>
-      <c r="D244" t="s">
-        <v>205</v>
-      </c>
-      <c r="E244" t="s">
-        <v>248</v>
-      </c>
-      <c r="F244" t="s">
-        <v>285</v>
-      </c>
-      <c r="G244" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E244,'feed rations'!$Y$13:$Y$46,0),MATCH(C244&amp;D244,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.12660167619678325</v>
-      </c>
-    </row>
-    <row r="245" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.79239853966713902</v>
+      </c>
+    </row>
+    <row r="244" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B244" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C244" s="97" t="str">
+        <f>C243</f>
+        <v>autumn lamb</v>
+      </c>
+      <c r="D244" s="97" t="str">
+        <f>D243</f>
+        <v>lambs</v>
+      </c>
+      <c r="E244" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F244" s="97" t="str">
+        <f>F243</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G244" s="99">
+        <f>G243</f>
+        <v>0.79239853966713902</v>
+      </c>
+      <c r="I244" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="245" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C245" t="s">
         <v>196</v>
       </c>
@@ -6505,17 +6577,17 @@
         <v>205</v>
       </c>
       <c r="E245" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F245" t="s">
         <v>285</v>
       </c>
       <c r="G245" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E245,'feed rations'!$Y$13:$Y$46,0),MATCH(C245&amp;D245,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13555393203476143</v>
-      </c>
-    </row>
-    <row r="246" spans="3:7" x14ac:dyDescent="0.25">
+        <v>4.6511184632405684E-3</v>
+      </c>
+    </row>
+    <row r="246" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C246" t="s">
         <v>196</v>
       </c>
@@ -6523,17 +6595,17 @@
         <v>205</v>
       </c>
       <c r="E246" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F246" t="s">
         <v>285</v>
       </c>
       <c r="G246" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E246,'feed rations'!$Y$13:$Y$46,0),MATCH(C246&amp;D246,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7665217689123641E-2</v>
-      </c>
-    </row>
-    <row r="247" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.3350746975688711E-2</v>
+      </c>
+    </row>
+    <row r="247" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C247" t="s">
         <v>196</v>
       </c>
@@ -6541,17 +6613,17 @@
         <v>205</v>
       </c>
       <c r="E247" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F247" t="s">
         <v>285</v>
       </c>
       <c r="G247" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E247,'feed rations'!$Y$13:$Y$46,0),MATCH(C247&amp;D247,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.10289578308767665</v>
+      </c>
+    </row>
+    <row r="248" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C248" t="s">
         <v>196</v>
       </c>
@@ -6559,17 +6631,17 @@
         <v>205</v>
       </c>
       <c r="E248" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F248" t="s">
         <v>285</v>
       </c>
       <c r="G248" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E248,'feed rations'!$Y$13:$Y$46,0),MATCH(C248&amp;D248,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.9262867400799252E-2</v>
-      </c>
-    </row>
-    <row r="249" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.61446052117016126</v>
+      </c>
+    </row>
+    <row r="249" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C249" t="s">
         <v>196</v>
       </c>
@@ -6577,17 +6649,17 @@
         <v>205</v>
       </c>
       <c r="E249" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F249" t="s">
         <v>285</v>
       </c>
       <c r="G249" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E249,'feed rations'!$Y$13:$Y$46,0),MATCH(C249&amp;D249,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.12660167619678325</v>
+      </c>
+    </row>
+    <row r="250" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C250" t="s">
         <v>196</v>
       </c>
@@ -6595,17 +6667,17 @@
         <v>205</v>
       </c>
       <c r="E250" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F250" t="s">
         <v>285</v>
       </c>
       <c r="G250" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E250,'feed rations'!$Y$13:$Y$46,0),MATCH(C250&amp;D250,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.7779896686803802E-4</v>
-      </c>
-    </row>
-    <row r="251" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.13555393203476143</v>
+      </c>
+    </row>
+    <row r="251" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C251" t="s">
         <v>196</v>
       </c>
@@ -6613,17 +6685,17 @@
         <v>205</v>
       </c>
       <c r="E251" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F251" t="s">
         <v>285</v>
       </c>
       <c r="G251" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E251,'feed rations'!$Y$13:$Y$46,0),MATCH(C251&amp;D251,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.5913900412465971E-2</v>
-      </c>
-    </row>
-    <row r="252" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.7665217689123641E-2</v>
+      </c>
+    </row>
+    <row r="252" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C252" t="s">
         <v>196</v>
       </c>
@@ -6631,17 +6703,17 @@
         <v>205</v>
       </c>
       <c r="E252" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F252" t="s">
         <v>285</v>
       </c>
       <c r="G252" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E252,'feed rations'!$Y$13:$Y$46,0),MATCH(C252&amp;D252,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.23311756334422978</v>
-      </c>
-    </row>
-    <row r="253" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C253" t="s">
         <v>196</v>
       </c>
@@ -6649,17 +6721,17 @@
         <v>205</v>
       </c>
       <c r="E253" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F253" t="s">
         <v>285</v>
       </c>
       <c r="G253" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E253,'feed rations'!$Y$13:$Y$46,0),MATCH(C253&amp;D253,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="3:7" x14ac:dyDescent="0.25">
+        <v>5.9262867400799252E-2</v>
+      </c>
+    </row>
+    <row r="254" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C254" t="s">
         <v>196</v>
       </c>
@@ -6667,17 +6739,17 @@
         <v>205</v>
       </c>
       <c r="E254" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F254" t="s">
         <v>285</v>
       </c>
       <c r="G254" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E254,'feed rations'!$Y$13:$Y$46,0),MATCH(C254&amp;D254,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8008560088857437E-4</v>
-      </c>
-    </row>
-    <row r="255" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C255" t="s">
         <v>196</v>
       </c>
@@ -6685,104 +6757,104 @@
         <v>205</v>
       </c>
       <c r="E255" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F255" t="s">
         <v>285</v>
       </c>
       <c r="G255" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E255,'feed rations'!$Y$13:$Y$46,0),MATCH(C255&amp;D255,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>5.7779896686803802E-4</v>
+      </c>
+    </row>
+    <row r="256" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C256" t="s">
+        <v>196</v>
+      </c>
+      <c r="D256" t="s">
+        <v>205</v>
+      </c>
+      <c r="E256" t="s">
+        <v>255</v>
+      </c>
+      <c r="F256" t="s">
+        <v>285</v>
+      </c>
+      <c r="G256" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E256,'feed rations'!$Y$13:$Y$46,0),MATCH(C256&amp;D256,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>7.5913900412465971E-2</v>
       </c>
     </row>
     <row r="257" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C257" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D257" t="s">
         <v>205</v>
       </c>
-      <c r="E257" s="21" t="s">
-        <v>276</v>
+      <c r="E257" t="s">
+        <v>256</v>
       </c>
       <c r="F257" t="s">
         <v>285</v>
       </c>
       <c r="G257" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E257,'feed rations'!$Y$13:$Y$46,0),MATCH(C257&amp;D257,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>16.081871345029242</v>
+        <v>0.23311756334422978</v>
       </c>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C258" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D258" t="s">
         <v>205</v>
       </c>
-      <c r="E258" s="21" t="s">
-        <v>274</v>
+      <c r="E258" t="s">
+        <v>257</v>
       </c>
       <c r="F258" t="s">
         <v>285</v>
       </c>
       <c r="G258" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E258,'feed rations'!$Y$13:$Y$46,0),MATCH(C258&amp;D258,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>32.163742690058484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C259" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D259" t="s">
         <v>205</v>
       </c>
       <c r="E259" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="F259" t="s">
         <v>285</v>
       </c>
       <c r="G259" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E259,'feed rations'!$Y$13:$Y$46,0),MATCH(C259&amp;D259,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>2.8008560088857437E-4</v>
       </c>
     </row>
     <row r="260" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C260" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D260" t="s">
         <v>205</v>
       </c>
       <c r="E260" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="F260" t="s">
         <v>285</v>
       </c>
       <c r="G260" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E260,'feed rations'!$Y$13:$Y$46,0),MATCH(C260&amp;D260,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>11.310331873032048</v>
-      </c>
-    </row>
-    <row r="261" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C261" t="s">
-        <v>197</v>
-      </c>
-      <c r="D261" t="s">
-        <v>205</v>
-      </c>
-      <c r="E261" t="s">
-        <v>230</v>
-      </c>
-      <c r="F261" t="s">
-        <v>285</v>
-      </c>
-      <c r="G261" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E261,'feed rations'!$Y$13:$Y$46,0),MATCH(C261&amp;D261,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.8417271735404546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="3:7" x14ac:dyDescent="0.25">
@@ -6792,15 +6864,15 @@
       <c r="D262" t="s">
         <v>205</v>
       </c>
-      <c r="E262" t="s">
-        <v>231</v>
+      <c r="E262" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F262" t="s">
         <v>285</v>
       </c>
       <c r="G262" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E262,'feed rations'!$Y$13:$Y$46,0),MATCH(C262&amp;D262,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.8556296455127299</v>
+        <v>16.081871345029242</v>
       </c>
     </row>
     <row r="263" spans="3:7" x14ac:dyDescent="0.25">
@@ -6810,15 +6882,15 @@
       <c r="D263" t="s">
         <v>205</v>
       </c>
-      <c r="E263" t="s">
-        <v>232</v>
+      <c r="E263" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F263" t="s">
         <v>285</v>
       </c>
       <c r="G263" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E263,'feed rations'!$Y$13:$Y$46,0),MATCH(C263&amp;D263,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.4745484950004523E-2</v>
+        <v>32.163742690058484</v>
       </c>
     </row>
     <row r="264" spans="3:7" x14ac:dyDescent="0.25">
@@ -6829,7 +6901,7 @@
         <v>205</v>
       </c>
       <c r="E264" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="F264" t="s">
         <v>285</v>
@@ -6847,14 +6919,14 @@
         <v>205</v>
       </c>
       <c r="E265" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F265" t="s">
         <v>285</v>
       </c>
       <c r="G265" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E265,'feed rations'!$Y$13:$Y$46,0),MATCH(C265&amp;D265,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3066476848441386</v>
+        <v>11.310331873032048</v>
       </c>
     </row>
     <row r="266" spans="3:7" x14ac:dyDescent="0.25">
@@ -6865,14 +6937,14 @@
         <v>205</v>
       </c>
       <c r="E266" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F266" t="s">
         <v>285</v>
       </c>
       <c r="G266" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E266,'feed rations'!$Y$13:$Y$46,0),MATCH(C266&amp;D266,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.0454801366638102E-2</v>
+        <v>5.8417271735404546</v>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.25">
@@ -6883,14 +6955,14 @@
         <v>205</v>
       </c>
       <c r="E267" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F267" t="s">
         <v>285</v>
       </c>
       <c r="G267" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E267,'feed rations'!$Y$13:$Y$46,0),MATCH(C267&amp;D267,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.31653009369900376</v>
+        <v>8.8556296455127299</v>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.25">
@@ -6901,14 +6973,14 @@
         <v>205</v>
       </c>
       <c r="E268" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F268" t="s">
         <v>285</v>
       </c>
       <c r="G268" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E268,'feed rations'!$Y$13:$Y$46,0),MATCH(C268&amp;D268,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.0956284985943601</v>
+        <v>5.4745484950004523E-2</v>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.25">
@@ -6919,14 +6991,14 @@
         <v>205</v>
       </c>
       <c r="E269" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F269" t="s">
         <v>285</v>
       </c>
       <c r="G269" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E269,'feed rations'!$Y$13:$Y$46,0),MATCH(C269&amp;D269,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.2152949719901079E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.25">
@@ -6937,14 +7009,14 @@
         <v>205</v>
       </c>
       <c r="E270" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F270" t="s">
         <v>285</v>
       </c>
       <c r="G270" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E270,'feed rations'!$Y$13:$Y$46,0),MATCH(C270&amp;D270,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.5708717828258543</v>
+        <v>2.3066476848441386</v>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.25">
@@ -6955,14 +7027,14 @@
         <v>205</v>
       </c>
       <c r="E271" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F271" t="s">
         <v>285</v>
       </c>
       <c r="G271" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E271,'feed rations'!$Y$13:$Y$46,0),MATCH(C271&amp;D271,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8769901483844112E-4</v>
+        <v>5.0454801366638102E-2</v>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.25">
@@ -6973,17 +7045,17 @@
         <v>205</v>
       </c>
       <c r="E272" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F272" t="s">
         <v>285</v>
       </c>
       <c r="G272" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E272,'feed rations'!$Y$13:$Y$46,0),MATCH(C272&amp;D272,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.5544408014587594</v>
-      </c>
-    </row>
-    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.31653009369900376</v>
+      </c>
+    </row>
+    <row r="273" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C273" t="s">
         <v>197</v>
       </c>
@@ -6991,17 +7063,17 @@
         <v>205</v>
       </c>
       <c r="E273" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F273" t="s">
         <v>285</v>
       </c>
       <c r="G273" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E273,'feed rations'!$Y$13:$Y$46,0),MATCH(C273&amp;D273,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.58929113354597E-4</v>
-      </c>
-    </row>
-    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.0956284985943601</v>
+      </c>
+    </row>
+    <row r="274" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C274" t="s">
         <v>197</v>
       </c>
@@ -7009,17 +7081,17 @@
         <v>205</v>
       </c>
       <c r="E274" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F274" t="s">
         <v>285</v>
       </c>
       <c r="G274" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E274,'feed rations'!$Y$13:$Y$46,0),MATCH(C274&amp;D274,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8094890150443339</v>
-      </c>
-    </row>
-    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.2152949719901079E-3</v>
+      </c>
+    </row>
+    <row r="275" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C275" t="s">
         <v>197</v>
       </c>
@@ -7027,17 +7099,17 @@
         <v>205</v>
       </c>
       <c r="E275" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="F275" t="s">
         <v>285</v>
       </c>
       <c r="G275" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E275,'feed rations'!$Y$13:$Y$46,0),MATCH(C275&amp;D275,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6490775255130326E-2</v>
-      </c>
-    </row>
-    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.5708717828258543</v>
+      </c>
+    </row>
+    <row r="276" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C276" t="s">
         <v>197</v>
       </c>
@@ -7045,17 +7117,17 @@
         <v>205</v>
       </c>
       <c r="E276" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F276" t="s">
         <v>285</v>
       </c>
       <c r="G276" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E276,'feed rations'!$Y$13:$Y$46,0),MATCH(C276&amp;D276,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.7335747219562054E-2</v>
-      </c>
-    </row>
-    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.8769901483844112E-4</v>
+      </c>
+    </row>
+    <row r="277" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C277" t="s">
         <v>197</v>
       </c>
@@ -7063,17 +7135,17 @@
         <v>205</v>
       </c>
       <c r="E277" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F277" t="s">
         <v>285</v>
       </c>
       <c r="G277" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E277,'feed rations'!$Y$13:$Y$46,0),MATCH(C277&amp;D277,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.36482219212651157</v>
-      </c>
-    </row>
-    <row r="278" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.5544408014587594</v>
+      </c>
+    </row>
+    <row r="278" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C278" t="s">
         <v>197</v>
       </c>
@@ -7081,17 +7153,20 @@
         <v>205</v>
       </c>
       <c r="E278" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F278" t="s">
         <v>285</v>
       </c>
       <c r="G278" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E278,'feed rations'!$Y$13:$Y$46,0),MATCH(C278&amp;D278,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1786007898640953</v>
-      </c>
-    </row>
-    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.58929113354597E-4</v>
+      </c>
+    </row>
+    <row r="279" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B279" t="s">
+        <v>300</v>
+      </c>
       <c r="C279" t="s">
         <v>197</v>
       </c>
@@ -7099,35 +7174,44 @@
         <v>205</v>
       </c>
       <c r="E279" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F279" t="s">
         <v>285</v>
       </c>
       <c r="G279" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E279,'feed rations'!$Y$13:$Y$46,0),MATCH(C279&amp;D279,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.44887263259025506</v>
-      </c>
-    </row>
-    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C280" t="s">
-        <v>197</v>
-      </c>
-      <c r="D280" t="s">
-        <v>205</v>
-      </c>
-      <c r="E280" t="s">
-        <v>249</v>
-      </c>
-      <c r="F280" t="s">
-        <v>285</v>
-      </c>
-      <c r="G280" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E280,'feed rations'!$Y$13:$Y$46,0),MATCH(C280&amp;D280,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.48061330748755038</v>
-      </c>
-    </row>
-    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.8094890150443339</v>
+      </c>
+    </row>
+    <row r="280" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B280" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C280" s="97" t="str">
+        <f>C279</f>
+        <v>spring lamb</v>
+      </c>
+      <c r="D280" s="97" t="str">
+        <f>D279</f>
+        <v>lambs</v>
+      </c>
+      <c r="E280" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F280" s="97" t="str">
+        <f>F279</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G280" s="99">
+        <f>G279</f>
+        <v>2.8094890150443339</v>
+      </c>
+      <c r="I280" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="281" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C281" t="s">
         <v>197</v>
       </c>
@@ -7135,17 +7219,17 @@
         <v>205</v>
       </c>
       <c r="E281" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F281" t="s">
         <v>285</v>
       </c>
       <c r="G281" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E281,'feed rations'!$Y$13:$Y$46,0),MATCH(C281&amp;D281,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13354393029459391</v>
-      </c>
-    </row>
-    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.6490775255130326E-2</v>
+      </c>
+    </row>
+    <row r="282" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C282" t="s">
         <v>197</v>
       </c>
@@ -7153,17 +7237,17 @@
         <v>205</v>
       </c>
       <c r="E282" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F282" t="s">
         <v>285</v>
       </c>
       <c r="G282" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E282,'feed rations'!$Y$13:$Y$46,0),MATCH(C282&amp;D282,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
+        <v>4.7335747219562054E-2</v>
+      </c>
+    </row>
+    <row r="283" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C283" t="s">
         <v>197</v>
       </c>
@@ -7171,17 +7255,17 @@
         <v>205</v>
       </c>
       <c r="E283" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F283" t="s">
         <v>285</v>
       </c>
       <c r="G283" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E283,'feed rations'!$Y$13:$Y$46,0),MATCH(C283&amp;D283,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.21011948738890288</v>
-      </c>
-    </row>
-    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.36482219212651157</v>
+      </c>
+    </row>
+    <row r="284" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C284" t="s">
         <v>197</v>
       </c>
@@ -7189,17 +7273,17 @@
         <v>205</v>
       </c>
       <c r="E284" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F284" t="s">
         <v>285</v>
       </c>
       <c r="G284" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E284,'feed rations'!$Y$13:$Y$46,0),MATCH(C284&amp;D284,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.1786007898640953</v>
+      </c>
+    </row>
+    <row r="285" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C285" t="s">
         <v>197</v>
       </c>
@@ -7207,17 +7291,17 @@
         <v>205</v>
       </c>
       <c r="E285" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F285" t="s">
         <v>285</v>
       </c>
       <c r="G285" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E285,'feed rations'!$Y$13:$Y$46,0),MATCH(C285&amp;D285,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0486153987633827E-3</v>
-      </c>
-    </row>
-    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.44887263259025506</v>
+      </c>
+    </row>
+    <row r="286" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C286" t="s">
         <v>197</v>
       </c>
@@ -7225,17 +7309,17 @@
         <v>205</v>
       </c>
       <c r="E286" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F286" t="s">
         <v>285</v>
       </c>
       <c r="G286" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E286,'feed rations'!$Y$13:$Y$46,0),MATCH(C286&amp;D286,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.26915656531571153</v>
-      </c>
-    </row>
-    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.48061330748755038</v>
+      </c>
+    </row>
+    <row r="287" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C287" t="s">
         <v>197</v>
       </c>
@@ -7243,17 +7327,17 @@
         <v>205</v>
       </c>
       <c r="E287" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F287" t="s">
         <v>285</v>
       </c>
       <c r="G287" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E287,'feed rations'!$Y$13:$Y$46,0),MATCH(C287&amp;D287,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.82653008636870395</v>
-      </c>
-    </row>
-    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.13354393029459391</v>
+      </c>
+    </row>
+    <row r="288" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C288" t="s">
         <v>197</v>
       </c>
@@ -7261,7 +7345,7 @@
         <v>205</v>
       </c>
       <c r="E288" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F288" t="s">
         <v>285</v>
@@ -7279,14 +7363,14 @@
         <v>205</v>
       </c>
       <c r="E289" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F289" t="s">
         <v>285</v>
       </c>
       <c r="G289" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E289,'feed rations'!$Y$13:$Y$46,0),MATCH(C289&amp;D289,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.9305763397682621E-4</v>
+        <v>0.21011948738890288</v>
       </c>
     </row>
     <row r="290" spans="3:7" x14ac:dyDescent="0.25">
@@ -7297,7 +7381,7 @@
         <v>205</v>
       </c>
       <c r="E290" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F290" t="s">
         <v>285</v>
@@ -7307,112 +7391,112 @@
         <v>0</v>
       </c>
     </row>
+    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C291" t="s">
+        <v>197</v>
+      </c>
+      <c r="D291" t="s">
+        <v>205</v>
+      </c>
+      <c r="E291" t="s">
+        <v>254</v>
+      </c>
+      <c r="F291" t="s">
+        <v>285</v>
+      </c>
+      <c r="G291" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E291,'feed rations'!$Y$13:$Y$46,0),MATCH(C291&amp;D291,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>2.0486153987633827E-3</v>
+      </c>
+    </row>
     <row r="292" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C292" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D292" t="s">
         <v>205</v>
       </c>
-      <c r="E292" s="21" t="s">
-        <v>276</v>
+      <c r="E292" t="s">
+        <v>255</v>
       </c>
       <c r="F292" t="s">
         <v>285</v>
       </c>
       <c r="G292" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E292,'feed rations'!$Y$13:$Y$46,0),MATCH(C292&amp;D292,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>18.580594474270001</v>
+        <v>0.26915656531571153</v>
       </c>
     </row>
     <row r="293" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C293" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D293" t="s">
         <v>205</v>
       </c>
-      <c r="E293" s="21" t="s">
-        <v>274</v>
+      <c r="E293" t="s">
+        <v>256</v>
       </c>
       <c r="F293" t="s">
         <v>285</v>
       </c>
       <c r="G293" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E293,'feed rations'!$Y$13:$Y$46,0),MATCH(C293&amp;D293,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>37.161188948540001</v>
+        <v>0.82653008636870395</v>
       </c>
     </row>
     <row r="294" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C294" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D294" t="s">
         <v>205</v>
       </c>
       <c r="E294" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="F294" t="s">
         <v>285</v>
       </c>
       <c r="G294" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E294,'feed rations'!$Y$13:$Y$46,0),MATCH(C294&amp;D294,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>41.770328663087604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C295" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D295" t="s">
         <v>205</v>
       </c>
       <c r="E295" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="F295" t="s">
         <v>285</v>
       </c>
       <c r="G295" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E295,'feed rations'!$Y$13:$Y$46,0),MATCH(C295&amp;D295,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.5436995811423736</v>
+        <v>9.9305763397682621E-4</v>
       </c>
     </row>
     <row r="296" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C296" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D296" t="s">
         <v>205</v>
       </c>
       <c r="E296" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="F296" t="s">
         <v>285</v>
       </c>
       <c r="G296" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E296,'feed rations'!$Y$13:$Y$46,0),MATCH(C296&amp;D296,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.28081798598457164</v>
-      </c>
-    </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C297" t="s">
-        <v>198</v>
-      </c>
-      <c r="D297" t="s">
-        <v>205</v>
-      </c>
-      <c r="E297" t="s">
-        <v>231</v>
-      </c>
-      <c r="F297" t="s">
-        <v>285</v>
-      </c>
-      <c r="G297" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E297,'feed rations'!$Y$13:$Y$46,0),MATCH(C297&amp;D297,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.42569945630839534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="3:7" x14ac:dyDescent="0.25">
@@ -7422,15 +7506,15 @@
       <c r="D298" t="s">
         <v>205</v>
       </c>
-      <c r="E298" t="s">
-        <v>232</v>
+      <c r="E298" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F298" t="s">
         <v>285</v>
       </c>
       <c r="G298" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E298,'feed rations'!$Y$13:$Y$46,0),MATCH(C298&amp;D298,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.6316731967630778E-3</v>
+        <v>18.580594474270001</v>
       </c>
     </row>
     <row r="299" spans="3:7" x14ac:dyDescent="0.25">
@@ -7440,15 +7524,15 @@
       <c r="D299" t="s">
         <v>205</v>
       </c>
-      <c r="E299" t="s">
-        <v>233</v>
+      <c r="E299" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F299" t="s">
         <v>285</v>
       </c>
       <c r="G299" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E299,'feed rations'!$Y$13:$Y$46,0),MATCH(C299&amp;D299,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>37.161188948540001</v>
       </c>
     </row>
     <row r="300" spans="3:7" x14ac:dyDescent="0.25">
@@ -7459,14 +7543,14 @@
         <v>205</v>
       </c>
       <c r="E300" t="s">
-        <v>234</v>
+        <v>277</v>
       </c>
       <c r="F300" t="s">
         <v>285</v>
       </c>
       <c r="G300" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E300,'feed rations'!$Y$13:$Y$46,0),MATCH(C300&amp;D300,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.11088298682756348</v>
+        <v>41.770328663087604</v>
       </c>
     </row>
     <row r="301" spans="3:7" x14ac:dyDescent="0.25">
@@ -7477,14 +7561,14 @@
         <v>205</v>
       </c>
       <c r="E301" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F301" t="s">
         <v>285</v>
       </c>
       <c r="G301" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E301,'feed rations'!$Y$13:$Y$46,0),MATCH(C301&amp;D301,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4254155119065326E-3</v>
+        <v>0.5436995811423736</v>
       </c>
     </row>
     <row r="302" spans="3:7" x14ac:dyDescent="0.25">
@@ -7495,14 +7579,14 @@
         <v>205</v>
       </c>
       <c r="E302" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F302" t="s">
         <v>285</v>
       </c>
       <c r="G302" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E302,'feed rations'!$Y$13:$Y$46,0),MATCH(C302&amp;D302,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5215935420378532E-2</v>
+        <v>0.28081798598457164</v>
       </c>
     </row>
     <row r="303" spans="3:7" x14ac:dyDescent="0.25">
@@ -7513,14 +7597,14 @@
         <v>205</v>
       </c>
       <c r="E303" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F303" t="s">
         <v>285</v>
       </c>
       <c r="G303" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E303,'feed rations'!$Y$13:$Y$46,0),MATCH(C303&amp;D303,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.29302329044716247</v>
+        <v>0.42569945630839534</v>
       </c>
     </row>
     <row r="304" spans="3:7" x14ac:dyDescent="0.25">
@@ -7531,17 +7615,17 @@
         <v>205</v>
       </c>
       <c r="E304" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F304" t="s">
         <v>285</v>
       </c>
       <c r="G304" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E304,'feed rations'!$Y$13:$Y$46,0),MATCH(C304&amp;D304,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.9491789324787145E-4</v>
-      </c>
-    </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.6316731967630778E-3</v>
+      </c>
+    </row>
+    <row r="305" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C305" t="s">
         <v>198</v>
       </c>
@@ -7549,17 +7633,17 @@
         <v>205</v>
       </c>
       <c r="E305" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F305" t="s">
         <v>285</v>
       </c>
       <c r="G305" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E305,'feed rations'!$Y$13:$Y$46,0),MATCH(C305&amp;D305,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.12358451787130892</v>
-      </c>
-    </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C306" t="s">
         <v>198</v>
       </c>
@@ -7567,17 +7651,17 @@
         <v>205</v>
       </c>
       <c r="E306" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F306" t="s">
         <v>285</v>
       </c>
       <c r="G306" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E306,'feed rations'!$Y$13:$Y$46,0),MATCH(C306&amp;D306,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3829995053964826E-5</v>
-      </c>
-    </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.11088298682756348</v>
+      </c>
+    </row>
+    <row r="307" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C307" t="s">
         <v>198</v>
       </c>
@@ -7585,17 +7669,17 @@
         <v>205</v>
       </c>
       <c r="E307" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F307" t="s">
         <v>285</v>
       </c>
       <c r="G307" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E307,'feed rations'!$Y$13:$Y$46,0),MATCH(C307&amp;D307,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.31507888171457132</v>
-      </c>
-    </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.4254155119065326E-3</v>
+      </c>
+    </row>
+    <row r="308" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C308" t="s">
         <v>198</v>
       </c>
@@ -7603,17 +7687,17 @@
         <v>205</v>
       </c>
       <c r="E308" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F308" t="s">
         <v>285</v>
       </c>
       <c r="G308" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E308,'feed rations'!$Y$13:$Y$46,0),MATCH(C308&amp;D308,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2446995548568345E-5</v>
-      </c>
-    </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.5215935420378532E-2</v>
+      </c>
+    </row>
+    <row r="309" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C309" t="s">
         <v>198</v>
       </c>
@@ -7621,17 +7705,17 @@
         <v>205</v>
       </c>
       <c r="E309" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F309" t="s">
         <v>285</v>
       </c>
       <c r="G309" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E309,'feed rations'!$Y$13:$Y$46,0),MATCH(C309&amp;D309,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13505509987252132</v>
-      </c>
-    </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.29302329044716247</v>
+      </c>
+    </row>
+    <row r="310" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C310" t="s">
         <v>198</v>
       </c>
@@ -7639,17 +7723,17 @@
         <v>205</v>
       </c>
       <c r="E310" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F310" t="s">
         <v>285</v>
       </c>
       <c r="G310" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E310,'feed rations'!$Y$13:$Y$46,0),MATCH(C310&amp;D310,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.9272895787484826E-4</v>
-      </c>
-    </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.9491789324787145E-4</v>
+      </c>
+    </row>
+    <row r="311" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C311" t="s">
         <v>198</v>
       </c>
@@ -7657,17 +7741,17 @@
         <v>205</v>
       </c>
       <c r="E311" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="F311" t="s">
         <v>285</v>
       </c>
       <c r="G311" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E311,'feed rations'!$Y$13:$Y$46,0),MATCH(C311&amp;D311,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.2754792896663078E-3</v>
-      </c>
-    </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.12358451787130892</v>
+      </c>
+    </row>
+    <row r="312" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C312" t="s">
         <v>198</v>
       </c>
@@ -7675,17 +7759,17 @@
         <v>205</v>
       </c>
       <c r="E312" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F312" t="s">
         <v>285</v>
       </c>
       <c r="G312" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E312,'feed rations'!$Y$13:$Y$46,0),MATCH(C312&amp;D312,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7537387521189746E-2</v>
-      </c>
-    </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.3829995053964826E-5</v>
+      </c>
+    </row>
+    <row r="313" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C313" t="s">
         <v>198</v>
       </c>
@@ -7693,17 +7777,17 @@
         <v>205</v>
       </c>
       <c r="E313" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F313" t="s">
         <v>285</v>
       </c>
       <c r="G313" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E313,'feed rations'!$Y$13:$Y$46,0),MATCH(C313&amp;D313,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10472763754614865</v>
-      </c>
-    </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.31507888171457132</v>
+      </c>
+    </row>
+    <row r="314" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C314" t="s">
         <v>198</v>
       </c>
@@ -7711,17 +7795,20 @@
         <v>205</v>
       </c>
       <c r="E314" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F314" t="s">
         <v>285</v>
       </c>
       <c r="G314" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E314,'feed rations'!$Y$13:$Y$46,0),MATCH(C314&amp;D314,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1577780834840472E-2</v>
-      </c>
-    </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.2446995548568345E-5</v>
+      </c>
+    </row>
+    <row r="315" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B315" t="s">
+        <v>300</v>
+      </c>
       <c r="C315" t="s">
         <v>198</v>
       </c>
@@ -7729,35 +7816,44 @@
         <v>205</v>
       </c>
       <c r="E315" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F315" t="s">
         <v>285</v>
       </c>
       <c r="G315" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E315,'feed rations'!$Y$13:$Y$46,0),MATCH(C315&amp;D315,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3103588551233269E-2</v>
-      </c>
-    </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C316" t="s">
-        <v>198</v>
-      </c>
-      <c r="D316" t="s">
-        <v>205</v>
-      </c>
-      <c r="E316" t="s">
-        <v>250</v>
-      </c>
-      <c r="F316" t="s">
-        <v>285</v>
-      </c>
-      <c r="G316" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E316,'feed rations'!$Y$13:$Y$46,0),MATCH(C316&amp;D316,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.41959756622177E-3</v>
-      </c>
-    </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.13505509987252132</v>
+      </c>
+    </row>
+    <row r="316" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B316" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C316" s="97" t="str">
+        <f>C315</f>
+        <v>winter lamb</v>
+      </c>
+      <c r="D316" s="97" t="str">
+        <f>D315</f>
+        <v>lambs</v>
+      </c>
+      <c r="E316" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F316" s="97" t="str">
+        <f>F315</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G316" s="99">
+        <f>G315</f>
+        <v>0.13505509987252132</v>
+      </c>
+      <c r="I316" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="317" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C317" t="s">
         <v>198</v>
       </c>
@@ -7765,17 +7861,17 @@
         <v>205</v>
       </c>
       <c r="E317" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F317" t="s">
         <v>285</v>
       </c>
       <c r="G317" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E317,'feed rations'!$Y$13:$Y$46,0),MATCH(C317&amp;D317,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.9272895787484826E-4</v>
+      </c>
+    </row>
+    <row r="318" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C318" t="s">
         <v>198</v>
       </c>
@@ -7783,17 +7879,17 @@
         <v>205</v>
       </c>
       <c r="E318" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F318" t="s">
         <v>285</v>
       </c>
       <c r="G318" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E318,'feed rations'!$Y$13:$Y$46,0),MATCH(C318&amp;D318,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.0100665353206037E-2</v>
-      </c>
-    </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.2754792896663078E-3</v>
+      </c>
+    </row>
+    <row r="319" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C319" t="s">
         <v>198</v>
       </c>
@@ -7801,17 +7897,17 @@
         <v>205</v>
       </c>
       <c r="E319" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F319" t="s">
         <v>285</v>
       </c>
       <c r="G319" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E319,'feed rations'!$Y$13:$Y$46,0),MATCH(C319&amp;D319,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.7537387521189746E-2</v>
+      </c>
+    </row>
+    <row r="320" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C320" t="s">
         <v>198</v>
       </c>
@@ -7819,14 +7915,14 @@
         <v>205</v>
       </c>
       <c r="E320" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F320" t="s">
         <v>285</v>
       </c>
       <c r="G320" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E320,'feed rations'!$Y$13:$Y$46,0),MATCH(C320&amp;D320,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.8479102711852997E-5</v>
+        <v>0.10472763754614865</v>
       </c>
     </row>
     <row r="321" spans="3:7" x14ac:dyDescent="0.25">
@@ -7837,14 +7933,14 @@
         <v>205</v>
       </c>
       <c r="E321" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F321" t="s">
         <v>285</v>
       </c>
       <c r="G321" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E321,'feed rations'!$Y$13:$Y$46,0),MATCH(C321&amp;D321,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2938639950327263E-2</v>
+        <v>2.1577780834840472E-2</v>
       </c>
     </row>
     <row r="322" spans="3:7" x14ac:dyDescent="0.25">
@@ -7855,14 +7951,14 @@
         <v>205</v>
       </c>
       <c r="E322" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F322" t="s">
         <v>285</v>
       </c>
       <c r="G322" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E322,'feed rations'!$Y$13:$Y$46,0),MATCH(C322&amp;D322,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.9732172919853009E-2</v>
+        <v>2.3103588551233269E-2</v>
       </c>
     </row>
     <row r="323" spans="3:7" x14ac:dyDescent="0.25">
@@ -7873,14 +7969,14 @@
         <v>205</v>
       </c>
       <c r="E323" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F323" t="s">
         <v>285</v>
       </c>
       <c r="G323" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E323,'feed rations'!$Y$13:$Y$46,0),MATCH(C323&amp;D323,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>6.41959756622177E-3</v>
       </c>
     </row>
     <row r="324" spans="3:7" x14ac:dyDescent="0.25">
@@ -7891,14 +7987,14 @@
         <v>205</v>
       </c>
       <c r="E324" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F324" t="s">
         <v>285</v>
       </c>
       <c r="G324" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E324,'feed rations'!$Y$13:$Y$46,0),MATCH(C324&amp;D324,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.773732775523721E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="3:7" x14ac:dyDescent="0.25">
@@ -7909,140 +8005,140 @@
         <v>205</v>
       </c>
       <c r="E325" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F325" t="s">
         <v>285</v>
       </c>
       <c r="G325" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E325,'feed rations'!$Y$13:$Y$46,0),MATCH(C325&amp;D325,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>1.0100665353206037E-2</v>
+      </c>
+    </row>
+    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C326" t="s">
+        <v>198</v>
+      </c>
+      <c r="D326" t="s">
+        <v>205</v>
+      </c>
+      <c r="E326" t="s">
+        <v>253</v>
+      </c>
+      <c r="F326" t="s">
+        <v>285</v>
+      </c>
+      <c r="G326" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E326,'feed rations'!$Y$13:$Y$46,0),MATCH(C326&amp;D326,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="327" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C327" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D327" t="s">
         <v>205</v>
       </c>
-      <c r="E327" s="21" t="s">
-        <v>276</v>
+      <c r="E327" t="s">
+        <v>254</v>
       </c>
       <c r="F327" t="s">
         <v>285</v>
       </c>
       <c r="G327" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E327,'feed rations'!$Y$13:$Y$46,0),MATCH(C327&amp;D327,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.69811719906917724</v>
+        <v>9.8479102711852997E-5</v>
       </c>
     </row>
     <row r="328" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C328" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D328" t="s">
         <v>205</v>
       </c>
-      <c r="E328" s="21" t="s">
-        <v>274</v>
+      <c r="E328" t="s">
+        <v>255</v>
       </c>
       <c r="F328" t="s">
         <v>285</v>
       </c>
       <c r="G328" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E328,'feed rations'!$Y$13:$Y$46,0),MATCH(C328&amp;D328,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3962343981383545</v>
+        <v>1.2938639950327263E-2</v>
       </c>
     </row>
     <row r="329" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C329" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D329" t="s">
         <v>205</v>
       </c>
       <c r="E329" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="F329" t="s">
         <v>285</v>
       </c>
       <c r="G329" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E329,'feed rations'!$Y$13:$Y$46,0),MATCH(C329&amp;D329,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>83.30865242225515</v>
+        <v>3.9732172919853009E-2</v>
       </c>
     </row>
     <row r="330" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C330" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D330" t="s">
         <v>205</v>
       </c>
       <c r="E330" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="F330" t="s">
         <v>285</v>
       </c>
       <c r="G330" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E330,'feed rations'!$Y$13:$Y$46,0),MATCH(C330&amp;D330,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.1900072971810016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C331" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D331" t="s">
         <v>205</v>
       </c>
       <c r="E331" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="F331" t="s">
         <v>285</v>
       </c>
       <c r="G331" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E331,'feed rations'!$Y$13:$Y$46,0),MATCH(C331&amp;D331,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6476220610438137</v>
+        <v>4.773732775523721E-5</v>
       </c>
     </row>
     <row r="332" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C332" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D332" t="s">
         <v>205</v>
       </c>
       <c r="E332" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="F332" t="s">
         <v>285</v>
       </c>
       <c r="G332" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E332,'feed rations'!$Y$13:$Y$46,0),MATCH(C332&amp;D332,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4976741184469726</v>
-      </c>
-    </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C333" t="s">
-        <v>204</v>
-      </c>
-      <c r="D333" t="s">
-        <v>205</v>
-      </c>
-      <c r="E333" t="s">
-        <v>232</v>
-      </c>
-      <c r="F333" t="s">
-        <v>285</v>
-      </c>
-      <c r="G333" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E333,'feed rations'!$Y$13:$Y$46,0),MATCH(C333&amp;D333,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.544061645924192E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="3:7" x14ac:dyDescent="0.25">
@@ -8052,15 +8148,15 @@
       <c r="D334" t="s">
         <v>205</v>
       </c>
-      <c r="E334" t="s">
-        <v>233</v>
+      <c r="E334" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F334" t="s">
         <v>285</v>
       </c>
       <c r="G334" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E334,'feed rations'!$Y$13:$Y$46,0),MATCH(C334&amp;D334,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.69811719906917724</v>
       </c>
     </row>
     <row r="335" spans="3:7" x14ac:dyDescent="0.25">
@@ -8070,15 +8166,15 @@
       <c r="D335" t="s">
         <v>205</v>
       </c>
-      <c r="E335" t="s">
-        <v>234</v>
+      <c r="E335" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="F335" t="s">
         <v>285</v>
       </c>
       <c r="G335" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E335,'feed rations'!$Y$13:$Y$46,0),MATCH(C335&amp;D335,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.65057533494867192</v>
+        <v>1.3962343981383545</v>
       </c>
     </row>
     <row r="336" spans="3:7" x14ac:dyDescent="0.25">
@@ -8089,17 +8185,17 @@
         <v>205</v>
       </c>
       <c r="E336" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F336" t="s">
         <v>285</v>
       </c>
       <c r="G336" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E336,'feed rations'!$Y$13:$Y$46,0),MATCH(C336&amp;D336,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.4230456395462613E-2</v>
-      </c>
-    </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
+        <v>83.30865242225515</v>
+      </c>
+    </row>
+    <row r="337" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C337" t="s">
         <v>204</v>
       </c>
@@ -8107,17 +8203,17 @@
         <v>205</v>
       </c>
       <c r="E337" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F337" t="s">
         <v>285</v>
       </c>
       <c r="G337" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E337,'feed rations'!$Y$13:$Y$46,0),MATCH(C337&amp;D337,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.9275303325517821E-2</v>
-      </c>
-    </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.1900072971810016</v>
+      </c>
+    </row>
+    <row r="338" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C338" t="s">
         <v>204</v>
       </c>
@@ -8125,17 +8221,17 @@
         <v>205</v>
       </c>
       <c r="E338" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F338" t="s">
         <v>285</v>
       </c>
       <c r="G338" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E338,'feed rations'!$Y$13:$Y$46,0),MATCH(C338&amp;D338,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7192333177936787</v>
-      </c>
-    </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.6476220610438137</v>
+      </c>
+    </row>
+    <row r="339" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C339" t="s">
         <v>204</v>
       </c>
@@ -8143,17 +8239,17 @@
         <v>205</v>
       </c>
       <c r="E339" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F339" t="s">
         <v>285</v>
       </c>
       <c r="G339" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E339,'feed rations'!$Y$13:$Y$46,0),MATCH(C339&amp;D339,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.317071789169115E-3</v>
-      </c>
-    </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.4976741184469726</v>
+      </c>
+    </row>
+    <row r="340" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C340" t="s">
         <v>204</v>
       </c>
@@ -8161,17 +8257,17 @@
         <v>205</v>
       </c>
       <c r="E340" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F340" t="s">
         <v>285</v>
       </c>
       <c r="G340" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E340,'feed rations'!$Y$13:$Y$46,0),MATCH(C340&amp;D340,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.72509806426508272</v>
-      </c>
-    </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.544061645924192E-2</v>
+      </c>
+    </row>
+    <row r="341" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C341" t="s">
         <v>204</v>
       </c>
@@ -8179,17 +8275,17 @@
         <v>205</v>
       </c>
       <c r="E341" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F341" t="s">
         <v>285</v>
       </c>
       <c r="G341" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E341,'feed rations'!$Y$13:$Y$46,0),MATCH(C341&amp;D341,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.1143680577109445E-5</v>
-      </c>
-    </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C342" t="s">
         <v>204</v>
       </c>
@@ -8197,17 +8293,17 @@
         <v>205</v>
       </c>
       <c r="E342" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F342" t="s">
         <v>285</v>
       </c>
       <c r="G342" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E342,'feed rations'!$Y$13:$Y$46,0),MATCH(C342&amp;D342,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.8486384148858024</v>
-      </c>
-    </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.65057533494867192</v>
+      </c>
+    </row>
+    <row r="343" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C343" t="s">
         <v>204</v>
       </c>
@@ -8215,17 +8311,17 @@
         <v>205</v>
       </c>
       <c r="E343" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F343" t="s">
         <v>285</v>
       </c>
       <c r="G343" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E343,'feed rations'!$Y$13:$Y$46,0),MATCH(C343&amp;D343,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.3029312519398498E-5</v>
-      </c>
-    </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.4230456395462613E-2</v>
+      </c>
+    </row>
+    <row r="344" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C344" t="s">
         <v>204</v>
       </c>
@@ -8233,17 +8329,17 @@
         <v>205</v>
       </c>
       <c r="E344" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F344" t="s">
         <v>285</v>
       </c>
       <c r="G344" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E344,'feed rations'!$Y$13:$Y$46,0),MATCH(C344&amp;D344,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.79239853966713902</v>
-      </c>
-    </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.9275303325517821E-2</v>
+      </c>
+    </row>
+    <row r="345" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C345" t="s">
         <v>204</v>
       </c>
@@ -8251,17 +8347,17 @@
         <v>205</v>
       </c>
       <c r="E345" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F345" t="s">
         <v>285</v>
       </c>
       <c r="G345" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E345,'feed rations'!$Y$13:$Y$46,0),MATCH(C345&amp;D345,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.6511184632405684E-3</v>
-      </c>
-    </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.7192333177936787</v>
+      </c>
+    </row>
+    <row r="346" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C346" t="s">
         <v>204</v>
       </c>
@@ -8269,17 +8365,17 @@
         <v>205</v>
       </c>
       <c r="E346" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F346" t="s">
         <v>285</v>
       </c>
       <c r="G346" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E346,'feed rations'!$Y$13:$Y$46,0),MATCH(C346&amp;D346,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3350746975688711E-2</v>
-      </c>
-    </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.317071789169115E-3</v>
+      </c>
+    </row>
+    <row r="347" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C347" t="s">
         <v>204</v>
       </c>
@@ -8287,17 +8383,17 @@
         <v>205</v>
       </c>
       <c r="E347" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F347" t="s">
         <v>285</v>
       </c>
       <c r="G347" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E347,'feed rations'!$Y$13:$Y$46,0),MATCH(C347&amp;D347,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10289578308767665</v>
-      </c>
-    </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.72509806426508272</v>
+      </c>
+    </row>
+    <row r="348" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C348" t="s">
         <v>204</v>
       </c>
@@ -8305,17 +8401,17 @@
         <v>205</v>
       </c>
       <c r="E348" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F348" t="s">
         <v>285</v>
       </c>
       <c r="G348" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E348,'feed rations'!$Y$13:$Y$46,0),MATCH(C348&amp;D348,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.61446052117016126</v>
-      </c>
-    </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.1143680577109445E-5</v>
+      </c>
+    </row>
+    <row r="349" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C349" t="s">
         <v>204</v>
       </c>
@@ -8323,17 +8419,17 @@
         <v>205</v>
       </c>
       <c r="E349" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F349" t="s">
         <v>285</v>
       </c>
       <c r="G349" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E349,'feed rations'!$Y$13:$Y$46,0),MATCH(C349&amp;D349,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.12660167619678325</v>
-      </c>
-    </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.8486384148858024</v>
+      </c>
+    </row>
+    <row r="350" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C350" t="s">
         <v>204</v>
       </c>
@@ -8341,17 +8437,20 @@
         <v>205</v>
       </c>
       <c r="E350" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F350" t="s">
         <v>285</v>
       </c>
       <c r="G350" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E350,'feed rations'!$Y$13:$Y$46,0),MATCH(C350&amp;D350,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13555393203476143</v>
-      </c>
-    </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.3029312519398498E-5</v>
+      </c>
+    </row>
+    <row r="351" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B351" t="s">
+        <v>300</v>
+      </c>
       <c r="C351" t="s">
         <v>204</v>
       </c>
@@ -8359,32 +8458,41 @@
         <v>205</v>
       </c>
       <c r="E351" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F351" t="s">
         <v>285</v>
       </c>
       <c r="G351" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E351,'feed rations'!$Y$13:$Y$46,0),MATCH(C351&amp;D351,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7665217689123641E-2</v>
-      </c>
-    </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C352" t="s">
-        <v>204</v>
-      </c>
-      <c r="D352" t="s">
-        <v>205</v>
-      </c>
-      <c r="E352" t="s">
-        <v>251</v>
-      </c>
-      <c r="F352" t="s">
-        <v>285</v>
-      </c>
-      <c r="G352" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E352,'feed rations'!$Y$13:$Y$46,0),MATCH(C352&amp;D352,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.79239853966713902</v>
+      </c>
+    </row>
+    <row r="352" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B352" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C352" s="97" t="str">
+        <f>C351</f>
+        <v>other sheep</v>
+      </c>
+      <c r="D352" s="97" t="str">
+        <f>D351</f>
+        <v>lambs</v>
+      </c>
+      <c r="E352" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F352" s="97" t="str">
+        <f>F351</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G352" s="99">
+        <f>G351</f>
+        <v>0.79239853966713902</v>
+      </c>
+      <c r="I352" s="97" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="353" spans="3:7" x14ac:dyDescent="0.25">
@@ -8395,14 +8503,14 @@
         <v>205</v>
       </c>
       <c r="E353" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F353" t="s">
         <v>285</v>
       </c>
       <c r="G353" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E353,'feed rations'!$Y$13:$Y$46,0),MATCH(C353&amp;D353,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.9262867400799252E-2</v>
+        <v>4.6511184632405684E-3</v>
       </c>
     </row>
     <row r="354" spans="3:7" x14ac:dyDescent="0.25">
@@ -8413,14 +8521,14 @@
         <v>205</v>
       </c>
       <c r="E354" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F354" t="s">
         <v>285</v>
       </c>
       <c r="G354" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E354,'feed rations'!$Y$13:$Y$46,0),MATCH(C354&amp;D354,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>1.3350746975688711E-2</v>
       </c>
     </row>
     <row r="355" spans="3:7" x14ac:dyDescent="0.25">
@@ -8431,14 +8539,14 @@
         <v>205</v>
       </c>
       <c r="E355" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F355" t="s">
         <v>285</v>
       </c>
       <c r="G355" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E355,'feed rations'!$Y$13:$Y$46,0),MATCH(C355&amp;D355,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.7779896686803802E-4</v>
+        <v>0.10289578308767665</v>
       </c>
     </row>
     <row r="356" spans="3:7" x14ac:dyDescent="0.25">
@@ -8449,14 +8557,14 @@
         <v>205</v>
       </c>
       <c r="E356" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="F356" t="s">
         <v>285</v>
       </c>
       <c r="G356" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E356,'feed rations'!$Y$13:$Y$46,0),MATCH(C356&amp;D356,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.5913900412465971E-2</v>
+        <v>0.61446052117016126</v>
       </c>
     </row>
     <row r="357" spans="3:7" x14ac:dyDescent="0.25">
@@ -8467,14 +8575,14 @@
         <v>205</v>
       </c>
       <c r="E357" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="F357" t="s">
         <v>285</v>
       </c>
       <c r="G357" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E357,'feed rations'!$Y$13:$Y$46,0),MATCH(C357&amp;D357,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.23311756334422978</v>
+        <v>0.12660167619678325</v>
       </c>
     </row>
     <row r="358" spans="3:7" x14ac:dyDescent="0.25">
@@ -8485,14 +8593,14 @@
         <v>205</v>
       </c>
       <c r="E358" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F358" t="s">
         <v>285</v>
       </c>
       <c r="G358" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E358,'feed rations'!$Y$13:$Y$46,0),MATCH(C358&amp;D358,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
+        <v>0.13555393203476143</v>
       </c>
     </row>
     <row r="359" spans="3:7" x14ac:dyDescent="0.25">
@@ -8503,14 +8611,14 @@
         <v>205</v>
       </c>
       <c r="E359" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F359" t="s">
         <v>285</v>
       </c>
       <c r="G359" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E359,'feed rations'!$Y$13:$Y$46,0),MATCH(C359&amp;D359,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8008560088857437E-4</v>
+        <v>3.7665217689123641E-2</v>
       </c>
     </row>
     <row r="360" spans="3:7" x14ac:dyDescent="0.25">
@@ -8521,13 +8629,157 @@
         <v>205</v>
       </c>
       <c r="E360" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="F360" t="s">
         <v>285</v>
       </c>
       <c r="G360" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E360,'feed rations'!$Y$13:$Y$46,0),MATCH(C360&amp;D360,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C361" t="s">
+        <v>204</v>
+      </c>
+      <c r="D361" t="s">
+        <v>205</v>
+      </c>
+      <c r="E361" t="s">
+        <v>252</v>
+      </c>
+      <c r="F361" t="s">
+        <v>285</v>
+      </c>
+      <c r="G361" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E361,'feed rations'!$Y$13:$Y$46,0),MATCH(C361&amp;D361,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>5.9262867400799252E-2</v>
+      </c>
+    </row>
+    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C362" t="s">
+        <v>204</v>
+      </c>
+      <c r="D362" t="s">
+        <v>205</v>
+      </c>
+      <c r="E362" t="s">
+        <v>253</v>
+      </c>
+      <c r="F362" t="s">
+        <v>285</v>
+      </c>
+      <c r="G362" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E362,'feed rations'!$Y$13:$Y$46,0),MATCH(C362&amp;D362,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C363" t="s">
+        <v>204</v>
+      </c>
+      <c r="D363" t="s">
+        <v>205</v>
+      </c>
+      <c r="E363" t="s">
+        <v>254</v>
+      </c>
+      <c r="F363" t="s">
+        <v>285</v>
+      </c>
+      <c r="G363" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E363,'feed rations'!$Y$13:$Y$46,0),MATCH(C363&amp;D363,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>5.7779896686803802E-4</v>
+      </c>
+    </row>
+    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C364" t="s">
+        <v>204</v>
+      </c>
+      <c r="D364" t="s">
+        <v>205</v>
+      </c>
+      <c r="E364" t="s">
+        <v>255</v>
+      </c>
+      <c r="F364" t="s">
+        <v>285</v>
+      </c>
+      <c r="G364" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E364,'feed rations'!$Y$13:$Y$46,0),MATCH(C364&amp;D364,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>7.5913900412465971E-2</v>
+      </c>
+    </row>
+    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C365" t="s">
+        <v>204</v>
+      </c>
+      <c r="D365" t="s">
+        <v>205</v>
+      </c>
+      <c r="E365" t="s">
+        <v>256</v>
+      </c>
+      <c r="F365" t="s">
+        <v>285</v>
+      </c>
+      <c r="G365" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E365,'feed rations'!$Y$13:$Y$46,0),MATCH(C365&amp;D365,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0.23311756334422978</v>
+      </c>
+    </row>
+    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C366" t="s">
+        <v>204</v>
+      </c>
+      <c r="D366" t="s">
+        <v>205</v>
+      </c>
+      <c r="E366" t="s">
+        <v>257</v>
+      </c>
+      <c r="F366" t="s">
+        <v>285</v>
+      </c>
+      <c r="G366" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E366,'feed rations'!$Y$13:$Y$46,0),MATCH(C366&amp;D366,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C367" t="s">
+        <v>204</v>
+      </c>
+      <c r="D367" t="s">
+        <v>205</v>
+      </c>
+      <c r="E367" t="s">
+        <v>258</v>
+      </c>
+      <c r="F367" t="s">
+        <v>285</v>
+      </c>
+      <c r="G367" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E367,'feed rations'!$Y$13:$Y$46,0),MATCH(C367&amp;D367,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>2.8008560088857437E-4</v>
+      </c>
+    </row>
+    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C368" t="s">
+        <v>204</v>
+      </c>
+      <c r="D368" t="s">
+        <v>205</v>
+      </c>
+      <c r="E368" t="s">
+        <v>259</v>
+      </c>
+      <c r="F368" t="s">
+        <v>285</v>
+      </c>
+      <c r="G368" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E368,'feed rations'!$Y$13:$Y$46,0),MATCH(C368&amp;D368,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>

--- a/data/default/SheepHerd.xlsx
+++ b/data/default/SheepHerd.xlsx
@@ -610,7 +610,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="307">
   <si>
     <t>Slakt av större lantbruksdjur vid slakteri efter Djurslag, Tabelluppgift och Månad</t>
   </si>
@@ -1518,6 +1518,21 @@
   </si>
   <si>
     <t>rapeseed cake for organic rations</t>
+  </si>
+  <si>
+    <t>birth_weight</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>live_weight_per_CW</t>
+  </si>
+  <si>
+    <t>kg LW/kg CW</t>
+  </si>
+  <si>
+    <t>assumed same as rams</t>
   </si>
 </sst>
 </file>
@@ -2890,7 +2905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J368"/>
+  <dimension ref="A1:J385"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -3168,37 +3183,34 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
+        <v>302</v>
+      </c>
+      <c r="G19" s="89">
+        <v>5</v>
+      </c>
+      <c r="H19" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G20" s="89"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
         <v>220</v>
       </c>
-      <c r="G19" s="93">
+      <c r="G21" s="93">
         <f>1/(4.5-1)*100</f>
         <v>28.571428571428569</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H21" t="s">
         <v>200</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I21" t="s">
         <v>221</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J21" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G20" s="89"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F21" t="s">
-        <v>217</v>
-      </c>
-      <c r="G21" s="89">
-        <v>12</v>
-      </c>
-      <c r="H21" t="s">
-        <v>216</v>
-      </c>
-      <c r="I21" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -3206,84 +3218,58 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F23" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G23" s="89">
-        <v>2.5000000000000001E-2</v>
+        <v>12</v>
       </c>
       <c r="H23" t="s">
-        <v>212</v>
-      </c>
-      <c r="J23" t="s">
-        <v>223</v>
+        <v>216</v>
+      </c>
+      <c r="I23" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G24" s="89"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="44" t="s">
-        <v>226</v>
-      </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="94"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
+      <c r="F25" t="s">
+        <v>213</v>
+      </c>
+      <c r="G25" s="89">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H25" t="s">
+        <v>212</v>
+      </c>
+      <c r="J25" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G26" s="89"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C27" t="s">
-        <v>196</v>
-      </c>
-      <c r="D27" t="s">
-        <v>201</v>
-      </c>
-      <c r="F27" t="s">
-        <v>202</v>
-      </c>
-      <c r="G27" s="89">
-        <v>3</v>
-      </c>
-      <c r="H27" t="s">
-        <v>200</v>
-      </c>
-      <c r="I27" t="s">
-        <v>214</v>
-      </c>
-      <c r="J27" t="s">
-        <v>222</v>
-      </c>
+      <c r="A27" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="94"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
-        <v>197</v>
-      </c>
-      <c r="D28" t="s">
-        <v>201</v>
-      </c>
-      <c r="F28" t="s">
-        <v>202</v>
-      </c>
-      <c r="G28" s="89">
-        <v>2</v>
-      </c>
-      <c r="H28" t="s">
-        <v>200</v>
-      </c>
-      <c r="J28" t="s">
-        <v>222</v>
-      </c>
+      <c r="G28" s="89"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D29" t="s">
         <v>201</v>
@@ -3297,13 +3283,16 @@
       <c r="H29" t="s">
         <v>200</v>
       </c>
+      <c r="I29" t="s">
+        <v>214</v>
+      </c>
       <c r="J29" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D30" t="s">
         <v>201</v>
@@ -3312,21 +3301,41 @@
         <v>202</v>
       </c>
       <c r="G30" s="89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" t="s">
         <v>200</v>
       </c>
-      <c r="I30" t="s">
-        <v>290</v>
+      <c r="J30" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G31" s="89"/>
+      <c r="C31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" t="s">
+        <v>201</v>
+      </c>
+      <c r="F31" t="s">
+        <v>202</v>
+      </c>
+      <c r="G31" s="89">
+        <v>3</v>
+      </c>
+      <c r="H31" t="s">
+        <v>200</v>
+      </c>
+      <c r="J31" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>204</v>
+      </c>
       <c r="D32" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F32" t="s">
         <v>202</v>
@@ -3338,257 +3347,237 @@
         <v>200</v>
       </c>
       <c r="I32" t="s">
-        <v>228</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G33" s="89"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
-        <v>196</v>
-      </c>
       <c r="D34" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="F34" t="s">
         <v>202</v>
       </c>
-      <c r="G34" s="95">
+      <c r="G34" s="89">
+        <v>3</v>
+      </c>
+      <c r="H34" t="s">
+        <v>200</v>
+      </c>
+      <c r="I34" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G35" s="89"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" t="s">
+        <v>205</v>
+      </c>
+      <c r="F36" t="s">
+        <v>202</v>
+      </c>
+      <c r="G36" s="95">
         <f>(11+9+11)/3</f>
         <v>10.333333333333334</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H36" t="s">
         <v>200</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I36" t="s">
         <v>215</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J36" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C35" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
         <v>197</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D37" t="s">
         <v>205</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F37" t="s">
         <v>202</v>
       </c>
-      <c r="G35" s="89">
+      <c r="G37" s="89">
         <v>9</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H37" t="s">
         <v>200</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J37" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C36" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
         <v>198</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D38" t="s">
         <v>205</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F38" t="s">
         <v>202</v>
       </c>
-      <c r="G36" s="95">
+      <c r="G38" s="95">
         <f>(11+11+14)/3</f>
         <v>12</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H38" t="s">
         <v>200</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J38" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C37" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
         <v>204</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D39" t="s">
         <v>205</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F39" t="s">
         <v>202</v>
       </c>
-      <c r="G37" s="89">
+      <c r="G39" s="89">
         <v>10</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H39" t="s">
         <v>200</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I39" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G38" s="89"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="44" t="s">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G40" s="89"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="44" t="s">
         <v>296</v>
       </c>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="94"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="46"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B41" s="44"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="46"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>297</v>
       </c>
-      <c r="G40" s="89"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C41" t="s">
+      <c r="G42" s="89"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
         <v>196</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F43" t="s">
         <v>294</v>
       </c>
-      <c r="G41" s="89">
+      <c r="G43" s="89">
         <f>30*1.1</f>
         <v>33</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H43" t="s">
         <v>200</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I43" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C42" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
         <v>197</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F44" t="s">
         <v>294</v>
       </c>
-      <c r="G42" s="95">
+      <c r="G44" s="95">
         <f>18</f>
         <v>18</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H44" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C43" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
         <v>198</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F45" t="s">
         <v>294</v>
       </c>
-      <c r="G43" s="95">
+      <c r="G45" s="95">
         <f>13*1.1</f>
         <v>14.3</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H45" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C44" t="s">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
         <v>204</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F46" t="s">
         <v>294</v>
       </c>
-      <c r="G44" s="95">
+      <c r="G46" s="95">
         <f>39*1.1</f>
         <v>42.900000000000006</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H46" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G45" s="89"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="94"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="46"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G47" s="89"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C48" t="s">
+      <c r="A48" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="94"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="46"/>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G49" s="89"/>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
         <v>196</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D50" t="s">
         <v>205</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F50" t="s">
         <v>209</v>
       </c>
-      <c r="G48" s="89">
+      <c r="G50" s="89">
         <f>(160+181+163)/3</f>
         <v>168</v>
       </c>
-      <c r="H48" t="s">
-        <v>210</v>
-      </c>
-      <c r="J48" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C49" t="s">
-        <v>197</v>
-      </c>
-      <c r="D49" t="s">
-        <v>205</v>
-      </c>
-      <c r="F49" t="s">
-        <v>209</v>
-      </c>
-      <c r="G49" s="89">
-        <v>113</v>
-      </c>
-      <c r="H49" t="s">
-        <v>210</v>
-      </c>
-      <c r="J49" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C50" t="s">
-        <v>198</v>
-      </c>
-      <c r="D50" t="s">
-        <v>205</v>
-      </c>
-      <c r="F50" t="s">
-        <v>209</v>
-      </c>
-      <c r="G50" s="89">
-        <v>308</v>
-      </c>
       <c r="H50" t="s">
         <v>210</v>
       </c>
@@ -3598,7 +3587,7 @@
     </row>
     <row r="51" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D51" t="s">
         <v>205</v>
@@ -3607,62 +3596,61 @@
         <v>209</v>
       </c>
       <c r="G51" s="89">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="H51" t="s">
         <v>210</v>
       </c>
-      <c r="I51" t="s">
-        <v>290</v>
+      <c r="J51" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="G52" s="89"/>
+      <c r="C52" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" t="s">
+        <v>205</v>
+      </c>
+      <c r="F52" t="s">
+        <v>209</v>
+      </c>
+      <c r="G52" s="89">
+        <v>308</v>
+      </c>
+      <c r="H52" t="s">
+        <v>210</v>
+      </c>
+      <c r="J52" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D53" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F53" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G53" s="89">
-        <f>(30+27+30)/3</f>
-        <v>29</v>
+        <v>168</v>
       </c>
       <c r="H53" t="s">
-        <v>208</v>
-      </c>
-      <c r="J53" t="s">
-        <v>225</v>
+        <v>210</v>
+      </c>
+      <c r="I53" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="54" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C54" t="s">
-        <v>197</v>
-      </c>
-      <c r="D54" t="s">
-        <v>201</v>
-      </c>
-      <c r="F54" t="s">
-        <v>206</v>
-      </c>
-      <c r="G54" s="89">
-        <v>33</v>
-      </c>
-      <c r="H54" t="s">
-        <v>208</v>
-      </c>
-      <c r="J54" t="s">
-        <v>225</v>
-      </c>
+      <c r="G54" s="89"/>
     </row>
     <row r="55" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D55" t="s">
         <v>201</v>
@@ -3683,7 +3671,7 @@
     </row>
     <row r="56" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D56" t="s">
         <v>201</v>
@@ -3692,61 +3680,62 @@
         <v>206</v>
       </c>
       <c r="G56" s="89">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H56" t="s">
         <v>208</v>
       </c>
-      <c r="I56" t="s">
-        <v>290</v>
+      <c r="J56" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="57" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="G57" s="89"/>
+      <c r="C57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D57" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" t="s">
+        <v>206</v>
+      </c>
+      <c r="G57" s="89">
+        <f>(30+27+30)/3</f>
+        <v>29</v>
+      </c>
+      <c r="H57" t="s">
+        <v>208</v>
+      </c>
+      <c r="J57" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="58" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D58" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F58" t="s">
         <v>206</v>
       </c>
       <c r="G58" s="89">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H58" t="s">
         <v>208</v>
       </c>
-      <c r="J58" t="s">
-        <v>223</v>
+      <c r="I58" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="59" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C59" t="s">
-        <v>197</v>
-      </c>
-      <c r="D59" t="s">
-        <v>219</v>
-      </c>
-      <c r="F59" t="s">
-        <v>206</v>
-      </c>
-      <c r="G59" s="89">
-        <v>48</v>
-      </c>
-      <c r="H59" t="s">
-        <v>208</v>
-      </c>
-      <c r="J59" t="s">
-        <v>223</v>
-      </c>
+      <c r="G59" s="89"/>
     </row>
     <row r="60" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D60" t="s">
         <v>219</v>
@@ -3766,7 +3755,7 @@
     </row>
     <row r="61" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D61" t="s">
         <v>219</v>
@@ -3775,62 +3764,61 @@
         <v>206</v>
       </c>
       <c r="G61" s="89">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H61" t="s">
         <v>208</v>
       </c>
-      <c r="I61" t="s">
-        <v>290</v>
+      <c r="J61" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="G62" s="89"/>
+      <c r="C62" t="s">
+        <v>198</v>
+      </c>
+      <c r="D62" t="s">
+        <v>219</v>
+      </c>
+      <c r="F62" t="s">
+        <v>206</v>
+      </c>
+      <c r="G62" s="89">
+        <v>45</v>
+      </c>
+      <c r="H62" t="s">
+        <v>208</v>
+      </c>
+      <c r="J62" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="63" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D63" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="F63" t="s">
         <v>206</v>
       </c>
-      <c r="G63" s="93">
-        <f>(20.2+19.2+20.2)/3</f>
-        <v>19.866666666666664</v>
+      <c r="G63" s="89">
+        <v>45</v>
       </c>
       <c r="H63" t="s">
         <v>208</v>
       </c>
-      <c r="J63" t="s">
-        <v>224</v>
+      <c r="I63" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="64" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C64" t="s">
-        <v>197</v>
-      </c>
-      <c r="D64" t="s">
-        <v>205</v>
-      </c>
-      <c r="F64" t="s">
-        <v>206</v>
-      </c>
-      <c r="G64" s="89">
-        <v>20.5</v>
-      </c>
-      <c r="H64" t="s">
-        <v>208</v>
-      </c>
-      <c r="J64" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G64" s="89"/>
+    </row>
+    <row r="65" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D65" t="s">
         <v>205</v>
@@ -3849,9 +3837,9 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D66" t="s">
         <v>205</v>
@@ -3860,864 +3848,929 @@
         <v>206</v>
       </c>
       <c r="G66" s="89">
-        <v>19.899999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="H66" t="s">
         <v>208</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="67" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>198</v>
+      </c>
+      <c r="D67" t="s">
+        <v>205</v>
+      </c>
+      <c r="F67" t="s">
+        <v>206</v>
+      </c>
+      <c r="G67" s="93">
+        <f>(20.2+19.2+20.2)/3</f>
+        <v>19.866666666666664</v>
+      </c>
+      <c r="H67" t="s">
+        <v>208</v>
+      </c>
+      <c r="J67" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="68" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
+        <v>204</v>
+      </c>
+      <c r="D68" t="s">
+        <v>205</v>
+      </c>
+      <c r="F68" t="s">
+        <v>206</v>
+      </c>
+      <c r="G68" s="89">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H68" t="s">
+        <v>208</v>
+      </c>
+      <c r="I68" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="44" t="s">
-        <v>227</v>
-      </c>
-      <c r="B68" s="44"/>
-      <c r="C68" s="44"/>
-      <c r="D68" s="45"/>
-      <c r="E68" s="45"/>
-      <c r="F68" s="45"/>
-      <c r="G68" s="45"/>
-      <c r="H68" s="45"/>
-      <c r="I68" s="45" t="s">
-        <v>287</v>
-      </c>
-      <c r="J68" s="46"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G69" s="89"/>
+    </row>
+    <row r="70" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>196</v>
       </c>
+      <c r="D70" t="s">
+        <v>201</v>
+      </c>
       <c r="F70" t="s">
+        <v>304</v>
+      </c>
+      <c r="G70" s="93">
+        <f>G75</f>
+        <v>2.2727272727272729</v>
+      </c>
+      <c r="H70" t="s">
+        <v>305</v>
+      </c>
+      <c r="I70" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>197</v>
+      </c>
+      <c r="D71" t="s">
+        <v>201</v>
+      </c>
+      <c r="F71" t="s">
+        <v>304</v>
+      </c>
+      <c r="G71" s="93">
+        <f t="shared" ref="G71:G73" si="0">G76</f>
+        <v>2.0833333333333335</v>
+      </c>
+      <c r="H71" t="s">
+        <v>305</v>
+      </c>
+      <c r="I71" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="72" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
+        <v>198</v>
+      </c>
+      <c r="D72" t="s">
+        <v>201</v>
+      </c>
+      <c r="F72" t="s">
+        <v>304</v>
+      </c>
+      <c r="G72" s="93">
+        <f t="shared" si="0"/>
+        <v>2.2727272727272729</v>
+      </c>
+      <c r="H72" t="s">
+        <v>305</v>
+      </c>
+      <c r="I72" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="73" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>204</v>
+      </c>
+      <c r="D73" t="s">
+        <v>201</v>
+      </c>
+      <c r="F73" t="s">
+        <v>304</v>
+      </c>
+      <c r="G73" s="93">
+        <f t="shared" si="0"/>
+        <v>2.2727272727272729</v>
+      </c>
+      <c r="H73" t="s">
+        <v>305</v>
+      </c>
+      <c r="I73" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="74" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G74" s="89"/>
+    </row>
+    <row r="75" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>196</v>
+      </c>
+      <c r="D75" t="s">
+        <v>219</v>
+      </c>
+      <c r="F75" t="s">
+        <v>304</v>
+      </c>
+      <c r="G75" s="93">
+        <f>1/0.44</f>
+        <v>2.2727272727272729</v>
+      </c>
+      <c r="H75" t="s">
+        <v>305</v>
+      </c>
+      <c r="J75" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>197</v>
+      </c>
+      <c r="D76" t="s">
+        <v>219</v>
+      </c>
+      <c r="F76" t="s">
+        <v>304</v>
+      </c>
+      <c r="G76" s="93">
+        <f>1/0.48</f>
+        <v>2.0833333333333335</v>
+      </c>
+      <c r="H76" t="s">
+        <v>305</v>
+      </c>
+      <c r="J76" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="77" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>198</v>
+      </c>
+      <c r="D77" t="s">
+        <v>219</v>
+      </c>
+      <c r="F77" t="s">
+        <v>304</v>
+      </c>
+      <c r="G77" s="93">
+        <f>1/0.44</f>
+        <v>2.2727272727272729</v>
+      </c>
+      <c r="H77" t="s">
+        <v>305</v>
+      </c>
+      <c r="J77" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="78" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
+        <v>204</v>
+      </c>
+      <c r="D78" t="s">
+        <v>219</v>
+      </c>
+      <c r="F78" t="s">
+        <v>304</v>
+      </c>
+      <c r="G78" s="93">
+        <f>G75</f>
+        <v>2.2727272727272729</v>
+      </c>
+      <c r="H78" t="s">
+        <v>305</v>
+      </c>
+      <c r="I78" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="79" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G79" s="89"/>
+    </row>
+    <row r="80" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>196</v>
+      </c>
+      <c r="D80" t="s">
+        <v>205</v>
+      </c>
+      <c r="F80" t="s">
+        <v>304</v>
+      </c>
+      <c r="G80" s="93">
+        <f>1/0.43</f>
+        <v>2.3255813953488373</v>
+      </c>
+      <c r="H80" t="s">
+        <v>305</v>
+      </c>
+      <c r="J80" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>197</v>
+      </c>
+      <c r="D81" t="s">
+        <v>205</v>
+      </c>
+      <c r="F81" t="s">
+        <v>304</v>
+      </c>
+      <c r="G81" s="93">
+        <f>1/0.45</f>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="H81" t="s">
+        <v>305</v>
+      </c>
+      <c r="J81" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
+        <v>198</v>
+      </c>
+      <c r="D82" t="s">
+        <v>205</v>
+      </c>
+      <c r="F82" t="s">
+        <v>304</v>
+      </c>
+      <c r="G82" s="93">
+        <f>1/0.42</f>
+        <v>2.3809523809523809</v>
+      </c>
+      <c r="H82" t="s">
+        <v>305</v>
+      </c>
+      <c r="J82" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C83" t="s">
+        <v>204</v>
+      </c>
+      <c r="D83" t="s">
+        <v>205</v>
+      </c>
+      <c r="F83" t="s">
+        <v>304</v>
+      </c>
+      <c r="G83" s="93">
+        <f>G80</f>
+        <v>2.3255813953488373</v>
+      </c>
+      <c r="H83" t="s">
+        <v>305</v>
+      </c>
+      <c r="I83" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G84" s="89"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="B85" s="44"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="45"/>
+      <c r="E85" s="45"/>
+      <c r="F85" s="45"/>
+      <c r="G85" s="45"/>
+      <c r="H85" s="45"/>
+      <c r="I85" s="45" t="s">
+        <v>287</v>
+      </c>
+      <c r="J85" s="46"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>196</v>
+      </c>
+      <c r="F87" t="s">
         <v>292</v>
       </c>
-      <c r="G70" s="19">
+      <c r="G87" s="19">
         <f>'feed rations'!G5</f>
         <v>748.40000000000009</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H87" t="s">
         <v>279</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J87" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C71" t="s">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C88" t="s">
         <v>197</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F88" t="s">
         <v>292</v>
       </c>
-      <c r="G71" s="19">
+      <c r="G88" s="19">
         <f>'feed rations'!G6</f>
         <v>554.1</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H88" t="s">
         <v>279</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J88" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C72" t="s">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
         <v>198</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F89" t="s">
         <v>292</v>
       </c>
-      <c r="G72" s="19">
+      <c r="G89" s="19">
         <f>'feed rations'!G7</f>
         <v>726.26666666666654</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H89" t="s">
         <v>279</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J89" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C73" t="s">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C90" t="s">
         <v>204</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F90" t="s">
         <v>292</v>
       </c>
-      <c r="G73" s="19">
+      <c r="G90" s="19">
         <f>'feed rations'!G8</f>
         <v>748.40000000000009</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H90" t="s">
         <v>279</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I90" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C75" t="s">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C92" t="s">
         <v>196</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D92" t="s">
         <v>205</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F92" t="s">
         <v>293</v>
       </c>
-      <c r="G75" s="19">
+      <c r="G92" s="19">
         <f>'feed rations'!N5</f>
         <v>157.56666666666666</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H92" t="s">
         <v>279</v>
       </c>
-      <c r="J75" t="s">
+      <c r="J92" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C76" t="s">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C93" t="s">
         <v>197</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D93" t="s">
         <v>205</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F93" t="s">
         <v>293</v>
       </c>
-      <c r="G76" s="19">
+      <c r="G93" s="19">
         <f>'feed rations'!N6</f>
         <v>114</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H93" t="s">
         <v>279</v>
       </c>
-      <c r="J76" t="s">
+      <c r="J93" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C77" t="s">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C94" t="s">
         <v>198</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D94" t="s">
         <v>205</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F94" t="s">
         <v>293</v>
       </c>
-      <c r="G77" s="19">
+      <c r="G94" s="19">
         <f>'feed rations'!N7</f>
         <v>254.56666666666669</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H94" t="s">
         <v>279</v>
       </c>
-      <c r="J77" t="s">
+      <c r="J94" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C78" t="s">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
         <v>204</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D95" t="s">
         <v>205</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F95" t="s">
         <v>293</v>
       </c>
-      <c r="G78" s="19">
+      <c r="G95" s="19">
         <f>'feed rations'!N8</f>
         <v>157.56666666666666</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H95" t="s">
         <v>279</v>
       </c>
-      <c r="I78" t="s">
+      <c r="I95" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="44" t="s">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="44" t="s">
         <v>281</v>
       </c>
-      <c r="B80" s="44"/>
-      <c r="C80" s="44"/>
-      <c r="D80" s="45"/>
-      <c r="E80" s="45"/>
-      <c r="F80" s="45"/>
-      <c r="G80" s="45"/>
-      <c r="H80" s="45" t="s">
+      <c r="B97" s="44"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="45"/>
+      <c r="E97" s="45"/>
+      <c r="F97" s="45"/>
+      <c r="G97" s="45"/>
+      <c r="H97" s="45" t="s">
         <v>266</v>
       </c>
-      <c r="I80" s="45" t="s">
+      <c r="I97" s="45" t="s">
         <v>287</v>
       </c>
-      <c r="J80" s="46"/>
-    </row>
-    <row r="81" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="F81" s="91" t="s">
-        <v>285</v>
-      </c>
-      <c r="G81" s="91">
+      <c r="J97" s="46"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F98" s="91" t="s">
+        <v>285</v>
+      </c>
+      <c r="G98" s="91">
         <v>0</v>
       </c>
-      <c r="H81" s="91"/>
-      <c r="I81" s="91" t="s">
+      <c r="H98" s="91"/>
+      <c r="I98" s="91" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="82" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C82" t="s">
-        <v>196</v>
-      </c>
-      <c r="E82" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F82" t="s">
-        <v>285</v>
-      </c>
-      <c r="G82" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E82,'feed rations'!$Y$13:$Y$46,0),MATCH(C82&amp;D82,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>14.502048815250316</v>
-      </c>
-    </row>
-    <row r="83" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C83" t="s">
-        <v>196</v>
-      </c>
-      <c r="E83" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="F83" t="s">
-        <v>285</v>
-      </c>
-      <c r="G83" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E83,'feed rations'!$Y$13:$Y$46,0),MATCH(C83&amp;D83,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>29.004097630500631</v>
-      </c>
-    </row>
-    <row r="84" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C84" t="s">
-        <v>196</v>
-      </c>
-      <c r="E84" t="s">
-        <v>277</v>
-      </c>
-      <c r="F84" t="s">
-        <v>285</v>
-      </c>
-      <c r="G84" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E84,'feed rations'!$Y$13:$Y$46,0),MATCH(C84&amp;D84,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>52.618920363442022</v>
-      </c>
-    </row>
-    <row r="85" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C85" t="s">
-        <v>196</v>
-      </c>
-      <c r="E85" t="s">
-        <v>229</v>
-      </c>
-      <c r="F85" t="s">
-        <v>285</v>
-      </c>
-      <c r="G85" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E85,'feed rations'!$Y$13:$Y$46,0),MATCH(C85&amp;D85,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.84682253603719471</v>
-      </c>
-    </row>
-    <row r="86" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C86" t="s">
-        <v>196</v>
-      </c>
-      <c r="E86" t="s">
-        <v>230</v>
-      </c>
-      <c r="F86" t="s">
-        <v>285</v>
-      </c>
-      <c r="G86" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E86,'feed rations'!$Y$13:$Y$46,0),MATCH(C86&amp;D86,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.43737940455400331</v>
-      </c>
-    </row>
-    <row r="87" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C87" t="s">
-        <v>196</v>
-      </c>
-      <c r="E87" t="s">
-        <v>231</v>
-      </c>
-      <c r="F87" t="s">
-        <v>285</v>
-      </c>
-      <c r="G87" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E87,'feed rations'!$Y$13:$Y$46,0),MATCH(C87&amp;D87,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.66303507614130686</v>
-      </c>
-    </row>
-    <row r="88" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C88" t="s">
-        <v>196</v>
-      </c>
-      <c r="E88" t="s">
-        <v>232</v>
-      </c>
-      <c r="F88" t="s">
-        <v>285</v>
-      </c>
-      <c r="G88" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E88,'feed rations'!$Y$13:$Y$46,0),MATCH(C88&amp;D88,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.0988815290634705E-3</v>
-      </c>
-    </row>
-    <row r="89" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C89" t="s">
-        <v>196</v>
-      </c>
-      <c r="E89" t="s">
-        <v>233</v>
-      </c>
-      <c r="F89" t="s">
-        <v>285</v>
-      </c>
-      <c r="G89" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E89,'feed rations'!$Y$13:$Y$46,0),MATCH(C89&amp;D89,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C90" t="s">
-        <v>196</v>
-      </c>
-      <c r="E90" t="s">
-        <v>234</v>
-      </c>
-      <c r="F90" t="s">
-        <v>285</v>
-      </c>
-      <c r="G90" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E90,'feed rations'!$Y$13:$Y$46,0),MATCH(C90&amp;D90,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.17270238081001552</v>
-      </c>
-    </row>
-    <row r="91" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C91" t="s">
-        <v>196</v>
-      </c>
-      <c r="E91" t="s">
-        <v>235</v>
-      </c>
-      <c r="F91" t="s">
-        <v>285</v>
-      </c>
-      <c r="G91" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E91,'feed rations'!$Y$13:$Y$46,0),MATCH(C91&amp;D91,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7776312249885764E-3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C92" t="s">
-        <v>196</v>
-      </c>
-      <c r="E92" t="s">
-        <v>236</v>
-      </c>
-      <c r="F92" t="s">
-        <v>285</v>
-      </c>
-      <c r="G92" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E92,'feed rations'!$Y$13:$Y$46,0),MATCH(C92&amp;D92,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3699111545736139E-2</v>
-      </c>
-    </row>
-    <row r="93" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C93" t="s">
-        <v>196</v>
-      </c>
-      <c r="E93" t="s">
-        <v>237</v>
-      </c>
-      <c r="F93" t="s">
-        <v>285</v>
-      </c>
-      <c r="G93" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E93,'feed rations'!$Y$13:$Y$46,0),MATCH(C93&amp;D93,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.45638940058232602</v>
-      </c>
-    </row>
-    <row r="94" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C94" t="s">
-        <v>196</v>
-      </c>
-      <c r="E94" t="s">
-        <v>238</v>
-      </c>
-      <c r="F94" t="s">
-        <v>285</v>
-      </c>
-      <c r="G94" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E94,'feed rations'!$Y$13:$Y$46,0),MATCH(C94&amp;D94,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.1509220070385851E-4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C95" t="s">
-        <v>196</v>
-      </c>
-      <c r="E95" t="s">
-        <v>239</v>
-      </c>
-      <c r="F95" t="s">
-        <v>285</v>
-      </c>
-      <c r="G95" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E95,'feed rations'!$Y$13:$Y$46,0),MATCH(C95&amp;D95,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.19248525926546745</v>
-      </c>
-    </row>
-    <row r="96" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C96" t="s">
-        <v>196</v>
-      </c>
-      <c r="E96" t="s">
-        <v>240</v>
-      </c>
-      <c r="F96" t="s">
-        <v>285</v>
-      </c>
-      <c r="G96" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E96,'feed rations'!$Y$13:$Y$46,0),MATCH(C96&amp;D96,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1540482816582413E-5</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C97" t="s">
-        <v>196</v>
-      </c>
-      <c r="E97" t="s">
-        <v>241</v>
-      </c>
-      <c r="F97" t="s">
-        <v>285</v>
-      </c>
-      <c r="G97" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E97,'feed rations'!$Y$13:$Y$46,0),MATCH(C97&amp;D97,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.49074140742335415</v>
-      </c>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C98" t="s">
-        <v>196</v>
-      </c>
-      <c r="E98" t="s">
-        <v>242</v>
-      </c>
-      <c r="F98" t="s">
-        <v>285</v>
-      </c>
-      <c r="G98" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E98,'feed rations'!$Y$13:$Y$46,0),MATCH(C98&amp;D98,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.938643453492417E-5</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B99" t="s">
-        <v>300</v>
-      </c>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C99" t="s">
         <v>196</v>
       </c>
-      <c r="E99" t="s">
-        <v>243</v>
+      <c r="E99" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F99" t="s">
         <v>285</v>
       </c>
       <c r="G99" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E99,'feed rations'!$Y$13:$Y$46,0),MATCH(C99&amp;D99,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.21035091095436523</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B100" s="98" t="s">
-        <v>299</v>
-      </c>
-      <c r="C100" s="97" t="str">
-        <f>C99</f>
-        <v>autumn lamb</v>
-      </c>
-      <c r="E100" s="97" t="s">
-        <v>298</v>
-      </c>
-      <c r="F100" s="97" t="str">
-        <f>F99</f>
-        <v>share_in_ration</v>
-      </c>
-      <c r="G100" s="99">
-        <f>G99</f>
-        <v>0.21035091095436523</v>
-      </c>
-      <c r="I100" s="97" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+        <v>14.502048815250316</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C100" t="s">
+        <v>196</v>
+      </c>
+      <c r="E100" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="F100" t="s">
+        <v>285</v>
+      </c>
+      <c r="G100" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E100,'feed rations'!$Y$13:$Y$46,0),MATCH(C100&amp;D100,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>29.004097630500631</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C101" t="s">
         <v>196</v>
       </c>
       <c r="E101" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F101" t="s">
         <v>285</v>
       </c>
       <c r="G101" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E101,'feed rations'!$Y$13:$Y$46,0),MATCH(C101&amp;D101,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2346905713762435E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+        <v>52.618920363442022</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C102" t="s">
         <v>196</v>
       </c>
       <c r="E102" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F102" t="s">
         <v>285</v>
       </c>
       <c r="G102" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E102,'feed rations'!$Y$13:$Y$46,0),MATCH(C102&amp;D102,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5441026802460426E-3</v>
-      </c>
-    </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.84682253603719471</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C103" t="s">
         <v>196</v>
       </c>
       <c r="E103" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="F103" t="s">
         <v>285</v>
       </c>
       <c r="G103" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E103,'feed rations'!$Y$13:$Y$46,0),MATCH(C103&amp;D103,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.7314817761965576E-2</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.43737940455400331</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C104" t="s">
         <v>196</v>
       </c>
       <c r="E104" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F104" t="s">
         <v>285</v>
       </c>
       <c r="G104" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E104,'feed rations'!$Y$13:$Y$46,0),MATCH(C104&amp;D104,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.16311530612857034</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.66303507614130686</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C105" t="s">
         <v>196</v>
       </c>
       <c r="E105" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F105" t="s">
         <v>285</v>
       </c>
       <c r="G105" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E105,'feed rations'!$Y$13:$Y$46,0),MATCH(C105&amp;D105,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.3607807918891001E-2</v>
-      </c>
-    </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+        <v>4.0988815290634705E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C106" t="s">
         <v>196</v>
       </c>
       <c r="E106" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F106" t="s">
         <v>285</v>
       </c>
       <c r="G106" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E106,'feed rations'!$Y$13:$Y$46,0),MATCH(C106&amp;D106,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.598428273092974E-2</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C107" t="s">
         <v>196</v>
       </c>
       <c r="E107" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F107" t="s">
         <v>285</v>
       </c>
       <c r="G107" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E107,'feed rations'!$Y$13:$Y$46,0),MATCH(C107&amp;D107,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.9986464582958335E-3</v>
-      </c>
-    </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.17270238081001552</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C108" t="s">
         <v>196</v>
       </c>
       <c r="E108" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="F108" t="s">
         <v>285</v>
       </c>
       <c r="G108" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E108,'feed rations'!$Y$13:$Y$46,0),MATCH(C108&amp;D108,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+        <v>3.7776312249885764E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C109" t="s">
         <v>196</v>
       </c>
       <c r="E109" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F109" t="s">
         <v>285</v>
       </c>
       <c r="G109" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E109,'feed rations'!$Y$13:$Y$46,0),MATCH(C109&amp;D109,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5731980208800535E-2</v>
-      </c>
-    </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.3699111545736139E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C110" t="s">
         <v>196</v>
       </c>
       <c r="E110" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F110" t="s">
         <v>285</v>
       </c>
       <c r="G110" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E110,'feed rations'!$Y$13:$Y$46,0),MATCH(C110&amp;D110,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.45638940058232602</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C111" t="s">
         <v>196</v>
       </c>
       <c r="E111" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="F111" t="s">
         <v>285</v>
       </c>
       <c r="G111" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E111,'feed rations'!$Y$13:$Y$46,0),MATCH(C111&amp;D111,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5338309315945754E-4</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+        <v>6.1509220070385851E-4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C112" t="s">
         <v>196</v>
       </c>
       <c r="E112" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="F112" t="s">
         <v>285</v>
       </c>
       <c r="G112" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E112,'feed rations'!$Y$13:$Y$46,0),MATCH(C112&amp;D112,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0152180129671942E-2</v>
-      </c>
-    </row>
-    <row r="113" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.19248525926546745</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C113" t="s">
         <v>196</v>
       </c>
       <c r="E113" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="F113" t="s">
         <v>285</v>
       </c>
       <c r="G113" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E113,'feed rations'!$Y$13:$Y$46,0),MATCH(C113&amp;D113,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.188362213479006E-2</v>
-      </c>
-    </row>
-    <row r="114" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.1540482816582413E-5</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C114" t="s">
         <v>196</v>
       </c>
       <c r="E114" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F114" t="s">
         <v>285</v>
       </c>
       <c r="G114" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E114,'feed rations'!$Y$13:$Y$46,0),MATCH(C114&amp;D114,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.49074140742335415</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C115" t="s">
         <v>196</v>
       </c>
       <c r="E115" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F115" t="s">
         <v>285</v>
       </c>
       <c r="G115" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E115,'feed rations'!$Y$13:$Y$46,0),MATCH(C115&amp;D115,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.4351804480686189E-5</v>
-      </c>
-    </row>
-    <row r="116" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.938643453492417E-5</v>
+      </c>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>300</v>
+      </c>
       <c r="C116" t="s">
         <v>196</v>
       </c>
       <c r="E116" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="F116" t="s">
         <v>285</v>
       </c>
       <c r="G116" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E116,'feed rations'!$Y$13:$Y$46,0),MATCH(C116&amp;D116,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.21035091095436523</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B117" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C117" s="97" t="str">
+        <f>C116</f>
+        <v>autumn lamb</v>
+      </c>
+      <c r="E117" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F117" s="97" t="str">
+        <f>F116</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G117" s="99">
+        <f>G116</f>
+        <v>0.21035091095436523</v>
+      </c>
+      <c r="I117" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C118" t="s">
-        <v>197</v>
-      </c>
-      <c r="E118" s="21" t="s">
-        <v>276</v>
+        <v>196</v>
+      </c>
+      <c r="E118" t="s">
+        <v>244</v>
       </c>
       <c r="F118" t="s">
         <v>285</v>
       </c>
       <c r="G118" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E118,'feed rations'!$Y$13:$Y$46,0),MATCH(C118&amp;D118,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>15.175760492490328</v>
-      </c>
-    </row>
-    <row r="119" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.2346905713762435E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C119" t="s">
-        <v>197</v>
-      </c>
-      <c r="E119" s="21" t="s">
-        <v>274</v>
+        <v>196</v>
+      </c>
+      <c r="E119" t="s">
+        <v>245</v>
       </c>
       <c r="F119" t="s">
         <v>285</v>
       </c>
       <c r="G119" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E119,'feed rations'!$Y$13:$Y$46,0),MATCH(C119&amp;D119,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>30.351520984980656</v>
-      </c>
-    </row>
-    <row r="120" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.5441026802460426E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C120" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E120" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="F120" t="s">
         <v>285</v>
       </c>
       <c r="G120" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E120,'feed rations'!$Y$13:$Y$46,0),MATCH(C120&amp;D120,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>43.343560127534147</v>
-      </c>
-    </row>
-    <row r="121" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.7314817761965576E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C121" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E121" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="F121" t="s">
         <v>285</v>
       </c>
       <c r="G121" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E121,'feed rations'!$Y$13:$Y$46,0),MATCH(C121&amp;D121,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4321508712376856</v>
-      </c>
-    </row>
-    <row r="122" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.16311530612857034</v>
+      </c>
+    </row>
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C122" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E122" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F122" t="s">
         <v>285</v>
       </c>
       <c r="G122" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E122,'feed rations'!$Y$13:$Y$46,0),MATCH(C122&amp;D122,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2561931863852942</v>
-      </c>
-    </row>
-    <row r="123" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.3607807918891001E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C123" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E123" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F123" t="s">
         <v>285</v>
       </c>
       <c r="G123" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E123,'feed rations'!$Y$13:$Y$46,0),MATCH(C123&amp;D123,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.9042966731194728</v>
-      </c>
-    </row>
-    <row r="124" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.598428273092974E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C124" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E124" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F124" t="s">
         <v>285</v>
       </c>
       <c r="G124" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E124,'feed rations'!$Y$13:$Y$46,0),MATCH(C124&amp;D124,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.1772358266069939E-2</v>
-      </c>
-    </row>
-    <row r="125" spans="3:7" x14ac:dyDescent="0.25">
+        <v>9.9986464582958335E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C125" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E125" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="F125" t="s">
         <v>285</v>
@@ -4727,533 +4780,533 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C126" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E126" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F126" t="s">
         <v>285</v>
       </c>
       <c r="G126" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E126,'feed rations'!$Y$13:$Y$46,0),MATCH(C126&amp;D126,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.4960168489581302</v>
-      </c>
-    </row>
-    <row r="127" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.5731980208800535E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C127" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E127" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="F127" t="s">
         <v>285</v>
       </c>
       <c r="G127" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E127,'feed rations'!$Y$13:$Y$46,0),MATCH(C127&amp;D127,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.084969835364313E-2</v>
-      </c>
-    </row>
-    <row r="128" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C128" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E128" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F128" t="s">
         <v>285</v>
       </c>
       <c r="G128" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E128,'feed rations'!$Y$13:$Y$46,0),MATCH(C128&amp;D128,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.8065990618593489E-2</v>
-      </c>
-    </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.5338309315945754E-4</v>
+      </c>
+    </row>
+    <row r="129" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C129" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E129" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F129" t="s">
         <v>285</v>
       </c>
       <c r="G129" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E129,'feed rations'!$Y$13:$Y$46,0),MATCH(C129&amp;D129,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.310791613369622</v>
-      </c>
-    </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.0152180129671942E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C130" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E130" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F130" t="s">
         <v>285</v>
       </c>
       <c r="G130" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E130,'feed rations'!$Y$13:$Y$46,0),MATCH(C130&amp;D130,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7666004011112982E-3</v>
-      </c>
-    </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+        <v>6.188362213479006E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C131" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E131" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="F131" t="s">
         <v>285</v>
       </c>
       <c r="G131" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E131,'feed rations'!$Y$13:$Y$46,0),MATCH(C131&amp;D131,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.55283506413716399</v>
-      </c>
-    </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C132" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E132" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="F132" t="s">
         <v>285</v>
       </c>
       <c r="G132" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E132,'feed rations'!$Y$13:$Y$46,0),MATCH(C132&amp;D132,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.1866213781219229E-5</v>
-      </c>
-    </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+        <v>7.4351804480686189E-5</v>
+      </c>
+    </row>
+    <row r="133" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C133" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E133" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="F133" t="s">
         <v>285</v>
       </c>
       <c r="G133" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E133,'feed rations'!$Y$13:$Y$46,0),MATCH(C133&amp;D133,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.4094536822348984</v>
-      </c>
-    </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C134" t="s">
-        <v>197</v>
-      </c>
-      <c r="E134" t="s">
-        <v>242</v>
-      </c>
-      <c r="F134" t="s">
-        <v>285</v>
-      </c>
-      <c r="G134" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E134,'feed rations'!$Y$13:$Y$46,0),MATCH(C134&amp;D134,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.5679592403097307E-5</v>
-      </c>
-    </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B135" t="s">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C135" t="s">
         <v>197</v>
       </c>
-      <c r="E135" t="s">
-        <v>243</v>
+      <c r="E135" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F135" t="s">
         <v>285</v>
       </c>
       <c r="G135" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E135,'feed rations'!$Y$13:$Y$46,0),MATCH(C135&amp;D135,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.60414683073671682</v>
-      </c>
-    </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B136" s="98" t="s">
-        <v>299</v>
-      </c>
-      <c r="C136" s="97" t="str">
-        <f>C135</f>
-        <v>spring lamb</v>
-      </c>
-      <c r="E136" s="97" t="s">
-        <v>298</v>
-      </c>
-      <c r="F136" s="97" t="str">
-        <f>F135</f>
-        <v>share_in_ration</v>
-      </c>
-      <c r="G136" s="99">
-        <f>G135</f>
-        <v>0.60414683073671682</v>
-      </c>
-      <c r="I136" s="97" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+        <v>15.175760492490328</v>
+      </c>
+    </row>
+    <row r="136" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C136" t="s">
+        <v>197</v>
+      </c>
+      <c r="E136" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="F136" t="s">
+        <v>285</v>
+      </c>
+      <c r="G136" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E136,'feed rations'!$Y$13:$Y$46,0),MATCH(C136&amp;D136,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>30.351520984980656</v>
+      </c>
+    </row>
+    <row r="137" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C137" t="s">
         <v>197</v>
       </c>
       <c r="E137" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F137" t="s">
         <v>285</v>
       </c>
       <c r="G137" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E137,'feed rations'!$Y$13:$Y$46,0),MATCH(C137&amp;D137,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5461429297032662E-3</v>
-      </c>
-    </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+        <v>43.343560127534147</v>
+      </c>
+    </row>
+    <row r="138" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C138" t="s">
         <v>197</v>
       </c>
       <c r="E138" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F138" t="s">
         <v>285</v>
       </c>
       <c r="G138" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E138,'feed rations'!$Y$13:$Y$46,0),MATCH(C138&amp;D138,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.0178983263546054E-2</v>
-      </c>
-    </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.4321508712376856</v>
+      </c>
+    </row>
+    <row r="139" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C139" t="s">
         <v>197</v>
       </c>
       <c r="E139" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="F139" t="s">
         <v>285</v>
       </c>
       <c r="G139" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E139,'feed rations'!$Y$13:$Y$46,0),MATCH(C139&amp;D139,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.8450625710019192E-2</v>
-      </c>
-    </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.2561931863852942</v>
+      </c>
+    </row>
+    <row r="140" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
         <v>197</v>
       </c>
       <c r="E140" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F140" t="s">
         <v>285</v>
       </c>
       <c r="G140" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E140,'feed rations'!$Y$13:$Y$46,0),MATCH(C140&amp;D140,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.4684819038582827</v>
-      </c>
-    </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.9042966731194728</v>
+      </c>
+    </row>
+    <row r="141" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C141" t="s">
         <v>197</v>
       </c>
       <c r="E141" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F141" t="s">
         <v>285</v>
       </c>
       <c r="G141" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E141,'feed rations'!$Y$13:$Y$46,0),MATCH(C141&amp;D141,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.6524662289726004E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.1772358266069939E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C142" t="s">
         <v>197</v>
       </c>
       <c r="E142" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F142" t="s">
         <v>285</v>
       </c>
       <c r="G142" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E142,'feed rations'!$Y$13:$Y$46,0),MATCH(C142&amp;D142,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10335011276914095</v>
-      </c>
-    </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C143" t="s">
         <v>197</v>
       </c>
       <c r="E143" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F143" t="s">
         <v>285</v>
       </c>
       <c r="G143" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E143,'feed rations'!$Y$13:$Y$46,0),MATCH(C143&amp;D143,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8717016446612009E-2</v>
-      </c>
-    </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.4960168489581302</v>
+      </c>
+    </row>
+    <row r="144" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C144" t="s">
         <v>197</v>
       </c>
       <c r="E144" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="F144" t="s">
         <v>285</v>
       </c>
       <c r="G144" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E144,'feed rations'!$Y$13:$Y$46,0),MATCH(C144&amp;D144,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.084969835364313E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C145" t="s">
         <v>197</v>
       </c>
       <c r="E145" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F145" t="s">
         <v>285</v>
       </c>
       <c r="G145" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E145,'feed rations'!$Y$13:$Y$46,0),MATCH(C145&amp;D145,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.5183669237455988E-2</v>
-      </c>
-    </row>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.8065990618593489E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C146" t="s">
         <v>197</v>
       </c>
       <c r="E146" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F146" t="s">
         <v>285</v>
       </c>
       <c r="G146" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E146,'feed rations'!$Y$13:$Y$46,0),MATCH(C146&amp;D146,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.310791613369622</v>
+      </c>
+    </row>
+    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C147" t="s">
         <v>197</v>
       </c>
       <c r="E147" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="F147" t="s">
         <v>285</v>
       </c>
       <c r="G147" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E147,'feed rations'!$Y$13:$Y$46,0),MATCH(C147&amp;D147,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.4053010847661285E-4</v>
-      </c>
-    </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.7666004011112982E-3</v>
+      </c>
+    </row>
+    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C148" t="s">
         <v>197</v>
       </c>
       <c r="E148" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="F148" t="s">
         <v>285</v>
       </c>
       <c r="G148" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E148,'feed rations'!$Y$13:$Y$46,0),MATCH(C148&amp;D148,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.7878882970076748E-2</v>
-      </c>
-    </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.55283506413716399</v>
+      </c>
+    </row>
+    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C149" t="s">
         <v>197</v>
       </c>
       <c r="E149" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="F149" t="s">
         <v>285</v>
       </c>
       <c r="G149" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E149,'feed rations'!$Y$13:$Y$46,0),MATCH(C149&amp;D149,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.17773535668382656</v>
-      </c>
-    </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.1866213781219229E-5</v>
+      </c>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C150" t="s">
         <v>197</v>
       </c>
       <c r="E150" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F150" t="s">
         <v>285</v>
       </c>
       <c r="G150" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E150,'feed rations'!$Y$13:$Y$46,0),MATCH(C150&amp;D150,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.4094536822348984</v>
+      </c>
+    </row>
+    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C151" t="s">
         <v>197</v>
       </c>
       <c r="E151" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F151" t="s">
         <v>285</v>
       </c>
       <c r="G151" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E151,'feed rations'!$Y$13:$Y$46,0),MATCH(C151&amp;D151,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1354510343103608E-4</v>
-      </c>
-    </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
+        <v>5.5679592403097307E-5</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>300</v>
+      </c>
       <c r="C152" t="s">
         <v>197</v>
       </c>
       <c r="E152" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="F152" t="s">
         <v>285</v>
       </c>
       <c r="G152" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E152,'feed rations'!$Y$13:$Y$46,0),MATCH(C152&amp;D152,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.60414683073671682</v>
+      </c>
+    </row>
+    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B153" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C153" s="97" t="str">
+        <f>C152</f>
+        <v>spring lamb</v>
+      </c>
+      <c r="E153" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F153" s="97" t="str">
+        <f>F152</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G153" s="99">
+        <f>G152</f>
+        <v>0.60414683073671682</v>
+      </c>
+      <c r="I153" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C154" t="s">
-        <v>198</v>
-      </c>
-      <c r="E154" s="21" t="s">
-        <v>276</v>
+        <v>197</v>
+      </c>
+      <c r="E154" t="s">
+        <v>244</v>
       </c>
       <c r="F154" t="s">
         <v>285</v>
       </c>
       <c r="G154" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E154,'feed rations'!$Y$13:$Y$46,0),MATCH(C154&amp;D154,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>14.556942659567957</v>
-      </c>
-    </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.5461429297032662E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C155" t="s">
-        <v>198</v>
-      </c>
-      <c r="E155" s="21" t="s">
-        <v>274</v>
+        <v>197</v>
+      </c>
+      <c r="E155" t="s">
+        <v>245</v>
       </c>
       <c r="F155" t="s">
         <v>285</v>
       </c>
       <c r="G155" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E155,'feed rations'!$Y$13:$Y$46,0),MATCH(C155&amp;D155,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>29.113885319135914</v>
-      </c>
-    </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.0178983263546054E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C156" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E156" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="F156" t="s">
         <v>285</v>
       </c>
       <c r="G156" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E156,'feed rations'!$Y$13:$Y$46,0),MATCH(C156&amp;D156,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>55.686616486139165</v>
-      </c>
-    </row>
-    <row r="157" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.8450625710019192E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C157" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E157" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="F157" t="s">
         <v>285</v>
       </c>
       <c r="G157" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E157,'feed rations'!$Y$13:$Y$46,0),MATCH(C157&amp;D157,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.14042319726111982</v>
-      </c>
-    </row>
-    <row r="158" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.4684819038582827</v>
+      </c>
+    </row>
+    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C158" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E158" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F158" t="s">
         <v>285</v>
       </c>
       <c r="G158" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E158,'feed rations'!$Y$13:$Y$46,0),MATCH(C158&amp;D158,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.252784590624109E-2</v>
-      </c>
-    </row>
-    <row r="159" spans="3:7" x14ac:dyDescent="0.25">
+        <v>9.6524662289726004E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C159" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E159" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F159" t="s">
         <v>285</v>
       </c>
       <c r="G159" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E159,'feed rations'!$Y$13:$Y$46,0),MATCH(C159&amp;D159,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10994689126216511</v>
-      </c>
-    </row>
-    <row r="160" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.10335011276914095</v>
+      </c>
+    </row>
+    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C160" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E160" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F160" t="s">
         <v>285</v>
       </c>
       <c r="G160" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E160,'feed rations'!$Y$13:$Y$46,0),MATCH(C160&amp;D160,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.7969146428143638E-4</v>
-      </c>
-    </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.8717016446612009E-2</v>
+      </c>
+    </row>
+    <row r="161" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C161" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E161" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="F161" t="s">
         <v>285</v>
@@ -5263,533 +5316,533 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C162" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E162" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F162" t="s">
         <v>285</v>
       </c>
       <c r="G162" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E162,'feed rations'!$Y$13:$Y$46,0),MATCH(C162&amp;D162,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8638137810357785E-2</v>
-      </c>
-    </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+        <v>4.5183669237455988E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C163" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E163" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="F163" t="s">
         <v>285</v>
       </c>
       <c r="G163" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E163,'feed rations'!$Y$13:$Y$46,0),MATCH(C163&amp;D163,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.2642056878731579E-4</v>
-      </c>
-    </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C164" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E164" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F164" t="s">
         <v>285</v>
       </c>
       <c r="G164" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E164,'feed rations'!$Y$13:$Y$46,0),MATCH(C164&amp;D164,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.9298729944924589E-3</v>
-      </c>
-    </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+        <v>4.4053010847661285E-4</v>
+      </c>
+    </row>
+    <row r="165" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C165" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E165" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F165" t="s">
         <v>285</v>
       </c>
       <c r="G165" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E165,'feed rations'!$Y$13:$Y$46,0),MATCH(C165&amp;D165,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.5680152686726926E-2</v>
-      </c>
-    </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+        <v>5.7878882970076748E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C166" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E166" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F166" t="s">
         <v>285</v>
       </c>
       <c r="G166" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E166,'feed rations'!$Y$13:$Y$46,0),MATCH(C166&amp;D166,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.01996829037413E-4</v>
-      </c>
-    </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.17773535668382656</v>
+      </c>
+    </row>
+    <row r="167" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C167" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E167" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="F167" t="s">
         <v>285</v>
       </c>
       <c r="G167" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E167,'feed rations'!$Y$13:$Y$46,0),MATCH(C167&amp;D167,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.1918606769937602E-2</v>
-      </c>
-    </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C168" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E168" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="F168" t="s">
         <v>285</v>
       </c>
       <c r="G168" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E168,'feed rations'!$Y$13:$Y$46,0),MATCH(C168&amp;D168,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5719213163687675E-6</v>
-      </c>
-    </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.1354510343103608E-4</v>
+      </c>
+    </row>
+    <row r="169" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C169" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E169" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="F169" t="s">
         <v>285</v>
       </c>
       <c r="G169" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E169,'feed rations'!$Y$13:$Y$46,0),MATCH(C169&amp;D169,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.1376527579542932E-2</v>
-      </c>
-    </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C170" t="s">
-        <v>198</v>
-      </c>
-      <c r="E170" t="s">
-        <v>242</v>
-      </c>
-      <c r="F170" t="s">
-        <v>285</v>
-      </c>
-      <c r="G170" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E170,'feed rations'!$Y$13:$Y$46,0),MATCH(C170&amp;D170,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.2147291847318914E-6</v>
-      </c>
-    </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B171" t="s">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C171" t="s">
         <v>198</v>
       </c>
-      <c r="E171" t="s">
-        <v>243</v>
+      <c r="E171" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F171" t="s">
         <v>285</v>
       </c>
       <c r="G171" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E171,'feed rations'!$Y$13:$Y$46,0),MATCH(C171&amp;D171,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.4881154204077169E-2</v>
-      </c>
-    </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B172" s="98" t="s">
-        <v>299</v>
-      </c>
-      <c r="C172" s="97" t="str">
-        <f>C171</f>
-        <v>winter lamb</v>
-      </c>
-      <c r="E172" s="97" t="s">
-        <v>298</v>
-      </c>
-      <c r="F172" s="97" t="str">
-        <f>F171</f>
-        <v>share_in_ration</v>
-      </c>
-      <c r="G172" s="99">
-        <f>G171</f>
-        <v>3.4881154204077169E-2</v>
-      </c>
-      <c r="I172" s="97" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+        <v>14.556942659567957</v>
+      </c>
+    </row>
+    <row r="172" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C172" t="s">
+        <v>198</v>
+      </c>
+      <c r="E172" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="F172" t="s">
+        <v>285</v>
+      </c>
+      <c r="G172" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E172,'feed rations'!$Y$13:$Y$46,0),MATCH(C172&amp;D172,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>29.113885319135914</v>
+      </c>
+    </row>
+    <row r="173" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C173" t="s">
         <v>198</v>
       </c>
       <c r="E173" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F173" t="s">
         <v>285</v>
       </c>
       <c r="G173" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E173,'feed rations'!$Y$13:$Y$46,0),MATCH(C173&amp;D173,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0474088759158359E-4</v>
-      </c>
-    </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+        <v>55.686616486139165</v>
+      </c>
+    </row>
+    <row r="174" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C174" t="s">
         <v>198</v>
       </c>
       <c r="E174" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F174" t="s">
         <v>285</v>
       </c>
       <c r="G174" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E174,'feed rations'!$Y$13:$Y$46,0),MATCH(C174&amp;D174,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.8769601492985593E-4</v>
-      </c>
-    </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.14042319726111982</v>
+      </c>
+    </row>
+    <row r="175" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C175" t="s">
         <v>198</v>
       </c>
       <c r="E175" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="F175" t="s">
         <v>285</v>
       </c>
       <c r="G175" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E175,'feed rations'!$Y$13:$Y$46,0),MATCH(C175&amp;D175,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.5294425685567267E-3</v>
-      </c>
-    </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+        <v>7.252784590624109E-2</v>
+      </c>
+    </row>
+    <row r="176" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C176" t="s">
         <v>198</v>
       </c>
       <c r="E176" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F176" t="s">
         <v>285</v>
       </c>
       <c r="G176" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E176,'feed rations'!$Y$13:$Y$46,0),MATCH(C176&amp;D176,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.7048374168202494E-2</v>
-      </c>
-    </row>
-    <row r="177" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.10994689126216511</v>
+      </c>
+    </row>
+    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C177" t="s">
         <v>198</v>
       </c>
       <c r="E177" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F177" t="s">
         <v>285</v>
       </c>
       <c r="G177" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E177,'feed rations'!$Y$13:$Y$46,0),MATCH(C177&amp;D177,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.5729691169921491E-3</v>
-      </c>
-    </row>
-    <row r="178" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.7969146428143638E-4</v>
+      </c>
+    </row>
+    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C178" t="s">
         <v>198</v>
       </c>
       <c r="E178" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F178" t="s">
         <v>285</v>
       </c>
       <c r="G178" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E178,'feed rations'!$Y$13:$Y$46,0),MATCH(C178&amp;D178,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.9670448260287137E-3</v>
-      </c>
-    </row>
-    <row r="179" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C179" t="s">
         <v>198</v>
       </c>
       <c r="E179" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F179" t="s">
         <v>285</v>
       </c>
       <c r="G179" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E179,'feed rations'!$Y$13:$Y$46,0),MATCH(C179&amp;D179,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6580119732380434E-3</v>
-      </c>
-    </row>
-    <row r="180" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.8638137810357785E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C180" t="s">
         <v>198</v>
       </c>
       <c r="E180" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="F180" t="s">
         <v>285</v>
       </c>
       <c r="G180" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E180,'feed rations'!$Y$13:$Y$46,0),MATCH(C180&amp;D180,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.2642056878731579E-4</v>
+      </c>
+    </row>
+    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C181" t="s">
         <v>198</v>
       </c>
       <c r="E181" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F181" t="s">
         <v>285</v>
       </c>
       <c r="G181" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E181,'feed rations'!$Y$13:$Y$46,0),MATCH(C181&amp;D181,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.6087342579548447E-3</v>
-      </c>
-    </row>
-    <row r="182" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.9298729944924589E-3</v>
+      </c>
+    </row>
+    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C182" t="s">
         <v>198</v>
       </c>
       <c r="E182" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F182" t="s">
         <v>285</v>
       </c>
       <c r="G182" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E182,'feed rations'!$Y$13:$Y$46,0),MATCH(C182&amp;D182,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.5680152686726926E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C183" t="s">
         <v>198</v>
       </c>
       <c r="E183" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="F183" t="s">
         <v>285</v>
       </c>
       <c r="G183" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E183,'feed rations'!$Y$13:$Y$46,0),MATCH(C183&amp;D183,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.5434543166556919E-5</v>
-      </c>
-    </row>
-    <row r="184" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.01996829037413E-4</v>
+      </c>
+    </row>
+    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C184" t="s">
         <v>198</v>
       </c>
       <c r="E184" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="F184" t="s">
         <v>285</v>
       </c>
       <c r="G184" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E184,'feed rations'!$Y$13:$Y$46,0),MATCH(C184&amp;D184,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.3417079082862866E-3</v>
-      </c>
-    </row>
-    <row r="185" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.1918606769937602E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C185" t="s">
         <v>198</v>
       </c>
       <c r="E185" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="F185" t="s">
         <v>285</v>
       </c>
       <c r="G185" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E185,'feed rations'!$Y$13:$Y$46,0),MATCH(C185&amp;D185,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.0261767617724977E-2</v>
-      </c>
-    </row>
-    <row r="186" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.5719213163687675E-6</v>
+      </c>
+    </row>
+    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C186" t="s">
         <v>198</v>
       </c>
       <c r="E186" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F186" t="s">
         <v>285</v>
       </c>
       <c r="G186" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E186,'feed rations'!$Y$13:$Y$46,0),MATCH(C186&amp;D186,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.1376527579542932E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C187" t="s">
         <v>198</v>
       </c>
       <c r="E187" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F187" t="s">
         <v>285</v>
       </c>
       <c r="G187" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E187,'feed rations'!$Y$13:$Y$46,0),MATCH(C187&amp;D187,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2329287026500471E-5</v>
-      </c>
-    </row>
-    <row r="188" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.2147291847318914E-6</v>
+      </c>
+    </row>
+    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B188" t="s">
+        <v>300</v>
+      </c>
       <c r="C188" t="s">
         <v>198</v>
       </c>
       <c r="E188" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="F188" t="s">
         <v>285</v>
       </c>
       <c r="G188" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E188,'feed rations'!$Y$13:$Y$46,0),MATCH(C188&amp;D188,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.4881154204077169E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B189" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C189" s="97" t="str">
+        <f>C188</f>
+        <v>winter lamb</v>
+      </c>
+      <c r="E189" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F189" s="97" t="str">
+        <f>F188</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G189" s="99">
+        <f>G188</f>
+        <v>3.4881154204077169E-2</v>
+      </c>
+      <c r="I189" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C190" t="s">
-        <v>204</v>
-      </c>
-      <c r="E190" s="21" t="s">
-        <v>276</v>
+        <v>198</v>
+      </c>
+      <c r="E190" t="s">
+        <v>244</v>
       </c>
       <c r="F190" t="s">
         <v>285</v>
       </c>
       <c r="G190" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E190,'feed rations'!$Y$13:$Y$46,0),MATCH(C190&amp;D190,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>14.502048815250316</v>
-      </c>
-    </row>
-    <row r="191" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.0474088759158359E-4</v>
+      </c>
+    </row>
+    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C191" t="s">
-        <v>204</v>
-      </c>
-      <c r="E191" s="21" t="s">
-        <v>274</v>
+        <v>198</v>
+      </c>
+      <c r="E191" t="s">
+        <v>245</v>
       </c>
       <c r="F191" t="s">
         <v>285</v>
       </c>
       <c r="G191" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E191,'feed rations'!$Y$13:$Y$46,0),MATCH(C191&amp;D191,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>29.004097630500631</v>
-      </c>
-    </row>
-    <row r="192" spans="3:7" x14ac:dyDescent="0.25">
+        <v>5.8769601492985593E-4</v>
+      </c>
+    </row>
+    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C192" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E192" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="F192" t="s">
         <v>285</v>
       </c>
       <c r="G192" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E192,'feed rations'!$Y$13:$Y$46,0),MATCH(C192&amp;D192,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>52.618920363442022</v>
-      </c>
-    </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+        <v>4.5294425685567267E-3</v>
+      </c>
+    </row>
+    <row r="193" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C193" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E193" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="F193" t="s">
         <v>285</v>
       </c>
       <c r="G193" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E193,'feed rations'!$Y$13:$Y$46,0),MATCH(C193&amp;D193,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.84682253603719471</v>
-      </c>
-    </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.7048374168202494E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C194" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E194" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F194" t="s">
         <v>285</v>
       </c>
       <c r="G194" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E194,'feed rations'!$Y$13:$Y$46,0),MATCH(C194&amp;D194,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.43737940455400331</v>
-      </c>
-    </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
+        <v>5.5729691169921491E-3</v>
+      </c>
+    </row>
+    <row r="195" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C195" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E195" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F195" t="s">
         <v>285</v>
       </c>
       <c r="G195" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E195,'feed rations'!$Y$13:$Y$46,0),MATCH(C195&amp;D195,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.66303507614130686</v>
-      </c>
-    </row>
-    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
+        <v>5.9670448260287137E-3</v>
+      </c>
+    </row>
+    <row r="196" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C196" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E196" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F196" t="s">
         <v>285</v>
       </c>
       <c r="G196" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E196,'feed rations'!$Y$13:$Y$46,0),MATCH(C196&amp;D196,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.0988815290634705E-3</v>
-      </c>
-    </row>
-    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.6580119732380434E-3</v>
+      </c>
+    </row>
+    <row r="197" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C197" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E197" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="F197" t="s">
         <v>285</v>
@@ -5799,557 +5852,533 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C198" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E198" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F198" t="s">
         <v>285</v>
       </c>
       <c r="G198" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E198,'feed rations'!$Y$13:$Y$46,0),MATCH(C198&amp;D198,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.17270238081001552</v>
-      </c>
-    </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.6087342579548447E-3</v>
+      </c>
+    </row>
+    <row r="199" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C199" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E199" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="F199" t="s">
         <v>285</v>
       </c>
       <c r="G199" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E199,'feed rations'!$Y$13:$Y$46,0),MATCH(C199&amp;D199,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7776312249885764E-3</v>
-      </c>
-    </row>
-    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C200" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E200" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F200" t="s">
         <v>285</v>
       </c>
       <c r="G200" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E200,'feed rations'!$Y$13:$Y$46,0),MATCH(C200&amp;D200,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3699111545736139E-2</v>
-      </c>
-    </row>
-    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.5434543166556919E-5</v>
+      </c>
+    </row>
+    <row r="201" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C201" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E201" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F201" t="s">
         <v>285</v>
       </c>
       <c r="G201" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E201,'feed rations'!$Y$13:$Y$46,0),MATCH(C201&amp;D201,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.45638940058232602</v>
-      </c>
-    </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
+        <v>3.3417079082862866E-3</v>
+      </c>
+    </row>
+    <row r="202" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C202" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E202" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F202" t="s">
         <v>285</v>
       </c>
       <c r="G202" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E202,'feed rations'!$Y$13:$Y$46,0),MATCH(C202&amp;D202,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.1509220070385851E-4</v>
-      </c>
-    </row>
-    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.0261767617724977E-2</v>
+      </c>
+    </row>
+    <row r="203" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C203" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E203" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="F203" t="s">
         <v>285</v>
       </c>
       <c r="G203" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E203,'feed rations'!$Y$13:$Y$46,0),MATCH(C203&amp;D203,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.19248525926546745</v>
-      </c>
-    </row>
-    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C204" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E204" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="F204" t="s">
         <v>285</v>
       </c>
       <c r="G204" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E204,'feed rations'!$Y$13:$Y$46,0),MATCH(C204&amp;D204,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1540482816582413E-5</v>
-      </c>
-    </row>
-    <row r="205" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.2329287026500471E-5</v>
+      </c>
+    </row>
+    <row r="205" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C205" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E205" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="F205" t="s">
         <v>285</v>
       </c>
       <c r="G205" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E205,'feed rations'!$Y$13:$Y$46,0),MATCH(C205&amp;D205,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.49074140742335415</v>
-      </c>
-    </row>
-    <row r="206" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C206" t="s">
-        <v>204</v>
-      </c>
-      <c r="E206" t="s">
-        <v>242</v>
-      </c>
-      <c r="F206" t="s">
-        <v>285</v>
-      </c>
-      <c r="G206" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E206,'feed rations'!$Y$13:$Y$46,0),MATCH(C206&amp;D206,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.938643453492417E-5</v>
-      </c>
-    </row>
-    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B207" t="s">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C207" t="s">
         <v>204</v>
       </c>
-      <c r="E207" t="s">
-        <v>243</v>
+      <c r="E207" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F207" t="s">
         <v>285</v>
       </c>
       <c r="G207" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E207,'feed rations'!$Y$13:$Y$46,0),MATCH(C207&amp;D207,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.21035091095436523</v>
-      </c>
-    </row>
-    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B208" s="98" t="s">
-        <v>299</v>
-      </c>
-      <c r="C208" s="97" t="str">
-        <f>C207</f>
-        <v>other sheep</v>
-      </c>
-      <c r="E208" s="97" t="s">
-        <v>298</v>
-      </c>
-      <c r="F208" s="97" t="str">
-        <f>F207</f>
-        <v>share_in_ration</v>
-      </c>
-      <c r="G208" s="99">
-        <f>G207</f>
-        <v>0.21035091095436523</v>
-      </c>
-      <c r="I208" s="97" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="209" spans="3:7" x14ac:dyDescent="0.25">
+        <v>14.502048815250316</v>
+      </c>
+    </row>
+    <row r="208" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C208" t="s">
+        <v>204</v>
+      </c>
+      <c r="E208" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="F208" t="s">
+        <v>285</v>
+      </c>
+      <c r="G208" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E208,'feed rations'!$Y$13:$Y$46,0),MATCH(C208&amp;D208,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>29.004097630500631</v>
+      </c>
+    </row>
+    <row r="209" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C209" t="s">
         <v>204</v>
       </c>
       <c r="E209" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F209" t="s">
         <v>285</v>
       </c>
       <c r="G209" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E209,'feed rations'!$Y$13:$Y$46,0),MATCH(C209&amp;D209,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2346905713762435E-3</v>
-      </c>
-    </row>
-    <row r="210" spans="3:7" x14ac:dyDescent="0.25">
+        <v>52.618920363442022</v>
+      </c>
+    </row>
+    <row r="210" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C210" t="s">
         <v>204</v>
       </c>
       <c r="E210" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F210" t="s">
         <v>285</v>
       </c>
       <c r="G210" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E210,'feed rations'!$Y$13:$Y$46,0),MATCH(C210&amp;D210,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.5441026802460426E-3</v>
-      </c>
-    </row>
-    <row r="211" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.84682253603719471</v>
+      </c>
+    </row>
+    <row r="211" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C211" t="s">
         <v>204</v>
       </c>
       <c r="E211" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="F211" t="s">
         <v>285</v>
       </c>
       <c r="G211" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E211,'feed rations'!$Y$13:$Y$46,0),MATCH(C211&amp;D211,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.7314817761965576E-2</v>
-      </c>
-    </row>
-    <row r="212" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.43737940455400331</v>
+      </c>
+    </row>
+    <row r="212" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C212" t="s">
         <v>204</v>
       </c>
       <c r="E212" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F212" t="s">
         <v>285</v>
       </c>
       <c r="G212" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E212,'feed rations'!$Y$13:$Y$46,0),MATCH(C212&amp;D212,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.16311530612857034</v>
-      </c>
-    </row>
-    <row r="213" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.66303507614130686</v>
+      </c>
+    </row>
+    <row r="213" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C213" t="s">
         <v>204</v>
       </c>
       <c r="E213" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F213" t="s">
         <v>285</v>
       </c>
       <c r="G213" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E213,'feed rations'!$Y$13:$Y$46,0),MATCH(C213&amp;D213,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.3607807918891001E-2</v>
-      </c>
-    </row>
-    <row r="214" spans="3:7" x14ac:dyDescent="0.25">
+        <v>4.0988815290634705E-3</v>
+      </c>
+    </row>
+    <row r="214" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C214" t="s">
         <v>204</v>
       </c>
       <c r="E214" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F214" t="s">
         <v>285</v>
       </c>
       <c r="G214" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E214,'feed rations'!$Y$13:$Y$46,0),MATCH(C214&amp;D214,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.598428273092974E-2</v>
-      </c>
-    </row>
-    <row r="215" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C215" t="s">
         <v>204</v>
       </c>
       <c r="E215" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F215" t="s">
         <v>285</v>
       </c>
       <c r="G215" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E215,'feed rations'!$Y$13:$Y$46,0),MATCH(C215&amp;D215,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.9986464582958335E-3</v>
-      </c>
-    </row>
-    <row r="216" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.17270238081001552</v>
+      </c>
+    </row>
+    <row r="216" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C216" t="s">
         <v>204</v>
       </c>
       <c r="E216" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="F216" t="s">
         <v>285</v>
       </c>
       <c r="G216" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E216,'feed rations'!$Y$13:$Y$46,0),MATCH(C216&amp;D216,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.7776312249885764E-3</v>
+      </c>
+    </row>
+    <row r="217" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C217" t="s">
         <v>204</v>
       </c>
       <c r="E217" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F217" t="s">
         <v>285</v>
       </c>
       <c r="G217" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E217,'feed rations'!$Y$13:$Y$46,0),MATCH(C217&amp;D217,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5731980208800535E-2</v>
-      </c>
-    </row>
-    <row r="218" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.3699111545736139E-2</v>
+      </c>
+    </row>
+    <row r="218" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C218" t="s">
         <v>204</v>
       </c>
       <c r="E218" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F218" t="s">
         <v>285</v>
       </c>
       <c r="G218" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E218,'feed rations'!$Y$13:$Y$46,0),MATCH(C218&amp;D218,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.45638940058232602</v>
+      </c>
+    </row>
+    <row r="219" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C219" t="s">
         <v>204</v>
       </c>
       <c r="E219" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="F219" t="s">
         <v>285</v>
       </c>
       <c r="G219" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E219,'feed rations'!$Y$13:$Y$46,0),MATCH(C219&amp;D219,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5338309315945754E-4</v>
-      </c>
-    </row>
-    <row r="220" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.1509220070385851E-4</v>
+      </c>
+    </row>
+    <row r="220" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C220" t="s">
         <v>204</v>
       </c>
       <c r="E220" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="F220" t="s">
         <v>285</v>
       </c>
       <c r="G220" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E220,'feed rations'!$Y$13:$Y$46,0),MATCH(C220&amp;D220,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0152180129671942E-2</v>
-      </c>
-    </row>
-    <row r="221" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.19248525926546745</v>
+      </c>
+    </row>
+    <row r="221" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C221" t="s">
         <v>204</v>
       </c>
       <c r="E221" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="F221" t="s">
         <v>285</v>
       </c>
       <c r="G221" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E221,'feed rations'!$Y$13:$Y$46,0),MATCH(C221&amp;D221,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.188362213479006E-2</v>
-      </c>
-    </row>
-    <row r="222" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.1540482816582413E-5</v>
+      </c>
+    </row>
+    <row r="222" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C222" t="s">
         <v>204</v>
       </c>
       <c r="E222" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F222" t="s">
         <v>285</v>
       </c>
       <c r="G222" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E222,'feed rations'!$Y$13:$Y$46,0),MATCH(C222&amp;D222,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.49074140742335415</v>
+      </c>
+    </row>
+    <row r="223" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C223" t="s">
         <v>204</v>
       </c>
       <c r="E223" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F223" t="s">
         <v>285</v>
       </c>
       <c r="G223" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E223,'feed rations'!$Y$13:$Y$46,0),MATCH(C223&amp;D223,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.4351804480686189E-5</v>
-      </c>
-    </row>
-    <row r="224" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.938643453492417E-5</v>
+      </c>
+    </row>
+    <row r="224" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B224" t="s">
+        <v>300</v>
+      </c>
       <c r="C224" t="s">
         <v>204</v>
       </c>
       <c r="E224" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="F224" t="s">
         <v>285</v>
       </c>
       <c r="G224" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E224,'feed rations'!$Y$13:$Y$46,0),MATCH(C224&amp;D224,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.21035091095436523</v>
+      </c>
+    </row>
+    <row r="225" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B225" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C225" s="97" t="str">
+        <f>C224</f>
+        <v>other sheep</v>
+      </c>
+      <c r="E225" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F225" s="97" t="str">
+        <f>F224</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G225" s="99">
+        <f>G224</f>
+        <v>0.21035091095436523</v>
+      </c>
+      <c r="I225" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="226" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C226" t="s">
-        <v>196</v>
-      </c>
-      <c r="D226" t="s">
-        <v>205</v>
-      </c>
-      <c r="E226" s="21" t="s">
-        <v>276</v>
+        <v>204</v>
+      </c>
+      <c r="E226" t="s">
+        <v>244</v>
       </c>
       <c r="F226" t="s">
         <v>285</v>
       </c>
       <c r="G226" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E226,'feed rations'!$Y$13:$Y$46,0),MATCH(C226&amp;D226,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.69811719906917724</v>
-      </c>
-    </row>
-    <row r="227" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.2346905713762435E-3</v>
+      </c>
+    </row>
+    <row r="227" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C227" t="s">
-        <v>196</v>
-      </c>
-      <c r="D227" t="s">
-        <v>205</v>
-      </c>
-      <c r="E227" s="21" t="s">
-        <v>274</v>
+        <v>204</v>
+      </c>
+      <c r="E227" t="s">
+        <v>245</v>
       </c>
       <c r="F227" t="s">
         <v>285</v>
       </c>
       <c r="G227" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E227,'feed rations'!$Y$13:$Y$46,0),MATCH(C227&amp;D227,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3962343981383545</v>
-      </c>
-    </row>
-    <row r="228" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.5441026802460426E-3</v>
+      </c>
+    </row>
+    <row r="228" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C228" t="s">
-        <v>196</v>
-      </c>
-      <c r="D228" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E228" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="F228" t="s">
         <v>285</v>
       </c>
       <c r="G228" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E228,'feed rations'!$Y$13:$Y$46,0),MATCH(C228&amp;D228,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>83.30865242225515</v>
-      </c>
-    </row>
-    <row r="229" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.7314817761965576E-2</v>
+      </c>
+    </row>
+    <row r="229" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C229" t="s">
-        <v>196</v>
-      </c>
-      <c r="D229" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E229" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="F229" t="s">
         <v>285</v>
       </c>
       <c r="G229" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E229,'feed rations'!$Y$13:$Y$46,0),MATCH(C229&amp;D229,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.1900072971810016</v>
-      </c>
-    </row>
-    <row r="230" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.16311530612857034</v>
+      </c>
+    </row>
+    <row r="230" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C230" t="s">
-        <v>196</v>
-      </c>
-      <c r="D230" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E230" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F230" t="s">
         <v>285</v>
       </c>
       <c r="G230" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E230,'feed rations'!$Y$13:$Y$46,0),MATCH(C230&amp;D230,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6476220610438137</v>
-      </c>
-    </row>
-    <row r="231" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.3607807918891001E-2</v>
+      </c>
+    </row>
+    <row r="231" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C231" t="s">
-        <v>196</v>
-      </c>
-      <c r="D231" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E231" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F231" t="s">
         <v>285</v>
       </c>
       <c r="G231" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E231,'feed rations'!$Y$13:$Y$46,0),MATCH(C231&amp;D231,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4976741184469726</v>
-      </c>
-    </row>
-    <row r="232" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.598428273092974E-2</v>
+      </c>
+    </row>
+    <row r="232" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C232" t="s">
-        <v>196</v>
-      </c>
-      <c r="D232" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E232" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F232" t="s">
         <v>285</v>
       </c>
       <c r="G232" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E232,'feed rations'!$Y$13:$Y$46,0),MATCH(C232&amp;D232,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.544061645924192E-2</v>
-      </c>
-    </row>
-    <row r="233" spans="3:7" x14ac:dyDescent="0.25">
+        <v>9.9986464582958335E-3</v>
+      </c>
+    </row>
+    <row r="233" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C233" t="s">
-        <v>196</v>
-      </c>
-      <c r="D233" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E233" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="F233" t="s">
         <v>285</v>
@@ -6359,217 +6388,163 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C234" t="s">
-        <v>196</v>
-      </c>
-      <c r="D234" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E234" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F234" t="s">
         <v>285</v>
       </c>
       <c r="G234" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E234,'feed rations'!$Y$13:$Y$46,0),MATCH(C234&amp;D234,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.65057533494867192</v>
-      </c>
-    </row>
-    <row r="235" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.5731980208800535E-2</v>
+      </c>
+    </row>
+    <row r="235" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C235" t="s">
-        <v>196</v>
-      </c>
-      <c r="D235" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E235" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="F235" t="s">
         <v>285</v>
       </c>
       <c r="G235" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E235,'feed rations'!$Y$13:$Y$46,0),MATCH(C235&amp;D235,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.4230456395462613E-2</v>
-      </c>
-    </row>
-    <row r="236" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C236" t="s">
-        <v>196</v>
-      </c>
-      <c r="D236" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E236" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F236" t="s">
         <v>285</v>
       </c>
       <c r="G236" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E236,'feed rations'!$Y$13:$Y$46,0),MATCH(C236&amp;D236,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.9275303325517821E-2</v>
-      </c>
-    </row>
-    <row r="237" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.5338309315945754E-4</v>
+      </c>
+    </row>
+    <row r="237" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C237" t="s">
-        <v>196</v>
-      </c>
-      <c r="D237" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E237" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F237" t="s">
         <v>285</v>
       </c>
       <c r="G237" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E237,'feed rations'!$Y$13:$Y$46,0),MATCH(C237&amp;D237,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7192333177936787</v>
-      </c>
-    </row>
-    <row r="238" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.0152180129671942E-2</v>
+      </c>
+    </row>
+    <row r="238" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C238" t="s">
-        <v>196</v>
-      </c>
-      <c r="D238" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E238" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F238" t="s">
         <v>285</v>
       </c>
       <c r="G238" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E238,'feed rations'!$Y$13:$Y$46,0),MATCH(C238&amp;D238,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.317071789169115E-3</v>
-      </c>
-    </row>
-    <row r="239" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.188362213479006E-2</v>
+      </c>
+    </row>
+    <row r="239" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C239" t="s">
-        <v>196</v>
-      </c>
-      <c r="D239" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E239" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="F239" t="s">
         <v>285</v>
       </c>
       <c r="G239" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E239,'feed rations'!$Y$13:$Y$46,0),MATCH(C239&amp;D239,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.72509806426508272</v>
-      </c>
-    </row>
-    <row r="240" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C240" t="s">
-        <v>196</v>
-      </c>
-      <c r="D240" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E240" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="F240" t="s">
         <v>285</v>
       </c>
       <c r="G240" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E240,'feed rations'!$Y$13:$Y$46,0),MATCH(C240&amp;D240,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.1143680577109445E-5</v>
-      </c>
-    </row>
-    <row r="241" spans="2:9" x14ac:dyDescent="0.25">
+        <v>7.4351804480686189E-5</v>
+      </c>
+    </row>
+    <row r="241" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C241" t="s">
-        <v>196</v>
-      </c>
-      <c r="D241" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E241" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="F241" t="s">
         <v>285</v>
       </c>
       <c r="G241" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E241,'feed rations'!$Y$13:$Y$46,0),MATCH(C241&amp;D241,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.8486384148858024</v>
-      </c>
-    </row>
-    <row r="242" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C242" t="s">
-        <v>196</v>
-      </c>
-      <c r="D242" t="s">
-        <v>205</v>
-      </c>
-      <c r="E242" t="s">
-        <v>242</v>
-      </c>
-      <c r="F242" t="s">
-        <v>285</v>
-      </c>
-      <c r="G242" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E242,'feed rations'!$Y$13:$Y$46,0),MATCH(C242&amp;D242,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.3029312519398498E-5</v>
-      </c>
-    </row>
-    <row r="243" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B243" t="s">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C243" t="s">
         <v>196</v>
       </c>
       <c r="D243" t="s">
         <v>205</v>
       </c>
-      <c r="E243" t="s">
-        <v>243</v>
+      <c r="E243" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F243" t="s">
         <v>285</v>
       </c>
       <c r="G243" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E243,'feed rations'!$Y$13:$Y$46,0),MATCH(C243&amp;D243,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.79239853966713902</v>
-      </c>
-    </row>
-    <row r="244" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B244" s="98" t="s">
-        <v>299</v>
-      </c>
-      <c r="C244" s="97" t="str">
-        <f>C243</f>
-        <v>autumn lamb</v>
-      </c>
-      <c r="D244" s="97" t="str">
-        <f>D243</f>
-        <v>lambs</v>
-      </c>
-      <c r="E244" s="97" t="s">
-        <v>298</v>
-      </c>
-      <c r="F244" s="97" t="str">
-        <f>F243</f>
-        <v>share_in_ration</v>
-      </c>
-      <c r="G244" s="99">
-        <f>G243</f>
-        <v>0.79239853966713902</v>
-      </c>
-      <c r="I244" s="97" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="245" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.69811719906917724</v>
+      </c>
+    </row>
+    <row r="244" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C244" t="s">
+        <v>196</v>
+      </c>
+      <c r="D244" t="s">
+        <v>205</v>
+      </c>
+      <c r="E244" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="F244" t="s">
+        <v>285</v>
+      </c>
+      <c r="G244" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E244,'feed rations'!$Y$13:$Y$46,0),MATCH(C244&amp;D244,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>1.3962343981383545</v>
+      </c>
+    </row>
+    <row r="245" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C245" t="s">
         <v>196</v>
       </c>
@@ -6577,17 +6552,17 @@
         <v>205</v>
       </c>
       <c r="E245" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F245" t="s">
         <v>285</v>
       </c>
       <c r="G245" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E245,'feed rations'!$Y$13:$Y$46,0),MATCH(C245&amp;D245,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.6511184632405684E-3</v>
-      </c>
-    </row>
-    <row r="246" spans="2:9" x14ac:dyDescent="0.25">
+        <v>83.30865242225515</v>
+      </c>
+    </row>
+    <row r="246" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C246" t="s">
         <v>196</v>
       </c>
@@ -6595,17 +6570,17 @@
         <v>205</v>
       </c>
       <c r="E246" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F246" t="s">
         <v>285</v>
       </c>
       <c r="G246" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E246,'feed rations'!$Y$13:$Y$46,0),MATCH(C246&amp;D246,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3350746975688711E-2</v>
-      </c>
-    </row>
-    <row r="247" spans="2:9" x14ac:dyDescent="0.25">
+        <v>3.1900072971810016</v>
+      </c>
+    </row>
+    <row r="247" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C247" t="s">
         <v>196</v>
       </c>
@@ -6613,17 +6588,17 @@
         <v>205</v>
       </c>
       <c r="E247" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="F247" t="s">
         <v>285</v>
       </c>
       <c r="G247" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E247,'feed rations'!$Y$13:$Y$46,0),MATCH(C247&amp;D247,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10289578308767665</v>
-      </c>
-    </row>
-    <row r="248" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.6476220610438137</v>
+      </c>
+    </row>
+    <row r="248" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C248" t="s">
         <v>196</v>
       </c>
@@ -6631,17 +6606,17 @@
         <v>205</v>
       </c>
       <c r="E248" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F248" t="s">
         <v>285</v>
       </c>
       <c r="G248" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E248,'feed rations'!$Y$13:$Y$46,0),MATCH(C248&amp;D248,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.61446052117016126</v>
-      </c>
-    </row>
-    <row r="249" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.4976741184469726</v>
+      </c>
+    </row>
+    <row r="249" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C249" t="s">
         <v>196</v>
       </c>
@@ -6649,17 +6624,17 @@
         <v>205</v>
       </c>
       <c r="E249" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F249" t="s">
         <v>285</v>
       </c>
       <c r="G249" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E249,'feed rations'!$Y$13:$Y$46,0),MATCH(C249&amp;D249,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.12660167619678325</v>
-      </c>
-    </row>
-    <row r="250" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.544061645924192E-2</v>
+      </c>
+    </row>
+    <row r="250" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C250" t="s">
         <v>196</v>
       </c>
@@ -6667,17 +6642,17 @@
         <v>205</v>
       </c>
       <c r="E250" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F250" t="s">
         <v>285</v>
       </c>
       <c r="G250" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E250,'feed rations'!$Y$13:$Y$46,0),MATCH(C250&amp;D250,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13555393203476143</v>
-      </c>
-    </row>
-    <row r="251" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C251" t="s">
         <v>196</v>
       </c>
@@ -6685,17 +6660,17 @@
         <v>205</v>
       </c>
       <c r="E251" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F251" t="s">
         <v>285</v>
       </c>
       <c r="G251" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E251,'feed rations'!$Y$13:$Y$46,0),MATCH(C251&amp;D251,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7665217689123641E-2</v>
-      </c>
-    </row>
-    <row r="252" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.65057533494867192</v>
+      </c>
+    </row>
+    <row r="252" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C252" t="s">
         <v>196</v>
       </c>
@@ -6703,17 +6678,17 @@
         <v>205</v>
       </c>
       <c r="E252" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="F252" t="s">
         <v>285</v>
       </c>
       <c r="G252" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E252,'feed rations'!$Y$13:$Y$46,0),MATCH(C252&amp;D252,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.4230456395462613E-2</v>
+      </c>
+    </row>
+    <row r="253" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C253" t="s">
         <v>196</v>
       </c>
@@ -6721,17 +6696,17 @@
         <v>205</v>
       </c>
       <c r="E253" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F253" t="s">
         <v>285</v>
       </c>
       <c r="G253" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E253,'feed rations'!$Y$13:$Y$46,0),MATCH(C253&amp;D253,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.9262867400799252E-2</v>
-      </c>
-    </row>
-    <row r="254" spans="2:9" x14ac:dyDescent="0.25">
+        <v>8.9275303325517821E-2</v>
+      </c>
+    </row>
+    <row r="254" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C254" t="s">
         <v>196</v>
       </c>
@@ -6739,17 +6714,17 @@
         <v>205</v>
       </c>
       <c r="E254" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F254" t="s">
         <v>285</v>
       </c>
       <c r="G254" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E254,'feed rations'!$Y$13:$Y$46,0),MATCH(C254&amp;D254,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.7192333177936787</v>
+      </c>
+    </row>
+    <row r="255" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C255" t="s">
         <v>196</v>
       </c>
@@ -6757,17 +6732,17 @@
         <v>205</v>
       </c>
       <c r="E255" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="F255" t="s">
         <v>285</v>
       </c>
       <c r="G255" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E255,'feed rations'!$Y$13:$Y$46,0),MATCH(C255&amp;D255,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.7779896686803802E-4</v>
-      </c>
-    </row>
-    <row r="256" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.317071789169115E-3</v>
+      </c>
+    </row>
+    <row r="256" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C256" t="s">
         <v>196</v>
       </c>
@@ -6775,17 +6750,17 @@
         <v>205</v>
       </c>
       <c r="E256" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="F256" t="s">
         <v>285</v>
       </c>
       <c r="G256" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E256,'feed rations'!$Y$13:$Y$46,0),MATCH(C256&amp;D256,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.5913900412465971E-2</v>
-      </c>
-    </row>
-    <row r="257" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.72509806426508272</v>
+      </c>
+    </row>
+    <row r="257" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C257" t="s">
         <v>196</v>
       </c>
@@ -6793,17 +6768,17 @@
         <v>205</v>
       </c>
       <c r="E257" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="F257" t="s">
         <v>285</v>
       </c>
       <c r="G257" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E257,'feed rations'!$Y$13:$Y$46,0),MATCH(C257&amp;D257,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.23311756334422978</v>
-      </c>
-    </row>
-    <row r="258" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.1143680577109445E-5</v>
+      </c>
+    </row>
+    <row r="258" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C258" t="s">
         <v>196</v>
       </c>
@@ -6811,17 +6786,17 @@
         <v>205</v>
       </c>
       <c r="E258" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F258" t="s">
         <v>285</v>
       </c>
       <c r="G258" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E258,'feed rations'!$Y$13:$Y$46,0),MATCH(C258&amp;D258,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.8486384148858024</v>
+      </c>
+    </row>
+    <row r="259" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C259" t="s">
         <v>196</v>
       </c>
@@ -6829,17 +6804,20 @@
         <v>205</v>
       </c>
       <c r="E259" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F259" t="s">
         <v>285</v>
       </c>
       <c r="G259" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E259,'feed rations'!$Y$13:$Y$46,0),MATCH(C259&amp;D259,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8008560088857437E-4</v>
-      </c>
-    </row>
-    <row r="260" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.3029312519398498E-5</v>
+      </c>
+    </row>
+    <row r="260" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B260" t="s">
+        <v>300</v>
+      </c>
       <c r="C260" t="s">
         <v>196</v>
       </c>
@@ -6847,151 +6825,178 @@
         <v>205</v>
       </c>
       <c r="E260" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="F260" t="s">
         <v>285</v>
       </c>
       <c r="G260" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E260,'feed rations'!$Y$13:$Y$46,0),MATCH(C260&amp;D260,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.79239853966713902</v>
+      </c>
+    </row>
+    <row r="261" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B261" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C261" s="97" t="str">
+        <f>C260</f>
+        <v>autumn lamb</v>
+      </c>
+      <c r="D261" s="97" t="str">
+        <f>D260</f>
+        <v>lambs</v>
+      </c>
+      <c r="E261" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F261" s="97" t="str">
+        <f>F260</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G261" s="99">
+        <f>G260</f>
+        <v>0.79239853966713902</v>
+      </c>
+      <c r="I261" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="262" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C262" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D262" t="s">
         <v>205</v>
       </c>
-      <c r="E262" s="21" t="s">
-        <v>276</v>
+      <c r="E262" t="s">
+        <v>244</v>
       </c>
       <c r="F262" t="s">
         <v>285</v>
       </c>
       <c r="G262" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E262,'feed rations'!$Y$13:$Y$46,0),MATCH(C262&amp;D262,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>16.081871345029242</v>
-      </c>
-    </row>
-    <row r="263" spans="3:7" x14ac:dyDescent="0.25">
+        <v>4.6511184632405684E-3</v>
+      </c>
+    </row>
+    <row r="263" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C263" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D263" t="s">
         <v>205</v>
       </c>
-      <c r="E263" s="21" t="s">
-        <v>274</v>
+      <c r="E263" t="s">
+        <v>245</v>
       </c>
       <c r="F263" t="s">
         <v>285</v>
       </c>
       <c r="G263" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E263,'feed rations'!$Y$13:$Y$46,0),MATCH(C263&amp;D263,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>32.163742690058484</v>
-      </c>
-    </row>
-    <row r="264" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.3350746975688711E-2</v>
+      </c>
+    </row>
+    <row r="264" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C264" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D264" t="s">
         <v>205</v>
       </c>
       <c r="E264" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="F264" t="s">
         <v>285</v>
       </c>
       <c r="G264" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E264,'feed rations'!$Y$13:$Y$46,0),MATCH(C264&amp;D264,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.10289578308767665</v>
+      </c>
+    </row>
+    <row r="265" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C265" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D265" t="s">
         <v>205</v>
       </c>
       <c r="E265" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="F265" t="s">
         <v>285</v>
       </c>
       <c r="G265" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E265,'feed rations'!$Y$13:$Y$46,0),MATCH(C265&amp;D265,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>11.310331873032048</v>
-      </c>
-    </row>
-    <row r="266" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.61446052117016126</v>
+      </c>
+    </row>
+    <row r="266" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C266" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D266" t="s">
         <v>205</v>
       </c>
       <c r="E266" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F266" t="s">
         <v>285</v>
       </c>
       <c r="G266" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E266,'feed rations'!$Y$13:$Y$46,0),MATCH(C266&amp;D266,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.8417271735404546</v>
-      </c>
-    </row>
-    <row r="267" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.12660167619678325</v>
+      </c>
+    </row>
+    <row r="267" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C267" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D267" t="s">
         <v>205</v>
       </c>
       <c r="E267" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F267" t="s">
         <v>285</v>
       </c>
       <c r="G267" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E267,'feed rations'!$Y$13:$Y$46,0),MATCH(C267&amp;D267,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.8556296455127299</v>
-      </c>
-    </row>
-    <row r="268" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.13555393203476143</v>
+      </c>
+    </row>
+    <row r="268" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C268" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D268" t="s">
         <v>205</v>
       </c>
       <c r="E268" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F268" t="s">
         <v>285</v>
       </c>
       <c r="G268" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E268,'feed rations'!$Y$13:$Y$46,0),MATCH(C268&amp;D268,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.4745484950004523E-2</v>
-      </c>
-    </row>
-    <row r="269" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.7665217689123641E-2</v>
+      </c>
+    </row>
+    <row r="269" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C269" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D269" t="s">
         <v>205</v>
       </c>
       <c r="E269" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="F269" t="s">
         <v>285</v>
@@ -7001,217 +7006,187 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C270" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D270" t="s">
         <v>205</v>
       </c>
       <c r="E270" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F270" t="s">
         <v>285</v>
       </c>
       <c r="G270" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E270,'feed rations'!$Y$13:$Y$46,0),MATCH(C270&amp;D270,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3066476848441386</v>
-      </c>
-    </row>
-    <row r="271" spans="3:7" x14ac:dyDescent="0.25">
+        <v>5.9262867400799252E-2</v>
+      </c>
+    </row>
+    <row r="271" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C271" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D271" t="s">
         <v>205</v>
       </c>
       <c r="E271" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="F271" t="s">
         <v>285</v>
       </c>
       <c r="G271" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E271,'feed rations'!$Y$13:$Y$46,0),MATCH(C271&amp;D271,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.0454801366638102E-2</v>
-      </c>
-    </row>
-    <row r="272" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C272" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D272" t="s">
         <v>205</v>
       </c>
       <c r="E272" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F272" t="s">
         <v>285</v>
       </c>
       <c r="G272" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E272,'feed rations'!$Y$13:$Y$46,0),MATCH(C272&amp;D272,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.31653009369900376</v>
-      </c>
-    </row>
-    <row r="273" spans="2:9" x14ac:dyDescent="0.25">
+        <v>5.7779896686803802E-4</v>
+      </c>
+    </row>
+    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C273" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D273" t="s">
         <v>205</v>
       </c>
       <c r="E273" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F273" t="s">
         <v>285</v>
       </c>
       <c r="G273" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E273,'feed rations'!$Y$13:$Y$46,0),MATCH(C273&amp;D273,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.0956284985943601</v>
-      </c>
-    </row>
-    <row r="274" spans="2:9" x14ac:dyDescent="0.25">
+        <v>7.5913900412465971E-2</v>
+      </c>
+    </row>
+    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C274" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D274" t="s">
         <v>205</v>
       </c>
       <c r="E274" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F274" t="s">
         <v>285</v>
       </c>
       <c r="G274" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E274,'feed rations'!$Y$13:$Y$46,0),MATCH(C274&amp;D274,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.2152949719901079E-3</v>
-      </c>
-    </row>
-    <row r="275" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.23311756334422978</v>
+      </c>
+    </row>
+    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C275" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D275" t="s">
         <v>205</v>
       </c>
       <c r="E275" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="F275" t="s">
         <v>285</v>
       </c>
       <c r="G275" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E275,'feed rations'!$Y$13:$Y$46,0),MATCH(C275&amp;D275,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.5708717828258543</v>
-      </c>
-    </row>
-    <row r="276" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C276" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D276" t="s">
         <v>205</v>
       </c>
       <c r="E276" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="F276" t="s">
         <v>285</v>
       </c>
       <c r="G276" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E276,'feed rations'!$Y$13:$Y$46,0),MATCH(C276&amp;D276,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8769901483844112E-4</v>
-      </c>
-    </row>
-    <row r="277" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.8008560088857437E-4</v>
+      </c>
+    </row>
+    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C277" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D277" t="s">
         <v>205</v>
       </c>
       <c r="E277" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="F277" t="s">
         <v>285</v>
       </c>
       <c r="G277" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E277,'feed rations'!$Y$13:$Y$46,0),MATCH(C277&amp;D277,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.5544408014587594</v>
-      </c>
-    </row>
-    <row r="278" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C278" t="s">
-        <v>197</v>
-      </c>
-      <c r="D278" t="s">
-        <v>205</v>
-      </c>
-      <c r="E278" t="s">
-        <v>242</v>
-      </c>
-      <c r="F278" t="s">
-        <v>285</v>
-      </c>
-      <c r="G278" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E278,'feed rations'!$Y$13:$Y$46,0),MATCH(C278&amp;D278,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.58929113354597E-4</v>
-      </c>
-    </row>
-    <row r="279" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B279" t="s">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C279" t="s">
         <v>197</v>
       </c>
       <c r="D279" t="s">
         <v>205</v>
       </c>
-      <c r="E279" t="s">
-        <v>243</v>
+      <c r="E279" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F279" t="s">
         <v>285</v>
       </c>
       <c r="G279" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E279,'feed rations'!$Y$13:$Y$46,0),MATCH(C279&amp;D279,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8094890150443339</v>
-      </c>
-    </row>
-    <row r="280" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B280" s="98" t="s">
-        <v>299</v>
-      </c>
-      <c r="C280" s="97" t="str">
-        <f>C279</f>
-        <v>spring lamb</v>
-      </c>
-      <c r="D280" s="97" t="str">
-        <f>D279</f>
-        <v>lambs</v>
-      </c>
-      <c r="E280" s="97" t="s">
-        <v>298</v>
-      </c>
-      <c r="F280" s="97" t="str">
-        <f>F279</f>
-        <v>share_in_ration</v>
-      </c>
-      <c r="G280" s="99">
-        <f>G279</f>
-        <v>2.8094890150443339</v>
-      </c>
-      <c r="I280" s="97" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="281" spans="2:9" x14ac:dyDescent="0.25">
+        <v>16.081871345029242</v>
+      </c>
+    </row>
+    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C280" t="s">
+        <v>197</v>
+      </c>
+      <c r="D280" t="s">
+        <v>205</v>
+      </c>
+      <c r="E280" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="F280" t="s">
+        <v>285</v>
+      </c>
+      <c r="G280" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E280,'feed rations'!$Y$13:$Y$46,0),MATCH(C280&amp;D280,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>32.163742690058484</v>
+      </c>
+    </row>
+    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C281" t="s">
         <v>197</v>
       </c>
@@ -7219,17 +7194,17 @@
         <v>205</v>
       </c>
       <c r="E281" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F281" t="s">
         <v>285</v>
       </c>
       <c r="G281" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E281,'feed rations'!$Y$13:$Y$46,0),MATCH(C281&amp;D281,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6490775255130326E-2</v>
-      </c>
-    </row>
-    <row r="282" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C282" t="s">
         <v>197</v>
       </c>
@@ -7237,17 +7212,17 @@
         <v>205</v>
       </c>
       <c r="E282" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F282" t="s">
         <v>285</v>
       </c>
       <c r="G282" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E282,'feed rations'!$Y$13:$Y$46,0),MATCH(C282&amp;D282,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.7335747219562054E-2</v>
-      </c>
-    </row>
-    <row r="283" spans="2:9" x14ac:dyDescent="0.25">
+        <v>11.310331873032048</v>
+      </c>
+    </row>
+    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C283" t="s">
         <v>197</v>
       </c>
@@ -7255,17 +7230,17 @@
         <v>205</v>
       </c>
       <c r="E283" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="F283" t="s">
         <v>285</v>
       </c>
       <c r="G283" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E283,'feed rations'!$Y$13:$Y$46,0),MATCH(C283&amp;D283,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.36482219212651157</v>
-      </c>
-    </row>
-    <row r="284" spans="2:9" x14ac:dyDescent="0.25">
+        <v>5.8417271735404546</v>
+      </c>
+    </row>
+    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C284" t="s">
         <v>197</v>
       </c>
@@ -7273,17 +7248,17 @@
         <v>205</v>
       </c>
       <c r="E284" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F284" t="s">
         <v>285</v>
       </c>
       <c r="G284" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E284,'feed rations'!$Y$13:$Y$46,0),MATCH(C284&amp;D284,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1786007898640953</v>
-      </c>
-    </row>
-    <row r="285" spans="2:9" x14ac:dyDescent="0.25">
+        <v>8.8556296455127299</v>
+      </c>
+    </row>
+    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C285" t="s">
         <v>197</v>
       </c>
@@ -7291,17 +7266,17 @@
         <v>205</v>
       </c>
       <c r="E285" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F285" t="s">
         <v>285</v>
       </c>
       <c r="G285" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E285,'feed rations'!$Y$13:$Y$46,0),MATCH(C285&amp;D285,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.44887263259025506</v>
-      </c>
-    </row>
-    <row r="286" spans="2:9" x14ac:dyDescent="0.25">
+        <v>5.4745484950004523E-2</v>
+      </c>
+    </row>
+    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C286" t="s">
         <v>197</v>
       </c>
@@ -7309,17 +7284,17 @@
         <v>205</v>
       </c>
       <c r="E286" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F286" t="s">
         <v>285</v>
       </c>
       <c r="G286" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E286,'feed rations'!$Y$13:$Y$46,0),MATCH(C286&amp;D286,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.48061330748755038</v>
-      </c>
-    </row>
-    <row r="287" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C287" t="s">
         <v>197</v>
       </c>
@@ -7327,17 +7302,17 @@
         <v>205</v>
       </c>
       <c r="E287" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F287" t="s">
         <v>285</v>
       </c>
       <c r="G287" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E287,'feed rations'!$Y$13:$Y$46,0),MATCH(C287&amp;D287,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13354393029459391</v>
-      </c>
-    </row>
-    <row r="288" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.3066476848441386</v>
+      </c>
+    </row>
+    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C288" t="s">
         <v>197</v>
       </c>
@@ -7345,17 +7320,17 @@
         <v>205</v>
       </c>
       <c r="E288" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="F288" t="s">
         <v>285</v>
       </c>
       <c r="G288" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E288,'feed rations'!$Y$13:$Y$46,0),MATCH(C288&amp;D288,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
+        <v>5.0454801366638102E-2</v>
+      </c>
+    </row>
+    <row r="289" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C289" t="s">
         <v>197</v>
       </c>
@@ -7363,17 +7338,17 @@
         <v>205</v>
       </c>
       <c r="E289" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F289" t="s">
         <v>285</v>
       </c>
       <c r="G289" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E289,'feed rations'!$Y$13:$Y$46,0),MATCH(C289&amp;D289,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.21011948738890288</v>
-      </c>
-    </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.31653009369900376</v>
+      </c>
+    </row>
+    <row r="290" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C290" t="s">
         <v>197</v>
       </c>
@@ -7381,17 +7356,17 @@
         <v>205</v>
       </c>
       <c r="E290" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F290" t="s">
         <v>285</v>
       </c>
       <c r="G290" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E290,'feed rations'!$Y$13:$Y$46,0),MATCH(C290&amp;D290,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.0956284985943601</v>
+      </c>
+    </row>
+    <row r="291" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C291" t="s">
         <v>197</v>
       </c>
@@ -7399,17 +7374,17 @@
         <v>205</v>
       </c>
       <c r="E291" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="F291" t="s">
         <v>285</v>
       </c>
       <c r="G291" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E291,'feed rations'!$Y$13:$Y$46,0),MATCH(C291&amp;D291,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.0486153987633827E-3</v>
-      </c>
-    </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.2152949719901079E-3</v>
+      </c>
+    </row>
+    <row r="292" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C292" t="s">
         <v>197</v>
       </c>
@@ -7417,17 +7392,17 @@
         <v>205</v>
       </c>
       <c r="E292" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="F292" t="s">
         <v>285</v>
       </c>
       <c r="G292" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E292,'feed rations'!$Y$13:$Y$46,0),MATCH(C292&amp;D292,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.26915656531571153</v>
-      </c>
-    </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.5708717828258543</v>
+      </c>
+    </row>
+    <row r="293" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C293" t="s">
         <v>197</v>
       </c>
@@ -7435,17 +7410,17 @@
         <v>205</v>
       </c>
       <c r="E293" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="F293" t="s">
         <v>285</v>
       </c>
       <c r="G293" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E293,'feed rations'!$Y$13:$Y$46,0),MATCH(C293&amp;D293,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.82653008636870395</v>
-      </c>
-    </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.8769901483844112E-4</v>
+      </c>
+    </row>
+    <row r="294" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C294" t="s">
         <v>197</v>
       </c>
@@ -7453,17 +7428,17 @@
         <v>205</v>
       </c>
       <c r="E294" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F294" t="s">
         <v>285</v>
       </c>
       <c r="G294" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E294,'feed rations'!$Y$13:$Y$46,0),MATCH(C294&amp;D294,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
+        <v>6.5544408014587594</v>
+      </c>
+    </row>
+    <row r="295" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C295" t="s">
         <v>197</v>
       </c>
@@ -7471,17 +7446,20 @@
         <v>205</v>
       </c>
       <c r="E295" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F295" t="s">
         <v>285</v>
       </c>
       <c r="G295" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E295,'feed rations'!$Y$13:$Y$46,0),MATCH(C295&amp;D295,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.9305763397682621E-4</v>
-      </c>
-    </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.58929113354597E-4</v>
+      </c>
+    </row>
+    <row r="296" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B296" t="s">
+        <v>300</v>
+      </c>
       <c r="C296" t="s">
         <v>197</v>
       </c>
@@ -7489,151 +7467,178 @@
         <v>205</v>
       </c>
       <c r="E296" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="F296" t="s">
         <v>285</v>
       </c>
       <c r="G296" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E296,'feed rations'!$Y$13:$Y$46,0),MATCH(C296&amp;D296,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.8094890150443339</v>
+      </c>
+    </row>
+    <row r="297" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B297" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C297" s="97" t="str">
+        <f>C296</f>
+        <v>spring lamb</v>
+      </c>
+      <c r="D297" s="97" t="str">
+        <f>D296</f>
+        <v>lambs</v>
+      </c>
+      <c r="E297" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F297" s="97" t="str">
+        <f>F296</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G297" s="99">
+        <f>G296</f>
+        <v>2.8094890150443339</v>
+      </c>
+      <c r="I297" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C298" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D298" t="s">
         <v>205</v>
       </c>
-      <c r="E298" s="21" t="s">
-        <v>276</v>
+      <c r="E298" t="s">
+        <v>244</v>
       </c>
       <c r="F298" t="s">
         <v>285</v>
       </c>
       <c r="G298" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E298,'feed rations'!$Y$13:$Y$46,0),MATCH(C298&amp;D298,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>18.580594474270001</v>
-      </c>
-    </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.6490775255130326E-2</v>
+      </c>
+    </row>
+    <row r="299" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C299" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D299" t="s">
         <v>205</v>
       </c>
-      <c r="E299" s="21" t="s">
-        <v>274</v>
+      <c r="E299" t="s">
+        <v>245</v>
       </c>
       <c r="F299" t="s">
         <v>285</v>
       </c>
       <c r="G299" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E299,'feed rations'!$Y$13:$Y$46,0),MATCH(C299&amp;D299,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>37.161188948540001</v>
-      </c>
-    </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
+        <v>4.7335747219562054E-2</v>
+      </c>
+    </row>
+    <row r="300" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C300" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D300" t="s">
         <v>205</v>
       </c>
       <c r="E300" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="F300" t="s">
         <v>285</v>
       </c>
       <c r="G300" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E300,'feed rations'!$Y$13:$Y$46,0),MATCH(C300&amp;D300,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>41.770328663087604</v>
-      </c>
-    </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.36482219212651157</v>
+      </c>
+    </row>
+    <row r="301" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C301" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D301" t="s">
         <v>205</v>
       </c>
       <c r="E301" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="F301" t="s">
         <v>285</v>
       </c>
       <c r="G301" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E301,'feed rations'!$Y$13:$Y$46,0),MATCH(C301&amp;D301,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.5436995811423736</v>
-      </c>
-    </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.1786007898640953</v>
+      </c>
+    </row>
+    <row r="302" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C302" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D302" t="s">
         <v>205</v>
       </c>
       <c r="E302" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F302" t="s">
         <v>285</v>
       </c>
       <c r="G302" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E302,'feed rations'!$Y$13:$Y$46,0),MATCH(C302&amp;D302,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.28081798598457164</v>
-      </c>
-    </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.44887263259025506</v>
+      </c>
+    </row>
+    <row r="303" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C303" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D303" t="s">
         <v>205</v>
       </c>
       <c r="E303" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F303" t="s">
         <v>285</v>
       </c>
       <c r="G303" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E303,'feed rations'!$Y$13:$Y$46,0),MATCH(C303&amp;D303,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.42569945630839534</v>
-      </c>
-    </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.48061330748755038</v>
+      </c>
+    </row>
+    <row r="304" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C304" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D304" t="s">
         <v>205</v>
       </c>
       <c r="E304" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F304" t="s">
         <v>285</v>
       </c>
       <c r="G304" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E304,'feed rations'!$Y$13:$Y$46,0),MATCH(C304&amp;D304,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.6316731967630778E-3</v>
-      </c>
-    </row>
-    <row r="305" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.13354393029459391</v>
+      </c>
+    </row>
+    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C305" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D305" t="s">
         <v>205</v>
       </c>
       <c r="E305" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="F305" t="s">
         <v>285</v>
@@ -7643,217 +7648,187 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C306" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D306" t="s">
         <v>205</v>
       </c>
       <c r="E306" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F306" t="s">
         <v>285</v>
       </c>
       <c r="G306" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E306,'feed rations'!$Y$13:$Y$46,0),MATCH(C306&amp;D306,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.11088298682756348</v>
-      </c>
-    </row>
-    <row r="307" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.21011948738890288</v>
+      </c>
+    </row>
+    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C307" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D307" t="s">
         <v>205</v>
       </c>
       <c r="E307" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="F307" t="s">
         <v>285</v>
       </c>
       <c r="G307" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E307,'feed rations'!$Y$13:$Y$46,0),MATCH(C307&amp;D307,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4254155119065326E-3</v>
-      </c>
-    </row>
-    <row r="308" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C308" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D308" t="s">
         <v>205</v>
       </c>
       <c r="E308" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F308" t="s">
         <v>285</v>
       </c>
       <c r="G308" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E308,'feed rations'!$Y$13:$Y$46,0),MATCH(C308&amp;D308,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.5215935420378532E-2</v>
-      </c>
-    </row>
-    <row r="309" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.0486153987633827E-3</v>
+      </c>
+    </row>
+    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C309" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D309" t="s">
         <v>205</v>
       </c>
       <c r="E309" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F309" t="s">
         <v>285</v>
       </c>
       <c r="G309" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E309,'feed rations'!$Y$13:$Y$46,0),MATCH(C309&amp;D309,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.29302329044716247</v>
-      </c>
-    </row>
-    <row r="310" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.26915656531571153</v>
+      </c>
+    </row>
+    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C310" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D310" t="s">
         <v>205</v>
       </c>
       <c r="E310" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F310" t="s">
         <v>285</v>
       </c>
       <c r="G310" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E310,'feed rations'!$Y$13:$Y$46,0),MATCH(C310&amp;D310,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.9491789324787145E-4</v>
-      </c>
-    </row>
-    <row r="311" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.82653008636870395</v>
+      </c>
+    </row>
+    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C311" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D311" t="s">
         <v>205</v>
       </c>
       <c r="E311" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="F311" t="s">
         <v>285</v>
       </c>
       <c r="G311" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E311,'feed rations'!$Y$13:$Y$46,0),MATCH(C311&amp;D311,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.12358451787130892</v>
-      </c>
-    </row>
-    <row r="312" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C312" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D312" t="s">
         <v>205</v>
       </c>
       <c r="E312" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="F312" t="s">
         <v>285</v>
       </c>
       <c r="G312" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E312,'feed rations'!$Y$13:$Y$46,0),MATCH(C312&amp;D312,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3829995053964826E-5</v>
-      </c>
-    </row>
-    <row r="313" spans="2:9" x14ac:dyDescent="0.25">
+        <v>9.9305763397682621E-4</v>
+      </c>
+    </row>
+    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C313" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D313" t="s">
         <v>205</v>
       </c>
       <c r="E313" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="F313" t="s">
         <v>285</v>
       </c>
       <c r="G313" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E313,'feed rations'!$Y$13:$Y$46,0),MATCH(C313&amp;D313,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.31507888171457132</v>
-      </c>
-    </row>
-    <row r="314" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C314" t="s">
-        <v>198</v>
-      </c>
-      <c r="D314" t="s">
-        <v>205</v>
-      </c>
-      <c r="E314" t="s">
-        <v>242</v>
-      </c>
-      <c r="F314" t="s">
-        <v>285</v>
-      </c>
-      <c r="G314" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E314,'feed rations'!$Y$13:$Y$46,0),MATCH(C314&amp;D314,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2446995548568345E-5</v>
-      </c>
-    </row>
-    <row r="315" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B315" t="s">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C315" t="s">
         <v>198</v>
       </c>
       <c r="D315" t="s">
         <v>205</v>
       </c>
-      <c r="E315" t="s">
-        <v>243</v>
+      <c r="E315" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F315" t="s">
         <v>285</v>
       </c>
       <c r="G315" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E315,'feed rations'!$Y$13:$Y$46,0),MATCH(C315&amp;D315,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13505509987252132</v>
-      </c>
-    </row>
-    <row r="316" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B316" s="98" t="s">
-        <v>299</v>
-      </c>
-      <c r="C316" s="97" t="str">
-        <f>C315</f>
-        <v>winter lamb</v>
-      </c>
-      <c r="D316" s="97" t="str">
-        <f>D315</f>
-        <v>lambs</v>
-      </c>
-      <c r="E316" s="97" t="s">
-        <v>298</v>
-      </c>
-      <c r="F316" s="97" t="str">
-        <f>F315</f>
-        <v>share_in_ration</v>
-      </c>
-      <c r="G316" s="99">
-        <f>G315</f>
-        <v>0.13505509987252132</v>
-      </c>
-      <c r="I316" s="97" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="317" spans="2:9" x14ac:dyDescent="0.25">
+        <v>18.580594474270001</v>
+      </c>
+    </row>
+    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C316" t="s">
+        <v>198</v>
+      </c>
+      <c r="D316" t="s">
+        <v>205</v>
+      </c>
+      <c r="E316" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="F316" t="s">
+        <v>285</v>
+      </c>
+      <c r="G316" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E316,'feed rations'!$Y$13:$Y$46,0),MATCH(C316&amp;D316,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>37.161188948540001</v>
+      </c>
+    </row>
+    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C317" t="s">
         <v>198</v>
       </c>
@@ -7861,17 +7836,17 @@
         <v>205</v>
       </c>
       <c r="E317" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F317" t="s">
         <v>285</v>
       </c>
       <c r="G317" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E317,'feed rations'!$Y$13:$Y$46,0),MATCH(C317&amp;D317,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.9272895787484826E-4</v>
-      </c>
-    </row>
-    <row r="318" spans="2:9" x14ac:dyDescent="0.25">
+        <v>41.770328663087604</v>
+      </c>
+    </row>
+    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C318" t="s">
         <v>198</v>
       </c>
@@ -7879,17 +7854,17 @@
         <v>205</v>
       </c>
       <c r="E318" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F318" t="s">
         <v>285</v>
       </c>
       <c r="G318" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E318,'feed rations'!$Y$13:$Y$46,0),MATCH(C318&amp;D318,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.2754792896663078E-3</v>
-      </c>
-    </row>
-    <row r="319" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.5436995811423736</v>
+      </c>
+    </row>
+    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C319" t="s">
         <v>198</v>
       </c>
@@ -7897,17 +7872,17 @@
         <v>205</v>
       </c>
       <c r="E319" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="F319" t="s">
         <v>285</v>
       </c>
       <c r="G319" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E319,'feed rations'!$Y$13:$Y$46,0),MATCH(C319&amp;D319,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7537387521189746E-2</v>
-      </c>
-    </row>
-    <row r="320" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.28081798598457164</v>
+      </c>
+    </row>
+    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C320" t="s">
         <v>198</v>
       </c>
@@ -7915,17 +7890,17 @@
         <v>205</v>
       </c>
       <c r="E320" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F320" t="s">
         <v>285</v>
       </c>
       <c r="G320" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E320,'feed rations'!$Y$13:$Y$46,0),MATCH(C320&amp;D320,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10472763754614865</v>
-      </c>
-    </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.42569945630839534</v>
+      </c>
+    </row>
+    <row r="321" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C321" t="s">
         <v>198</v>
       </c>
@@ -7933,17 +7908,17 @@
         <v>205</v>
       </c>
       <c r="E321" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F321" t="s">
         <v>285</v>
       </c>
       <c r="G321" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E321,'feed rations'!$Y$13:$Y$46,0),MATCH(C321&amp;D321,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.1577780834840472E-2</v>
-      </c>
-    </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.6316731967630778E-3</v>
+      </c>
+    </row>
+    <row r="322" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C322" t="s">
         <v>198</v>
       </c>
@@ -7951,17 +7926,17 @@
         <v>205</v>
       </c>
       <c r="E322" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F322" t="s">
         <v>285</v>
       </c>
       <c r="G322" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E322,'feed rations'!$Y$13:$Y$46,0),MATCH(C322&amp;D322,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.3103588551233269E-2</v>
-      </c>
-    </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C323" t="s">
         <v>198</v>
       </c>
@@ -7969,17 +7944,17 @@
         <v>205</v>
       </c>
       <c r="E323" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F323" t="s">
         <v>285</v>
       </c>
       <c r="G323" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E323,'feed rations'!$Y$13:$Y$46,0),MATCH(C323&amp;D323,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>6.41959756622177E-3</v>
-      </c>
-    </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.11088298682756348</v>
+      </c>
+    </row>
+    <row r="324" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C324" t="s">
         <v>198</v>
       </c>
@@ -7987,17 +7962,17 @@
         <v>205</v>
       </c>
       <c r="E324" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="F324" t="s">
         <v>285</v>
       </c>
       <c r="G324" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E324,'feed rations'!$Y$13:$Y$46,0),MATCH(C324&amp;D324,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.4254155119065326E-3</v>
+      </c>
+    </row>
+    <row r="325" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C325" t="s">
         <v>198</v>
       </c>
@@ -8005,17 +7980,17 @@
         <v>205</v>
       </c>
       <c r="E325" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F325" t="s">
         <v>285</v>
       </c>
       <c r="G325" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E325,'feed rations'!$Y$13:$Y$46,0),MATCH(C325&amp;D325,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.0100665353206037E-2</v>
-      </c>
-    </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.5215935420378532E-2</v>
+      </c>
+    </row>
+    <row r="326" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C326" t="s">
         <v>198</v>
       </c>
@@ -8023,17 +7998,17 @@
         <v>205</v>
       </c>
       <c r="E326" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F326" t="s">
         <v>285</v>
       </c>
       <c r="G326" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E326,'feed rations'!$Y$13:$Y$46,0),MATCH(C326&amp;D326,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.29302329044716247</v>
+      </c>
+    </row>
+    <row r="327" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C327" t="s">
         <v>198</v>
       </c>
@@ -8041,17 +8016,17 @@
         <v>205</v>
       </c>
       <c r="E327" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="F327" t="s">
         <v>285</v>
       </c>
       <c r="G327" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E327,'feed rations'!$Y$13:$Y$46,0),MATCH(C327&amp;D327,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>9.8479102711852997E-5</v>
-      </c>
-    </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.9491789324787145E-4</v>
+      </c>
+    </row>
+    <row r="328" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C328" t="s">
         <v>198</v>
       </c>
@@ -8059,17 +8034,17 @@
         <v>205</v>
       </c>
       <c r="E328" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="F328" t="s">
         <v>285</v>
       </c>
       <c r="G328" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E328,'feed rations'!$Y$13:$Y$46,0),MATCH(C328&amp;D328,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.2938639950327263E-2</v>
-      </c>
-    </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.12358451787130892</v>
+      </c>
+    </row>
+    <row r="329" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C329" t="s">
         <v>198</v>
       </c>
@@ -8077,17 +8052,17 @@
         <v>205</v>
       </c>
       <c r="E329" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="F329" t="s">
         <v>285</v>
       </c>
       <c r="G329" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E329,'feed rations'!$Y$13:$Y$46,0),MATCH(C329&amp;D329,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.9732172919853009E-2</v>
-      </c>
-    </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.3829995053964826E-5</v>
+      </c>
+    </row>
+    <row r="330" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C330" t="s">
         <v>198</v>
       </c>
@@ -8095,17 +8070,17 @@
         <v>205</v>
       </c>
       <c r="E330" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F330" t="s">
         <v>285</v>
       </c>
       <c r="G330" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E330,'feed rations'!$Y$13:$Y$46,0),MATCH(C330&amp;D330,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.31507888171457132</v>
+      </c>
+    </row>
+    <row r="331" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C331" t="s">
         <v>198</v>
       </c>
@@ -8113,17 +8088,20 @@
         <v>205</v>
       </c>
       <c r="E331" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F331" t="s">
         <v>285</v>
       </c>
       <c r="G331" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E331,'feed rations'!$Y$13:$Y$46,0),MATCH(C331&amp;D331,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.773732775523721E-5</v>
-      </c>
-    </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.2446995548568345E-5</v>
+      </c>
+    </row>
+    <row r="332" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B332" t="s">
+        <v>300</v>
+      </c>
       <c r="C332" t="s">
         <v>198</v>
       </c>
@@ -8131,151 +8109,178 @@
         <v>205</v>
       </c>
       <c r="E332" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="F332" t="s">
         <v>285</v>
       </c>
       <c r="G332" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E332,'feed rations'!$Y$13:$Y$46,0),MATCH(C332&amp;D332,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.13505509987252132</v>
+      </c>
+    </row>
+    <row r="333" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B333" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C333" s="97" t="str">
+        <f>C332</f>
+        <v>winter lamb</v>
+      </c>
+      <c r="D333" s="97" t="str">
+        <f>D332</f>
+        <v>lambs</v>
+      </c>
+      <c r="E333" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F333" s="97" t="str">
+        <f>F332</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G333" s="99">
+        <f>G332</f>
+        <v>0.13505509987252132</v>
+      </c>
+      <c r="I333" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="334" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C334" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D334" t="s">
         <v>205</v>
       </c>
-      <c r="E334" s="21" t="s">
-        <v>276</v>
+      <c r="E334" t="s">
+        <v>244</v>
       </c>
       <c r="F334" t="s">
         <v>285</v>
       </c>
       <c r="G334" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E334,'feed rations'!$Y$13:$Y$46,0),MATCH(C334&amp;D334,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.69811719906917724</v>
-      </c>
-    </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.9272895787484826E-4</v>
+      </c>
+    </row>
+    <row r="335" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C335" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D335" t="s">
         <v>205</v>
       </c>
-      <c r="E335" s="21" t="s">
-        <v>274</v>
+      <c r="E335" t="s">
+        <v>245</v>
       </c>
       <c r="F335" t="s">
         <v>285</v>
       </c>
       <c r="G335" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E335,'feed rations'!$Y$13:$Y$46,0),MATCH(C335&amp;D335,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3962343981383545</v>
-      </c>
-    </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.2754792896663078E-3</v>
+      </c>
+    </row>
+    <row r="336" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C336" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D336" t="s">
         <v>205</v>
       </c>
       <c r="E336" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="F336" t="s">
         <v>285</v>
       </c>
       <c r="G336" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E336,'feed rations'!$Y$13:$Y$46,0),MATCH(C336&amp;D336,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>83.30865242225515</v>
-      </c>
-    </row>
-    <row r="337" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.7537387521189746E-2</v>
+      </c>
+    </row>
+    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C337" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D337" t="s">
         <v>205</v>
       </c>
       <c r="E337" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="F337" t="s">
         <v>285</v>
       </c>
       <c r="G337" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E337,'feed rations'!$Y$13:$Y$46,0),MATCH(C337&amp;D337,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.1900072971810016</v>
-      </c>
-    </row>
-    <row r="338" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0.10472763754614865</v>
+      </c>
+    </row>
+    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C338" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D338" t="s">
         <v>205</v>
       </c>
       <c r="E338" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F338" t="s">
         <v>285</v>
       </c>
       <c r="G338" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E338,'feed rations'!$Y$13:$Y$46,0),MATCH(C338&amp;D338,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.6476220610438137</v>
-      </c>
-    </row>
-    <row r="339" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.1577780834840472E-2</v>
+      </c>
+    </row>
+    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C339" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D339" t="s">
         <v>205</v>
       </c>
       <c r="E339" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F339" t="s">
         <v>285</v>
       </c>
       <c r="G339" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E339,'feed rations'!$Y$13:$Y$46,0),MATCH(C339&amp;D339,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.4976741184469726</v>
-      </c>
-    </row>
-    <row r="340" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.3103588551233269E-2</v>
+      </c>
+    </row>
+    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C340" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D340" t="s">
         <v>205</v>
       </c>
       <c r="E340" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F340" t="s">
         <v>285</v>
       </c>
       <c r="G340" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E340,'feed rations'!$Y$13:$Y$46,0),MATCH(C340&amp;D340,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.544061645924192E-2</v>
-      </c>
-    </row>
-    <row r="341" spans="2:9" x14ac:dyDescent="0.25">
+        <v>6.41959756622177E-3</v>
+      </c>
+    </row>
+    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C341" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D341" t="s">
         <v>205</v>
       </c>
       <c r="E341" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="F341" t="s">
         <v>285</v>
@@ -8285,217 +8290,187 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C342" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D342" t="s">
         <v>205</v>
       </c>
       <c r="E342" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F342" t="s">
         <v>285</v>
       </c>
       <c r="G342" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E342,'feed rations'!$Y$13:$Y$46,0),MATCH(C342&amp;D342,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.65057533494867192</v>
-      </c>
-    </row>
-    <row r="343" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.0100665353206037E-2</v>
+      </c>
+    </row>
+    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C343" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D343" t="s">
         <v>205</v>
       </c>
       <c r="E343" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="F343" t="s">
         <v>285</v>
       </c>
       <c r="G343" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E343,'feed rations'!$Y$13:$Y$46,0),MATCH(C343&amp;D343,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.4230456395462613E-2</v>
-      </c>
-    </row>
-    <row r="344" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C344" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D344" t="s">
         <v>205</v>
       </c>
       <c r="E344" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F344" t="s">
         <v>285</v>
       </c>
       <c r="G344" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E344,'feed rations'!$Y$13:$Y$46,0),MATCH(C344&amp;D344,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.9275303325517821E-2</v>
-      </c>
-    </row>
-    <row r="345" spans="2:9" x14ac:dyDescent="0.25">
+        <v>9.8479102711852997E-5</v>
+      </c>
+    </row>
+    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C345" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D345" t="s">
         <v>205</v>
       </c>
       <c r="E345" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F345" t="s">
         <v>285</v>
       </c>
       <c r="G345" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E345,'feed rations'!$Y$13:$Y$46,0),MATCH(C345&amp;D345,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.7192333177936787</v>
-      </c>
-    </row>
-    <row r="346" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.2938639950327263E-2</v>
+      </c>
+    </row>
+    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C346" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D346" t="s">
         <v>205</v>
       </c>
       <c r="E346" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F346" t="s">
         <v>285</v>
       </c>
       <c r="G346" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E346,'feed rations'!$Y$13:$Y$46,0),MATCH(C346&amp;D346,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.317071789169115E-3</v>
-      </c>
-    </row>
-    <row r="347" spans="2:9" x14ac:dyDescent="0.25">
+        <v>3.9732172919853009E-2</v>
+      </c>
+    </row>
+    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C347" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D347" t="s">
         <v>205</v>
       </c>
       <c r="E347" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="F347" t="s">
         <v>285</v>
       </c>
       <c r="G347" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E347,'feed rations'!$Y$13:$Y$46,0),MATCH(C347&amp;D347,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.72509806426508272</v>
-      </c>
-    </row>
-    <row r="348" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C348" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D348" t="s">
         <v>205</v>
       </c>
       <c r="E348" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="F348" t="s">
         <v>285</v>
       </c>
       <c r="G348" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E348,'feed rations'!$Y$13:$Y$46,0),MATCH(C348&amp;D348,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>8.1143680577109445E-5</v>
-      </c>
-    </row>
-    <row r="349" spans="2:9" x14ac:dyDescent="0.25">
+        <v>4.773732775523721E-5</v>
+      </c>
+    </row>
+    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C349" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D349" t="s">
         <v>205</v>
       </c>
       <c r="E349" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="F349" t="s">
         <v>285</v>
       </c>
       <c r="G349" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E349,'feed rations'!$Y$13:$Y$46,0),MATCH(C349&amp;D349,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.8486384148858024</v>
-      </c>
-    </row>
-    <row r="350" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C350" t="s">
-        <v>204</v>
-      </c>
-      <c r="D350" t="s">
-        <v>205</v>
-      </c>
-      <c r="E350" t="s">
-        <v>242</v>
-      </c>
-      <c r="F350" t="s">
-        <v>285</v>
-      </c>
-      <c r="G350" s="3">
-        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E350,'feed rations'!$Y$13:$Y$46,0),MATCH(C350&amp;D350,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.3029312519398498E-5</v>
-      </c>
-    </row>
-    <row r="351" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B351" t="s">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C351" t="s">
         <v>204</v>
       </c>
       <c r="D351" t="s">
         <v>205</v>
       </c>
-      <c r="E351" t="s">
-        <v>243</v>
+      <c r="E351" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="F351" t="s">
         <v>285</v>
       </c>
       <c r="G351" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E351,'feed rations'!$Y$13:$Y$46,0),MATCH(C351&amp;D351,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.79239853966713902</v>
-      </c>
-    </row>
-    <row r="352" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B352" s="98" t="s">
-        <v>299</v>
-      </c>
-      <c r="C352" s="97" t="str">
-        <f>C351</f>
-        <v>other sheep</v>
-      </c>
-      <c r="D352" s="97" t="str">
-        <f>D351</f>
-        <v>lambs</v>
-      </c>
-      <c r="E352" s="97" t="s">
-        <v>298</v>
-      </c>
-      <c r="F352" s="97" t="str">
-        <f>F351</f>
-        <v>share_in_ration</v>
-      </c>
-      <c r="G352" s="99">
-        <f>G351</f>
-        <v>0.79239853966713902</v>
-      </c>
-      <c r="I352" s="97" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.69811719906917724</v>
+      </c>
+    </row>
+    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C352" t="s">
+        <v>204</v>
+      </c>
+      <c r="D352" t="s">
+        <v>205</v>
+      </c>
+      <c r="E352" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="F352" t="s">
+        <v>285</v>
+      </c>
+      <c r="G352" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E352,'feed rations'!$Y$13:$Y$46,0),MATCH(C352&amp;D352,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>1.3962343981383545</v>
+      </c>
+    </row>
+    <row r="353" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C353" t="s">
         <v>204</v>
       </c>
@@ -8503,17 +8478,17 @@
         <v>205</v>
       </c>
       <c r="E353" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F353" t="s">
         <v>285</v>
       </c>
       <c r="G353" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E353,'feed rations'!$Y$13:$Y$46,0),MATCH(C353&amp;D353,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>4.6511184632405684E-3</v>
-      </c>
-    </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
+        <v>83.30865242225515</v>
+      </c>
+    </row>
+    <row r="354" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C354" t="s">
         <v>204</v>
       </c>
@@ -8521,17 +8496,17 @@
         <v>205</v>
       </c>
       <c r="E354" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F354" t="s">
         <v>285</v>
       </c>
       <c r="G354" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E354,'feed rations'!$Y$13:$Y$46,0),MATCH(C354&amp;D354,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>1.3350746975688711E-2</v>
-      </c>
-    </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
+        <v>3.1900072971810016</v>
+      </c>
+    </row>
+    <row r="355" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C355" t="s">
         <v>204</v>
       </c>
@@ -8539,17 +8514,17 @@
         <v>205</v>
       </c>
       <c r="E355" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="F355" t="s">
         <v>285</v>
       </c>
       <c r="G355" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E355,'feed rations'!$Y$13:$Y$46,0),MATCH(C355&amp;D355,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.10289578308767665</v>
-      </c>
-    </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.6476220610438137</v>
+      </c>
+    </row>
+    <row r="356" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C356" t="s">
         <v>204</v>
       </c>
@@ -8557,17 +8532,17 @@
         <v>205</v>
       </c>
       <c r="E356" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F356" t="s">
         <v>285</v>
       </c>
       <c r="G356" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E356,'feed rations'!$Y$13:$Y$46,0),MATCH(C356&amp;D356,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.61446052117016126</v>
-      </c>
-    </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.4976741184469726</v>
+      </c>
+    </row>
+    <row r="357" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C357" t="s">
         <v>204</v>
       </c>
@@ -8575,17 +8550,17 @@
         <v>205</v>
       </c>
       <c r="E357" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F357" t="s">
         <v>285</v>
       </c>
       <c r="G357" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E357,'feed rations'!$Y$13:$Y$46,0),MATCH(C357&amp;D357,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.12660167619678325</v>
-      </c>
-    </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.544061645924192E-2</v>
+      </c>
+    </row>
+    <row r="358" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C358" t="s">
         <v>204</v>
       </c>
@@ -8593,17 +8568,17 @@
         <v>205</v>
       </c>
       <c r="E358" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F358" t="s">
         <v>285</v>
       </c>
       <c r="G358" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E358,'feed rations'!$Y$13:$Y$46,0),MATCH(C358&amp;D358,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.13555393203476143</v>
-      </c>
-    </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C359" t="s">
         <v>204</v>
       </c>
@@ -8611,17 +8586,17 @@
         <v>205</v>
       </c>
       <c r="E359" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F359" t="s">
         <v>285</v>
       </c>
       <c r="G359" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E359,'feed rations'!$Y$13:$Y$46,0),MATCH(C359&amp;D359,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>3.7665217689123641E-2</v>
-      </c>
-    </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.65057533494867192</v>
+      </c>
+    </row>
+    <row r="360" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C360" t="s">
         <v>204</v>
       </c>
@@ -8629,17 +8604,17 @@
         <v>205</v>
       </c>
       <c r="E360" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="F360" t="s">
         <v>285</v>
       </c>
       <c r="G360" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E360,'feed rations'!$Y$13:$Y$46,0),MATCH(C360&amp;D360,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.4230456395462613E-2</v>
+      </c>
+    </row>
+    <row r="361" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C361" t="s">
         <v>204</v>
       </c>
@@ -8647,17 +8622,17 @@
         <v>205</v>
       </c>
       <c r="E361" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F361" t="s">
         <v>285</v>
       </c>
       <c r="G361" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E361,'feed rations'!$Y$13:$Y$46,0),MATCH(C361&amp;D361,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.9262867400799252E-2</v>
-      </c>
-    </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.9275303325517821E-2</v>
+      </c>
+    </row>
+    <row r="362" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C362" t="s">
         <v>204</v>
       </c>
@@ -8665,17 +8640,17 @@
         <v>205</v>
       </c>
       <c r="E362" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F362" t="s">
         <v>285</v>
       </c>
       <c r="G362" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E362,'feed rations'!$Y$13:$Y$46,0),MATCH(C362&amp;D362,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.7192333177936787</v>
+      </c>
+    </row>
+    <row r="363" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C363" t="s">
         <v>204</v>
       </c>
@@ -8683,17 +8658,17 @@
         <v>205</v>
       </c>
       <c r="E363" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="F363" t="s">
         <v>285</v>
       </c>
       <c r="G363" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E363,'feed rations'!$Y$13:$Y$46,0),MATCH(C363&amp;D363,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>5.7779896686803802E-4</v>
-      </c>
-    </row>
-    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
+        <v>2.317071789169115E-3</v>
+      </c>
+    </row>
+    <row r="364" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C364" t="s">
         <v>204</v>
       </c>
@@ -8701,17 +8676,17 @@
         <v>205</v>
       </c>
       <c r="E364" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="F364" t="s">
         <v>285</v>
       </c>
       <c r="G364" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E364,'feed rations'!$Y$13:$Y$46,0),MATCH(C364&amp;D364,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>7.5913900412465971E-2</v>
-      </c>
-    </row>
-    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0.72509806426508272</v>
+      </c>
+    </row>
+    <row r="365" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C365" t="s">
         <v>204</v>
       </c>
@@ -8719,17 +8694,17 @@
         <v>205</v>
       </c>
       <c r="E365" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="F365" t="s">
         <v>285</v>
       </c>
       <c r="G365" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E365,'feed rations'!$Y$13:$Y$46,0),MATCH(C365&amp;D365,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0.23311756334422978</v>
-      </c>
-    </row>
-    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
+        <v>8.1143680577109445E-5</v>
+      </c>
+    </row>
+    <row r="366" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C366" t="s">
         <v>204</v>
       </c>
@@ -8737,17 +8712,17 @@
         <v>205</v>
       </c>
       <c r="E366" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F366" t="s">
         <v>285</v>
       </c>
       <c r="G366" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E366,'feed rations'!$Y$13:$Y$46,0),MATCH(C366&amp;D366,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1.8486384148858024</v>
+      </c>
+    </row>
+    <row r="367" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C367" t="s">
         <v>204</v>
       </c>
@@ -8755,17 +8730,20 @@
         <v>205</v>
       </c>
       <c r="E367" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F367" t="s">
         <v>285</v>
       </c>
       <c r="G367" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E367,'feed rations'!$Y$13:$Y$46,0),MATCH(C367&amp;D367,'feed rations'!$AB$12:$AI$12,0))</f>
-        <v>2.8008560088857437E-4</v>
-      </c>
-    </row>
-    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
+        <v>7.3029312519398498E-5</v>
+      </c>
+    </row>
+    <row r="368" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B368" t="s">
+        <v>300</v>
+      </c>
       <c r="C368" t="s">
         <v>204</v>
       </c>
@@ -8773,13 +8751,328 @@
         <v>205</v>
       </c>
       <c r="E368" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="F368" t="s">
         <v>285</v>
       </c>
       <c r="G368" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E368,'feed rations'!$Y$13:$Y$46,0),MATCH(C368&amp;D368,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0.79239853966713902</v>
+      </c>
+    </row>
+    <row r="369" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B369" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="C369" s="97" t="str">
+        <f>C368</f>
+        <v>other sheep</v>
+      </c>
+      <c r="D369" s="97" t="str">
+        <f>D368</f>
+        <v>lambs</v>
+      </c>
+      <c r="E369" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="F369" s="97" t="str">
+        <f>F368</f>
+        <v>share_in_ration</v>
+      </c>
+      <c r="G369" s="99">
+        <f>G368</f>
+        <v>0.79239853966713902</v>
+      </c>
+      <c r="I369" s="97" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="370" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C370" t="s">
+        <v>204</v>
+      </c>
+      <c r="D370" t="s">
+        <v>205</v>
+      </c>
+      <c r="E370" t="s">
+        <v>244</v>
+      </c>
+      <c r="F370" t="s">
+        <v>285</v>
+      </c>
+      <c r="G370" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E370,'feed rations'!$Y$13:$Y$46,0),MATCH(C370&amp;D370,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>4.6511184632405684E-3</v>
+      </c>
+    </row>
+    <row r="371" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C371" t="s">
+        <v>204</v>
+      </c>
+      <c r="D371" t="s">
+        <v>205</v>
+      </c>
+      <c r="E371" t="s">
+        <v>245</v>
+      </c>
+      <c r="F371" t="s">
+        <v>285</v>
+      </c>
+      <c r="G371" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E371,'feed rations'!$Y$13:$Y$46,0),MATCH(C371&amp;D371,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>1.3350746975688711E-2</v>
+      </c>
+    </row>
+    <row r="372" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C372" t="s">
+        <v>204</v>
+      </c>
+      <c r="D372" t="s">
+        <v>205</v>
+      </c>
+      <c r="E372" t="s">
+        <v>246</v>
+      </c>
+      <c r="F372" t="s">
+        <v>285</v>
+      </c>
+      <c r="G372" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E372,'feed rations'!$Y$13:$Y$46,0),MATCH(C372&amp;D372,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0.10289578308767665</v>
+      </c>
+    </row>
+    <row r="373" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C373" t="s">
+        <v>204</v>
+      </c>
+      <c r="D373" t="s">
+        <v>205</v>
+      </c>
+      <c r="E373" t="s">
+        <v>247</v>
+      </c>
+      <c r="F373" t="s">
+        <v>285</v>
+      </c>
+      <c r="G373" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E373,'feed rations'!$Y$13:$Y$46,0),MATCH(C373&amp;D373,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0.61446052117016126</v>
+      </c>
+    </row>
+    <row r="374" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C374" t="s">
+        <v>204</v>
+      </c>
+      <c r="D374" t="s">
+        <v>205</v>
+      </c>
+      <c r="E374" t="s">
+        <v>248</v>
+      </c>
+      <c r="F374" t="s">
+        <v>285</v>
+      </c>
+      <c r="G374" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E374,'feed rations'!$Y$13:$Y$46,0),MATCH(C374&amp;D374,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0.12660167619678325</v>
+      </c>
+    </row>
+    <row r="375" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C375" t="s">
+        <v>204</v>
+      </c>
+      <c r="D375" t="s">
+        <v>205</v>
+      </c>
+      <c r="E375" t="s">
+        <v>249</v>
+      </c>
+      <c r="F375" t="s">
+        <v>285</v>
+      </c>
+      <c r="G375" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E375,'feed rations'!$Y$13:$Y$46,0),MATCH(C375&amp;D375,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0.13555393203476143</v>
+      </c>
+    </row>
+    <row r="376" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C376" t="s">
+        <v>204</v>
+      </c>
+      <c r="D376" t="s">
+        <v>205</v>
+      </c>
+      <c r="E376" t="s">
+        <v>250</v>
+      </c>
+      <c r="F376" t="s">
+        <v>285</v>
+      </c>
+      <c r="G376" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E376,'feed rations'!$Y$13:$Y$46,0),MATCH(C376&amp;D376,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>3.7665217689123641E-2</v>
+      </c>
+    </row>
+    <row r="377" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C377" t="s">
+        <v>204</v>
+      </c>
+      <c r="D377" t="s">
+        <v>205</v>
+      </c>
+      <c r="E377" t="s">
+        <v>251</v>
+      </c>
+      <c r="F377" t="s">
+        <v>285</v>
+      </c>
+      <c r="G377" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E377,'feed rations'!$Y$13:$Y$46,0),MATCH(C377&amp;D377,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C378" t="s">
+        <v>204</v>
+      </c>
+      <c r="D378" t="s">
+        <v>205</v>
+      </c>
+      <c r="E378" t="s">
+        <v>252</v>
+      </c>
+      <c r="F378" t="s">
+        <v>285</v>
+      </c>
+      <c r="G378" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E378,'feed rations'!$Y$13:$Y$46,0),MATCH(C378&amp;D378,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>5.9262867400799252E-2</v>
+      </c>
+    </row>
+    <row r="379" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C379" t="s">
+        <v>204</v>
+      </c>
+      <c r="D379" t="s">
+        <v>205</v>
+      </c>
+      <c r="E379" t="s">
+        <v>253</v>
+      </c>
+      <c r="F379" t="s">
+        <v>285</v>
+      </c>
+      <c r="G379" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E379,'feed rations'!$Y$13:$Y$46,0),MATCH(C379&amp;D379,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C380" t="s">
+        <v>204</v>
+      </c>
+      <c r="D380" t="s">
+        <v>205</v>
+      </c>
+      <c r="E380" t="s">
+        <v>254</v>
+      </c>
+      <c r="F380" t="s">
+        <v>285</v>
+      </c>
+      <c r="G380" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E380,'feed rations'!$Y$13:$Y$46,0),MATCH(C380&amp;D380,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>5.7779896686803802E-4</v>
+      </c>
+    </row>
+    <row r="381" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C381" t="s">
+        <v>204</v>
+      </c>
+      <c r="D381" t="s">
+        <v>205</v>
+      </c>
+      <c r="E381" t="s">
+        <v>255</v>
+      </c>
+      <c r="F381" t="s">
+        <v>285</v>
+      </c>
+      <c r="G381" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E381,'feed rations'!$Y$13:$Y$46,0),MATCH(C381&amp;D381,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>7.5913900412465971E-2</v>
+      </c>
+    </row>
+    <row r="382" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C382" t="s">
+        <v>204</v>
+      </c>
+      <c r="D382" t="s">
+        <v>205</v>
+      </c>
+      <c r="E382" t="s">
+        <v>256</v>
+      </c>
+      <c r="F382" t="s">
+        <v>285</v>
+      </c>
+      <c r="G382" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E382,'feed rations'!$Y$13:$Y$46,0),MATCH(C382&amp;D382,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0.23311756334422978</v>
+      </c>
+    </row>
+    <row r="383" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C383" t="s">
+        <v>204</v>
+      </c>
+      <c r="D383" t="s">
+        <v>205</v>
+      </c>
+      <c r="E383" t="s">
+        <v>257</v>
+      </c>
+      <c r="F383" t="s">
+        <v>285</v>
+      </c>
+      <c r="G383" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E383,'feed rations'!$Y$13:$Y$46,0),MATCH(C383&amp;D383,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C384" t="s">
+        <v>204</v>
+      </c>
+      <c r="D384" t="s">
+        <v>205</v>
+      </c>
+      <c r="E384" t="s">
+        <v>258</v>
+      </c>
+      <c r="F384" t="s">
+        <v>285</v>
+      </c>
+      <c r="G384" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E384,'feed rations'!$Y$13:$Y$46,0),MATCH(C384&amp;D384,'feed rations'!$AB$12:$AI$12,0))</f>
+        <v>2.8008560088857437E-4</v>
+      </c>
+    </row>
+    <row r="385" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C385" t="s">
+        <v>204</v>
+      </c>
+      <c r="D385" t="s">
+        <v>205</v>
+      </c>
+      <c r="E385" t="s">
+        <v>259</v>
+      </c>
+      <c r="F385" t="s">
+        <v>285</v>
+      </c>
+      <c r="G385" s="3">
+        <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E385,'feed rations'!$Y$13:$Y$46,0),MATCH(C385&amp;D385,'feed rations'!$AB$12:$AI$12,0))</f>
         <v>0</v>
       </c>
     </row>

--- a/data/default/SheepHerd.xlsx
+++ b/data/default/SheepHerd.xlsx
@@ -1223,9 +1223,6 @@
     <t>mortality</t>
   </si>
   <si>
-    <t>recruitment_rate</t>
-  </si>
-  <si>
     <t>other sheep</t>
   </si>
   <si>
@@ -1274,9 +1271,6 @@
     <t>rams</t>
   </si>
   <si>
-    <t>recruitment_rate_rams</t>
-  </si>
-  <si>
     <t>assumes rams start being rams at 1 year</t>
   </si>
   <si>
@@ -1533,6 +1527,12 @@
   </si>
   <si>
     <t>assumed same as rams</t>
+  </si>
+  <si>
+    <t>replacement_rate</t>
+  </si>
+  <si>
+    <t>replacement_rate_rams</t>
   </si>
 </sst>
 </file>
@@ -2980,7 +2980,7 @@
         <v>200</v>
       </c>
       <c r="J4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2997,7 +2997,7 @@
         <v>200</v>
       </c>
       <c r="J5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -3014,12 +3014,12 @@
         <v>200</v>
       </c>
       <c r="J6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F7" t="s">
         <v>199</v>
@@ -3031,7 +3031,7 @@
         <v>200</v>
       </c>
       <c r="I7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -3042,17 +3042,17 @@
         <v>196</v>
       </c>
       <c r="F9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G9" s="89">
         <f>(2.02+1.84+2.02)/3</f>
         <v>1.9600000000000002</v>
       </c>
       <c r="H9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3060,16 +3060,16 @@
         <v>197</v>
       </c>
       <c r="F10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G10" s="92">
         <v>1.8</v>
       </c>
       <c r="H10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -3077,34 +3077,34 @@
         <v>198</v>
       </c>
       <c r="F11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G11" s="92">
         <f>(1.8+1.64+1.74)/3</f>
         <v>1.7266666666666666</v>
       </c>
       <c r="H11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G12" s="89">
         <v>1.7</v>
       </c>
       <c r="H12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -3115,7 +3115,7 @@
         <v>196</v>
       </c>
       <c r="F14" t="s">
-        <v>203</v>
+        <v>305</v>
       </c>
       <c r="G14" s="89">
         <v>23</v>
@@ -3124,7 +3124,7 @@
         <v>200</v>
       </c>
       <c r="J14" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -3132,7 +3132,7 @@
         <v>197</v>
       </c>
       <c r="F15" t="s">
-        <v>203</v>
+        <v>305</v>
       </c>
       <c r="G15" s="89">
         <v>25</v>
@@ -3141,7 +3141,7 @@
         <v>200</v>
       </c>
       <c r="J15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -3149,7 +3149,7 @@
         <v>198</v>
       </c>
       <c r="F16" t="s">
-        <v>203</v>
+        <v>305</v>
       </c>
       <c r="G16" s="89">
         <v>22</v>
@@ -3158,15 +3158,15 @@
         <v>200</v>
       </c>
       <c r="J16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F17" t="s">
-        <v>203</v>
+        <v>305</v>
       </c>
       <c r="G17" s="89">
         <v>12</v>
@@ -3175,7 +3175,7 @@
         <v>200</v>
       </c>
       <c r="I17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -3183,13 +3183,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G19" s="89">
         <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -3197,7 +3197,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F21" t="s">
-        <v>220</v>
+        <v>306</v>
       </c>
       <c r="G21" s="93">
         <f>1/(4.5-1)*100</f>
@@ -3207,10 +3207,10 @@
         <v>200</v>
       </c>
       <c r="I21" t="s">
+        <v>219</v>
+      </c>
+      <c r="J21" t="s">
         <v>221</v>
-      </c>
-      <c r="J21" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -3218,16 +3218,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G23" s="89">
         <v>12</v>
       </c>
       <c r="H23" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3235,16 +3235,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G25" s="89">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="H25" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -3252,7 +3252,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B27" s="44"/>
       <c r="C27" s="44"/>
@@ -3284,10 +3284,10 @@
         <v>200</v>
       </c>
       <c r="I29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -3307,7 +3307,7 @@
         <v>200</v>
       </c>
       <c r="J30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -3327,12 +3327,12 @@
         <v>200</v>
       </c>
       <c r="J31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D32" t="s">
         <v>201</v>
@@ -3347,7 +3347,7 @@
         <v>200</v>
       </c>
       <c r="I32" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -3355,7 +3355,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F34" t="s">
         <v>202</v>
@@ -3367,7 +3367,7 @@
         <v>200</v>
       </c>
       <c r="I34" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -3378,7 +3378,7 @@
         <v>196</v>
       </c>
       <c r="D36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F36" t="s">
         <v>202</v>
@@ -3391,10 +3391,10 @@
         <v>200</v>
       </c>
       <c r="I36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -3402,7 +3402,7 @@
         <v>197</v>
       </c>
       <c r="D37" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F37" t="s">
         <v>202</v>
@@ -3414,7 +3414,7 @@
         <v>200</v>
       </c>
       <c r="J37" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -3422,7 +3422,7 @@
         <v>198</v>
       </c>
       <c r="D38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F38" t="s">
         <v>202</v>
@@ -3435,15 +3435,15 @@
         <v>200</v>
       </c>
       <c r="J38" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" t="s">
         <v>204</v>
-      </c>
-      <c r="D39" t="s">
-        <v>205</v>
       </c>
       <c r="F39" t="s">
         <v>202</v>
@@ -3455,7 +3455,7 @@
         <v>200</v>
       </c>
       <c r="I39" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -3463,7 +3463,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="44" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B41" s="44"/>
       <c r="C41" s="44"/>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G42" s="89"/>
     </row>
@@ -3486,7 +3486,7 @@
         <v>196</v>
       </c>
       <c r="F43" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G43" s="89">
         <f>30*1.1</f>
@@ -3496,7 +3496,7 @@
         <v>200</v>
       </c>
       <c r="I43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -3504,7 +3504,7 @@
         <v>197</v>
       </c>
       <c r="F44" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G44" s="95">
         <f>18</f>
@@ -3519,7 +3519,7 @@
         <v>198</v>
       </c>
       <c r="F45" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G45" s="95">
         <f>13*1.1</f>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F46" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G46" s="95">
         <f>39*1.1</f>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B48" s="44"/>
       <c r="C48" s="44"/>
@@ -3569,20 +3569,20 @@
         <v>196</v>
       </c>
       <c r="D50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G50" s="89">
         <f>(160+181+163)/3</f>
         <v>168</v>
       </c>
       <c r="H50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J50" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" spans="3:10" x14ac:dyDescent="0.25">
@@ -3590,19 +3590,19 @@
         <v>197</v>
       </c>
       <c r="D51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G51" s="89">
         <v>113</v>
       </c>
       <c r="H51" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J51" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.25">
@@ -3610,39 +3610,39 @@
         <v>198</v>
       </c>
       <c r="D52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F52" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G52" s="89">
         <v>308</v>
       </c>
       <c r="H52" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J52" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D53" t="s">
         <v>204</v>
       </c>
-      <c r="D53" t="s">
-        <v>205</v>
-      </c>
       <c r="F53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G53" s="89">
         <v>168</v>
       </c>
       <c r="H53" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I53" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="3:10" x14ac:dyDescent="0.25">
@@ -3656,17 +3656,17 @@
         <v>201</v>
       </c>
       <c r="F55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G55" s="89">
         <f>(30+27+30)/3</f>
         <v>29</v>
       </c>
       <c r="H55" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J55" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="3:10" x14ac:dyDescent="0.25">
@@ -3677,16 +3677,16 @@
         <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G56" s="89">
         <v>33</v>
       </c>
       <c r="H56" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J56" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="3:10" x14ac:dyDescent="0.25">
@@ -3697,37 +3697,37 @@
         <v>201</v>
       </c>
       <c r="F57" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G57" s="89">
         <f>(30+27+30)/3</f>
         <v>29</v>
       </c>
       <c r="H57" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J57" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D58" t="s">
         <v>201</v>
       </c>
       <c r="F58" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G58" s="89">
         <v>29</v>
       </c>
       <c r="H58" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I58" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="3:10" x14ac:dyDescent="0.25">
@@ -3738,19 +3738,19 @@
         <v>196</v>
       </c>
       <c r="D60" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F60" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G60" s="89">
         <v>45</v>
       </c>
       <c r="H60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J60" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="61" spans="3:10" x14ac:dyDescent="0.25">
@@ -3758,19 +3758,19 @@
         <v>197</v>
       </c>
       <c r="D61" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G61" s="89">
         <v>48</v>
       </c>
       <c r="H61" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J61" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="62" spans="3:10" x14ac:dyDescent="0.25">
@@ -3778,39 +3778,39 @@
         <v>198</v>
       </c>
       <c r="D62" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F62" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G62" s="89">
         <v>45</v>
       </c>
       <c r="H62" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J62" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="63" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D63" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F63" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G63" s="89">
         <v>45</v>
       </c>
       <c r="H63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I63" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="3:10" x14ac:dyDescent="0.25">
@@ -3821,20 +3821,20 @@
         <v>196</v>
       </c>
       <c r="D65" t="s">
+        <v>204</v>
+      </c>
+      <c r="F65" t="s">
         <v>205</v>
-      </c>
-      <c r="F65" t="s">
-        <v>206</v>
       </c>
       <c r="G65" s="93">
         <f>(20.2+19.2+20.2)/3</f>
         <v>19.866666666666664</v>
       </c>
       <c r="H65" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J65" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="3:10" x14ac:dyDescent="0.25">
@@ -3842,19 +3842,19 @@
         <v>197</v>
       </c>
       <c r="D66" t="s">
+        <v>204</v>
+      </c>
+      <c r="F66" t="s">
         <v>205</v>
-      </c>
-      <c r="F66" t="s">
-        <v>206</v>
       </c>
       <c r="G66" s="89">
         <v>20.5</v>
       </c>
       <c r="H66" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J66" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="3:10" x14ac:dyDescent="0.25">
@@ -3862,40 +3862,40 @@
         <v>198</v>
       </c>
       <c r="D67" t="s">
+        <v>204</v>
+      </c>
+      <c r="F67" t="s">
         <v>205</v>
-      </c>
-      <c r="F67" t="s">
-        <v>206</v>
       </c>
       <c r="G67" s="93">
         <f>(20.2+19.2+20.2)/3</f>
         <v>19.866666666666664</v>
       </c>
       <c r="H67" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J67" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
+        <v>203</v>
+      </c>
+      <c r="D68" t="s">
         <v>204</v>
       </c>
-      <c r="D68" t="s">
+      <c r="F68" t="s">
         <v>205</v>
-      </c>
-      <c r="F68" t="s">
-        <v>206</v>
       </c>
       <c r="G68" s="89">
         <v>19.899999999999999</v>
       </c>
       <c r="H68" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I68" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="69" spans="3:10" x14ac:dyDescent="0.25">
@@ -3909,17 +3909,17 @@
         <v>201</v>
       </c>
       <c r="F70" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G70" s="93">
         <f>G75</f>
         <v>2.2727272727272729</v>
       </c>
       <c r="H70" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I70" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="3:10" x14ac:dyDescent="0.25">
@@ -3930,17 +3930,17 @@
         <v>201</v>
       </c>
       <c r="F71" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G71" s="93">
         <f t="shared" ref="G71:G73" si="0">G76</f>
         <v>2.0833333333333335</v>
       </c>
       <c r="H71" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I71" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="72" spans="3:10" x14ac:dyDescent="0.25">
@@ -3951,38 +3951,38 @@
         <v>201</v>
       </c>
       <c r="F72" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G72" s="93">
         <f t="shared" si="0"/>
         <v>2.2727272727272729</v>
       </c>
       <c r="H72" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I72" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C73" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D73" t="s">
         <v>201</v>
       </c>
       <c r="F73" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G73" s="93">
         <f t="shared" si="0"/>
         <v>2.2727272727272729</v>
       </c>
       <c r="H73" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I73" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="74" spans="3:10" x14ac:dyDescent="0.25">
@@ -3993,20 +3993,20 @@
         <v>196</v>
       </c>
       <c r="D75" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F75" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G75" s="93">
         <f>1/0.44</f>
         <v>2.2727272727272729</v>
       </c>
       <c r="H75" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J75" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" spans="3:10" x14ac:dyDescent="0.25">
@@ -4014,20 +4014,20 @@
         <v>197</v>
       </c>
       <c r="D76" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F76" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G76" s="93">
         <f>1/0.48</f>
         <v>2.0833333333333335</v>
       </c>
       <c r="H76" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J76" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="3:10" x14ac:dyDescent="0.25">
@@ -4035,41 +4035,41 @@
         <v>198</v>
       </c>
       <c r="D77" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F77" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G77" s="93">
         <f>1/0.44</f>
         <v>2.2727272727272729</v>
       </c>
       <c r="H77" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J77" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D78" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F78" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G78" s="93">
         <f>G75</f>
         <v>2.2727272727272729</v>
       </c>
       <c r="H78" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I78" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="79" spans="3:10" x14ac:dyDescent="0.25">
@@ -4080,20 +4080,20 @@
         <v>196</v>
       </c>
       <c r="D80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F80" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G80" s="93">
         <f>1/0.43</f>
         <v>2.3255813953488373</v>
       </c>
       <c r="H80" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J80" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -4101,20 +4101,20 @@
         <v>197</v>
       </c>
       <c r="D81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F81" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G81" s="93">
         <f>1/0.45</f>
         <v>2.2222222222222223</v>
       </c>
       <c r="H81" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J81" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -4122,41 +4122,41 @@
         <v>198</v>
       </c>
       <c r="D82" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F82" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G82" s="93">
         <f>1/0.42</f>
         <v>2.3809523809523809</v>
       </c>
       <c r="H82" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J82" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C83" t="s">
+        <v>203</v>
+      </c>
+      <c r="D83" t="s">
         <v>204</v>
       </c>
-      <c r="D83" t="s">
-        <v>205</v>
-      </c>
       <c r="F83" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G83" s="93">
         <f>G80</f>
         <v>2.3255813953488373</v>
       </c>
       <c r="H83" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I83" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -4164,7 +4164,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="44" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B85" s="44"/>
       <c r="C85" s="44"/>
@@ -4174,7 +4174,7 @@
       <c r="G85" s="45"/>
       <c r="H85" s="45"/>
       <c r="I85" s="45" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J85" s="46"/>
     </row>
@@ -4183,14 +4183,14 @@
         <v>196</v>
       </c>
       <c r="F87" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G87" s="19">
         <f>'feed rations'!G5</f>
         <v>748.40000000000009</v>
       </c>
       <c r="H87" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J87" t="s">
         <v>163</v>
@@ -4201,14 +4201,14 @@
         <v>197</v>
       </c>
       <c r="F88" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G88" s="19">
         <f>'feed rations'!G6</f>
         <v>554.1</v>
       </c>
       <c r="H88" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J88" t="s">
         <v>163</v>
@@ -4219,14 +4219,14 @@
         <v>198</v>
       </c>
       <c r="F89" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G89" s="19">
         <f>'feed rations'!G7</f>
         <v>726.26666666666654</v>
       </c>
       <c r="H89" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J89" t="s">
         <v>163</v>
@@ -4234,20 +4234,20 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C90" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F90" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G90" s="19">
         <f>'feed rations'!G8</f>
         <v>748.40000000000009</v>
       </c>
       <c r="H90" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I90" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -4255,17 +4255,17 @@
         <v>196</v>
       </c>
       <c r="D92" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F92" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G92" s="19">
         <f>'feed rations'!N5</f>
         <v>157.56666666666666</v>
       </c>
       <c r="H92" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J92" t="s">
         <v>163</v>
@@ -4276,17 +4276,17 @@
         <v>197</v>
       </c>
       <c r="D93" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F93" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G93" s="19">
         <f>'feed rations'!N6</f>
         <v>114</v>
       </c>
       <c r="H93" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J93" t="s">
         <v>163</v>
@@ -4297,17 +4297,17 @@
         <v>198</v>
       </c>
       <c r="D94" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F94" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G94" s="19">
         <f>'feed rations'!N7</f>
         <v>254.56666666666669</v>
       </c>
       <c r="H94" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J94" t="s">
         <v>163</v>
@@ -4315,28 +4315,28 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
+        <v>203</v>
+      </c>
+      <c r="D95" t="s">
         <v>204</v>
       </c>
-      <c r="D95" t="s">
-        <v>205</v>
-      </c>
       <c r="F95" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G95" s="19">
         <f>'feed rations'!N8</f>
         <v>157.56666666666666</v>
       </c>
       <c r="H95" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I95" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="44" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B97" s="44"/>
       <c r="C97" s="44"/>
@@ -4345,23 +4345,23 @@
       <c r="F97" s="45"/>
       <c r="G97" s="45"/>
       <c r="H97" s="45" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I97" s="45" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J97" s="46"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F98" s="91" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G98" s="91">
         <v>0</v>
       </c>
       <c r="H98" s="91"/>
       <c r="I98" s="91" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -4369,10 +4369,10 @@
         <v>196</v>
       </c>
       <c r="E99" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F99" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G99" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E99,'feed rations'!$Y$13:$Y$46,0),MATCH(C99&amp;D99,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4384,10 +4384,10 @@
         <v>196</v>
       </c>
       <c r="E100" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F100" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G100" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E100,'feed rations'!$Y$13:$Y$46,0),MATCH(C100&amp;D100,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4399,10 +4399,10 @@
         <v>196</v>
       </c>
       <c r="E101" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F101" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G101" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E101,'feed rations'!$Y$13:$Y$46,0),MATCH(C101&amp;D101,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4414,10 +4414,10 @@
         <v>196</v>
       </c>
       <c r="E102" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F102" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G102" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E102,'feed rations'!$Y$13:$Y$46,0),MATCH(C102&amp;D102,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4429,10 +4429,10 @@
         <v>196</v>
       </c>
       <c r="E103" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F103" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G103" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E103,'feed rations'!$Y$13:$Y$46,0),MATCH(C103&amp;D103,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4444,10 +4444,10 @@
         <v>196</v>
       </c>
       <c r="E104" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F104" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G104" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E104,'feed rations'!$Y$13:$Y$46,0),MATCH(C104&amp;D104,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4459,10 +4459,10 @@
         <v>196</v>
       </c>
       <c r="E105" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F105" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G105" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E105,'feed rations'!$Y$13:$Y$46,0),MATCH(C105&amp;D105,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4474,10 +4474,10 @@
         <v>196</v>
       </c>
       <c r="E106" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F106" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G106" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E106,'feed rations'!$Y$13:$Y$46,0),MATCH(C106&amp;D106,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4489,10 +4489,10 @@
         <v>196</v>
       </c>
       <c r="E107" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F107" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G107" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E107,'feed rations'!$Y$13:$Y$46,0),MATCH(C107&amp;D107,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4504,10 +4504,10 @@
         <v>196</v>
       </c>
       <c r="E108" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F108" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G108" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E108,'feed rations'!$Y$13:$Y$46,0),MATCH(C108&amp;D108,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4519,10 +4519,10 @@
         <v>196</v>
       </c>
       <c r="E109" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F109" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G109" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E109,'feed rations'!$Y$13:$Y$46,0),MATCH(C109&amp;D109,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4534,10 +4534,10 @@
         <v>196</v>
       </c>
       <c r="E110" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F110" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G110" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E110,'feed rations'!$Y$13:$Y$46,0),MATCH(C110&amp;D110,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4549,10 +4549,10 @@
         <v>196</v>
       </c>
       <c r="E111" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F111" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G111" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E111,'feed rations'!$Y$13:$Y$46,0),MATCH(C111&amp;D111,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4564,10 +4564,10 @@
         <v>196</v>
       </c>
       <c r="E112" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F112" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G112" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E112,'feed rations'!$Y$13:$Y$46,0),MATCH(C112&amp;D112,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4579,10 +4579,10 @@
         <v>196</v>
       </c>
       <c r="E113" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F113" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G113" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E113,'feed rations'!$Y$13:$Y$46,0),MATCH(C113&amp;D113,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4594,10 +4594,10 @@
         <v>196</v>
       </c>
       <c r="E114" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F114" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G114" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E114,'feed rations'!$Y$13:$Y$46,0),MATCH(C114&amp;D114,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4609,10 +4609,10 @@
         <v>196</v>
       </c>
       <c r="E115" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G115" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E115,'feed rations'!$Y$13:$Y$46,0),MATCH(C115&amp;D115,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4621,16 +4621,16 @@
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C116" t="s">
         <v>196</v>
       </c>
       <c r="E116" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F116" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G116" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E116,'feed rations'!$Y$13:$Y$46,0),MATCH(C116&amp;D116,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4639,14 +4639,14 @@
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B117" s="98" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C117" s="97" t="str">
         <f>C116</f>
         <v>autumn lamb</v>
       </c>
       <c r="E117" s="97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F117" s="97" t="str">
         <f>F116</f>
@@ -4657,7 +4657,7 @@
         <v>0.21035091095436523</v>
       </c>
       <c r="I117" s="97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.25">
@@ -4665,10 +4665,10 @@
         <v>196</v>
       </c>
       <c r="E118" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F118" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G118" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E118,'feed rations'!$Y$13:$Y$46,0),MATCH(C118&amp;D118,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4680,10 +4680,10 @@
         <v>196</v>
       </c>
       <c r="E119" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F119" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G119" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E119,'feed rations'!$Y$13:$Y$46,0),MATCH(C119&amp;D119,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4695,10 +4695,10 @@
         <v>196</v>
       </c>
       <c r="E120" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F120" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G120" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E120,'feed rations'!$Y$13:$Y$46,0),MATCH(C120&amp;D120,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4710,10 +4710,10 @@
         <v>196</v>
       </c>
       <c r="E121" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F121" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G121" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E121,'feed rations'!$Y$13:$Y$46,0),MATCH(C121&amp;D121,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4725,10 +4725,10 @@
         <v>196</v>
       </c>
       <c r="E122" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F122" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G122" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E122,'feed rations'!$Y$13:$Y$46,0),MATCH(C122&amp;D122,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4740,10 +4740,10 @@
         <v>196</v>
       </c>
       <c r="E123" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F123" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G123" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E123,'feed rations'!$Y$13:$Y$46,0),MATCH(C123&amp;D123,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4755,10 +4755,10 @@
         <v>196</v>
       </c>
       <c r="E124" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F124" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G124" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E124,'feed rations'!$Y$13:$Y$46,0),MATCH(C124&amp;D124,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4770,10 +4770,10 @@
         <v>196</v>
       </c>
       <c r="E125" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F125" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G125" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E125,'feed rations'!$Y$13:$Y$46,0),MATCH(C125&amp;D125,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4785,10 +4785,10 @@
         <v>196</v>
       </c>
       <c r="E126" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F126" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G126" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E126,'feed rations'!$Y$13:$Y$46,0),MATCH(C126&amp;D126,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4800,10 +4800,10 @@
         <v>196</v>
       </c>
       <c r="E127" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F127" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G127" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E127,'feed rations'!$Y$13:$Y$46,0),MATCH(C127&amp;D127,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4815,10 +4815,10 @@
         <v>196</v>
       </c>
       <c r="E128" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F128" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G128" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E128,'feed rations'!$Y$13:$Y$46,0),MATCH(C128&amp;D128,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4830,10 +4830,10 @@
         <v>196</v>
       </c>
       <c r="E129" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F129" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G129" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E129,'feed rations'!$Y$13:$Y$46,0),MATCH(C129&amp;D129,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4845,10 +4845,10 @@
         <v>196</v>
       </c>
       <c r="E130" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F130" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G130" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E130,'feed rations'!$Y$13:$Y$46,0),MATCH(C130&amp;D130,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4860,10 +4860,10 @@
         <v>196</v>
       </c>
       <c r="E131" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F131" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G131" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E131,'feed rations'!$Y$13:$Y$46,0),MATCH(C131&amp;D131,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4875,10 +4875,10 @@
         <v>196</v>
       </c>
       <c r="E132" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F132" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G132" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E132,'feed rations'!$Y$13:$Y$46,0),MATCH(C132&amp;D132,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4890,10 +4890,10 @@
         <v>196</v>
       </c>
       <c r="E133" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F133" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G133" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E133,'feed rations'!$Y$13:$Y$46,0),MATCH(C133&amp;D133,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4905,10 +4905,10 @@
         <v>197</v>
       </c>
       <c r="E135" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F135" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G135" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E135,'feed rations'!$Y$13:$Y$46,0),MATCH(C135&amp;D135,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4920,10 +4920,10 @@
         <v>197</v>
       </c>
       <c r="E136" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F136" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G136" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E136,'feed rations'!$Y$13:$Y$46,0),MATCH(C136&amp;D136,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4935,10 +4935,10 @@
         <v>197</v>
       </c>
       <c r="E137" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F137" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G137" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E137,'feed rations'!$Y$13:$Y$46,0),MATCH(C137&amp;D137,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4950,10 +4950,10 @@
         <v>197</v>
       </c>
       <c r="E138" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F138" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G138" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E138,'feed rations'!$Y$13:$Y$46,0),MATCH(C138&amp;D138,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4965,10 +4965,10 @@
         <v>197</v>
       </c>
       <c r="E139" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F139" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G139" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E139,'feed rations'!$Y$13:$Y$46,0),MATCH(C139&amp;D139,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4980,10 +4980,10 @@
         <v>197</v>
       </c>
       <c r="E140" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F140" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G140" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E140,'feed rations'!$Y$13:$Y$46,0),MATCH(C140&amp;D140,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -4995,10 +4995,10 @@
         <v>197</v>
       </c>
       <c r="E141" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F141" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G141" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E141,'feed rations'!$Y$13:$Y$46,0),MATCH(C141&amp;D141,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5010,10 +5010,10 @@
         <v>197</v>
       </c>
       <c r="E142" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F142" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G142" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E142,'feed rations'!$Y$13:$Y$46,0),MATCH(C142&amp;D142,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5025,10 +5025,10 @@
         <v>197</v>
       </c>
       <c r="E143" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F143" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G143" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E143,'feed rations'!$Y$13:$Y$46,0),MATCH(C143&amp;D143,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5040,10 +5040,10 @@
         <v>197</v>
       </c>
       <c r="E144" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F144" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G144" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E144,'feed rations'!$Y$13:$Y$46,0),MATCH(C144&amp;D144,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5055,10 +5055,10 @@
         <v>197</v>
       </c>
       <c r="E145" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F145" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G145" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E145,'feed rations'!$Y$13:$Y$46,0),MATCH(C145&amp;D145,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5070,10 +5070,10 @@
         <v>197</v>
       </c>
       <c r="E146" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F146" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G146" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E146,'feed rations'!$Y$13:$Y$46,0),MATCH(C146&amp;D146,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5085,10 +5085,10 @@
         <v>197</v>
       </c>
       <c r="E147" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F147" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G147" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E147,'feed rations'!$Y$13:$Y$46,0),MATCH(C147&amp;D147,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5100,10 +5100,10 @@
         <v>197</v>
       </c>
       <c r="E148" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F148" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G148" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E148,'feed rations'!$Y$13:$Y$46,0),MATCH(C148&amp;D148,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5115,10 +5115,10 @@
         <v>197</v>
       </c>
       <c r="E149" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F149" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G149" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E149,'feed rations'!$Y$13:$Y$46,0),MATCH(C149&amp;D149,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5130,10 +5130,10 @@
         <v>197</v>
       </c>
       <c r="E150" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F150" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G150" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E150,'feed rations'!$Y$13:$Y$46,0),MATCH(C150&amp;D150,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5145,10 +5145,10 @@
         <v>197</v>
       </c>
       <c r="E151" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F151" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G151" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E151,'feed rations'!$Y$13:$Y$46,0),MATCH(C151&amp;D151,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5157,16 +5157,16 @@
     </row>
     <row r="152" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C152" t="s">
         <v>197</v>
       </c>
       <c r="E152" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F152" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G152" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E152,'feed rations'!$Y$13:$Y$46,0),MATCH(C152&amp;D152,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5175,14 +5175,14 @@
     </row>
     <row r="153" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B153" s="98" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C153" s="97" t="str">
         <f>C152</f>
         <v>spring lamb</v>
       </c>
       <c r="E153" s="97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F153" s="97" t="str">
         <f>F152</f>
@@ -5193,7 +5193,7 @@
         <v>0.60414683073671682</v>
       </c>
       <c r="I153" s="97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="154" spans="2:9" x14ac:dyDescent="0.25">
@@ -5201,10 +5201,10 @@
         <v>197</v>
       </c>
       <c r="E154" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F154" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G154" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E154,'feed rations'!$Y$13:$Y$46,0),MATCH(C154&amp;D154,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5216,10 +5216,10 @@
         <v>197</v>
       </c>
       <c r="E155" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F155" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G155" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E155,'feed rations'!$Y$13:$Y$46,0),MATCH(C155&amp;D155,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5231,10 +5231,10 @@
         <v>197</v>
       </c>
       <c r="E156" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F156" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G156" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E156,'feed rations'!$Y$13:$Y$46,0),MATCH(C156&amp;D156,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5246,10 +5246,10 @@
         <v>197</v>
       </c>
       <c r="E157" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F157" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G157" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E157,'feed rations'!$Y$13:$Y$46,0),MATCH(C157&amp;D157,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5261,10 +5261,10 @@
         <v>197</v>
       </c>
       <c r="E158" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F158" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G158" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E158,'feed rations'!$Y$13:$Y$46,0),MATCH(C158&amp;D158,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5276,10 +5276,10 @@
         <v>197</v>
       </c>
       <c r="E159" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F159" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G159" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E159,'feed rations'!$Y$13:$Y$46,0),MATCH(C159&amp;D159,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5291,10 +5291,10 @@
         <v>197</v>
       </c>
       <c r="E160" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F160" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G160" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E160,'feed rations'!$Y$13:$Y$46,0),MATCH(C160&amp;D160,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5306,10 +5306,10 @@
         <v>197</v>
       </c>
       <c r="E161" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F161" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G161" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E161,'feed rations'!$Y$13:$Y$46,0),MATCH(C161&amp;D161,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5321,10 +5321,10 @@
         <v>197</v>
       </c>
       <c r="E162" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F162" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G162" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E162,'feed rations'!$Y$13:$Y$46,0),MATCH(C162&amp;D162,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5336,10 +5336,10 @@
         <v>197</v>
       </c>
       <c r="E163" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F163" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G163" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E163,'feed rations'!$Y$13:$Y$46,0),MATCH(C163&amp;D163,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5351,10 +5351,10 @@
         <v>197</v>
       </c>
       <c r="E164" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F164" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G164" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E164,'feed rations'!$Y$13:$Y$46,0),MATCH(C164&amp;D164,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5366,10 +5366,10 @@
         <v>197</v>
       </c>
       <c r="E165" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F165" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G165" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E165,'feed rations'!$Y$13:$Y$46,0),MATCH(C165&amp;D165,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5381,10 +5381,10 @@
         <v>197</v>
       </c>
       <c r="E166" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F166" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G166" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E166,'feed rations'!$Y$13:$Y$46,0),MATCH(C166&amp;D166,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5396,10 +5396,10 @@
         <v>197</v>
       </c>
       <c r="E167" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F167" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G167" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E167,'feed rations'!$Y$13:$Y$46,0),MATCH(C167&amp;D167,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5411,10 +5411,10 @@
         <v>197</v>
       </c>
       <c r="E168" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F168" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G168" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E168,'feed rations'!$Y$13:$Y$46,0),MATCH(C168&amp;D168,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5426,10 +5426,10 @@
         <v>197</v>
       </c>
       <c r="E169" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F169" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G169" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E169,'feed rations'!$Y$13:$Y$46,0),MATCH(C169&amp;D169,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5441,10 +5441,10 @@
         <v>198</v>
       </c>
       <c r="E171" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F171" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G171" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E171,'feed rations'!$Y$13:$Y$46,0),MATCH(C171&amp;D171,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5456,10 +5456,10 @@
         <v>198</v>
       </c>
       <c r="E172" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F172" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G172" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E172,'feed rations'!$Y$13:$Y$46,0),MATCH(C172&amp;D172,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5471,10 +5471,10 @@
         <v>198</v>
       </c>
       <c r="E173" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F173" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G173" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E173,'feed rations'!$Y$13:$Y$46,0),MATCH(C173&amp;D173,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5486,10 +5486,10 @@
         <v>198</v>
       </c>
       <c r="E174" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F174" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G174" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E174,'feed rations'!$Y$13:$Y$46,0),MATCH(C174&amp;D174,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5501,10 +5501,10 @@
         <v>198</v>
       </c>
       <c r="E175" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F175" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G175" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E175,'feed rations'!$Y$13:$Y$46,0),MATCH(C175&amp;D175,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5516,10 +5516,10 @@
         <v>198</v>
       </c>
       <c r="E176" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F176" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G176" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E176,'feed rations'!$Y$13:$Y$46,0),MATCH(C176&amp;D176,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5531,10 +5531,10 @@
         <v>198</v>
       </c>
       <c r="E177" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F177" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G177" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E177,'feed rations'!$Y$13:$Y$46,0),MATCH(C177&amp;D177,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5546,10 +5546,10 @@
         <v>198</v>
       </c>
       <c r="E178" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F178" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G178" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E178,'feed rations'!$Y$13:$Y$46,0),MATCH(C178&amp;D178,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5561,10 +5561,10 @@
         <v>198</v>
       </c>
       <c r="E179" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F179" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G179" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E179,'feed rations'!$Y$13:$Y$46,0),MATCH(C179&amp;D179,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5576,10 +5576,10 @@
         <v>198</v>
       </c>
       <c r="E180" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F180" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G180" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E180,'feed rations'!$Y$13:$Y$46,0),MATCH(C180&amp;D180,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5591,10 +5591,10 @@
         <v>198</v>
       </c>
       <c r="E181" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F181" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G181" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E181,'feed rations'!$Y$13:$Y$46,0),MATCH(C181&amp;D181,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5606,10 +5606,10 @@
         <v>198</v>
       </c>
       <c r="E182" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F182" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G182" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E182,'feed rations'!$Y$13:$Y$46,0),MATCH(C182&amp;D182,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5621,10 +5621,10 @@
         <v>198</v>
       </c>
       <c r="E183" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F183" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G183" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E183,'feed rations'!$Y$13:$Y$46,0),MATCH(C183&amp;D183,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5636,10 +5636,10 @@
         <v>198</v>
       </c>
       <c r="E184" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F184" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G184" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E184,'feed rations'!$Y$13:$Y$46,0),MATCH(C184&amp;D184,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5651,10 +5651,10 @@
         <v>198</v>
       </c>
       <c r="E185" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F185" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G185" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E185,'feed rations'!$Y$13:$Y$46,0),MATCH(C185&amp;D185,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5666,10 +5666,10 @@
         <v>198</v>
       </c>
       <c r="E186" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F186" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G186" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E186,'feed rations'!$Y$13:$Y$46,0),MATCH(C186&amp;D186,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5681,10 +5681,10 @@
         <v>198</v>
       </c>
       <c r="E187" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F187" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G187" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E187,'feed rations'!$Y$13:$Y$46,0),MATCH(C187&amp;D187,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5693,16 +5693,16 @@
     </row>
     <row r="188" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C188" t="s">
         <v>198</v>
       </c>
       <c r="E188" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F188" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G188" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E188,'feed rations'!$Y$13:$Y$46,0),MATCH(C188&amp;D188,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5711,14 +5711,14 @@
     </row>
     <row r="189" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B189" s="98" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C189" s="97" t="str">
         <f>C188</f>
         <v>winter lamb</v>
       </c>
       <c r="E189" s="97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F189" s="97" t="str">
         <f>F188</f>
@@ -5729,7 +5729,7 @@
         <v>3.4881154204077169E-2</v>
       </c>
       <c r="I189" s="97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="190" spans="2:9" x14ac:dyDescent="0.25">
@@ -5737,10 +5737,10 @@
         <v>198</v>
       </c>
       <c r="E190" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F190" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G190" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E190,'feed rations'!$Y$13:$Y$46,0),MATCH(C190&amp;D190,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5752,10 +5752,10 @@
         <v>198</v>
       </c>
       <c r="E191" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F191" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G191" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E191,'feed rations'!$Y$13:$Y$46,0),MATCH(C191&amp;D191,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5767,10 +5767,10 @@
         <v>198</v>
       </c>
       <c r="E192" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F192" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G192" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E192,'feed rations'!$Y$13:$Y$46,0),MATCH(C192&amp;D192,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5782,10 +5782,10 @@
         <v>198</v>
       </c>
       <c r="E193" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F193" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G193" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E193,'feed rations'!$Y$13:$Y$46,0),MATCH(C193&amp;D193,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5797,10 +5797,10 @@
         <v>198</v>
       </c>
       <c r="E194" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F194" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G194" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E194,'feed rations'!$Y$13:$Y$46,0),MATCH(C194&amp;D194,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5812,10 +5812,10 @@
         <v>198</v>
       </c>
       <c r="E195" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F195" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G195" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E195,'feed rations'!$Y$13:$Y$46,0),MATCH(C195&amp;D195,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5827,10 +5827,10 @@
         <v>198</v>
       </c>
       <c r="E196" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F196" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G196" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E196,'feed rations'!$Y$13:$Y$46,0),MATCH(C196&amp;D196,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5842,10 +5842,10 @@
         <v>198</v>
       </c>
       <c r="E197" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F197" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G197" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E197,'feed rations'!$Y$13:$Y$46,0),MATCH(C197&amp;D197,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5857,10 +5857,10 @@
         <v>198</v>
       </c>
       <c r="E198" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F198" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G198" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E198,'feed rations'!$Y$13:$Y$46,0),MATCH(C198&amp;D198,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5872,10 +5872,10 @@
         <v>198</v>
       </c>
       <c r="E199" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F199" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G199" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E199,'feed rations'!$Y$13:$Y$46,0),MATCH(C199&amp;D199,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5887,10 +5887,10 @@
         <v>198</v>
       </c>
       <c r="E200" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F200" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G200" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E200,'feed rations'!$Y$13:$Y$46,0),MATCH(C200&amp;D200,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5902,10 +5902,10 @@
         <v>198</v>
       </c>
       <c r="E201" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F201" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G201" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E201,'feed rations'!$Y$13:$Y$46,0),MATCH(C201&amp;D201,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5917,10 +5917,10 @@
         <v>198</v>
       </c>
       <c r="E202" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F202" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G202" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E202,'feed rations'!$Y$13:$Y$46,0),MATCH(C202&amp;D202,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5932,10 +5932,10 @@
         <v>198</v>
       </c>
       <c r="E203" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F203" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G203" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E203,'feed rations'!$Y$13:$Y$46,0),MATCH(C203&amp;D203,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5947,10 +5947,10 @@
         <v>198</v>
       </c>
       <c r="E204" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F204" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G204" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E204,'feed rations'!$Y$13:$Y$46,0),MATCH(C204&amp;D204,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5962,10 +5962,10 @@
         <v>198</v>
       </c>
       <c r="E205" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F205" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G205" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E205,'feed rations'!$Y$13:$Y$46,0),MATCH(C205&amp;D205,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5974,13 +5974,13 @@
     </row>
     <row r="207" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C207" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E207" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F207" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G207" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E207,'feed rations'!$Y$13:$Y$46,0),MATCH(C207&amp;D207,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -5989,13 +5989,13 @@
     </row>
     <row r="208" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C208" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E208" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F208" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G208" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E208,'feed rations'!$Y$13:$Y$46,0),MATCH(C208&amp;D208,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="209" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C209" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E209" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F209" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G209" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E209,'feed rations'!$Y$13:$Y$46,0),MATCH(C209&amp;D209,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6019,13 +6019,13 @@
     </row>
     <row r="210" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C210" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E210" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F210" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G210" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E210,'feed rations'!$Y$13:$Y$46,0),MATCH(C210&amp;D210,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6034,13 +6034,13 @@
     </row>
     <row r="211" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C211" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E211" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F211" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G211" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E211,'feed rations'!$Y$13:$Y$46,0),MATCH(C211&amp;D211,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6049,13 +6049,13 @@
     </row>
     <row r="212" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C212" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E212" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F212" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G212" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E212,'feed rations'!$Y$13:$Y$46,0),MATCH(C212&amp;D212,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6064,13 +6064,13 @@
     </row>
     <row r="213" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C213" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E213" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F213" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G213" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E213,'feed rations'!$Y$13:$Y$46,0),MATCH(C213&amp;D213,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6079,13 +6079,13 @@
     </row>
     <row r="214" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C214" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E214" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F214" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G214" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E214,'feed rations'!$Y$13:$Y$46,0),MATCH(C214&amp;D214,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6094,13 +6094,13 @@
     </row>
     <row r="215" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C215" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E215" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F215" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G215" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E215,'feed rations'!$Y$13:$Y$46,0),MATCH(C215&amp;D215,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6109,13 +6109,13 @@
     </row>
     <row r="216" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C216" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E216" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F216" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G216" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E216,'feed rations'!$Y$13:$Y$46,0),MATCH(C216&amp;D216,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6124,13 +6124,13 @@
     </row>
     <row r="217" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E217" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F217" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G217" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E217,'feed rations'!$Y$13:$Y$46,0),MATCH(C217&amp;D217,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6139,13 +6139,13 @@
     </row>
     <row r="218" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C218" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E218" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F218" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G218" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E218,'feed rations'!$Y$13:$Y$46,0),MATCH(C218&amp;D218,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6154,13 +6154,13 @@
     </row>
     <row r="219" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C219" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E219" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F219" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G219" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E219,'feed rations'!$Y$13:$Y$46,0),MATCH(C219&amp;D219,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6169,13 +6169,13 @@
     </row>
     <row r="220" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C220" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E220" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F220" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G220" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E220,'feed rations'!$Y$13:$Y$46,0),MATCH(C220&amp;D220,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6184,13 +6184,13 @@
     </row>
     <row r="221" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C221" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E221" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F221" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G221" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E221,'feed rations'!$Y$13:$Y$46,0),MATCH(C221&amp;D221,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6199,13 +6199,13 @@
     </row>
     <row r="222" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C222" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E222" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F222" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G222" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E222,'feed rations'!$Y$13:$Y$46,0),MATCH(C222&amp;D222,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6214,13 +6214,13 @@
     </row>
     <row r="223" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C223" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E223" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F223" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G223" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E223,'feed rations'!$Y$13:$Y$46,0),MATCH(C223&amp;D223,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6229,16 +6229,16 @@
     </row>
     <row r="224" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C224" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E224" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F224" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G224" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E224,'feed rations'!$Y$13:$Y$46,0),MATCH(C224&amp;D224,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6247,14 +6247,14 @@
     </row>
     <row r="225" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B225" s="98" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C225" s="97" t="str">
         <f>C224</f>
         <v>other sheep</v>
       </c>
       <c r="E225" s="97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F225" s="97" t="str">
         <f>F224</f>
@@ -6265,18 +6265,18 @@
         <v>0.21035091095436523</v>
       </c>
       <c r="I225" s="97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="226" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C226" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E226" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F226" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G226" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E226,'feed rations'!$Y$13:$Y$46,0),MATCH(C226&amp;D226,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6285,13 +6285,13 @@
     </row>
     <row r="227" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C227" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E227" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F227" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G227" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E227,'feed rations'!$Y$13:$Y$46,0),MATCH(C227&amp;D227,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6300,13 +6300,13 @@
     </row>
     <row r="228" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C228" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E228" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F228" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G228" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E228,'feed rations'!$Y$13:$Y$46,0),MATCH(C228&amp;D228,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6315,13 +6315,13 @@
     </row>
     <row r="229" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C229" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E229" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F229" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G229" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E229,'feed rations'!$Y$13:$Y$46,0),MATCH(C229&amp;D229,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6330,13 +6330,13 @@
     </row>
     <row r="230" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C230" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E230" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F230" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G230" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E230,'feed rations'!$Y$13:$Y$46,0),MATCH(C230&amp;D230,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6345,13 +6345,13 @@
     </row>
     <row r="231" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C231" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E231" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F231" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G231" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E231,'feed rations'!$Y$13:$Y$46,0),MATCH(C231&amp;D231,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6360,13 +6360,13 @@
     </row>
     <row r="232" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C232" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E232" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F232" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G232" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E232,'feed rations'!$Y$13:$Y$46,0),MATCH(C232&amp;D232,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6375,13 +6375,13 @@
     </row>
     <row r="233" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C233" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E233" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F233" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G233" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E233,'feed rations'!$Y$13:$Y$46,0),MATCH(C233&amp;D233,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6390,13 +6390,13 @@
     </row>
     <row r="234" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C234" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E234" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F234" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G234" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E234,'feed rations'!$Y$13:$Y$46,0),MATCH(C234&amp;D234,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6405,13 +6405,13 @@
     </row>
     <row r="235" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C235" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E235" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F235" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G235" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E235,'feed rations'!$Y$13:$Y$46,0),MATCH(C235&amp;D235,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6420,13 +6420,13 @@
     </row>
     <row r="236" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C236" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E236" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F236" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G236" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E236,'feed rations'!$Y$13:$Y$46,0),MATCH(C236&amp;D236,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6435,13 +6435,13 @@
     </row>
     <row r="237" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C237" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E237" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F237" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G237" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E237,'feed rations'!$Y$13:$Y$46,0),MATCH(C237&amp;D237,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6450,13 +6450,13 @@
     </row>
     <row r="238" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C238" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E238" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F238" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G238" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E238,'feed rations'!$Y$13:$Y$46,0),MATCH(C238&amp;D238,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6465,13 +6465,13 @@
     </row>
     <row r="239" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C239" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E239" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F239" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G239" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E239,'feed rations'!$Y$13:$Y$46,0),MATCH(C239&amp;D239,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6480,13 +6480,13 @@
     </row>
     <row r="240" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C240" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E240" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F240" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G240" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E240,'feed rations'!$Y$13:$Y$46,0),MATCH(C240&amp;D240,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6495,13 +6495,13 @@
     </row>
     <row r="241" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C241" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E241" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F241" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G241" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E241,'feed rations'!$Y$13:$Y$46,0),MATCH(C241&amp;D241,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6513,13 +6513,13 @@
         <v>196</v>
       </c>
       <c r="D243" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E243" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F243" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G243" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E243,'feed rations'!$Y$13:$Y$46,0),MATCH(C243&amp;D243,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6531,13 +6531,13 @@
         <v>196</v>
       </c>
       <c r="D244" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E244" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F244" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G244" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E244,'feed rations'!$Y$13:$Y$46,0),MATCH(C244&amp;D244,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6549,13 +6549,13 @@
         <v>196</v>
       </c>
       <c r="D245" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E245" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F245" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G245" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E245,'feed rations'!$Y$13:$Y$46,0),MATCH(C245&amp;D245,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6567,13 +6567,13 @@
         <v>196</v>
       </c>
       <c r="D246" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E246" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F246" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G246" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E246,'feed rations'!$Y$13:$Y$46,0),MATCH(C246&amp;D246,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6585,13 +6585,13 @@
         <v>196</v>
       </c>
       <c r="D247" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E247" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F247" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G247" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E247,'feed rations'!$Y$13:$Y$46,0),MATCH(C247&amp;D247,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6603,13 +6603,13 @@
         <v>196</v>
       </c>
       <c r="D248" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E248" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F248" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G248" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E248,'feed rations'!$Y$13:$Y$46,0),MATCH(C248&amp;D248,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6621,13 +6621,13 @@
         <v>196</v>
       </c>
       <c r="D249" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E249" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F249" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G249" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E249,'feed rations'!$Y$13:$Y$46,0),MATCH(C249&amp;D249,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6639,13 +6639,13 @@
         <v>196</v>
       </c>
       <c r="D250" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E250" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F250" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G250" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E250,'feed rations'!$Y$13:$Y$46,0),MATCH(C250&amp;D250,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6657,13 +6657,13 @@
         <v>196</v>
       </c>
       <c r="D251" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E251" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F251" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G251" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E251,'feed rations'!$Y$13:$Y$46,0),MATCH(C251&amp;D251,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6675,13 +6675,13 @@
         <v>196</v>
       </c>
       <c r="D252" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E252" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F252" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G252" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E252,'feed rations'!$Y$13:$Y$46,0),MATCH(C252&amp;D252,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6693,13 +6693,13 @@
         <v>196</v>
       </c>
       <c r="D253" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E253" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F253" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G253" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E253,'feed rations'!$Y$13:$Y$46,0),MATCH(C253&amp;D253,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6711,13 +6711,13 @@
         <v>196</v>
       </c>
       <c r="D254" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E254" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F254" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G254" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E254,'feed rations'!$Y$13:$Y$46,0),MATCH(C254&amp;D254,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6729,13 +6729,13 @@
         <v>196</v>
       </c>
       <c r="D255" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E255" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F255" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G255" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E255,'feed rations'!$Y$13:$Y$46,0),MATCH(C255&amp;D255,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6747,13 +6747,13 @@
         <v>196</v>
       </c>
       <c r="D256" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E256" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F256" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G256" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E256,'feed rations'!$Y$13:$Y$46,0),MATCH(C256&amp;D256,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6765,13 +6765,13 @@
         <v>196</v>
       </c>
       <c r="D257" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E257" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F257" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G257" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E257,'feed rations'!$Y$13:$Y$46,0),MATCH(C257&amp;D257,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6783,13 +6783,13 @@
         <v>196</v>
       </c>
       <c r="D258" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E258" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F258" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G258" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E258,'feed rations'!$Y$13:$Y$46,0),MATCH(C258&amp;D258,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6801,13 +6801,13 @@
         <v>196</v>
       </c>
       <c r="D259" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E259" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F259" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G259" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E259,'feed rations'!$Y$13:$Y$46,0),MATCH(C259&amp;D259,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6816,19 +6816,19 @@
     </row>
     <row r="260" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C260" t="s">
         <v>196</v>
       </c>
       <c r="D260" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E260" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F260" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G260" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E260,'feed rations'!$Y$13:$Y$46,0),MATCH(C260&amp;D260,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="261" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B261" s="98" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C261" s="97" t="str">
         <f>C260</f>
@@ -6848,7 +6848,7 @@
         <v>lambs</v>
       </c>
       <c r="E261" s="97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F261" s="97" t="str">
         <f>F260</f>
@@ -6859,7 +6859,7 @@
         <v>0.79239853966713902</v>
       </c>
       <c r="I261" s="97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="262" spans="2:9" x14ac:dyDescent="0.25">
@@ -6867,13 +6867,13 @@
         <v>196</v>
       </c>
       <c r="D262" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E262" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F262" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G262" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E262,'feed rations'!$Y$13:$Y$46,0),MATCH(C262&amp;D262,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6885,13 +6885,13 @@
         <v>196</v>
       </c>
       <c r="D263" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E263" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F263" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G263" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E263,'feed rations'!$Y$13:$Y$46,0),MATCH(C263&amp;D263,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6903,13 +6903,13 @@
         <v>196</v>
       </c>
       <c r="D264" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E264" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F264" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G264" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E264,'feed rations'!$Y$13:$Y$46,0),MATCH(C264&amp;D264,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6921,13 +6921,13 @@
         <v>196</v>
       </c>
       <c r="D265" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E265" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F265" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G265" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E265,'feed rations'!$Y$13:$Y$46,0),MATCH(C265&amp;D265,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6939,13 +6939,13 @@
         <v>196</v>
       </c>
       <c r="D266" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E266" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F266" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G266" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E266,'feed rations'!$Y$13:$Y$46,0),MATCH(C266&amp;D266,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6957,13 +6957,13 @@
         <v>196</v>
       </c>
       <c r="D267" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E267" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F267" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G267" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E267,'feed rations'!$Y$13:$Y$46,0),MATCH(C267&amp;D267,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6975,13 +6975,13 @@
         <v>196</v>
       </c>
       <c r="D268" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E268" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F268" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G268" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E268,'feed rations'!$Y$13:$Y$46,0),MATCH(C268&amp;D268,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -6993,13 +6993,13 @@
         <v>196</v>
       </c>
       <c r="D269" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E269" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F269" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G269" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E269,'feed rations'!$Y$13:$Y$46,0),MATCH(C269&amp;D269,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7011,13 +7011,13 @@
         <v>196</v>
       </c>
       <c r="D270" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E270" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F270" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G270" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E270,'feed rations'!$Y$13:$Y$46,0),MATCH(C270&amp;D270,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7029,13 +7029,13 @@
         <v>196</v>
       </c>
       <c r="D271" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E271" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F271" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G271" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E271,'feed rations'!$Y$13:$Y$46,0),MATCH(C271&amp;D271,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7047,13 +7047,13 @@
         <v>196</v>
       </c>
       <c r="D272" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E272" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F272" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G272" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E272,'feed rations'!$Y$13:$Y$46,0),MATCH(C272&amp;D272,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7065,13 +7065,13 @@
         <v>196</v>
       </c>
       <c r="D273" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E273" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F273" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G273" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E273,'feed rations'!$Y$13:$Y$46,0),MATCH(C273&amp;D273,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7083,13 +7083,13 @@
         <v>196</v>
       </c>
       <c r="D274" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E274" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F274" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G274" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E274,'feed rations'!$Y$13:$Y$46,0),MATCH(C274&amp;D274,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7101,13 +7101,13 @@
         <v>196</v>
       </c>
       <c r="D275" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E275" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F275" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G275" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E275,'feed rations'!$Y$13:$Y$46,0),MATCH(C275&amp;D275,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7119,13 +7119,13 @@
         <v>196</v>
       </c>
       <c r="D276" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E276" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F276" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G276" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E276,'feed rations'!$Y$13:$Y$46,0),MATCH(C276&amp;D276,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7137,13 +7137,13 @@
         <v>196</v>
       </c>
       <c r="D277" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E277" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F277" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G277" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E277,'feed rations'!$Y$13:$Y$46,0),MATCH(C277&amp;D277,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7155,13 +7155,13 @@
         <v>197</v>
       </c>
       <c r="D279" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E279" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F279" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G279" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E279,'feed rations'!$Y$13:$Y$46,0),MATCH(C279&amp;D279,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7173,13 +7173,13 @@
         <v>197</v>
       </c>
       <c r="D280" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E280" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F280" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G280" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E280,'feed rations'!$Y$13:$Y$46,0),MATCH(C280&amp;D280,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7191,13 +7191,13 @@
         <v>197</v>
       </c>
       <c r="D281" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E281" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F281" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G281" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E281,'feed rations'!$Y$13:$Y$46,0),MATCH(C281&amp;D281,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7209,13 +7209,13 @@
         <v>197</v>
       </c>
       <c r="D282" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E282" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F282" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G282" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E282,'feed rations'!$Y$13:$Y$46,0),MATCH(C282&amp;D282,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7227,13 +7227,13 @@
         <v>197</v>
       </c>
       <c r="D283" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E283" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F283" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G283" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E283,'feed rations'!$Y$13:$Y$46,0),MATCH(C283&amp;D283,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7245,13 +7245,13 @@
         <v>197</v>
       </c>
       <c r="D284" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E284" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F284" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G284" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E284,'feed rations'!$Y$13:$Y$46,0),MATCH(C284&amp;D284,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7263,13 +7263,13 @@
         <v>197</v>
       </c>
       <c r="D285" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E285" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F285" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G285" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E285,'feed rations'!$Y$13:$Y$46,0),MATCH(C285&amp;D285,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7281,13 +7281,13 @@
         <v>197</v>
       </c>
       <c r="D286" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E286" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F286" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G286" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E286,'feed rations'!$Y$13:$Y$46,0),MATCH(C286&amp;D286,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7299,13 +7299,13 @@
         <v>197</v>
       </c>
       <c r="D287" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E287" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F287" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G287" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E287,'feed rations'!$Y$13:$Y$46,0),MATCH(C287&amp;D287,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7317,13 +7317,13 @@
         <v>197</v>
       </c>
       <c r="D288" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E288" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F288" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G288" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E288,'feed rations'!$Y$13:$Y$46,0),MATCH(C288&amp;D288,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7335,13 +7335,13 @@
         <v>197</v>
       </c>
       <c r="D289" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E289" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F289" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G289" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E289,'feed rations'!$Y$13:$Y$46,0),MATCH(C289&amp;D289,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7353,13 +7353,13 @@
         <v>197</v>
       </c>
       <c r="D290" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E290" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F290" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G290" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E290,'feed rations'!$Y$13:$Y$46,0),MATCH(C290&amp;D290,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7371,13 +7371,13 @@
         <v>197</v>
       </c>
       <c r="D291" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E291" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F291" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G291" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E291,'feed rations'!$Y$13:$Y$46,0),MATCH(C291&amp;D291,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7389,13 +7389,13 @@
         <v>197</v>
       </c>
       <c r="D292" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E292" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F292" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G292" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E292,'feed rations'!$Y$13:$Y$46,0),MATCH(C292&amp;D292,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7407,13 +7407,13 @@
         <v>197</v>
       </c>
       <c r="D293" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E293" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F293" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G293" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E293,'feed rations'!$Y$13:$Y$46,0),MATCH(C293&amp;D293,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7425,13 +7425,13 @@
         <v>197</v>
       </c>
       <c r="D294" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E294" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F294" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G294" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E294,'feed rations'!$Y$13:$Y$46,0),MATCH(C294&amp;D294,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7443,13 +7443,13 @@
         <v>197</v>
       </c>
       <c r="D295" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E295" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F295" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G295" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E295,'feed rations'!$Y$13:$Y$46,0),MATCH(C295&amp;D295,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7458,19 +7458,19 @@
     </row>
     <row r="296" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C296" t="s">
         <v>197</v>
       </c>
       <c r="D296" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E296" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F296" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G296" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E296,'feed rations'!$Y$13:$Y$46,0),MATCH(C296&amp;D296,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="297" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B297" s="98" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C297" s="97" t="str">
         <f>C296</f>
@@ -7490,7 +7490,7 @@
         <v>lambs</v>
       </c>
       <c r="E297" s="97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F297" s="97" t="str">
         <f>F296</f>
@@ -7501,7 +7501,7 @@
         <v>2.8094890150443339</v>
       </c>
       <c r="I297" s="97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="298" spans="2:9" x14ac:dyDescent="0.25">
@@ -7509,13 +7509,13 @@
         <v>197</v>
       </c>
       <c r="D298" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E298" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F298" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G298" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E298,'feed rations'!$Y$13:$Y$46,0),MATCH(C298&amp;D298,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7527,13 +7527,13 @@
         <v>197</v>
       </c>
       <c r="D299" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E299" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F299" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G299" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E299,'feed rations'!$Y$13:$Y$46,0),MATCH(C299&amp;D299,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7545,13 +7545,13 @@
         <v>197</v>
       </c>
       <c r="D300" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E300" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F300" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G300" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E300,'feed rations'!$Y$13:$Y$46,0),MATCH(C300&amp;D300,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7563,13 +7563,13 @@
         <v>197</v>
       </c>
       <c r="D301" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E301" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F301" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G301" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E301,'feed rations'!$Y$13:$Y$46,0),MATCH(C301&amp;D301,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7581,13 +7581,13 @@
         <v>197</v>
       </c>
       <c r="D302" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E302" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F302" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G302" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E302,'feed rations'!$Y$13:$Y$46,0),MATCH(C302&amp;D302,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7599,13 +7599,13 @@
         <v>197</v>
       </c>
       <c r="D303" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E303" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F303" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G303" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E303,'feed rations'!$Y$13:$Y$46,0),MATCH(C303&amp;D303,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7617,13 +7617,13 @@
         <v>197</v>
       </c>
       <c r="D304" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E304" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F304" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G304" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E304,'feed rations'!$Y$13:$Y$46,0),MATCH(C304&amp;D304,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7635,13 +7635,13 @@
         <v>197</v>
       </c>
       <c r="D305" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E305" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F305" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G305" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E305,'feed rations'!$Y$13:$Y$46,0),MATCH(C305&amp;D305,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7653,13 +7653,13 @@
         <v>197</v>
       </c>
       <c r="D306" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E306" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F306" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G306" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E306,'feed rations'!$Y$13:$Y$46,0),MATCH(C306&amp;D306,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7671,13 +7671,13 @@
         <v>197</v>
       </c>
       <c r="D307" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E307" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F307" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G307" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E307,'feed rations'!$Y$13:$Y$46,0),MATCH(C307&amp;D307,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7689,13 +7689,13 @@
         <v>197</v>
       </c>
       <c r="D308" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E308" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F308" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G308" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E308,'feed rations'!$Y$13:$Y$46,0),MATCH(C308&amp;D308,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7707,13 +7707,13 @@
         <v>197</v>
       </c>
       <c r="D309" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E309" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F309" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G309" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E309,'feed rations'!$Y$13:$Y$46,0),MATCH(C309&amp;D309,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7725,13 +7725,13 @@
         <v>197</v>
       </c>
       <c r="D310" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E310" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F310" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G310" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E310,'feed rations'!$Y$13:$Y$46,0),MATCH(C310&amp;D310,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7743,13 +7743,13 @@
         <v>197</v>
       </c>
       <c r="D311" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E311" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F311" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G311" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E311,'feed rations'!$Y$13:$Y$46,0),MATCH(C311&amp;D311,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7761,13 +7761,13 @@
         <v>197</v>
       </c>
       <c r="D312" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E312" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F312" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G312" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E312,'feed rations'!$Y$13:$Y$46,0),MATCH(C312&amp;D312,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7779,13 +7779,13 @@
         <v>197</v>
       </c>
       <c r="D313" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E313" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F313" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G313" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E313,'feed rations'!$Y$13:$Y$46,0),MATCH(C313&amp;D313,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7797,13 +7797,13 @@
         <v>198</v>
       </c>
       <c r="D315" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E315" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F315" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G315" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E315,'feed rations'!$Y$13:$Y$46,0),MATCH(C315&amp;D315,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7815,13 +7815,13 @@
         <v>198</v>
       </c>
       <c r="D316" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E316" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F316" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G316" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E316,'feed rations'!$Y$13:$Y$46,0),MATCH(C316&amp;D316,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7833,13 +7833,13 @@
         <v>198</v>
       </c>
       <c r="D317" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E317" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F317" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G317" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E317,'feed rations'!$Y$13:$Y$46,0),MATCH(C317&amp;D317,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7851,13 +7851,13 @@
         <v>198</v>
       </c>
       <c r="D318" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E318" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F318" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G318" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E318,'feed rations'!$Y$13:$Y$46,0),MATCH(C318&amp;D318,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7869,13 +7869,13 @@
         <v>198</v>
       </c>
       <c r="D319" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E319" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F319" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G319" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E319,'feed rations'!$Y$13:$Y$46,0),MATCH(C319&amp;D319,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7887,13 +7887,13 @@
         <v>198</v>
       </c>
       <c r="D320" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E320" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F320" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G320" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E320,'feed rations'!$Y$13:$Y$46,0),MATCH(C320&amp;D320,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7905,13 +7905,13 @@
         <v>198</v>
       </c>
       <c r="D321" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E321" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F321" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G321" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E321,'feed rations'!$Y$13:$Y$46,0),MATCH(C321&amp;D321,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7923,13 +7923,13 @@
         <v>198</v>
       </c>
       <c r="D322" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E322" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F322" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G322" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E322,'feed rations'!$Y$13:$Y$46,0),MATCH(C322&amp;D322,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7941,13 +7941,13 @@
         <v>198</v>
       </c>
       <c r="D323" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E323" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F323" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G323" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E323,'feed rations'!$Y$13:$Y$46,0),MATCH(C323&amp;D323,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7959,13 +7959,13 @@
         <v>198</v>
       </c>
       <c r="D324" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E324" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F324" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G324" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E324,'feed rations'!$Y$13:$Y$46,0),MATCH(C324&amp;D324,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7977,13 +7977,13 @@
         <v>198</v>
       </c>
       <c r="D325" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E325" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F325" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G325" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E325,'feed rations'!$Y$13:$Y$46,0),MATCH(C325&amp;D325,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -7995,13 +7995,13 @@
         <v>198</v>
       </c>
       <c r="D326" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E326" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F326" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G326" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E326,'feed rations'!$Y$13:$Y$46,0),MATCH(C326&amp;D326,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8013,13 +8013,13 @@
         <v>198</v>
       </c>
       <c r="D327" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E327" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F327" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G327" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E327,'feed rations'!$Y$13:$Y$46,0),MATCH(C327&amp;D327,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8031,13 +8031,13 @@
         <v>198</v>
       </c>
       <c r="D328" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E328" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F328" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G328" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E328,'feed rations'!$Y$13:$Y$46,0),MATCH(C328&amp;D328,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8049,13 +8049,13 @@
         <v>198</v>
       </c>
       <c r="D329" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E329" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F329" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G329" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E329,'feed rations'!$Y$13:$Y$46,0),MATCH(C329&amp;D329,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8067,13 +8067,13 @@
         <v>198</v>
       </c>
       <c r="D330" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E330" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F330" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G330" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E330,'feed rations'!$Y$13:$Y$46,0),MATCH(C330&amp;D330,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8085,13 +8085,13 @@
         <v>198</v>
       </c>
       <c r="D331" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E331" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F331" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G331" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E331,'feed rations'!$Y$13:$Y$46,0),MATCH(C331&amp;D331,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8100,19 +8100,19 @@
     </row>
     <row r="332" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B332" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C332" t="s">
         <v>198</v>
       </c>
       <c r="D332" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E332" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F332" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G332" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E332,'feed rations'!$Y$13:$Y$46,0),MATCH(C332&amp;D332,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8121,7 +8121,7 @@
     </row>
     <row r="333" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B333" s="98" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C333" s="97" t="str">
         <f>C332</f>
@@ -8132,7 +8132,7 @@
         <v>lambs</v>
       </c>
       <c r="E333" s="97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F333" s="97" t="str">
         <f>F332</f>
@@ -8143,7 +8143,7 @@
         <v>0.13505509987252132</v>
       </c>
       <c r="I333" s="97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="334" spans="2:9" x14ac:dyDescent="0.25">
@@ -8151,13 +8151,13 @@
         <v>198</v>
       </c>
       <c r="D334" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E334" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F334" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G334" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E334,'feed rations'!$Y$13:$Y$46,0),MATCH(C334&amp;D334,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8169,13 +8169,13 @@
         <v>198</v>
       </c>
       <c r="D335" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E335" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F335" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G335" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E335,'feed rations'!$Y$13:$Y$46,0),MATCH(C335&amp;D335,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8187,13 +8187,13 @@
         <v>198</v>
       </c>
       <c r="D336" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E336" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F336" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G336" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E336,'feed rations'!$Y$13:$Y$46,0),MATCH(C336&amp;D336,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8205,13 +8205,13 @@
         <v>198</v>
       </c>
       <c r="D337" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E337" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F337" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G337" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E337,'feed rations'!$Y$13:$Y$46,0),MATCH(C337&amp;D337,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8223,13 +8223,13 @@
         <v>198</v>
       </c>
       <c r="D338" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E338" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F338" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G338" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E338,'feed rations'!$Y$13:$Y$46,0),MATCH(C338&amp;D338,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8241,13 +8241,13 @@
         <v>198</v>
       </c>
       <c r="D339" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E339" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F339" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G339" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E339,'feed rations'!$Y$13:$Y$46,0),MATCH(C339&amp;D339,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8259,13 +8259,13 @@
         <v>198</v>
       </c>
       <c r="D340" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E340" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F340" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G340" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E340,'feed rations'!$Y$13:$Y$46,0),MATCH(C340&amp;D340,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8277,13 +8277,13 @@
         <v>198</v>
       </c>
       <c r="D341" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E341" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F341" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G341" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E341,'feed rations'!$Y$13:$Y$46,0),MATCH(C341&amp;D341,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8295,13 +8295,13 @@
         <v>198</v>
       </c>
       <c r="D342" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E342" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F342" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G342" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E342,'feed rations'!$Y$13:$Y$46,0),MATCH(C342&amp;D342,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8313,13 +8313,13 @@
         <v>198</v>
       </c>
       <c r="D343" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E343" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F343" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G343" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E343,'feed rations'!$Y$13:$Y$46,0),MATCH(C343&amp;D343,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8331,13 +8331,13 @@
         <v>198</v>
       </c>
       <c r="D344" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E344" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F344" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G344" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E344,'feed rations'!$Y$13:$Y$46,0),MATCH(C344&amp;D344,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8349,13 +8349,13 @@
         <v>198</v>
       </c>
       <c r="D345" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E345" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F345" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G345" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E345,'feed rations'!$Y$13:$Y$46,0),MATCH(C345&amp;D345,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8367,13 +8367,13 @@
         <v>198</v>
       </c>
       <c r="D346" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E346" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F346" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G346" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E346,'feed rations'!$Y$13:$Y$46,0),MATCH(C346&amp;D346,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8385,13 +8385,13 @@
         <v>198</v>
       </c>
       <c r="D347" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E347" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F347" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G347" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E347,'feed rations'!$Y$13:$Y$46,0),MATCH(C347&amp;D347,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8403,13 +8403,13 @@
         <v>198</v>
       </c>
       <c r="D348" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E348" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F348" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G348" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E348,'feed rations'!$Y$13:$Y$46,0),MATCH(C348&amp;D348,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8421,13 +8421,13 @@
         <v>198</v>
       </c>
       <c r="D349" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E349" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F349" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G349" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E349,'feed rations'!$Y$13:$Y$46,0),MATCH(C349&amp;D349,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8436,16 +8436,16 @@
     </row>
     <row r="351" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C351" t="s">
+        <v>203</v>
+      </c>
+      <c r="D351" t="s">
         <v>204</v>
       </c>
-      <c r="D351" t="s">
-        <v>205</v>
-      </c>
       <c r="E351" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F351" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G351" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E351,'feed rations'!$Y$13:$Y$46,0),MATCH(C351&amp;D351,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8454,16 +8454,16 @@
     </row>
     <row r="352" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C352" t="s">
+        <v>203</v>
+      </c>
+      <c r="D352" t="s">
         <v>204</v>
       </c>
-      <c r="D352" t="s">
-        <v>205</v>
-      </c>
       <c r="E352" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F352" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G352" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E352,'feed rations'!$Y$13:$Y$46,0),MATCH(C352&amp;D352,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8472,16 +8472,16 @@
     </row>
     <row r="353" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C353" t="s">
+        <v>203</v>
+      </c>
+      <c r="D353" t="s">
         <v>204</v>
       </c>
-      <c r="D353" t="s">
-        <v>205</v>
-      </c>
       <c r="E353" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F353" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G353" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E353,'feed rations'!$Y$13:$Y$46,0),MATCH(C353&amp;D353,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8490,16 +8490,16 @@
     </row>
     <row r="354" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C354" t="s">
+        <v>203</v>
+      </c>
+      <c r="D354" t="s">
         <v>204</v>
       </c>
-      <c r="D354" t="s">
-        <v>205</v>
-      </c>
       <c r="E354" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F354" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G354" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E354,'feed rations'!$Y$13:$Y$46,0),MATCH(C354&amp;D354,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8508,16 +8508,16 @@
     </row>
     <row r="355" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C355" t="s">
+        <v>203</v>
+      </c>
+      <c r="D355" t="s">
         <v>204</v>
       </c>
-      <c r="D355" t="s">
-        <v>205</v>
-      </c>
       <c r="E355" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F355" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G355" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E355,'feed rations'!$Y$13:$Y$46,0),MATCH(C355&amp;D355,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8526,16 +8526,16 @@
     </row>
     <row r="356" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C356" t="s">
+        <v>203</v>
+      </c>
+      <c r="D356" t="s">
         <v>204</v>
       </c>
-      <c r="D356" t="s">
-        <v>205</v>
-      </c>
       <c r="E356" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F356" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G356" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E356,'feed rations'!$Y$13:$Y$46,0),MATCH(C356&amp;D356,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8544,16 +8544,16 @@
     </row>
     <row r="357" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C357" t="s">
+        <v>203</v>
+      </c>
+      <c r="D357" t="s">
         <v>204</v>
       </c>
-      <c r="D357" t="s">
-        <v>205</v>
-      </c>
       <c r="E357" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F357" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G357" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E357,'feed rations'!$Y$13:$Y$46,0),MATCH(C357&amp;D357,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8562,16 +8562,16 @@
     </row>
     <row r="358" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C358" t="s">
+        <v>203</v>
+      </c>
+      <c r="D358" t="s">
         <v>204</v>
       </c>
-      <c r="D358" t="s">
-        <v>205</v>
-      </c>
       <c r="E358" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F358" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G358" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E358,'feed rations'!$Y$13:$Y$46,0),MATCH(C358&amp;D358,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8580,16 +8580,16 @@
     </row>
     <row r="359" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C359" t="s">
+        <v>203</v>
+      </c>
+      <c r="D359" t="s">
         <v>204</v>
       </c>
-      <c r="D359" t="s">
-        <v>205</v>
-      </c>
       <c r="E359" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F359" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G359" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E359,'feed rations'!$Y$13:$Y$46,0),MATCH(C359&amp;D359,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8598,16 +8598,16 @@
     </row>
     <row r="360" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C360" t="s">
+        <v>203</v>
+      </c>
+      <c r="D360" t="s">
         <v>204</v>
       </c>
-      <c r="D360" t="s">
-        <v>205</v>
-      </c>
       <c r="E360" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F360" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G360" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E360,'feed rations'!$Y$13:$Y$46,0),MATCH(C360&amp;D360,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8616,16 +8616,16 @@
     </row>
     <row r="361" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C361" t="s">
+        <v>203</v>
+      </c>
+      <c r="D361" t="s">
         <v>204</v>
       </c>
-      <c r="D361" t="s">
-        <v>205</v>
-      </c>
       <c r="E361" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F361" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G361" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E361,'feed rations'!$Y$13:$Y$46,0),MATCH(C361&amp;D361,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8634,16 +8634,16 @@
     </row>
     <row r="362" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C362" t="s">
+        <v>203</v>
+      </c>
+      <c r="D362" t="s">
         <v>204</v>
       </c>
-      <c r="D362" t="s">
-        <v>205</v>
-      </c>
       <c r="E362" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F362" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G362" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E362,'feed rations'!$Y$13:$Y$46,0),MATCH(C362&amp;D362,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8652,16 +8652,16 @@
     </row>
     <row r="363" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C363" t="s">
+        <v>203</v>
+      </c>
+      <c r="D363" t="s">
         <v>204</v>
       </c>
-      <c r="D363" t="s">
-        <v>205</v>
-      </c>
       <c r="E363" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F363" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G363" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E363,'feed rations'!$Y$13:$Y$46,0),MATCH(C363&amp;D363,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8670,16 +8670,16 @@
     </row>
     <row r="364" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C364" t="s">
+        <v>203</v>
+      </c>
+      <c r="D364" t="s">
         <v>204</v>
       </c>
-      <c r="D364" t="s">
-        <v>205</v>
-      </c>
       <c r="E364" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F364" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G364" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E364,'feed rations'!$Y$13:$Y$46,0),MATCH(C364&amp;D364,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8688,16 +8688,16 @@
     </row>
     <row r="365" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C365" t="s">
+        <v>203</v>
+      </c>
+      <c r="D365" t="s">
         <v>204</v>
       </c>
-      <c r="D365" t="s">
-        <v>205</v>
-      </c>
       <c r="E365" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F365" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G365" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E365,'feed rations'!$Y$13:$Y$46,0),MATCH(C365&amp;D365,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8706,16 +8706,16 @@
     </row>
     <row r="366" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C366" t="s">
+        <v>203</v>
+      </c>
+      <c r="D366" t="s">
         <v>204</v>
       </c>
-      <c r="D366" t="s">
-        <v>205</v>
-      </c>
       <c r="E366" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F366" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G366" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E366,'feed rations'!$Y$13:$Y$46,0),MATCH(C366&amp;D366,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8724,16 +8724,16 @@
     </row>
     <row r="367" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C367" t="s">
+        <v>203</v>
+      </c>
+      <c r="D367" t="s">
         <v>204</v>
       </c>
-      <c r="D367" t="s">
-        <v>205</v>
-      </c>
       <c r="E367" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F367" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G367" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E367,'feed rations'!$Y$13:$Y$46,0),MATCH(C367&amp;D367,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8742,19 +8742,19 @@
     </row>
     <row r="368" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B368" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C368" t="s">
+        <v>203</v>
+      </c>
+      <c r="D368" t="s">
         <v>204</v>
       </c>
-      <c r="D368" t="s">
-        <v>205</v>
-      </c>
       <c r="E368" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F368" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G368" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E368,'feed rations'!$Y$13:$Y$46,0),MATCH(C368&amp;D368,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8763,7 +8763,7 @@
     </row>
     <row r="369" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B369" s="98" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C369" s="97" t="str">
         <f>C368</f>
@@ -8774,7 +8774,7 @@
         <v>lambs</v>
       </c>
       <c r="E369" s="97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F369" s="97" t="str">
         <f>F368</f>
@@ -8785,21 +8785,21 @@
         <v>0.79239853966713902</v>
       </c>
       <c r="I369" s="97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="370" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C370" t="s">
+        <v>203</v>
+      </c>
+      <c r="D370" t="s">
         <v>204</v>
       </c>
-      <c r="D370" t="s">
-        <v>205</v>
-      </c>
       <c r="E370" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F370" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G370" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E370,'feed rations'!$Y$13:$Y$46,0),MATCH(C370&amp;D370,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8808,16 +8808,16 @@
     </row>
     <row r="371" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C371" t="s">
+        <v>203</v>
+      </c>
+      <c r="D371" t="s">
         <v>204</v>
       </c>
-      <c r="D371" t="s">
-        <v>205</v>
-      </c>
       <c r="E371" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F371" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G371" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E371,'feed rations'!$Y$13:$Y$46,0),MATCH(C371&amp;D371,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8826,16 +8826,16 @@
     </row>
     <row r="372" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C372" t="s">
+        <v>203</v>
+      </c>
+      <c r="D372" t="s">
         <v>204</v>
       </c>
-      <c r="D372" t="s">
-        <v>205</v>
-      </c>
       <c r="E372" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F372" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G372" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E372,'feed rations'!$Y$13:$Y$46,0),MATCH(C372&amp;D372,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8844,16 +8844,16 @@
     </row>
     <row r="373" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C373" t="s">
+        <v>203</v>
+      </c>
+      <c r="D373" t="s">
         <v>204</v>
       </c>
-      <c r="D373" t="s">
-        <v>205</v>
-      </c>
       <c r="E373" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F373" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G373" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E373,'feed rations'!$Y$13:$Y$46,0),MATCH(C373&amp;D373,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8862,16 +8862,16 @@
     </row>
     <row r="374" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C374" t="s">
+        <v>203</v>
+      </c>
+      <c r="D374" t="s">
         <v>204</v>
       </c>
-      <c r="D374" t="s">
-        <v>205</v>
-      </c>
       <c r="E374" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F374" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G374" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E374,'feed rations'!$Y$13:$Y$46,0),MATCH(C374&amp;D374,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8880,16 +8880,16 @@
     </row>
     <row r="375" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C375" t="s">
+        <v>203</v>
+      </c>
+      <c r="D375" t="s">
         <v>204</v>
       </c>
-      <c r="D375" t="s">
-        <v>205</v>
-      </c>
       <c r="E375" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F375" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G375" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E375,'feed rations'!$Y$13:$Y$46,0),MATCH(C375&amp;D375,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8898,16 +8898,16 @@
     </row>
     <row r="376" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C376" t="s">
+        <v>203</v>
+      </c>
+      <c r="D376" t="s">
         <v>204</v>
       </c>
-      <c r="D376" t="s">
-        <v>205</v>
-      </c>
       <c r="E376" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F376" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G376" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E376,'feed rations'!$Y$13:$Y$46,0),MATCH(C376&amp;D376,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8916,16 +8916,16 @@
     </row>
     <row r="377" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C377" t="s">
+        <v>203</v>
+      </c>
+      <c r="D377" t="s">
         <v>204</v>
       </c>
-      <c r="D377" t="s">
-        <v>205</v>
-      </c>
       <c r="E377" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F377" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G377" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E377,'feed rations'!$Y$13:$Y$46,0),MATCH(C377&amp;D377,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8934,16 +8934,16 @@
     </row>
     <row r="378" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C378" t="s">
+        <v>203</v>
+      </c>
+      <c r="D378" t="s">
         <v>204</v>
       </c>
-      <c r="D378" t="s">
-        <v>205</v>
-      </c>
       <c r="E378" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F378" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G378" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E378,'feed rations'!$Y$13:$Y$46,0),MATCH(C378&amp;D378,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8952,16 +8952,16 @@
     </row>
     <row r="379" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C379" t="s">
+        <v>203</v>
+      </c>
+      <c r="D379" t="s">
         <v>204</v>
       </c>
-      <c r="D379" t="s">
-        <v>205</v>
-      </c>
       <c r="E379" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F379" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G379" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E379,'feed rations'!$Y$13:$Y$46,0),MATCH(C379&amp;D379,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8970,16 +8970,16 @@
     </row>
     <row r="380" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C380" t="s">
+        <v>203</v>
+      </c>
+      <c r="D380" t="s">
         <v>204</v>
       </c>
-      <c r="D380" t="s">
-        <v>205</v>
-      </c>
       <c r="E380" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F380" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G380" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E380,'feed rations'!$Y$13:$Y$46,0),MATCH(C380&amp;D380,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -8988,16 +8988,16 @@
     </row>
     <row r="381" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C381" t="s">
+        <v>203</v>
+      </c>
+      <c r="D381" t="s">
         <v>204</v>
       </c>
-      <c r="D381" t="s">
-        <v>205</v>
-      </c>
       <c r="E381" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F381" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G381" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E381,'feed rations'!$Y$13:$Y$46,0),MATCH(C381&amp;D381,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -9006,16 +9006,16 @@
     </row>
     <row r="382" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C382" t="s">
+        <v>203</v>
+      </c>
+      <c r="D382" t="s">
         <v>204</v>
       </c>
-      <c r="D382" t="s">
-        <v>205</v>
-      </c>
       <c r="E382" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F382" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G382" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E382,'feed rations'!$Y$13:$Y$46,0),MATCH(C382&amp;D382,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -9024,16 +9024,16 @@
     </row>
     <row r="383" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C383" t="s">
+        <v>203</v>
+      </c>
+      <c r="D383" t="s">
         <v>204</v>
       </c>
-      <c r="D383" t="s">
-        <v>205</v>
-      </c>
       <c r="E383" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F383" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G383" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E383,'feed rations'!$Y$13:$Y$46,0),MATCH(C383&amp;D383,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -9042,16 +9042,16 @@
     </row>
     <row r="384" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C384" t="s">
+        <v>203</v>
+      </c>
+      <c r="D384" t="s">
         <v>204</v>
       </c>
-      <c r="D384" t="s">
-        <v>205</v>
-      </c>
       <c r="E384" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F384" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G384" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E384,'feed rations'!$Y$13:$Y$46,0),MATCH(C384&amp;D384,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -9060,16 +9060,16 @@
     </row>
     <row r="385" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C385" t="s">
+        <v>203</v>
+      </c>
+      <c r="D385" t="s">
         <v>204</v>
       </c>
-      <c r="D385" t="s">
-        <v>205</v>
-      </c>
       <c r="E385" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F385" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G385" s="3">
         <f>INDEX('feed rations'!$AB$13:$AI$46,MATCH(E385,'feed rations'!$Y$13:$Y$46,0),MATCH(C385&amp;D385,'feed rations'!$AB$12:$AI$12,0))</f>
@@ -9088,7 +9088,7 @@
   <sheetData>
     <row r="2" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C2" s="64"/>
       <c r="D2" s="64"/>
@@ -9096,7 +9096,7 @@
       <c r="F2" s="64"/>
       <c r="G2" s="65"/>
       <c r="I2" s="63" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J2" s="64"/>
       <c r="K2" s="64"/>
@@ -9126,30 +9126,30 @@
       <c r="B4" s="67"/>
       <c r="C4" s="37"/>
       <c r="D4" s="68" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F4" s="68" t="s">
         <v>157</v>
       </c>
       <c r="G4" s="69" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I4" s="67"/>
       <c r="J4" s="37"/>
       <c r="K4" s="68" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L4" s="68" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M4" s="68" t="s">
         <v>157</v>
       </c>
       <c r="N4" s="69" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="2:35" x14ac:dyDescent="0.25">
@@ -9278,7 +9278,7 @@
     </row>
     <row r="8" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B8" s="71" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C8" s="72"/>
       <c r="D8" s="73">
@@ -9298,7 +9298,7 @@
         <v>748.40000000000009</v>
       </c>
       <c r="I8" s="71" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J8" s="72"/>
       <c r="K8" s="73">
@@ -9318,15 +9318,15 @@
         <v>157.56666666666666</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B10" s="75" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C10" s="76"/>
       <c r="D10" s="76"/>
@@ -9338,7 +9338,7 @@
       <c r="J10" s="76"/>
       <c r="K10" s="77"/>
       <c r="O10" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P10" t="s">
         <v>196</v>
@@ -9359,13 +9359,13 @@
         <v>198</v>
       </c>
       <c r="V10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AB10" t="s">
         <v>196</v>
@@ -9386,15 +9386,15 @@
         <v>198</v>
       </c>
       <c r="AH10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AI10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B11" s="78" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C11" s="50"/>
       <c r="D11" s="50"/>
@@ -9406,34 +9406,34 @@
       <c r="J11" s="49"/>
       <c r="K11" s="79"/>
       <c r="O11" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Q11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="U11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AC11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AE11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AI11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="2:35" x14ac:dyDescent="0.25">
@@ -9442,25 +9442,25 @@
       <c r="D12" s="50"/>
       <c r="E12" s="50"/>
       <c r="F12" s="51" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G12" s="56" t="s">
+        <v>259</v>
+      </c>
+      <c r="H12" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="I12" s="56" t="s">
         <v>261</v>
       </c>
-      <c r="H12" s="56" t="s">
-        <v>262</v>
-      </c>
-      <c r="I12" s="56" t="s">
+      <c r="J12" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="J12" s="52" t="s">
-        <v>265</v>
-      </c>
       <c r="K12" s="81" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P12" s="90" t="str">
         <f>P10&amp;P11</f>
@@ -9495,7 +9495,7 @@
         <v>other sheeplambs</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AB12" s="90" t="str">
         <f>AB10&amp;AB11</f>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="13" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B13" s="80" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C13" s="50"/>
       <c r="D13" s="50"/>
@@ -9559,7 +9559,7 @@
         <v>0.21853861585180565</v>
       </c>
       <c r="M13" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P13" s="19">
         <f>D5*(1/3)</f>
@@ -9594,7 +9594,7 @@
         <v>1.0999999999999999</v>
       </c>
       <c r="Y13" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AB13" s="19">
         <f>P13/P$48*100</f>
@@ -9631,7 +9631,7 @@
     </row>
     <row r="14" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B14" s="80" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C14" s="50"/>
       <c r="D14" s="50"/>
@@ -9658,7 +9658,7 @@
         <v>0.11287405047179862</v>
       </c>
       <c r="M14" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P14" s="19">
         <f>D5*(2/3)</f>
@@ -9693,7 +9693,7 @@
         <v>2.1999999999999997</v>
       </c>
       <c r="Y14" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AB14" s="19">
         <f t="shared" ref="AB14:AB46" si="14">P14/P$48*100</f>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="15" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B15" s="80" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C15" s="50"/>
       <c r="D15" s="50"/>
@@ -9757,7 +9757,7 @@
         <v>0.17110877620143239</v>
       </c>
       <c r="M15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P15" s="19">
         <f>E5</f>
@@ -9792,7 +9792,7 @@
         <v>131.26666666666665</v>
       </c>
       <c r="Y15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AB15" s="19">
         <f t="shared" si="14"/>
@@ -9829,7 +9829,7 @@
     </row>
     <row r="16" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B16" s="80" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C16" s="50"/>
       <c r="D16" s="50"/>
@@ -9856,7 +9856,7 @@
         <v>1.0577941159831382E-3</v>
       </c>
       <c r="M16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P16" s="47">
         <f t="shared" ref="P16:P46" si="22">F$5*K13</f>
@@ -9891,7 +9891,7 @@
         <v>5.0263881645915296</v>
       </c>
       <c r="Y16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AB16" s="47">
         <f t="shared" si="14"/>
@@ -9928,7 +9928,7 @@
     </row>
     <row r="17" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B17" s="80" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C17" s="50"/>
       <c r="D17" s="50"/>
@@ -9955,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P17" s="47">
         <f t="shared" si="22"/>
@@ -9990,7 +9990,7 @@
         <v>2.5961031608513681</v>
       </c>
       <c r="Y17" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AB17" s="47">
         <f t="shared" si="14"/>
@@ -10027,7 +10027,7 @@
     </row>
     <row r="18" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B18" s="80" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C18" s="50"/>
       <c r="D18" s="50"/>
@@ -10054,7 +10054,7 @@
         <v>4.4569124758005382E-2</v>
       </c>
       <c r="M18" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P18" s="47">
         <f t="shared" si="22"/>
@@ -10089,7 +10089,7 @@
         <v>3.9355018526329451</v>
       </c>
       <c r="Y18" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AB18" s="47">
         <f t="shared" si="14"/>
@@ -10126,7 +10126,7 @@
     </row>
     <row r="19" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B19" s="80" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="50"/>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="L19" s="58"/>
       <c r="M19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P19" s="47">
         <f t="shared" si="22"/>
@@ -10189,7 +10189,7 @@
         <v>2.4329264667612177E-2</v>
       </c>
       <c r="Y19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AB19" s="47">
         <f t="shared" si="14"/>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="20" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B20" s="80" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="50"/>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="L20" s="59"/>
       <c r="M20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P20" s="47">
         <f t="shared" si="22"/>
@@ -10289,7 +10289,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AB20" s="47">
         <f t="shared" si="14"/>
@@ -10326,7 +10326,7 @@
     </row>
     <row r="21" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B21" s="80" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="50"/>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="L21" s="60"/>
       <c r="M21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P21" s="47">
         <f t="shared" si="22"/>
@@ -10389,7 +10389,7 @@
         <v>1.0250898694341237</v>
       </c>
       <c r="Y21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AB21" s="47">
         <f t="shared" si="14"/>
@@ -10426,7 +10426,7 @@
     </row>
     <row r="22" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B22" s="80" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C22" s="50"/>
       <c r="D22" s="50"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="L22" s="61"/>
       <c r="M22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P22" s="47">
         <f t="shared" si="22"/>
@@ -10489,7 +10489,7 @@
         <v>2.2422455793783914E-2</v>
       </c>
       <c r="Y22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AB22" s="47">
         <f t="shared" si="14"/>
@@ -10526,7 +10526,7 @@
     </row>
     <row r="23" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B23" s="80" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="50"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="L23" s="61"/>
       <c r="M23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P23" s="47">
         <f t="shared" si="22"/>
@@ -10589,7 +10589,7 @@
         <v>0.14066811960657419</v>
       </c>
       <c r="Y23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AB23" s="47">
         <f t="shared" si="14"/>
@@ -10626,7 +10626,7 @@
     </row>
     <row r="24" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B24" s="80" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C24" s="50"/>
       <c r="D24" s="50"/>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="L24" s="61"/>
       <c r="M24" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P24" s="47">
         <f t="shared" si="22"/>
@@ -10689,7 +10689,7 @@
         <v>2.7089386310702386</v>
       </c>
       <c r="Y24" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AB24" s="47">
         <f t="shared" si="14"/>
@@ -10726,7 +10726,7 @@
     </row>
     <row r="25" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B25" s="80" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C25" s="50"/>
       <c r="D25" s="50"/>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="L25" s="61"/>
       <c r="M25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P25" s="47">
         <f t="shared" si="22"/>
@@ -10789,7 +10789,7 @@
         <v>3.6509327824674675E-3</v>
       </c>
       <c r="Y25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AB25" s="47">
         <f t="shared" si="14"/>
@@ -10826,7 +10826,7 @@
     </row>
     <row r="26" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B26" s="80" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C26" s="50"/>
       <c r="D26" s="50"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="L26" s="61"/>
       <c r="M26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P26" s="47">
         <f t="shared" si="22"/>
@@ -10889,7 +10889,7 @@
         <v>1.142512849927015</v>
       </c>
       <c r="Y26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AB26" s="47">
         <f t="shared" si="14"/>
@@ -10926,7 +10926,7 @@
     </row>
     <row r="27" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B27" s="80" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C27" s="50"/>
       <c r="D27" s="50"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="L27" s="61"/>
       <c r="M27" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P27" s="47">
         <f t="shared" si="22"/>
@@ -10989,7 +10989,7 @@
         <v>1.2785539269599873E-4</v>
       </c>
       <c r="Y27" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AB27" s="47">
         <f t="shared" si="14"/>
@@ -11026,7 +11026,7 @@
     </row>
     <row r="28" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B28" s="80" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C28" s="50"/>
       <c r="D28" s="50"/>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="L28" s="61"/>
       <c r="M28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P28" s="47">
         <f t="shared" si="22"/>
@@ -11089,7 +11089,7 @@
         <v>2.9128379290550614</v>
       </c>
       <c r="Y28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AB28" s="47">
         <f t="shared" si="14"/>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="29" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B29" s="80" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C29" s="50"/>
       <c r="D29" s="50"/>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="L29" s="61"/>
       <c r="M29" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="P29" s="47">
         <f t="shared" si="22"/>
@@ -11189,7 +11189,7 @@
         <v>1.1506985342639886E-4</v>
       </c>
       <c r="Y29" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AB29" s="47">
         <f t="shared" si="14"/>
@@ -11226,7 +11226,7 @@
     </row>
     <row r="30" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B30" s="80" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C30" s="50"/>
       <c r="D30" s="50"/>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="L30" s="61"/>
       <c r="M30" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P30" s="47">
         <f t="shared" si="22"/>
@@ -11289,7 +11289,7 @@
         <v>1.2485559656688547</v>
       </c>
       <c r="Y30" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AB30" s="47">
         <f t="shared" si="14"/>
@@ -11326,7 +11326,7 @@
     </row>
     <row r="31" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B31" s="80" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C31" s="50"/>
       <c r="D31" s="50"/>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="L31" s="61"/>
       <c r="M31" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P31" s="47">
         <f t="shared" si="22"/>
@@ -11389,7 +11389,7 @@
         <v>7.3286123252460523E-3</v>
       </c>
       <c r="Y31" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AB31" s="47">
         <f t="shared" si="14"/>
@@ -11426,7 +11426,7 @@
     </row>
     <row r="32" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B32" s="80" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C32" s="50"/>
       <c r="D32" s="50"/>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="L32" s="61"/>
       <c r="M32" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P32" s="47">
         <f t="shared" si="22"/>
@@ -11489,7 +11489,7 @@
         <v>2.1036326984693505E-2</v>
       </c>
       <c r="Y32" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AB32" s="47">
         <f t="shared" si="14"/>
@@ -11526,7 +11526,7 @@
     </row>
     <row r="33" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B33" s="80" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C33" s="50"/>
       <c r="D33" s="50"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="L33" s="61"/>
       <c r="M33" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P33" s="47">
         <f t="shared" si="22"/>
@@ -11589,7 +11589,7 @@
         <v>0.16212945555181579</v>
       </c>
       <c r="Y33" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AB33" s="47">
         <f t="shared" si="14"/>
@@ -11626,7 +11626,7 @@
     </row>
     <row r="34" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B34" s="80" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C34" s="50"/>
       <c r="D34" s="50"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="L34" s="61"/>
       <c r="M34" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P34" s="47">
         <f t="shared" si="22"/>
@@ -11689,7 +11689,7 @@
         <v>0.96818496119045039</v>
       </c>
       <c r="Y34" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AB34" s="47">
         <f t="shared" si="14"/>
@@ -11726,7 +11726,7 @@
     </row>
     <row r="35" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B35" s="80" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C35" s="50"/>
       <c r="D35" s="50"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="L35" s="61"/>
       <c r="M35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P35" s="47">
         <f t="shared" si="22"/>
@@ -11789,7 +11789,7 @@
         <v>0.19948204112739809</v>
       </c>
       <c r="Y35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AB35" s="47">
         <f t="shared" si="14"/>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="36" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B36" s="80" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C36" s="50"/>
       <c r="D36" s="50"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="L36" s="61"/>
       <c r="M36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P36" s="47">
         <f t="shared" si="22"/>
@@ -11889,7 +11889,7 @@
         <v>0.21358781224277235</v>
       </c>
       <c r="Y36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AB36" s="47">
         <f t="shared" si="14"/>
@@ -11926,7 +11926,7 @@
     </row>
     <row r="37" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B37" s="80" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C37" s="50"/>
       <c r="D37" s="50"/>
@@ -11950,7 +11950,7 @@
       </c>
       <c r="L37" s="61"/>
       <c r="M37" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P37" s="47">
         <f t="shared" si="22"/>
@@ -11985,7 +11985,7 @@
         <v>5.9347828005495797E-2</v>
       </c>
       <c r="Y37" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AB37" s="47">
         <f t="shared" si="14"/>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="38" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B38" s="80" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C38" s="50"/>
       <c r="D38" s="50"/>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="L38" s="61"/>
       <c r="M38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P38" s="47">
         <f t="shared" si="22"/>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AB38" s="47">
         <f t="shared" si="14"/>
@@ -12122,7 +12122,7 @@
     </row>
     <row r="39" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B39" s="80" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C39" s="50"/>
       <c r="D39" s="50"/>
@@ -12150,7 +12150,7 @@
       </c>
       <c r="L39" s="61"/>
       <c r="M39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P39" s="47">
         <f t="shared" si="22"/>
@@ -12185,7 +12185,7 @@
         <v>9.3378524734525986E-2</v>
       </c>
       <c r="Y39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AB39" s="47">
         <f t="shared" si="14"/>
@@ -12222,7 +12222,7 @@
     </row>
     <row r="40" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B40" s="80" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C40" s="50"/>
       <c r="D40" s="50"/>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="L40" s="61"/>
       <c r="M40" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P40" s="47">
         <f t="shared" si="22"/>
@@ -12285,7 +12285,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AB40" s="47">
         <f t="shared" si="14"/>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="41" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B41" s="80" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C41" s="50"/>
       <c r="D41" s="50"/>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="L41" s="61"/>
       <c r="M41" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P41" s="47">
         <f t="shared" si="22"/>
@@ -12385,7 +12385,7 @@
         <v>9.1041857212840484E-4</v>
       </c>
       <c r="Y41" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AB41" s="47">
         <f t="shared" si="14"/>
@@ -12422,7 +12422,7 @@
     </row>
     <row r="42" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B42" s="80" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C42" s="50"/>
       <c r="D42" s="50"/>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="L42" s="61"/>
       <c r="M42" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P42" s="47">
         <f t="shared" si="22"/>
@@ -12485,7 +12485,7 @@
         <v>0.11961500241657551</v>
       </c>
       <c r="Y42" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AB42" s="47">
         <f t="shared" si="14"/>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="43" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B43" s="80" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C43" s="50"/>
       <c r="D43" s="50"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="L43" s="61"/>
       <c r="M43" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P43" s="47">
         <f t="shared" si="22"/>
@@ -12585,7 +12585,7 @@
         <v>0.36731557397605791</v>
       </c>
       <c r="Y43" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AB43" s="47">
         <f t="shared" si="14"/>
@@ -12622,7 +12622,7 @@
     </row>
     <row r="44" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B44" s="83" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C44" s="84"/>
       <c r="D44" s="84"/>
@@ -12647,7 +12647,7 @@
       <c r="K44" s="88"/>
       <c r="L44" s="61"/>
       <c r="M44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P44" s="47">
         <f t="shared" si="22"/>
@@ -12682,7 +12682,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AB44" s="47">
         <f t="shared" si="14"/>
@@ -12720,7 +12720,7 @@
     <row r="45" spans="2:35" x14ac:dyDescent="0.25">
       <c r="L45" s="61"/>
       <c r="M45" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P45" s="47">
         <f t="shared" si="22"/>
@@ -12755,7 +12755,7 @@
         <v>4.4132154513343015E-4</v>
       </c>
       <c r="Y45" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AB45" s="47">
         <f t="shared" si="14"/>
@@ -12793,7 +12793,7 @@
     <row r="46" spans="2:35" x14ac:dyDescent="0.25">
       <c r="L46" s="61"/>
       <c r="M46" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P46" s="47">
         <f t="shared" si="22"/>
@@ -12828,7 +12828,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AB46" s="47">
         <f t="shared" si="14"/>
@@ -12872,7 +12872,7 @@
     <row r="48" spans="2:35" x14ac:dyDescent="0.25">
       <c r="L48" s="61"/>
       <c r="M48" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N48" s="61"/>
       <c r="O48" s="61"/>
@@ -12909,7 +12909,7 @@
         <v>157.56666666666661</v>
       </c>
       <c r="Y48" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z48" s="61"/>
       <c r="AA48" s="61"/>
